--- a/درب-مؤشرات-الأداء-2026.xlsx
+++ b/درب-مؤشرات-الأداء-2026.xlsx
@@ -9,14 +9,15 @@
   <sheets>
     <sheet name="دليل الاستخدام" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="الاستراتيجية" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="لوحة الإدارة التنفيذية" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="الامتياز · المؤشرات" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="الامتياز · الموظفون" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="الامتياز · مدير الإدارة" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="الامتياز · مسؤول الامتياز" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="الامتياز · المراقب الميداني" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="الامتياز · مسؤول التعاقدات" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="الامتياز · الموظف الإداري" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="الخارطة التنفيذية" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="لوحة الإدارة التنفيذية" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="الامتياز · المؤشرات" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="الامتياز · الموظفون" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="الامتياز · مدير الإدارة" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="الامتياز · مسؤول الامتياز" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="الامتياز · المراقب الميداني" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="الامتياز · مسؤول التعاقدات" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="الامتياز · الموظف الإداري" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="#,##0 &quot;ر.س&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,7 +42,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3864"/>
-      <sz val="18"/>
+      <sz val="17"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -58,7 +59,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -131,8 +132,14 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="002E5496"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="20"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -145,6 +152,12 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="22"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -165,12 +178,11 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
       <color rgb="001F3864"/>
-      <sz val="11"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -205,6 +217,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="008EAADB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
   </fills>
@@ -311,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -349,56 +366,80 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -411,6 +452,9 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -446,13 +490,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -484,10 +525,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="22" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="24" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -865,7 +906,7 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>درب · منظومة مؤشرات الأداء 2026 — ملف موحّد</t>
+          <t>درب · المنظومة الاستراتيجية لمؤشرات الأداء 2026 — قطاع المحطات والعقار</t>
         </is>
       </c>
     </row>
@@ -931,6 +972,455 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>إدارة الامتياز التجاري · نموذج تقييم الأداء — مسؤول التعاقدات</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>الكود: FM-04   ·   فترة القياس: ربع سنوي   ·   🟩 أدخل «نسبة التحقيق» فقط — الدرجة تُحسب تلقائياً</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="57" t="inlineStr">
+        <is>
+          <t>اسم الموظف:</t>
+        </is>
+      </c>
+      <c r="B3" s="58" t="inlineStr"/>
+      <c r="C3" s="59" t="n"/>
+      <c r="D3" s="57" t="inlineStr">
+        <is>
+          <t>القسم: الامتياز التجاري</t>
+        </is>
+      </c>
+      <c r="E3" s="58" t="inlineStr"/>
+      <c r="F3" s="60" t="n"/>
+      <c r="G3" s="59" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="57" t="inlineStr">
+        <is>
+          <t>المدير المباشر:</t>
+        </is>
+      </c>
+      <c r="B4" s="58" t="inlineStr"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="57" t="inlineStr">
+        <is>
+          <t>الربع / السنة:</t>
+        </is>
+      </c>
+      <c r="E4" s="58" t="inlineStr"/>
+      <c r="F4" s="60" t="n"/>
+      <c r="G4" s="59" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>تاريخ التقييم:</t>
+        </is>
+      </c>
+      <c r="B5" s="58" t="inlineStr"/>
+      <c r="C5" s="59" t="n"/>
+      <c r="D5" s="57" t="inlineStr">
+        <is>
+          <t>حالة التقييم:</t>
+        </is>
+      </c>
+      <c r="E5" s="58" t="inlineStr"/>
+      <c r="F5" s="60" t="n"/>
+      <c r="G5" s="59" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>مؤشر الأداء</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>الوزن %</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>المستهدف</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>نسبة التحقيق</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>الدرجة المحققة</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>جودة التفاوض مع العملاء</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D7" s="61" t="inlineStr">
+        <is>
+          <t>98% توافق مع المستهدفات</t>
+        </is>
+      </c>
+      <c r="E7" s="62" t="n"/>
+      <c r="F7" s="36">
+        <f>C7*MIN(E7,1)</f>
+        <v/>
+      </c>
+      <c r="G7" s="58" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>اكتمال المستندات النظامية قبل التوقيع</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D8" s="61" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E8" s="62" t="n"/>
+      <c r="F8" s="36">
+        <f>C8*MIN(E8,1)</f>
+        <v/>
+      </c>
+      <c r="G8" s="58" t="inlineStr"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>سرعة إنجاز إجراءات العقد</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D9" s="61" t="inlineStr">
+        <is>
+          <t>خلال يومي عمل 100%</t>
+        </is>
+      </c>
+      <c r="E9" s="62" t="n"/>
+      <c r="F9" s="36">
+        <f>C9*MIN(E9,1)</f>
+        <v/>
+      </c>
+      <c r="G9" s="58" t="inlineStr"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>أرشفة العقود الإلكترونية</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="61" t="inlineStr">
+        <is>
+          <t>خلال 48 ساعة 100%</t>
+        </is>
+      </c>
+      <c r="E10" s="62" t="n"/>
+      <c r="F10" s="36">
+        <f>C10*MIN(E10,1)</f>
+        <v/>
+      </c>
+      <c r="G10" s="58" t="inlineStr"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>متابعة تنفيذ بنود العقد</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D11" s="61" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E11" s="62" t="n"/>
+      <c r="F11" s="36">
+        <f>C11*MIN(E11,1)</f>
+        <v/>
+      </c>
+      <c r="G11" s="58" t="inlineStr"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>مدى رضا العملاء</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="61" t="inlineStr">
+        <is>
+          <t>95% رضا</t>
+        </is>
+      </c>
+      <c r="E12" s="62" t="n"/>
+      <c r="F12" s="36">
+        <f>C12*MIN(E12,1)</f>
+        <v/>
+      </c>
+      <c r="G12" s="58" t="inlineStr"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>تحديث قاعدة بيانات العملاء</t>
+        </is>
+      </c>
+      <c r="C13" s="45" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D13" s="61" t="inlineStr">
+        <is>
+          <t>100% دوري</t>
+        </is>
+      </c>
+      <c r="E13" s="62" t="n"/>
+      <c r="F13" s="36">
+        <f>C13*MIN(E13,1)</f>
+        <v/>
+      </c>
+      <c r="G13" s="58" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr"/>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>المجموع الكلي</t>
+        </is>
+      </c>
+      <c r="C14" s="64">
+        <f>SUM(C7:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="65" t="inlineStr"/>
+      <c r="E14" s="63" t="inlineStr">
+        <is>
+          <t>الدرجة:</t>
+        </is>
+      </c>
+      <c r="F14" s="66">
+        <f>SUM(F7:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="65" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>التقدير</t>
+        </is>
+      </c>
+      <c r="C15" s="67">
+        <f>IF(F14&gt;=0.9,"ممتاز",IF(F14&gt;=0.8,"جيد جداً",IF(F14&gt;=0.7,"جيد",IF(F14&gt;=0.6,"مقبول","ضعيف"))))</f>
+        <v/>
+      </c>
+      <c r="D15" s="29" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>سلّم التقييم</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="29" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>ممتاز</t>
+        </is>
+      </c>
+      <c r="C18" s="55" t="inlineStr">
+        <is>
+          <t>90% – 100%</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>تجاوز المستهدف</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>جيد جداً</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="inlineStr">
+        <is>
+          <t>80% – 89%</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>حقق المستهدف تقريباً</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>جيد</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>70% – 79%</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>حقق معظم المستهدفات</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>مقبول</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="inlineStr">
+        <is>
+          <t>60% – 69%</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>يحتاج تحسين</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>ضعيف</t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="inlineStr">
+        <is>
+          <t>أقل من 60%</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>يحتاج خطة تطوير</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
+  <mergeCells count="18">
+    <mergeCell ref="D22"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D18"/>
+    <mergeCell ref="A4"/>
+    <mergeCell ref="D20"/>
+    <mergeCell ref="A3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="D21"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="D19"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A5"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="E7 E8 E9 E10 E11 E12 E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="نسبة التحقيق" error="أدخل نسبة بين 0% و120%" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1.2</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -949,249 +1439,249 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="56" t="inlineStr">
         <is>
           <t>إدارة الامتياز التجاري · نموذج تقييم الأداء — الموظف الإداري</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>الكود: FM-05   ·   فترة القياس: ربع سنوي   ·   🟩 أدخل «نسبة التحقيق» فقط — الدرجة تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="57" t="inlineStr">
         <is>
           <t>اسم الموظف:</t>
         </is>
       </c>
-      <c r="B3" s="50" t="inlineStr"/>
-      <c r="C3" s="51" t="n"/>
-      <c r="D3" s="49" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr"/>
+      <c r="C3" s="59" t="n"/>
+      <c r="D3" s="57" t="inlineStr">
         <is>
           <t>القسم: الامتياز التجاري</t>
         </is>
       </c>
-      <c r="E3" s="50" t="inlineStr"/>
-      <c r="F3" s="52" t="n"/>
-      <c r="G3" s="51" t="n"/>
+      <c r="E3" s="58" t="inlineStr"/>
+      <c r="F3" s="60" t="n"/>
+      <c r="G3" s="59" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="57" t="inlineStr">
         <is>
           <t>المدير المباشر:</t>
         </is>
       </c>
-      <c r="B4" s="50" t="inlineStr"/>
-      <c r="C4" s="51" t="n"/>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="57" t="inlineStr">
         <is>
           <t>الربع / السنة:</t>
         </is>
       </c>
-      <c r="E4" s="50" t="inlineStr"/>
-      <c r="F4" s="52" t="n"/>
-      <c r="G4" s="51" t="n"/>
+      <c r="E4" s="58" t="inlineStr"/>
+      <c r="F4" s="60" t="n"/>
+      <c r="G4" s="59" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>تاريخ التقييم:</t>
         </is>
       </c>
-      <c r="B5" s="50" t="inlineStr"/>
-      <c r="C5" s="51" t="n"/>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr"/>
+      <c r="C5" s="59" t="n"/>
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>حالة التقييم:</t>
         </is>
       </c>
-      <c r="E5" s="50" t="inlineStr"/>
-      <c r="F5" s="52" t="n"/>
-      <c r="G5" s="51" t="n"/>
+      <c r="E5" s="58" t="inlineStr"/>
+      <c r="F5" s="60" t="n"/>
+      <c r="G5" s="59" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>مؤشر الأداء</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>الوزن %</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>المستهدف</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>نسبة التحقيق</t>
         </is>
       </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>الدرجة المحققة</t>
         </is>
       </c>
-      <c r="G6" s="31" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>دقة وسرعة إعداد التقارير الدورية</t>
         </is>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="45" t="n">
         <v>0.3</v>
       </c>
-      <c r="D7" s="53" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>100% في الوقت المحدد</t>
         </is>
       </c>
-      <c r="E7" s="54" t="n"/>
-      <c r="F7" s="25">
+      <c r="E7" s="62" t="n"/>
+      <c r="F7" s="36">
         <f>C7*MIN(E7,1)</f>
         <v/>
       </c>
-      <c r="G7" s="50" t="inlineStr"/>
+      <c r="G7" s="58" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>متابعة الشكاوى وحالات العملاء</t>
         </is>
       </c>
-      <c r="C8" s="36" t="n">
+      <c r="C8" s="45" t="n">
         <v>0.3</v>
       </c>
-      <c r="D8" s="53" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>100% حتى الإغلاق</t>
         </is>
       </c>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="25">
+      <c r="E8" s="62" t="n"/>
+      <c r="F8" s="36">
         <f>C8*MIN(E8,1)</f>
         <v/>
       </c>
-      <c r="G8" s="50" t="inlineStr"/>
+      <c r="G8" s="58" t="inlineStr"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>متابعة عمولات تأجير الوحدات</t>
         </is>
       </c>
-      <c r="C9" s="36" t="n">
+      <c r="C9" s="45" t="n">
         <v>0.2</v>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E9" s="54" t="n"/>
-      <c r="F9" s="25">
+      <c r="E9" s="62" t="n"/>
+      <c r="F9" s="36">
         <f>C9*MIN(E9,1)</f>
         <v/>
       </c>
-      <c r="G9" s="50" t="inlineStr"/>
+      <c r="G9" s="58" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>تحديث بيانات العملاء والمحطات</t>
         </is>
       </c>
-      <c r="C10" s="36" t="n">
+      <c r="C10" s="45" t="n">
         <v>0.1</v>
       </c>
-      <c r="D10" s="53" t="inlineStr">
+      <c r="D10" s="61" t="inlineStr">
         <is>
           <t>100% دقة</t>
         </is>
       </c>
-      <c r="E10" s="54" t="n"/>
-      <c r="F10" s="25">
+      <c r="E10" s="62" t="n"/>
+      <c r="F10" s="36">
         <f>C10*MIN(E10,1)</f>
         <v/>
       </c>
-      <c r="G10" s="50" t="inlineStr"/>
+      <c r="G10" s="58" t="inlineStr"/>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>إعداد المراسلات الرسمية</t>
         </is>
       </c>
-      <c r="C11" s="36" t="n">
+      <c r="C11" s="45" t="n">
         <v>0.1</v>
       </c>
-      <c r="D11" s="53" t="inlineStr">
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>100% في الوقت المحدد</t>
         </is>
       </c>
-      <c r="E11" s="54" t="n"/>
-      <c r="F11" s="25">
+      <c r="E11" s="62" t="n"/>
+      <c r="F11" s="36">
         <f>C11*MIN(E11,1)</f>
         <v/>
       </c>
-      <c r="G11" s="50" t="inlineStr"/>
+      <c r="G11" s="58" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr"/>
-      <c r="B12" s="55" t="inlineStr">
+      <c r="B12" s="63" t="inlineStr">
         <is>
           <t>المجموع الكلي</t>
         </is>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="64">
         <f>SUM(C7:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="57" t="inlineStr"/>
-      <c r="E12" s="55" t="inlineStr">
+      <c r="D12" s="65" t="inlineStr"/>
+      <c r="E12" s="63" t="inlineStr">
         <is>
           <t>الدرجة:</t>
         </is>
       </c>
-      <c r="F12" s="58">
+      <c r="F12" s="66">
         <f>SUM(F7:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="57" t="inlineStr"/>
+      <c r="G12" s="65" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
@@ -1199,11 +1689,11 @@
           <t>التقدير</t>
         </is>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="67">
         <f>IF(F12&gt;=0.9,"ممتاز",IF(F12&gt;=0.8,"جيد جداً",IF(F12&gt;=0.7,"جيد",IF(F12&gt;=0.6,"مقبول","ضعيف"))))</f>
         <v/>
       </c>
-      <c r="D13" s="22" t="n"/>
+      <c r="D13" s="29" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="5" t="inlineStr">
@@ -1211,89 +1701,89 @@
           <t>سلّم التقييم</t>
         </is>
       </c>
-      <c r="C15" s="21" t="n"/>
-      <c r="D15" s="22" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="29" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>ممتاز</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="55" t="inlineStr">
         <is>
           <t>90% – 100%</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>تجاوز المستهدف</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>جيد جداً</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="55" t="inlineStr">
         <is>
           <t>80% – 89%</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>حقق المستهدف تقريباً</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>جيد</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="55" t="inlineStr">
         <is>
           <t>70% – 79%</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>حقق معظم المستهدفات</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>مقبول</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="55" t="inlineStr">
         <is>
           <t>60% – 69%</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>يحتاج تحسين</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>ضعيف</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="55" t="inlineStr">
         <is>
           <t>أقل من 60%</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>يحتاج خطة تطوير</t>
         </is>
@@ -1349,7 +1839,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>ركائز واستراتيجية درب 2026</t>
+          <t>ركائز واستراتيجية درب 2026 — قطاع المحطات والعقار</t>
         </is>
       </c>
     </row>
@@ -1590,318 +2080,488 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F24"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="38" customHeight="1">
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>درب · لوحة الإدارة التنفيذية 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>مؤشر الإنجاز العام (الامتياز)</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>✅ محقق</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>🟡 قريب</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>🔴 تحت الهدف</t>
-        </is>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>الخارطة التنفيذية 2026 — مشاريع الشركة وربطها بالمؤشرات (قطاع المحطات والعقار)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>المصدر: «رؤية وأهداف 2026» — سحور درب  ·  التغطية: ✅ مرتبط 🟡 جزئي 🔴 فجوة  ·  أداء المؤشرات يُحسب آلياً من المؤشرات المرتبطة</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>الركيزة</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>المشروع</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>الإدارة المسؤولة</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>المؤشرات المرتبطة</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>التغطية</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>أداء المؤشرات (مباشر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>التوسع في المواقع</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>التشغيل + الامتياز + الاستثمار</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>محطات الامتياز المشغّلة (150) · تشغيل 85 محطة · 190 عقد استثماري</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>✅ مرتبط</t>
+        </is>
+      </c>
+      <c r="G4" s="21">
+        <f>IF(COUNTIFS('الامتياز · المؤشرات'!$Y$4:$Y$39,"التوسع في المواقع")=0,"—",IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$Y$4:$Y$39,"التوسع في المواقع"),"—"))</f>
+        <v/>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="17">
-        <f>IFERROR(AVERAGE('الامتياز · المؤشرات'!$V$4:$V$39),0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="18">
-        <f>COUNTIF('الامتياز · المؤشرات'!$W$4:$W$39,"✅ محقق")</f>
-        <v/>
-      </c>
-      <c r="E5" s="18">
-        <f>COUNTIF('الامتياز · المؤشرات'!$W$4:$W$39,"🟡 قريب")</f>
-        <v/>
-      </c>
-      <c r="F5" s="18">
-        <f>COUNTIF('الامتياز · المؤشرات'!$W$4:$W$39,"🔴 تحت الهدف")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="D6" s="19" t="n"/>
-      <c r="E6" s="19" t="n"/>
-      <c r="F6" s="19" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>الأداء حسب المحور — إدارة الامتياز</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="n"/>
-      <c r="D8" s="22" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>المحور</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>نسبة التحقيق</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>الحالة</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>النمو والتوسع</t>
-        </is>
-      </c>
-      <c r="C10" s="25">
-        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"النمو والتوسع"),0)</f>
-        <v/>
-      </c>
-      <c r="D10" s="26">
-        <f>IF(C10&gt;=1,"✅ محقق",IF(C10&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>المبيعات والأداء التجاري</t>
-        </is>
-      </c>
-      <c r="C11" s="25">
-        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"المبيعات والأداء التجاري"),0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="26">
-        <f>IF(C11&gt;=1,"✅ محقق",IF(C11&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>الأداء المالي</t>
-        </is>
-      </c>
-      <c r="C12" s="25">
-        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"الأداء المالي"),0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="26">
-        <f>IF(C12&gt;=1,"✅ محقق",IF(C12&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>التشغيل والجودة</t>
-        </is>
-      </c>
-      <c r="C13" s="25">
-        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"التشغيل والجودة"),0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="26">
-        <f>IF(C13&gt;=1,"✅ محقق",IF(C13&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>الهوية والتسويق</t>
-        </is>
-      </c>
-      <c r="C14" s="25">
-        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"الهوية والتسويق"),0)</f>
-        <v/>
-      </c>
-      <c r="D14" s="26">
-        <f>IF(C14&gt;=1,"✅ محقق",IF(C14&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>التوسع الإقليمي</t>
-        </is>
-      </c>
-      <c r="C15" s="25">
-        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"التوسع الإقليمي"),0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="26">
-        <f>IF(C15&gt;=1,"✅ محقق",IF(C15&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>تجربة العملاء والشركاء</t>
-        </is>
-      </c>
-      <c r="C16" s="25">
-        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"تجربة العملاء والشركاء"),0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="26">
-        <f>IF(C16&gt;=1,"✅ محقق",IF(C16&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
+      <c r="A5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>الامتياز التجاري</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>الامتياز التجاري</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>عقود الامتياز الجديدة (167) · إجمالي مبيعات الوقود</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>✅ مرتبط</t>
+        </is>
+      </c>
+      <c r="G5" s="21">
+        <f>IF(COUNTIFS('الامتياز · المؤشرات'!$Y$4:$Y$39,"الامتياز التجاري")=0,"—",IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$Y$4:$Y$39,"الامتياز التجاري"),"—"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>زيادة وصول العملاء</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>الامتياز + التسويق</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>إجمالي مبيعات الوقود (718.8M) · تغطية 13 منطقة</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>✅ مرتبط</t>
+        </is>
+      </c>
+      <c r="G6" s="21">
+        <f>IF(COUNTIFS('الامتياز · المؤشرات'!$Y$4:$Y$39,"زيادة وصول العملاء")=0,"—",IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$Y$4:$Y$39,"زيادة وصول العملاء"),"—"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>إطلاق مشاريع جديدة</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>غير محددة — مقترح: الاستثمار/التطوير</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>— لا يوجد مؤشر مخصص —</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>🔴 فجوة</t>
+        </is>
+      </c>
+      <c r="G7" s="21">
+        <f>IF(COUNTIFS('الامتياز · المؤشرات'!$Y$4:$Y$39,"إطلاق مشاريع جديدة")=0,"—",IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$Y$4:$Y$39,"إطلاق مشاريع جديدة"),"—"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>تطوير التصاميم والهوية</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>غير محددة — مقترح: التسويق والعلامة</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>نسبة التزام المحطات بالهوية (55%) فقط</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>🟡 مرتبط جزئياً</t>
+        </is>
+      </c>
+      <c r="G8" s="21">
+        <f>IF(COUNTIFS('الامتياز · المؤشرات'!$Y$4:$Y$39,"تطوير التصاميم والهوية")=0,"—",IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$Y$4:$Y$39,"تطوير التصاميم والهوية"),"—"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>غير محددة — مقترح: تقنية المعلومات</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>أتمتة المحطات (90%) · المعيار الشامل (30%)</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>🟡 مرتبط جزئياً</t>
+        </is>
+      </c>
+      <c r="G9" s="21">
+        <f>IF(COUNTIFS('الامتياز · المؤشرات'!$Y$4:$Y$39,"التحول التقني")=0,"—",IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$Y$4:$Y$39,"التحول التقني"),"—"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>ساحات درب</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>العقار</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>تأجير ساحة درب (≥80%) · 6 علامات جديدة</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>✅ مرتبط</t>
+        </is>
+      </c>
+      <c r="G10" s="21">
+        <f>IF(COUNTIFS('الامتياز · المؤشرات'!$Y$4:$Y$39,"ساحات درب")=0,"—",IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$Y$4:$Y$39,"ساحات درب"),"—"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>تطبيق «تانكي»</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>غير محددة</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>— لا يوجد مؤشر ولا إدارة مسؤولة —</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>🔴 فجوة</t>
+        </is>
+      </c>
+      <c r="G11" s="21">
+        <f>IF(COUNTIFS('الامتياز · المؤشرات'!$Y$4:$Y$39,"تطبيق «تانكي»")=0,"—",IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$Y$4:$Y$39,"تطبيق «تانكي»"),"—"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>تعزيز تجربة العملاء</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>الامتياز + التشغيل</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>CSAT (90%) · تقييم قوقل (4.5+) · حل الشكاوى</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>✅ مرتبط</t>
+        </is>
+      </c>
+      <c r="G12" s="21">
+        <f>IF(COUNTIFS('الامتياز · المؤشرات'!$Y$4:$Y$39,"تعزيز تجربة العملاء")=0,"—",IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$Y$4:$Y$39,"تعزيز تجربة العملاء"),"—"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>التشغيل + الامتياز</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>جاهزية 99% · السلامة 100% · 15 مؤشر تشغيلي</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>✅ مرتبط</t>
+        </is>
+      </c>
+      <c r="G13" s="21">
+        <f>IF(COUNTIFS('الامتياز · المؤشرات'!$Y$4:$Y$39,"جودة التشغيل")=0,"—",IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$Y$4:$Y$39,"جودة التشغيل"),"—"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>منظومة التأجير</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>العقار</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>الإشغال (≥60%) · 68 وحدة/شهر · التحصيل (95%+)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>✅ مرتبط</t>
+        </is>
+      </c>
+      <c r="G14" s="21">
+        <f>IF(COUNTIFS('الامتياز · المؤشرات'!$Y$4:$Y$39,"منظومة التأجير")=0,"—",IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$Y$4:$Y$39,"منظومة التأجير"),"—"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>غير محددة — مقترح: الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>— لا يوجد مؤشر لتطوير/استبقاء الموظفين —</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>🔴 فجوة</t>
+        </is>
+      </c>
+      <c r="G15" s="21">
+        <f>IF(COUNTIFS('الامتياز · المؤشرات'!$Y$4:$Y$39,"الاستثمار في الموظفين")=0,"—",IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$Y$4:$Y$39,"الاستثمار في الموظفين"),"—"))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>استدامة الشراكة والامتثال</t>
-        </is>
-      </c>
-      <c r="C17" s="25">
-        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"استدامة الشراكة والامتثال"),0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="26">
-        <f>IF(C17&gt;=1,"✅ محقق",IF(C17&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>نظرة الإدارات (تغذي نفس الملف)</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="n"/>
-      <c r="D19" s="22" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>الإدارة</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>الإنجاز</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>الحالة</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>الامتياز التجاري والمبيعات</t>
-        </is>
-      </c>
-      <c r="C21" s="25">
-        <f>IFERROR(AVERAGE('الامتياز · المؤشرات'!$V$4:$V$39),0)</f>
-        <v/>
-      </c>
-      <c r="D21" s="26">
-        <f>IF(C21&gt;=1,"✅ محقق",IF(C21&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>التشغيل والمحطات</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="inlineStr">
-        <is>
-          <t>قيد الإضافة</t>
-        </is>
-      </c>
-      <c r="D22" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>الاستثمار</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="inlineStr">
-        <is>
-          <t>قيد الإضافة</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>العقار</t>
-        </is>
-      </c>
-      <c r="C24" s="27" t="inlineStr">
-        <is>
-          <t>قيد الإضافة</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>⚠️ ملخص الفجوات — مشاريع تحتاج مؤشراً أو إدارة مسؤولة</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>🔴 تطبيق «تانكي» — لا مؤشر ولا إدارة مسؤولة (منتج رقمي بلا مالك).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>🔴 الاستثمار في الموظفين — لا مؤشر موظفين ولا إدارة موارد بشرية ضمن الملفات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>🔴 إطلاق مشاريع جديدة — مبادرة بلا مؤشر مخصص ولا مالك واضح.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>🟡 التحول التقني — مغطّى جزئياً بالأتمتة فقط؛ بلا إدارة تقنية مالكة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>🟡 تطوير التصاميم والهوية — مغطّى بمؤشر التزام الهوية فقط؛ بلا إدارة تسويق/علامة.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
-  <mergeCells count="8">
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D5:D6"/>
+  <mergeCells count="11">
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B7:B11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1913,7 +2573,397 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W39"/>
+  <dimension ref="B2:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="38" customHeight="1">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>درب · لوحة الإدارة التنفيذية 2026 — المحطات والعقار</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>مؤشر الإنجاز العام (الامتياز)</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>✅ محقق</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>🟡 قريب</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>🔴 تحت الهدف</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="inlineStr">
+        <is>
+          <t>الأداء حسب الركائز (5 سنوات)</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="n"/>
+      <c r="J4" s="29" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="30">
+        <f>IFERROR(AVERAGE('الامتياز · المؤشرات'!$V$4:$V$39),0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="31">
+        <f>COUNTIF('الامتياز · المؤشرات'!$W$4:$W$39,"✅ محقق")</f>
+        <v/>
+      </c>
+      <c r="E5" s="31">
+        <f>COUNTIF('الامتياز · المؤشرات'!$W$4:$W$39,"🟡 قريب")</f>
+        <v/>
+      </c>
+      <c r="F5" s="31">
+        <f>COUNTIF('الامتياز · المؤشرات'!$W$4:$W$39,"🔴 تحت الهدف")</f>
+        <v/>
+      </c>
+      <c r="H5" s="32" t="inlineStr">
+        <is>
+          <t>الركيزة</t>
+        </is>
+      </c>
+      <c r="I5" s="32" t="inlineStr">
+        <is>
+          <t>الإنجاز</t>
+        </is>
+      </c>
+      <c r="J5" s="32" t="inlineStr">
+        <is>
+          <t>الحالة</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="H6" s="34" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="I6" s="21">
+        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$X$4:$X$39,"النمو"),"—")</f>
+        <v/>
+      </c>
+      <c r="J6" s="35">
+        <f>IF(ISNUMBER(I6),IF(I6&gt;=1,"✅",IF(I6&gt;=0.85,"🟡","🔴")),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7" s="34" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="I7" s="21">
+        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$X$4:$X$39,"الابتكار"),"—")</f>
+        <v/>
+      </c>
+      <c r="J7" s="35">
+        <f>IF(ISNUMBER(I7),IF(I7&gt;=1,"✅",IF(I7&gt;=0.85,"🟡","🔴")),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>الأداء حسب المحور — إدارة الامتياز</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="H8" s="34" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="I8" s="21">
+        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$X$4:$X$39,"الاستدامة"),"—")</f>
+        <v/>
+      </c>
+      <c r="J8" s="35">
+        <f>IF(ISNUMBER(I8),IF(I8&gt;=1,"✅",IF(I8&gt;=0.85,"🟡","🔴")),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>المحور</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>نسبة التحقيق</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>الحالة</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>النمو والتوسع</t>
+        </is>
+      </c>
+      <c r="C10" s="36">
+        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"النمو والتوسع"),0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="16">
+        <f>IF(C10&gt;=1,"✅ محقق",IF(C10&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>المبيعات والأداء التجاري</t>
+        </is>
+      </c>
+      <c r="C11" s="36">
+        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"المبيعات والأداء التجاري"),0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="16">
+        <f>IF(C11&gt;=1,"✅ محقق",IF(C11&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>الأداء المالي</t>
+        </is>
+      </c>
+      <c r="C12" s="36">
+        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"الأداء المالي"),0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="16">
+        <f>IF(C12&gt;=1,"✅ محقق",IF(C12&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>التشغيل والجودة</t>
+        </is>
+      </c>
+      <c r="C13" s="36">
+        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"التشغيل والجودة"),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="16">
+        <f>IF(C13&gt;=1,"✅ محقق",IF(C13&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>الهوية والتسويق</t>
+        </is>
+      </c>
+      <c r="C14" s="36">
+        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"الهوية والتسويق"),0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="16">
+        <f>IF(C14&gt;=1,"✅ محقق",IF(C14&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>التوسع الإقليمي</t>
+        </is>
+      </c>
+      <c r="C15" s="36">
+        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"التوسع الإقليمي"),0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="16">
+        <f>IF(C15&gt;=1,"✅ محقق",IF(C15&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>تجربة العملاء والشركاء</t>
+        </is>
+      </c>
+      <c r="C16" s="36">
+        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"تجربة العملاء والشركاء"),0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>IF(C16&gt;=1,"✅ محقق",IF(C16&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>استدامة الشراكة والامتثال</t>
+        </is>
+      </c>
+      <c r="C17" s="36">
+        <f>IFERROR(AVERAGEIFS('الامتياز · المؤشرات'!$V$4:$V$39,'الامتياز · المؤشرات'!$B$4:$B$39,"استدامة الشراكة والامتثال"),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="16">
+        <f>IF(C17&gt;=1,"✅ محقق",IF(C17&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>نظرة الإدارات (تغذي نفس الملف)</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="29" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>الإدارة</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>الإنجاز</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>الحالة</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>الامتياز التجاري والمبيعات</t>
+        </is>
+      </c>
+      <c r="C21" s="36">
+        <f>IFERROR(AVERAGE('الامتياز · المؤشرات'!$V$4:$V$39),0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="16">
+        <f>IF(C21&gt;=1,"✅ محقق",IF(C21&gt;=0.85,"🟡 قريب","🔴 تحت الهدف"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>التشغيل والمحطات</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="inlineStr">
+        <is>
+          <t>قيد الإضافة</t>
+        </is>
+      </c>
+      <c r="D22" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>الاستثمار</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>قيد الإضافة</t>
+        </is>
+      </c>
+      <c r="D23" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>العقار</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="inlineStr">
+        <is>
+          <t>قيد الإضافة</t>
+        </is>
+      </c>
+      <c r="D24" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
+  <mergeCells count="9">
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D5:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1939,2368 +2989,2740 @@
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>إدارة الامتياز التجاري والمبيعات · مؤشرات الأداء 2026  (36 مؤشر / 8 محاور)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
-        <is>
-          <t>🟩 الخلايا الخضراء = إدخال شهري للمسؤول   ·   باقي الأعمدة محسوبة/مقفولة   ·   YTD ونسبة التحقيق والحالة تلقائية</t>
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>🟩 الخلايا الخضراء = إدخال شهري للمسؤول   ·   باقي الأعمدة محسوبة/مقفولة   ·   كل مؤشر يغذّي ركيزته ومشروعه تلقائياً</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>المحور</t>
         </is>
       </c>
-      <c r="C3" s="31" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="D3" s="31" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>الوحدة</t>
         </is>
       </c>
-      <c r="E3" s="31" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>القطبية</t>
         </is>
       </c>
-      <c r="F3" s="31" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>التجميع</t>
         </is>
       </c>
-      <c r="G3" s="31" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>المستهدف</t>
         </is>
       </c>
-      <c r="H3" s="31" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>نص المستهدف</t>
         </is>
       </c>
-      <c r="I3" s="31" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>يناير</t>
         </is>
       </c>
-      <c r="J3" s="31" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>فبراير</t>
         </is>
       </c>
-      <c r="K3" s="31" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t>مارس</t>
         </is>
       </c>
-      <c r="L3" s="31" t="inlineStr">
+      <c r="L3" s="15" t="inlineStr">
         <is>
           <t>أبريل</t>
         </is>
       </c>
-      <c r="M3" s="31" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>مايو</t>
         </is>
       </c>
-      <c r="N3" s="31" t="inlineStr">
+      <c r="N3" s="15" t="inlineStr">
         <is>
           <t>يونيو</t>
         </is>
       </c>
-      <c r="O3" s="31" t="inlineStr">
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t>يوليو</t>
         </is>
       </c>
-      <c r="P3" s="31" t="inlineStr">
+      <c r="P3" s="15" t="inlineStr">
         <is>
           <t>أغسطس</t>
         </is>
       </c>
-      <c r="Q3" s="31" t="inlineStr">
+      <c r="Q3" s="15" t="inlineStr">
         <is>
           <t>سبتمبر</t>
         </is>
       </c>
-      <c r="R3" s="31" t="inlineStr">
+      <c r="R3" s="15" t="inlineStr">
         <is>
           <t>أكتوبر</t>
         </is>
       </c>
-      <c r="S3" s="31" t="inlineStr">
+      <c r="S3" s="15" t="inlineStr">
         <is>
           <t>نوفمبر</t>
         </is>
       </c>
-      <c r="T3" s="31" t="inlineStr">
+      <c r="T3" s="15" t="inlineStr">
         <is>
           <t>ديسمبر</t>
         </is>
       </c>
-      <c r="U3" s="31" t="inlineStr">
+      <c r="U3" s="15" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="V3" s="31" t="inlineStr">
+      <c r="V3" s="15" t="inlineStr">
         <is>
           <t>نسبة التحقيق</t>
         </is>
       </c>
-      <c r="W3" s="31" t="inlineStr">
+      <c r="W3" s="15" t="inlineStr">
         <is>
           <t>الحالة</t>
         </is>
       </c>
+      <c r="X3" s="15" t="inlineStr">
+        <is>
+          <t>الركيزة (5س)</t>
+        </is>
+      </c>
+      <c r="Y3" s="15" t="inlineStr">
+        <is>
+          <t>المشروع (الخارطة)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="26" t="n">
+      <c r="A4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>النمو والتوسع</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>عدد محطات الامتياز المشغّلة (تراكمي)</t>
         </is>
       </c>
-      <c r="D4" s="28" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>محطة</t>
         </is>
       </c>
-      <c r="E4" s="28" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F4" s="28" t="inlineStr">
+      <c r="F4" s="38" t="inlineStr">
         <is>
           <t>LAST</t>
         </is>
       </c>
-      <c r="G4" s="32" t="n">
+      <c r="G4" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="H4" s="33" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>150 محطة</t>
         </is>
       </c>
-      <c r="I4" s="34" t="n"/>
-      <c r="J4" s="34" t="n"/>
-      <c r="K4" s="34" t="n"/>
-      <c r="L4" s="34" t="n"/>
-      <c r="M4" s="34" t="n"/>
-      <c r="N4" s="34" t="n"/>
-      <c r="O4" s="34" t="n"/>
-      <c r="P4" s="34" t="n"/>
-      <c r="Q4" s="34" t="n"/>
-      <c r="R4" s="34" t="n"/>
-      <c r="S4" s="34" t="n"/>
-      <c r="T4" s="34" t="n"/>
-      <c r="U4" s="35">
+      <c r="I4" s="42" t="n"/>
+      <c r="J4" s="42" t="n"/>
+      <c r="K4" s="42" t="n"/>
+      <c r="L4" s="42" t="n"/>
+      <c r="M4" s="42" t="n"/>
+      <c r="N4" s="42" t="n"/>
+      <c r="O4" s="42" t="n"/>
+      <c r="P4" s="42" t="n"/>
+      <c r="Q4" s="42" t="n"/>
+      <c r="R4" s="42" t="n"/>
+      <c r="S4" s="42" t="n"/>
+      <c r="T4" s="42" t="n"/>
+      <c r="U4" s="43">
         <f>IF($F4="SUM",IF(COUNT($I4:$T4)=0,"",SUM($I4:$T4)),IF($F4="AVG",IFERROR(AVERAGE($I4:$T4),""),IF($F4="LAST",IFERROR(LOOKUP(2,1/($I4:$T4&lt;&gt;""),$I4:$T4),""),"")))</f>
         <v/>
       </c>
-      <c r="V4" s="25">
+      <c r="V4" s="36">
         <f>IF($G4="","",IF($U4="","",IF($G4=0,IF($U4&lt;=0,1,0),IF($E4="↓",IFERROR($G4/$U4,0),IFERROR($U4/$G4,0)))))</f>
         <v/>
       </c>
-      <c r="W4" s="26">
+      <c r="W4" s="16">
         <f>IF($V4="","—",IF($V4&gt;=1,"✅ محقق",IF($V4&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X4" s="44" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="Y4" s="19" t="inlineStr">
+        <is>
+          <t>التوسع في المواقع</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="26" t="n">
+      <c r="A5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>النمو والتوسع</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>عدد عقود الامتياز الجديدة الموقّعة</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>عقد</t>
         </is>
       </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
+      <c r="F5" s="38" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
-      <c r="G5" s="32" t="n">
+      <c r="G5" s="40" t="n">
         <v>167</v>
       </c>
-      <c r="H5" s="33" t="inlineStr">
+      <c r="H5" s="41" t="inlineStr">
         <is>
           <t>167 عقد</t>
         </is>
       </c>
-      <c r="I5" s="34" t="n"/>
-      <c r="J5" s="34" t="n"/>
-      <c r="K5" s="34" t="n"/>
-      <c r="L5" s="34" t="n"/>
-      <c r="M5" s="34" t="n"/>
-      <c r="N5" s="34" t="n"/>
-      <c r="O5" s="34" t="n"/>
-      <c r="P5" s="34" t="n"/>
-      <c r="Q5" s="34" t="n"/>
-      <c r="R5" s="34" t="n"/>
-      <c r="S5" s="34" t="n"/>
-      <c r="T5" s="34" t="n"/>
-      <c r="U5" s="35">
+      <c r="I5" s="42" t="n"/>
+      <c r="J5" s="42" t="n"/>
+      <c r="K5" s="42" t="n"/>
+      <c r="L5" s="42" t="n"/>
+      <c r="M5" s="42" t="n"/>
+      <c r="N5" s="42" t="n"/>
+      <c r="O5" s="42" t="n"/>
+      <c r="P5" s="42" t="n"/>
+      <c r="Q5" s="42" t="n"/>
+      <c r="R5" s="42" t="n"/>
+      <c r="S5" s="42" t="n"/>
+      <c r="T5" s="42" t="n"/>
+      <c r="U5" s="43">
         <f>IF($F5="SUM",IF(COUNT($I5:$T5)=0,"",SUM($I5:$T5)),IF($F5="AVG",IFERROR(AVERAGE($I5:$T5),""),IF($F5="LAST",IFERROR(LOOKUP(2,1/($I5:$T5&lt;&gt;""),$I5:$T5),""),"")))</f>
         <v/>
       </c>
-      <c r="V5" s="25">
+      <c r="V5" s="36">
         <f>IF($G5="","",IF($U5="","",IF($G5=0,IF($U5&lt;=0,1,0),IF($E5="↓",IFERROR($G5/$U5,0),IFERROR($U5/$G5,0)))))</f>
         <v/>
       </c>
-      <c r="W5" s="26">
+      <c r="W5" s="16">
         <f>IF($V5="","—",IF($V5&gt;=1,"✅ محقق",IF($V5&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X5" s="44" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="Y5" s="19" t="inlineStr">
+        <is>
+          <t>الامتياز التجاري</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>المبيعات والأداء التجاري</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>إجمالي مبيعات وقود محطات الامتياز</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
         <is>
           <t>لتر</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="E6" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="F6" s="38" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="40" t="n">
         <v>718838077</v>
       </c>
-      <c r="H6" s="33" t="inlineStr">
+      <c r="H6" s="41" t="inlineStr">
         <is>
           <t>718.8M لتر</t>
         </is>
       </c>
-      <c r="I6" s="34" t="n"/>
-      <c r="J6" s="34" t="n"/>
-      <c r="K6" s="34" t="n"/>
-      <c r="L6" s="34" t="n"/>
-      <c r="M6" s="34" t="n"/>
-      <c r="N6" s="34" t="n"/>
-      <c r="O6" s="34" t="n"/>
-      <c r="P6" s="34" t="n"/>
-      <c r="Q6" s="34" t="n"/>
-      <c r="R6" s="34" t="n"/>
-      <c r="S6" s="34" t="n"/>
-      <c r="T6" s="34" t="n"/>
-      <c r="U6" s="35">
+      <c r="I6" s="42" t="n"/>
+      <c r="J6" s="42" t="n"/>
+      <c r="K6" s="42" t="n"/>
+      <c r="L6" s="42" t="n"/>
+      <c r="M6" s="42" t="n"/>
+      <c r="N6" s="42" t="n"/>
+      <c r="O6" s="42" t="n"/>
+      <c r="P6" s="42" t="n"/>
+      <c r="Q6" s="42" t="n"/>
+      <c r="R6" s="42" t="n"/>
+      <c r="S6" s="42" t="n"/>
+      <c r="T6" s="42" t="n"/>
+      <c r="U6" s="43">
         <f>IF($F6="SUM",IF(COUNT($I6:$T6)=0,"",SUM($I6:$T6)),IF($F6="AVG",IFERROR(AVERAGE($I6:$T6),""),IF($F6="LAST",IFERROR(LOOKUP(2,1/($I6:$T6&lt;&gt;""),$I6:$T6),""),"")))</f>
         <v/>
       </c>
-      <c r="V6" s="25">
+      <c r="V6" s="36">
         <f>IF($G6="","",IF($U6="","",IF($G6=0,IF($U6&lt;=0,1,0),IF($E6="↓",IFERROR($G6/$U6,0),IFERROR($U6/$G6,0)))))</f>
         <v/>
       </c>
-      <c r="W6" s="26">
+      <c r="W6" s="16">
         <f>IF($V6="","—",IF($V6&gt;=1,"✅ محقق",IF($V6&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X6" s="44" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="Y6" s="19" t="inlineStr">
+        <is>
+          <t>زيادة وصول العملاء</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>المبيعات والأداء التجاري</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>نسبة المحطات التي حققت مستهدف المبيعات</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G7" s="36" t="n">
+      <c r="G7" s="45" t="n">
         <v>0.9</v>
       </c>
-      <c r="H7" s="33" t="inlineStr">
+      <c r="H7" s="41" t="inlineStr">
         <is>
           <t>90%+</t>
         </is>
       </c>
-      <c r="I7" s="37" t="n"/>
-      <c r="J7" s="37" t="n"/>
-      <c r="K7" s="37" t="n"/>
-      <c r="L7" s="37" t="n"/>
-      <c r="M7" s="37" t="n"/>
-      <c r="N7" s="37" t="n"/>
-      <c r="O7" s="37" t="n"/>
-      <c r="P7" s="37" t="n"/>
-      <c r="Q7" s="37" t="n"/>
-      <c r="R7" s="37" t="n"/>
-      <c r="S7" s="37" t="n"/>
-      <c r="T7" s="37" t="n"/>
-      <c r="U7" s="38">
+      <c r="I7" s="46" t="n"/>
+      <c r="J7" s="46" t="n"/>
+      <c r="K7" s="46" t="n"/>
+      <c r="L7" s="46" t="n"/>
+      <c r="M7" s="46" t="n"/>
+      <c r="N7" s="46" t="n"/>
+      <c r="O7" s="46" t="n"/>
+      <c r="P7" s="46" t="n"/>
+      <c r="Q7" s="46" t="n"/>
+      <c r="R7" s="46" t="n"/>
+      <c r="S7" s="46" t="n"/>
+      <c r="T7" s="46" t="n"/>
+      <c r="U7" s="47">
         <f>IF($F7="SUM",IF(COUNT($I7:$T7)=0,"",SUM($I7:$T7)),IF($F7="AVG",IFERROR(AVERAGE($I7:$T7),""),IF($F7="LAST",IFERROR(LOOKUP(2,1/($I7:$T7&lt;&gt;""),$I7:$T7),""),"")))</f>
         <v/>
       </c>
-      <c r="V7" s="25">
+      <c r="V7" s="36">
         <f>IF($G7="","",IF($U7="","",IF($G7=0,IF($U7&lt;=0,1,0),IF($E7="↓",IFERROR($G7/$U7,0),IFERROR($U7/$G7,0)))))</f>
         <v/>
       </c>
-      <c r="W7" s="26">
+      <c r="W7" s="16">
         <f>IF($V7="","—",IF($V7&gt;=1,"✅ محقق",IF($V7&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X7" s="44" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="Y7" s="19" t="inlineStr">
+        <is>
+          <t>زيادة وصول العملاء</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>المبيعات والأداء التجاري</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>متوسط مبيعات المحطة الواحدة شهرياً</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>لتر/محطة</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr"/>
-      <c r="H8" s="33" t="inlineStr">
+      <c r="G8" s="38" t="inlineStr"/>
+      <c r="H8" s="41" t="inlineStr">
         <is>
           <t>+10% نمو شهري</t>
         </is>
       </c>
-      <c r="I8" s="34" t="n"/>
-      <c r="J8" s="34" t="n"/>
-      <c r="K8" s="34" t="n"/>
-      <c r="L8" s="34" t="n"/>
-      <c r="M8" s="34" t="n"/>
-      <c r="N8" s="34" t="n"/>
-      <c r="O8" s="34" t="n"/>
-      <c r="P8" s="34" t="n"/>
-      <c r="Q8" s="34" t="n"/>
-      <c r="R8" s="34" t="n"/>
-      <c r="S8" s="34" t="n"/>
-      <c r="T8" s="34" t="n"/>
-      <c r="U8" s="35">
+      <c r="I8" s="42" t="n"/>
+      <c r="J8" s="42" t="n"/>
+      <c r="K8" s="42" t="n"/>
+      <c r="L8" s="42" t="n"/>
+      <c r="M8" s="42" t="n"/>
+      <c r="N8" s="42" t="n"/>
+      <c r="O8" s="42" t="n"/>
+      <c r="P8" s="42" t="n"/>
+      <c r="Q8" s="42" t="n"/>
+      <c r="R8" s="42" t="n"/>
+      <c r="S8" s="42" t="n"/>
+      <c r="T8" s="42" t="n"/>
+      <c r="U8" s="43">
         <f>IF($F8="SUM",IF(COUNT($I8:$T8)=0,"",SUM($I8:$T8)),IF($F8="AVG",IFERROR(AVERAGE($I8:$T8),""),IF($F8="LAST",IFERROR(LOOKUP(2,1/($I8:$T8&lt;&gt;""),$I8:$T8),""),"")))</f>
         <v/>
       </c>
-      <c r="V8" s="25">
+      <c r="V8" s="36">
         <f>IF($G8="","",IF($U8="","",IF($G8=0,IF($U8&lt;=0,1,0),IF($E8="↓",IFERROR($G8/$U8,0),IFERROR($U8/$G8,0)))))</f>
         <v/>
       </c>
-      <c r="W8" s="26">
+      <c r="W8" s="16">
         <f>IF($V8="","—",IF($V8&gt;=1,"✅ محقق",IF($V8&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X8" s="44" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="Y8" s="19" t="inlineStr">
+        <is>
+          <t>زيادة وصول العملاء</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>المبيعات والأداء التجاري</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>نسبة تأجير وحدات الامتياز</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G9" s="36" t="n">
+      <c r="G9" s="45" t="n">
         <v>0.7</v>
       </c>
-      <c r="H9" s="33" t="inlineStr">
+      <c r="H9" s="41" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="I9" s="37" t="n"/>
-      <c r="J9" s="37" t="n"/>
-      <c r="K9" s="37" t="n"/>
-      <c r="L9" s="37" t="n"/>
-      <c r="M9" s="37" t="n"/>
-      <c r="N9" s="37" t="n"/>
-      <c r="O9" s="37" t="n"/>
-      <c r="P9" s="37" t="n"/>
-      <c r="Q9" s="37" t="n"/>
-      <c r="R9" s="37" t="n"/>
-      <c r="S9" s="37" t="n"/>
-      <c r="T9" s="37" t="n"/>
-      <c r="U9" s="38">
+      <c r="I9" s="46" t="n"/>
+      <c r="J9" s="46" t="n"/>
+      <c r="K9" s="46" t="n"/>
+      <c r="L9" s="46" t="n"/>
+      <c r="M9" s="46" t="n"/>
+      <c r="N9" s="46" t="n"/>
+      <c r="O9" s="46" t="n"/>
+      <c r="P9" s="46" t="n"/>
+      <c r="Q9" s="46" t="n"/>
+      <c r="R9" s="46" t="n"/>
+      <c r="S9" s="46" t="n"/>
+      <c r="T9" s="46" t="n"/>
+      <c r="U9" s="47">
         <f>IF($F9="SUM",IF(COUNT($I9:$T9)=0,"",SUM($I9:$T9)),IF($F9="AVG",IFERROR(AVERAGE($I9:$T9),""),IF($F9="LAST",IFERROR(LOOKUP(2,1/($I9:$T9&lt;&gt;""),$I9:$T9),""),"")))</f>
         <v/>
       </c>
-      <c r="V9" s="25">
+      <c r="V9" s="36">
         <f>IF($G9="","",IF($U9="","",IF($G9=0,IF($U9&lt;=0,1,0),IF($E9="↓",IFERROR($G9/$U9,0),IFERROR($U9/$G9,0)))))</f>
         <v/>
       </c>
-      <c r="W9" s="26">
+      <c r="W9" s="16">
         <f>IF($V9="","—",IF($V9&gt;=1,"✅ محقق",IF($V9&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X9" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y9" s="19" t="inlineStr">
+        <is>
+          <t>منظومة التأجير</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>الأداء المالي</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>إجمالي إيرادات إدارة الامتياز</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>ر.س</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" s="38" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
-      <c r="G10" s="28" t="inlineStr"/>
-      <c r="H10" s="33" t="inlineStr">
+      <c r="G10" s="38" t="inlineStr"/>
+      <c r="H10" s="41" t="inlineStr">
         <is>
           <t>تصاعدي مستمر</t>
         </is>
       </c>
-      <c r="I10" s="39" t="n"/>
-      <c r="J10" s="39" t="n"/>
-      <c r="K10" s="39" t="n"/>
-      <c r="L10" s="39" t="n"/>
-      <c r="M10" s="39" t="n"/>
-      <c r="N10" s="39" t="n"/>
-      <c r="O10" s="39" t="n"/>
-      <c r="P10" s="39" t="n"/>
-      <c r="Q10" s="39" t="n"/>
-      <c r="R10" s="39" t="n"/>
-      <c r="S10" s="39" t="n"/>
-      <c r="T10" s="39" t="n"/>
-      <c r="U10" s="40">
+      <c r="I10" s="48" t="n"/>
+      <c r="J10" s="48" t="n"/>
+      <c r="K10" s="48" t="n"/>
+      <c r="L10" s="48" t="n"/>
+      <c r="M10" s="48" t="n"/>
+      <c r="N10" s="48" t="n"/>
+      <c r="O10" s="48" t="n"/>
+      <c r="P10" s="48" t="n"/>
+      <c r="Q10" s="48" t="n"/>
+      <c r="R10" s="48" t="n"/>
+      <c r="S10" s="48" t="n"/>
+      <c r="T10" s="48" t="n"/>
+      <c r="U10" s="49">
         <f>IF($F10="SUM",IF(COUNT($I10:$T10)=0,"",SUM($I10:$T10)),IF($F10="AVG",IFERROR(AVERAGE($I10:$T10),""),IF($F10="LAST",IFERROR(LOOKUP(2,1/($I10:$T10&lt;&gt;""),$I10:$T10),""),"")))</f>
         <v/>
       </c>
-      <c r="V10" s="25">
+      <c r="V10" s="36">
         <f>IF($G10="","",IF($U10="","",IF($G10=0,IF($U10&lt;=0,1,0),IF($E10="↓",IFERROR($G10/$U10,0),IFERROR($U10/$G10,0)))))</f>
         <v/>
       </c>
-      <c r="W10" s="26">
+      <c r="W10" s="16">
         <f>IF($V10="","—",IF($V10&gt;=1,"✅ محقق",IF($V10&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X10" s="44" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="Y10" s="19" t="inlineStr">
+        <is>
+          <t>الامتياز التجاري</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>الأداء المالي</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>رفع هامش الربحية للامتياز</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>هللة/لتر</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F11" s="28" t="inlineStr">
+      <c r="F11" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G11" s="41" t="n">
+      <c r="G11" s="50" t="n">
         <v>1.8</v>
       </c>
-      <c r="H11" s="33" t="inlineStr">
+      <c r="H11" s="41" t="inlineStr">
         <is>
           <t>+1.8 هللة/لتر</t>
         </is>
       </c>
-      <c r="I11" s="42" t="n"/>
-      <c r="J11" s="42" t="n"/>
-      <c r="K11" s="42" t="n"/>
-      <c r="L11" s="42" t="n"/>
-      <c r="M11" s="42" t="n"/>
-      <c r="N11" s="42" t="n"/>
-      <c r="O11" s="42" t="n"/>
-      <c r="P11" s="42" t="n"/>
-      <c r="Q11" s="42" t="n"/>
-      <c r="R11" s="42" t="n"/>
-      <c r="S11" s="42" t="n"/>
-      <c r="T11" s="42" t="n"/>
-      <c r="U11" s="43">
+      <c r="I11" s="51" t="n"/>
+      <c r="J11" s="51" t="n"/>
+      <c r="K11" s="51" t="n"/>
+      <c r="L11" s="51" t="n"/>
+      <c r="M11" s="51" t="n"/>
+      <c r="N11" s="51" t="n"/>
+      <c r="O11" s="51" t="n"/>
+      <c r="P11" s="51" t="n"/>
+      <c r="Q11" s="51" t="n"/>
+      <c r="R11" s="51" t="n"/>
+      <c r="S11" s="51" t="n"/>
+      <c r="T11" s="51" t="n"/>
+      <c r="U11" s="52">
         <f>IF($F11="SUM",IF(COUNT($I11:$T11)=0,"",SUM($I11:$T11)),IF($F11="AVG",IFERROR(AVERAGE($I11:$T11),""),IF($F11="LAST",IFERROR(LOOKUP(2,1/($I11:$T11&lt;&gt;""),$I11:$T11),""),"")))</f>
         <v/>
       </c>
-      <c r="V11" s="25">
+      <c r="V11" s="36">
         <f>IF($G11="","",IF($U11="","",IF($G11=0,IF($U11&lt;=0,1,0),IF($E11="↓",IFERROR($G11/$U11,0),IFERROR($U11/$G11,0)))))</f>
         <v/>
       </c>
-      <c r="W11" s="26">
+      <c r="W11" s="16">
         <f>IF($V11="","—",IF($V11&gt;=1,"✅ محقق",IF($V11&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X11" s="44" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="Y11" s="19" t="inlineStr">
+        <is>
+          <t>الامتياز التجاري</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="26" t="n">
+      <c r="A12" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>الأداء المالي</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>نسبة التحصيل المالي من شركاء الامتياز</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G12" s="36" t="n">
+      <c r="G12" s="45" t="n">
         <v>0.95</v>
       </c>
-      <c r="H12" s="33" t="inlineStr">
+      <c r="H12" s="41" t="inlineStr">
         <is>
           <t>95%+</t>
         </is>
       </c>
-      <c r="I12" s="37" t="n"/>
-      <c r="J12" s="37" t="n"/>
-      <c r="K12" s="37" t="n"/>
-      <c r="L12" s="37" t="n"/>
-      <c r="M12" s="37" t="n"/>
-      <c r="N12" s="37" t="n"/>
-      <c r="O12" s="37" t="n"/>
-      <c r="P12" s="37" t="n"/>
-      <c r="Q12" s="37" t="n"/>
-      <c r="R12" s="37" t="n"/>
-      <c r="S12" s="37" t="n"/>
-      <c r="T12" s="37" t="n"/>
-      <c r="U12" s="38">
+      <c r="I12" s="46" t="n"/>
+      <c r="J12" s="46" t="n"/>
+      <c r="K12" s="46" t="n"/>
+      <c r="L12" s="46" t="n"/>
+      <c r="M12" s="46" t="n"/>
+      <c r="N12" s="46" t="n"/>
+      <c r="O12" s="46" t="n"/>
+      <c r="P12" s="46" t="n"/>
+      <c r="Q12" s="46" t="n"/>
+      <c r="R12" s="46" t="n"/>
+      <c r="S12" s="46" t="n"/>
+      <c r="T12" s="46" t="n"/>
+      <c r="U12" s="47">
         <f>IF($F12="SUM",IF(COUNT($I12:$T12)=0,"",SUM($I12:$T12)),IF($F12="AVG",IFERROR(AVERAGE($I12:$T12),""),IF($F12="LAST",IFERROR(LOOKUP(2,1/($I12:$T12&lt;&gt;""),$I12:$T12),""),"")))</f>
         <v/>
       </c>
-      <c r="V12" s="25">
+      <c r="V12" s="36">
         <f>IF($G12="","",IF($U12="","",IF($G12=0,IF($U12&lt;=0,1,0),IF($E12="↓",IFERROR($G12/$U12,0),IFERROR($U12/$G12,0)))))</f>
         <v/>
       </c>
-      <c r="W12" s="26">
+      <c r="W12" s="16">
         <f>IF($V12="","—",IF($V12&gt;=1,"✅ محقق",IF($V12&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X12" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y12" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="26" t="n">
+      <c r="A13" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>الأداء المالي</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>متوسط أيام التحصيل (DSO)</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>يوم</t>
         </is>
       </c>
-      <c r="E13" s="28" t="inlineStr">
+      <c r="E13" s="38" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="F13" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G13" s="41" t="n">
+      <c r="G13" s="50" t="n">
         <v>30</v>
       </c>
-      <c r="H13" s="33" t="inlineStr">
+      <c r="H13" s="41" t="inlineStr">
         <is>
           <t>≤ 30 يوم</t>
         </is>
       </c>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="42" t="n"/>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="42" t="n"/>
-      <c r="N13" s="42" t="n"/>
-      <c r="O13" s="42" t="n"/>
-      <c r="P13" s="42" t="n"/>
-      <c r="Q13" s="42" t="n"/>
-      <c r="R13" s="42" t="n"/>
-      <c r="S13" s="42" t="n"/>
-      <c r="T13" s="42" t="n"/>
-      <c r="U13" s="43">
+      <c r="I13" s="51" t="n"/>
+      <c r="J13" s="51" t="n"/>
+      <c r="K13" s="51" t="n"/>
+      <c r="L13" s="51" t="n"/>
+      <c r="M13" s="51" t="n"/>
+      <c r="N13" s="51" t="n"/>
+      <c r="O13" s="51" t="n"/>
+      <c r="P13" s="51" t="n"/>
+      <c r="Q13" s="51" t="n"/>
+      <c r="R13" s="51" t="n"/>
+      <c r="S13" s="51" t="n"/>
+      <c r="T13" s="51" t="n"/>
+      <c r="U13" s="52">
         <f>IF($F13="SUM",IF(COUNT($I13:$T13)=0,"",SUM($I13:$T13)),IF($F13="AVG",IFERROR(AVERAGE($I13:$T13),""),IF($F13="LAST",IFERROR(LOOKUP(2,1/($I13:$T13&lt;&gt;""),$I13:$T13),""),"")))</f>
         <v/>
       </c>
-      <c r="V13" s="25">
+      <c r="V13" s="36">
         <f>IF($G13="","",IF($U13="","",IF($G13=0,IF($U13&lt;=0,1,0),IF($E13="↓",IFERROR($G13/$U13,0),IFERROR($U13/$G13,0)))))</f>
         <v/>
       </c>
-      <c r="W13" s="26">
+      <c r="W13" s="16">
         <f>IF($V13="","—",IF($V13&gt;=1,"✅ محقق",IF($V13&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X13" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y13" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>الأداء المالي</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>إجمالي المستحقات المتأخرة (+30 يوم)</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>ر.س</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E14" s="38" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" s="38" t="inlineStr">
         <is>
           <t>LAST</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr"/>
-      <c r="H14" s="33" t="inlineStr">
+      <c r="G14" s="38" t="inlineStr"/>
+      <c r="H14" s="41" t="inlineStr">
         <is>
           <t>تراجع مستمر</t>
         </is>
       </c>
-      <c r="I14" s="39" t="n"/>
-      <c r="J14" s="39" t="n"/>
-      <c r="K14" s="39" t="n"/>
-      <c r="L14" s="39" t="n"/>
-      <c r="M14" s="39" t="n"/>
-      <c r="N14" s="39" t="n"/>
-      <c r="O14" s="39" t="n"/>
-      <c r="P14" s="39" t="n"/>
-      <c r="Q14" s="39" t="n"/>
-      <c r="R14" s="39" t="n"/>
-      <c r="S14" s="39" t="n"/>
-      <c r="T14" s="39" t="n"/>
-      <c r="U14" s="40">
+      <c r="I14" s="48" t="n"/>
+      <c r="J14" s="48" t="n"/>
+      <c r="K14" s="48" t="n"/>
+      <c r="L14" s="48" t="n"/>
+      <c r="M14" s="48" t="n"/>
+      <c r="N14" s="48" t="n"/>
+      <c r="O14" s="48" t="n"/>
+      <c r="P14" s="48" t="n"/>
+      <c r="Q14" s="48" t="n"/>
+      <c r="R14" s="48" t="n"/>
+      <c r="S14" s="48" t="n"/>
+      <c r="T14" s="48" t="n"/>
+      <c r="U14" s="49">
         <f>IF($F14="SUM",IF(COUNT($I14:$T14)=0,"",SUM($I14:$T14)),IF($F14="AVG",IFERROR(AVERAGE($I14:$T14),""),IF($F14="LAST",IFERROR(LOOKUP(2,1/($I14:$T14&lt;&gt;""),$I14:$T14),""),"")))</f>
         <v/>
       </c>
-      <c r="V14" s="25">
+      <c r="V14" s="36">
         <f>IF($G14="","",IF($U14="","",IF($G14=0,IF($U14&lt;=0,1,0),IF($E14="↓",IFERROR($G14/$U14,0),IFERROR($U14/$G14,0)))))</f>
         <v/>
       </c>
-      <c r="W14" s="26">
+      <c r="W14" s="16">
         <f>IF($V14="","—",IF($V14&gt;=1,"✅ محقق",IF($V14&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X14" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y14" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>الأداء المالي</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>نسبة الشركاء الملتزمين بمواعيد السداد</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
+      <c r="D15" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E15" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G15" s="36" t="n">
+      <c r="G15" s="45" t="n">
         <v>0.9</v>
       </c>
-      <c r="H15" s="33" t="inlineStr">
+      <c r="H15" s="41" t="inlineStr">
         <is>
           <t>90%+</t>
         </is>
       </c>
-      <c r="I15" s="37" t="n"/>
-      <c r="J15" s="37" t="n"/>
-      <c r="K15" s="37" t="n"/>
-      <c r="L15" s="37" t="n"/>
-      <c r="M15" s="37" t="n"/>
-      <c r="N15" s="37" t="n"/>
-      <c r="O15" s="37" t="n"/>
-      <c r="P15" s="37" t="n"/>
-      <c r="Q15" s="37" t="n"/>
-      <c r="R15" s="37" t="n"/>
-      <c r="S15" s="37" t="n"/>
-      <c r="T15" s="37" t="n"/>
-      <c r="U15" s="38">
+      <c r="I15" s="46" t="n"/>
+      <c r="J15" s="46" t="n"/>
+      <c r="K15" s="46" t="n"/>
+      <c r="L15" s="46" t="n"/>
+      <c r="M15" s="46" t="n"/>
+      <c r="N15" s="46" t="n"/>
+      <c r="O15" s="46" t="n"/>
+      <c r="P15" s="46" t="n"/>
+      <c r="Q15" s="46" t="n"/>
+      <c r="R15" s="46" t="n"/>
+      <c r="S15" s="46" t="n"/>
+      <c r="T15" s="46" t="n"/>
+      <c r="U15" s="47">
         <f>IF($F15="SUM",IF(COUNT($I15:$T15)=0,"",SUM($I15:$T15)),IF($F15="AVG",IFERROR(AVERAGE($I15:$T15),""),IF($F15="LAST",IFERROR(LOOKUP(2,1/($I15:$T15&lt;&gt;""),$I15:$T15),""),"")))</f>
         <v/>
       </c>
-      <c r="V15" s="25">
+      <c r="V15" s="36">
         <f>IF($G15="","",IF($U15="","",IF($G15=0,IF($U15&lt;=0,1,0),IF($E15="↓",IFERROR($G15/$U15,0),IFERROR($U15/$G15,0)))))</f>
         <v/>
       </c>
-      <c r="W15" s="26">
+      <c r="W15" s="16">
         <f>IF($V15="","—",IF($V15&gt;=1,"✅ محقق",IF($V15&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X15" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y15" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>الأداء المالي</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>معدل دوران رأس المال (أيام الدورة)</t>
         </is>
       </c>
-      <c r="D16" s="28" t="inlineStr">
+      <c r="D16" s="38" t="inlineStr">
         <is>
           <t>يوم</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="38" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G16" s="41" t="n">
+      <c r="G16" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="33" t="inlineStr">
+      <c r="H16" s="41" t="inlineStr">
         <is>
           <t>≤ 5 أيام</t>
         </is>
       </c>
-      <c r="I16" s="42" t="n"/>
-      <c r="J16" s="42" t="n"/>
-      <c r="K16" s="42" t="n"/>
-      <c r="L16" s="42" t="n"/>
-      <c r="M16" s="42" t="n"/>
-      <c r="N16" s="42" t="n"/>
-      <c r="O16" s="42" t="n"/>
-      <c r="P16" s="42" t="n"/>
-      <c r="Q16" s="42" t="n"/>
-      <c r="R16" s="42" t="n"/>
-      <c r="S16" s="42" t="n"/>
-      <c r="T16" s="42" t="n"/>
-      <c r="U16" s="43">
+      <c r="I16" s="51" t="n"/>
+      <c r="J16" s="51" t="n"/>
+      <c r="K16" s="51" t="n"/>
+      <c r="L16" s="51" t="n"/>
+      <c r="M16" s="51" t="n"/>
+      <c r="N16" s="51" t="n"/>
+      <c r="O16" s="51" t="n"/>
+      <c r="P16" s="51" t="n"/>
+      <c r="Q16" s="51" t="n"/>
+      <c r="R16" s="51" t="n"/>
+      <c r="S16" s="51" t="n"/>
+      <c r="T16" s="51" t="n"/>
+      <c r="U16" s="52">
         <f>IF($F16="SUM",IF(COUNT($I16:$T16)=0,"",SUM($I16:$T16)),IF($F16="AVG",IFERROR(AVERAGE($I16:$T16),""),IF($F16="LAST",IFERROR(LOOKUP(2,1/($I16:$T16&lt;&gt;""),$I16:$T16),""),"")))</f>
         <v/>
       </c>
-      <c r="V16" s="25">
+      <c r="V16" s="36">
         <f>IF($G16="","",IF($U16="","",IF($G16=0,IF($U16&lt;=0,1,0),IF($E16="↓",IFERROR($G16/$U16,0),IFERROR($U16/$G16,0)))))</f>
         <v/>
       </c>
-      <c r="W16" s="26">
+      <c r="W16" s="16">
         <f>IF($V16="","—",IF($V16&gt;=1,"✅ محقق",IF($V16&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X16" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y16" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="26" t="n">
+      <c r="A17" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>التشغيل والجودة</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>نسبة جاهزية محطات الامتياز (صفر انقطاع)</t>
         </is>
       </c>
-      <c r="D17" s="28" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G17" s="36" t="n">
+      <c r="G17" s="45" t="n">
         <v>0.99</v>
       </c>
-      <c r="H17" s="33" t="inlineStr">
+      <c r="H17" s="41" t="inlineStr">
         <is>
           <t>99%+</t>
         </is>
       </c>
-      <c r="I17" s="37" t="n"/>
-      <c r="J17" s="37" t="n"/>
-      <c r="K17" s="37" t="n"/>
-      <c r="L17" s="37" t="n"/>
-      <c r="M17" s="37" t="n"/>
-      <c r="N17" s="37" t="n"/>
-      <c r="O17" s="37" t="n"/>
-      <c r="P17" s="37" t="n"/>
-      <c r="Q17" s="37" t="n"/>
-      <c r="R17" s="37" t="n"/>
-      <c r="S17" s="37" t="n"/>
-      <c r="T17" s="37" t="n"/>
-      <c r="U17" s="38">
+      <c r="I17" s="46" t="n"/>
+      <c r="J17" s="46" t="n"/>
+      <c r="K17" s="46" t="n"/>
+      <c r="L17" s="46" t="n"/>
+      <c r="M17" s="46" t="n"/>
+      <c r="N17" s="46" t="n"/>
+      <c r="O17" s="46" t="n"/>
+      <c r="P17" s="46" t="n"/>
+      <c r="Q17" s="46" t="n"/>
+      <c r="R17" s="46" t="n"/>
+      <c r="S17" s="46" t="n"/>
+      <c r="T17" s="46" t="n"/>
+      <c r="U17" s="47">
         <f>IF($F17="SUM",IF(COUNT($I17:$T17)=0,"",SUM($I17:$T17)),IF($F17="AVG",IFERROR(AVERAGE($I17:$T17),""),IF($F17="LAST",IFERROR(LOOKUP(2,1/($I17:$T17&lt;&gt;""),$I17:$T17),""),"")))</f>
         <v/>
       </c>
-      <c r="V17" s="25">
+      <c r="V17" s="36">
         <f>IF($G17="","",IF($U17="","",IF($G17=0,IF($U17&lt;=0,1,0),IF($E17="↓",IFERROR($G17/$U17,0),IFERROR($U17/$G17,0)))))</f>
         <v/>
       </c>
-      <c r="W17" s="26">
+      <c r="W17" s="16">
         <f>IF($V17="","—",IF($V17&gt;=1,"✅ محقق",IF($V17&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X17" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y17" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>التشغيل والجودة</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>عدد حالات انقطاع الوقود الموثّقة</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="D18" s="38" t="inlineStr">
         <is>
           <t>حالة</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="38" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" s="38" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
-      <c r="G18" s="32" t="n">
+      <c r="G18" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="33" t="inlineStr">
+      <c r="H18" s="41" t="inlineStr">
         <is>
           <t>0 حالة</t>
         </is>
       </c>
-      <c r="I18" s="34" t="n"/>
-      <c r="J18" s="34" t="n"/>
-      <c r="K18" s="34" t="n"/>
-      <c r="L18" s="34" t="n"/>
-      <c r="M18" s="34" t="n"/>
-      <c r="N18" s="34" t="n"/>
-      <c r="O18" s="34" t="n"/>
-      <c r="P18" s="34" t="n"/>
-      <c r="Q18" s="34" t="n"/>
-      <c r="R18" s="34" t="n"/>
-      <c r="S18" s="34" t="n"/>
-      <c r="T18" s="34" t="n"/>
-      <c r="U18" s="35">
+      <c r="I18" s="42" t="n"/>
+      <c r="J18" s="42" t="n"/>
+      <c r="K18" s="42" t="n"/>
+      <c r="L18" s="42" t="n"/>
+      <c r="M18" s="42" t="n"/>
+      <c r="N18" s="42" t="n"/>
+      <c r="O18" s="42" t="n"/>
+      <c r="P18" s="42" t="n"/>
+      <c r="Q18" s="42" t="n"/>
+      <c r="R18" s="42" t="n"/>
+      <c r="S18" s="42" t="n"/>
+      <c r="T18" s="42" t="n"/>
+      <c r="U18" s="43">
         <f>IF($F18="SUM",IF(COUNT($I18:$T18)=0,"",SUM($I18:$T18)),IF($F18="AVG",IFERROR(AVERAGE($I18:$T18),""),IF($F18="LAST",IFERROR(LOOKUP(2,1/($I18:$T18&lt;&gt;""),$I18:$T18),""),"")))</f>
         <v/>
       </c>
-      <c r="V18" s="25">
+      <c r="V18" s="36">
         <f>IF($G18="","",IF($U18="","",IF($G18=0,IF($U18&lt;=0,1,0),IF($E18="↓",IFERROR($G18/$U18,0),IFERROR($U18/$G18,0)))))</f>
         <v/>
       </c>
-      <c r="W18" s="26">
+      <c r="W18" s="16">
         <f>IF($V18="","—",IF($V18&gt;=1,"✅ محقق",IF($V18&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X18" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y18" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="26" t="n">
+      <c r="A19" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>التشغيل والجودة</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>نسبة إغلاق ملاحظات الجودة الميدانية</t>
         </is>
       </c>
-      <c r="D19" s="28" t="inlineStr">
+      <c r="D19" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E19" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G19" s="36" t="n">
+      <c r="G19" s="45" t="n">
         <v>0.95</v>
       </c>
-      <c r="H19" s="33" t="inlineStr">
+      <c r="H19" s="41" t="inlineStr">
         <is>
           <t>95%+</t>
         </is>
       </c>
-      <c r="I19" s="37" t="n"/>
-      <c r="J19" s="37" t="n"/>
-      <c r="K19" s="37" t="n"/>
-      <c r="L19" s="37" t="n"/>
-      <c r="M19" s="37" t="n"/>
-      <c r="N19" s="37" t="n"/>
-      <c r="O19" s="37" t="n"/>
-      <c r="P19" s="37" t="n"/>
-      <c r="Q19" s="37" t="n"/>
-      <c r="R19" s="37" t="n"/>
-      <c r="S19" s="37" t="n"/>
-      <c r="T19" s="37" t="n"/>
-      <c r="U19" s="38">
+      <c r="I19" s="46" t="n"/>
+      <c r="J19" s="46" t="n"/>
+      <c r="K19" s="46" t="n"/>
+      <c r="L19" s="46" t="n"/>
+      <c r="M19" s="46" t="n"/>
+      <c r="N19" s="46" t="n"/>
+      <c r="O19" s="46" t="n"/>
+      <c r="P19" s="46" t="n"/>
+      <c r="Q19" s="46" t="n"/>
+      <c r="R19" s="46" t="n"/>
+      <c r="S19" s="46" t="n"/>
+      <c r="T19" s="46" t="n"/>
+      <c r="U19" s="47">
         <f>IF($F19="SUM",IF(COUNT($I19:$T19)=0,"",SUM($I19:$T19)),IF($F19="AVG",IFERROR(AVERAGE($I19:$T19),""),IF($F19="LAST",IFERROR(LOOKUP(2,1/($I19:$T19&lt;&gt;""),$I19:$T19),""),"")))</f>
         <v/>
       </c>
-      <c r="V19" s="25">
+      <c r="V19" s="36">
         <f>IF($G19="","",IF($U19="","",IF($G19=0,IF($U19&lt;=0,1,0),IF($E19="↓",IFERROR($G19/$U19,0),IFERROR($U19/$G19,0)))))</f>
         <v/>
       </c>
-      <c r="W19" s="26">
+      <c r="W19" s="16">
         <f>IF($V19="","—",IF($V19&gt;=1,"✅ محقق",IF($V19&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X19" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y19" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="16" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>التشغيل والجودة</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>متوسط درجة تقييم جودة المحطة (قائمة التحقق)</t>
         </is>
       </c>
-      <c r="D20" s="28" t="inlineStr">
+      <c r="D20" s="38" t="inlineStr">
         <is>
           <t>درجة/100</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G20" s="41" t="n">
+      <c r="G20" s="50" t="n">
         <v>85</v>
       </c>
-      <c r="H20" s="33" t="inlineStr">
+      <c r="H20" s="41" t="inlineStr">
         <is>
           <t>85+</t>
         </is>
       </c>
-      <c r="I20" s="42" t="n"/>
-      <c r="J20" s="42" t="n"/>
-      <c r="K20" s="42" t="n"/>
-      <c r="L20" s="42" t="n"/>
-      <c r="M20" s="42" t="n"/>
-      <c r="N20" s="42" t="n"/>
-      <c r="O20" s="42" t="n"/>
-      <c r="P20" s="42" t="n"/>
-      <c r="Q20" s="42" t="n"/>
-      <c r="R20" s="42" t="n"/>
-      <c r="S20" s="42" t="n"/>
-      <c r="T20" s="42" t="n"/>
-      <c r="U20" s="43">
+      <c r="I20" s="51" t="n"/>
+      <c r="J20" s="51" t="n"/>
+      <c r="K20" s="51" t="n"/>
+      <c r="L20" s="51" t="n"/>
+      <c r="M20" s="51" t="n"/>
+      <c r="N20" s="51" t="n"/>
+      <c r="O20" s="51" t="n"/>
+      <c r="P20" s="51" t="n"/>
+      <c r="Q20" s="51" t="n"/>
+      <c r="R20" s="51" t="n"/>
+      <c r="S20" s="51" t="n"/>
+      <c r="T20" s="51" t="n"/>
+      <c r="U20" s="52">
         <f>IF($F20="SUM",IF(COUNT($I20:$T20)=0,"",SUM($I20:$T20)),IF($F20="AVG",IFERROR(AVERAGE($I20:$T20),""),IF($F20="LAST",IFERROR(LOOKUP(2,1/($I20:$T20&lt;&gt;""),$I20:$T20),""),"")))</f>
         <v/>
       </c>
-      <c r="V20" s="25">
+      <c r="V20" s="36">
         <f>IF($G20="","",IF($U20="","",IF($G20=0,IF($U20&lt;=0,1,0),IF($E20="↓",IFERROR($G20/$U20,0),IFERROR($U20/$G20,0)))))</f>
         <v/>
       </c>
-      <c r="W20" s="26">
+      <c r="W20" s="16">
         <f>IF($V20="","—",IF($V20&gt;=1,"✅ محقق",IF($V20&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X20" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y20" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="26" t="n">
+      <c r="A21" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>التشغيل والجودة</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>نسبة تنفيذ الزيارات الميدانية المجدولة</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="D21" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G21" s="36" t="n">
+      <c r="G21" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="33" t="inlineStr">
+      <c r="H21" s="41" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I21" s="37" t="n"/>
-      <c r="J21" s="37" t="n"/>
-      <c r="K21" s="37" t="n"/>
-      <c r="L21" s="37" t="n"/>
-      <c r="M21" s="37" t="n"/>
-      <c r="N21" s="37" t="n"/>
-      <c r="O21" s="37" t="n"/>
-      <c r="P21" s="37" t="n"/>
-      <c r="Q21" s="37" t="n"/>
-      <c r="R21" s="37" t="n"/>
-      <c r="S21" s="37" t="n"/>
-      <c r="T21" s="37" t="n"/>
-      <c r="U21" s="38">
+      <c r="I21" s="46" t="n"/>
+      <c r="J21" s="46" t="n"/>
+      <c r="K21" s="46" t="n"/>
+      <c r="L21" s="46" t="n"/>
+      <c r="M21" s="46" t="n"/>
+      <c r="N21" s="46" t="n"/>
+      <c r="O21" s="46" t="n"/>
+      <c r="P21" s="46" t="n"/>
+      <c r="Q21" s="46" t="n"/>
+      <c r="R21" s="46" t="n"/>
+      <c r="S21" s="46" t="n"/>
+      <c r="T21" s="46" t="n"/>
+      <c r="U21" s="47">
         <f>IF($F21="SUM",IF(COUNT($I21:$T21)=0,"",SUM($I21:$T21)),IF($F21="AVG",IFERROR(AVERAGE($I21:$T21),""),IF($F21="LAST",IFERROR(LOOKUP(2,1/($I21:$T21&lt;&gt;""),$I21:$T21),""),"")))</f>
         <v/>
       </c>
-      <c r="V21" s="25">
+      <c r="V21" s="36">
         <f>IF($G21="","",IF($U21="","",IF($G21=0,IF($U21&lt;=0,1,0),IF($E21="↓",IFERROR($G21/$U21,0),IFERROR($U21/$G21,0)))))</f>
         <v/>
       </c>
-      <c r="W21" s="26">
+      <c r="W21" s="16">
         <f>IF($V21="","—",IF($V21&gt;=1,"✅ محقق",IF($V21&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X21" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y21" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="26" t="n">
+      <c r="A22" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>التشغيل والجودة</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>نسبة المحطات المستوفية لمعايير السلامة</t>
         </is>
       </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D22" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G22" s="36" t="n">
+      <c r="G22" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="33" t="inlineStr">
+      <c r="H22" s="41" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I22" s="37" t="n"/>
-      <c r="J22" s="37" t="n"/>
-      <c r="K22" s="37" t="n"/>
-      <c r="L22" s="37" t="n"/>
-      <c r="M22" s="37" t="n"/>
-      <c r="N22" s="37" t="n"/>
-      <c r="O22" s="37" t="n"/>
-      <c r="P22" s="37" t="n"/>
-      <c r="Q22" s="37" t="n"/>
-      <c r="R22" s="37" t="n"/>
-      <c r="S22" s="37" t="n"/>
-      <c r="T22" s="37" t="n"/>
-      <c r="U22" s="38">
+      <c r="I22" s="46" t="n"/>
+      <c r="J22" s="46" t="n"/>
+      <c r="K22" s="46" t="n"/>
+      <c r="L22" s="46" t="n"/>
+      <c r="M22" s="46" t="n"/>
+      <c r="N22" s="46" t="n"/>
+      <c r="O22" s="46" t="n"/>
+      <c r="P22" s="46" t="n"/>
+      <c r="Q22" s="46" t="n"/>
+      <c r="R22" s="46" t="n"/>
+      <c r="S22" s="46" t="n"/>
+      <c r="T22" s="46" t="n"/>
+      <c r="U22" s="47">
         <f>IF($F22="SUM",IF(COUNT($I22:$T22)=0,"",SUM($I22:$T22)),IF($F22="AVG",IFERROR(AVERAGE($I22:$T22),""),IF($F22="LAST",IFERROR(LOOKUP(2,1/($I22:$T22&lt;&gt;""),$I22:$T22),""),"")))</f>
         <v/>
       </c>
-      <c r="V22" s="25">
+      <c r="V22" s="36">
         <f>IF($G22="","",IF($U22="","",IF($G22=0,IF($U22&lt;=0,1,0),IF($E22="↓",IFERROR($G22/$U22,0),IFERROR($U22/$G22,0)))))</f>
         <v/>
       </c>
-      <c r="W22" s="26">
+      <c r="W22" s="16">
         <f>IF($V22="","—",IF($V22&gt;=1,"✅ محقق",IF($V22&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X22" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y22" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="26" t="n">
+      <c r="A23" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>التشغيل والجودة</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>متوسط وقت معالجة البلاغات التشغيلية</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D23" s="38" t="inlineStr">
         <is>
           <t>ساعة</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="38" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F23" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G23" s="41" t="n">
+      <c r="G23" s="50" t="n">
         <v>24</v>
       </c>
-      <c r="H23" s="33" t="inlineStr">
+      <c r="H23" s="41" t="inlineStr">
         <is>
           <t>≤ 24 ساعة</t>
         </is>
       </c>
-      <c r="I23" s="42" t="n"/>
-      <c r="J23" s="42" t="n"/>
-      <c r="K23" s="42" t="n"/>
-      <c r="L23" s="42" t="n"/>
-      <c r="M23" s="42" t="n"/>
-      <c r="N23" s="42" t="n"/>
-      <c r="O23" s="42" t="n"/>
-      <c r="P23" s="42" t="n"/>
-      <c r="Q23" s="42" t="n"/>
-      <c r="R23" s="42" t="n"/>
-      <c r="S23" s="42" t="n"/>
-      <c r="T23" s="42" t="n"/>
-      <c r="U23" s="43">
+      <c r="I23" s="51" t="n"/>
+      <c r="J23" s="51" t="n"/>
+      <c r="K23" s="51" t="n"/>
+      <c r="L23" s="51" t="n"/>
+      <c r="M23" s="51" t="n"/>
+      <c r="N23" s="51" t="n"/>
+      <c r="O23" s="51" t="n"/>
+      <c r="P23" s="51" t="n"/>
+      <c r="Q23" s="51" t="n"/>
+      <c r="R23" s="51" t="n"/>
+      <c r="S23" s="51" t="n"/>
+      <c r="T23" s="51" t="n"/>
+      <c r="U23" s="52">
         <f>IF($F23="SUM",IF(COUNT($I23:$T23)=0,"",SUM($I23:$T23)),IF($F23="AVG",IFERROR(AVERAGE($I23:$T23),""),IF($F23="LAST",IFERROR(LOOKUP(2,1/($I23:$T23&lt;&gt;""),$I23:$T23),""),"")))</f>
         <v/>
       </c>
-      <c r="V23" s="25">
+      <c r="V23" s="36">
         <f>IF($G23="","",IF($U23="","",IF($G23=0,IF($U23&lt;=0,1,0),IF($E23="↓",IFERROR($G23/$U23,0),IFERROR($U23/$G23,0)))))</f>
         <v/>
       </c>
-      <c r="W23" s="26">
+      <c r="W23" s="16">
         <f>IF($V23="","—",IF($V23&gt;=1,"✅ محقق",IF($V23&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X23" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y23" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="26" t="n">
+      <c r="A24" s="16" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>التشغيل والجودة</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>نسبة أتمتة محطات الامتياز</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D24" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="38" t="inlineStr">
         <is>
           <t>LAST</t>
         </is>
       </c>
-      <c r="G24" s="36" t="n">
+      <c r="G24" s="45" t="n">
         <v>0.9</v>
       </c>
-      <c r="H24" s="33" t="inlineStr">
+      <c r="H24" s="41" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="I24" s="37" t="n"/>
-      <c r="J24" s="37" t="n"/>
-      <c r="K24" s="37" t="n"/>
-      <c r="L24" s="37" t="n"/>
-      <c r="M24" s="37" t="n"/>
-      <c r="N24" s="37" t="n"/>
-      <c r="O24" s="37" t="n"/>
-      <c r="P24" s="37" t="n"/>
-      <c r="Q24" s="37" t="n"/>
-      <c r="R24" s="37" t="n"/>
-      <c r="S24" s="37" t="n"/>
-      <c r="T24" s="37" t="n"/>
-      <c r="U24" s="38">
+      <c r="I24" s="46" t="n"/>
+      <c r="J24" s="46" t="n"/>
+      <c r="K24" s="46" t="n"/>
+      <c r="L24" s="46" t="n"/>
+      <c r="M24" s="46" t="n"/>
+      <c r="N24" s="46" t="n"/>
+      <c r="O24" s="46" t="n"/>
+      <c r="P24" s="46" t="n"/>
+      <c r="Q24" s="46" t="n"/>
+      <c r="R24" s="46" t="n"/>
+      <c r="S24" s="46" t="n"/>
+      <c r="T24" s="46" t="n"/>
+      <c r="U24" s="47">
         <f>IF($F24="SUM",IF(COUNT($I24:$T24)=0,"",SUM($I24:$T24)),IF($F24="AVG",IFERROR(AVERAGE($I24:$T24),""),IF($F24="LAST",IFERROR(LOOKUP(2,1/($I24:$T24&lt;&gt;""),$I24:$T24),""),"")))</f>
         <v/>
       </c>
-      <c r="V24" s="25">
+      <c r="V24" s="36">
         <f>IF($G24="","",IF($U24="","",IF($G24=0,IF($U24&lt;=0,1,0),IF($E24="↓",IFERROR($G24/$U24,0),IFERROR($U24/$G24,0)))))</f>
         <v/>
       </c>
-      <c r="W24" s="26">
+      <c r="W24" s="16">
         <f>IF($V24="","—",IF($V24&gt;=1,"✅ محقق",IF($V24&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X24" s="44" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="Y24" s="19" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="26" t="n">
+      <c r="A25" s="16" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>التشغيل والجودة</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>نسبة تطبيق المعيار الشامل داخل المحطات</t>
         </is>
       </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="D25" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F25" s="28" t="inlineStr">
+      <c r="F25" s="38" t="inlineStr">
         <is>
           <t>LAST</t>
         </is>
       </c>
-      <c r="G25" s="36" t="n">
+      <c r="G25" s="45" t="n">
         <v>0.3</v>
       </c>
-      <c r="H25" s="33" t="inlineStr">
+      <c r="H25" s="41" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I25" s="37" t="n"/>
-      <c r="J25" s="37" t="n"/>
-      <c r="K25" s="37" t="n"/>
-      <c r="L25" s="37" t="n"/>
-      <c r="M25" s="37" t="n"/>
-      <c r="N25" s="37" t="n"/>
-      <c r="O25" s="37" t="n"/>
-      <c r="P25" s="37" t="n"/>
-      <c r="Q25" s="37" t="n"/>
-      <c r="R25" s="37" t="n"/>
-      <c r="S25" s="37" t="n"/>
-      <c r="T25" s="37" t="n"/>
-      <c r="U25" s="38">
+      <c r="I25" s="46" t="n"/>
+      <c r="J25" s="46" t="n"/>
+      <c r="K25" s="46" t="n"/>
+      <c r="L25" s="46" t="n"/>
+      <c r="M25" s="46" t="n"/>
+      <c r="N25" s="46" t="n"/>
+      <c r="O25" s="46" t="n"/>
+      <c r="P25" s="46" t="n"/>
+      <c r="Q25" s="46" t="n"/>
+      <c r="R25" s="46" t="n"/>
+      <c r="S25" s="46" t="n"/>
+      <c r="T25" s="46" t="n"/>
+      <c r="U25" s="47">
         <f>IF($F25="SUM",IF(COUNT($I25:$T25)=0,"",SUM($I25:$T25)),IF($F25="AVG",IFERROR(AVERAGE($I25:$T25),""),IF($F25="LAST",IFERROR(LOOKUP(2,1/($I25:$T25&lt;&gt;""),$I25:$T25),""),"")))</f>
         <v/>
       </c>
-      <c r="V25" s="25">
+      <c r="V25" s="36">
         <f>IF($G25="","",IF($U25="","",IF($G25=0,IF($U25&lt;=0,1,0),IF($E25="↓",IFERROR($G25/$U25,0),IFERROR($U25/$G25,0)))))</f>
         <v/>
       </c>
-      <c r="W25" s="26">
+      <c r="W25" s="16">
         <f>IF($V25="","—",IF($V25&gt;=1,"✅ محقق",IF($V25&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X25" s="44" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="Y25" s="19" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="26" t="n">
+      <c r="A26" s="16" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>الهوية والتسويق</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>نسبة التزام المحطات بالهوية المؤسسية</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr">
+      <c r="D26" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F26" s="28" t="inlineStr">
+      <c r="F26" s="38" t="inlineStr">
         <is>
           <t>LAST</t>
         </is>
       </c>
-      <c r="G26" s="36" t="n">
+      <c r="G26" s="45" t="n">
         <v>0.55</v>
       </c>
-      <c r="H26" s="33" t="inlineStr">
+      <c r="H26" s="41" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="I26" s="37" t="n"/>
-      <c r="J26" s="37" t="n"/>
-      <c r="K26" s="37" t="n"/>
-      <c r="L26" s="37" t="n"/>
-      <c r="M26" s="37" t="n"/>
-      <c r="N26" s="37" t="n"/>
-      <c r="O26" s="37" t="n"/>
-      <c r="P26" s="37" t="n"/>
-      <c r="Q26" s="37" t="n"/>
-      <c r="R26" s="37" t="n"/>
-      <c r="S26" s="37" t="n"/>
-      <c r="T26" s="37" t="n"/>
-      <c r="U26" s="38">
+      <c r="I26" s="46" t="n"/>
+      <c r="J26" s="46" t="n"/>
+      <c r="K26" s="46" t="n"/>
+      <c r="L26" s="46" t="n"/>
+      <c r="M26" s="46" t="n"/>
+      <c r="N26" s="46" t="n"/>
+      <c r="O26" s="46" t="n"/>
+      <c r="P26" s="46" t="n"/>
+      <c r="Q26" s="46" t="n"/>
+      <c r="R26" s="46" t="n"/>
+      <c r="S26" s="46" t="n"/>
+      <c r="T26" s="46" t="n"/>
+      <c r="U26" s="47">
         <f>IF($F26="SUM",IF(COUNT($I26:$T26)=0,"",SUM($I26:$T26)),IF($F26="AVG",IFERROR(AVERAGE($I26:$T26),""),IF($F26="LAST",IFERROR(LOOKUP(2,1/($I26:$T26&lt;&gt;""),$I26:$T26),""),"")))</f>
         <v/>
       </c>
-      <c r="V26" s="25">
+      <c r="V26" s="36">
         <f>IF($G26="","",IF($U26="","",IF($G26=0,IF($U26&lt;=0,1,0),IF($E26="↓",IFERROR($G26/$U26,0),IFERROR($U26/$G26,0)))))</f>
         <v/>
       </c>
-      <c r="W26" s="26">
+      <c r="W26" s="16">
         <f>IF($V26="","—",IF($V26&gt;=1,"✅ محقق",IF($V26&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X26" s="44" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="Y26" s="19" t="inlineStr">
+        <is>
+          <t>تطوير التصاميم والهوية</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="26" t="n">
+      <c r="A27" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>التوسع الإقليمي</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>نسبة العقود التي تغطي المناطق الـ13</t>
         </is>
       </c>
-      <c r="D27" s="28" t="inlineStr">
+      <c r="D27" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F27" s="28" t="inlineStr">
+      <c r="F27" s="38" t="inlineStr">
         <is>
           <t>LAST</t>
         </is>
       </c>
-      <c r="G27" s="36" t="n">
+      <c r="G27" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="33" t="inlineStr">
+      <c r="H27" s="41" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I27" s="37" t="n"/>
-      <c r="J27" s="37" t="n"/>
-      <c r="K27" s="37" t="n"/>
-      <c r="L27" s="37" t="n"/>
-      <c r="M27" s="37" t="n"/>
-      <c r="N27" s="37" t="n"/>
-      <c r="O27" s="37" t="n"/>
-      <c r="P27" s="37" t="n"/>
-      <c r="Q27" s="37" t="n"/>
-      <c r="R27" s="37" t="n"/>
-      <c r="S27" s="37" t="n"/>
-      <c r="T27" s="37" t="n"/>
-      <c r="U27" s="38">
+      <c r="I27" s="46" t="n"/>
+      <c r="J27" s="46" t="n"/>
+      <c r="K27" s="46" t="n"/>
+      <c r="L27" s="46" t="n"/>
+      <c r="M27" s="46" t="n"/>
+      <c r="N27" s="46" t="n"/>
+      <c r="O27" s="46" t="n"/>
+      <c r="P27" s="46" t="n"/>
+      <c r="Q27" s="46" t="n"/>
+      <c r="R27" s="46" t="n"/>
+      <c r="S27" s="46" t="n"/>
+      <c r="T27" s="46" t="n"/>
+      <c r="U27" s="47">
         <f>IF($F27="SUM",IF(COUNT($I27:$T27)=0,"",SUM($I27:$T27)),IF($F27="AVG",IFERROR(AVERAGE($I27:$T27),""),IF($F27="LAST",IFERROR(LOOKUP(2,1/($I27:$T27&lt;&gt;""),$I27:$T27),""),"")))</f>
         <v/>
       </c>
-      <c r="V27" s="25">
+      <c r="V27" s="36">
         <f>IF($G27="","",IF($U27="","",IF($G27=0,IF($U27&lt;=0,1,0),IF($E27="↓",IFERROR($G27/$U27,0),IFERROR($U27/$G27,0)))))</f>
         <v/>
       </c>
-      <c r="W27" s="26">
+      <c r="W27" s="16">
         <f>IF($V27="","—",IF($V27&gt;=1,"✅ محقق",IF($V27&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X27" s="44" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="Y27" s="19" t="inlineStr">
+        <is>
+          <t>التوسع في المواقع</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="26" t="n">
+      <c r="A28" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>التوسع الإقليمي</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>نسبة العقود في الـ12 مدينة الرئيسية</t>
         </is>
       </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D28" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="38" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="F28" s="38" t="inlineStr">
         <is>
           <t>LAST</t>
         </is>
       </c>
-      <c r="G28" s="36" t="n">
+      <c r="G28" s="45" t="n">
         <v>0.4</v>
       </c>
-      <c r="H28" s="33" t="inlineStr">
+      <c r="H28" s="41" t="inlineStr">
         <is>
           <t>&lt; 40%</t>
         </is>
       </c>
-      <c r="I28" s="37" t="n"/>
-      <c r="J28" s="37" t="n"/>
-      <c r="K28" s="37" t="n"/>
-      <c r="L28" s="37" t="n"/>
-      <c r="M28" s="37" t="n"/>
-      <c r="N28" s="37" t="n"/>
-      <c r="O28" s="37" t="n"/>
-      <c r="P28" s="37" t="n"/>
-      <c r="Q28" s="37" t="n"/>
-      <c r="R28" s="37" t="n"/>
-      <c r="S28" s="37" t="n"/>
-      <c r="T28" s="37" t="n"/>
-      <c r="U28" s="38">
+      <c r="I28" s="46" t="n"/>
+      <c r="J28" s="46" t="n"/>
+      <c r="K28" s="46" t="n"/>
+      <c r="L28" s="46" t="n"/>
+      <c r="M28" s="46" t="n"/>
+      <c r="N28" s="46" t="n"/>
+      <c r="O28" s="46" t="n"/>
+      <c r="P28" s="46" t="n"/>
+      <c r="Q28" s="46" t="n"/>
+      <c r="R28" s="46" t="n"/>
+      <c r="S28" s="46" t="n"/>
+      <c r="T28" s="46" t="n"/>
+      <c r="U28" s="47">
         <f>IF($F28="SUM",IF(COUNT($I28:$T28)=0,"",SUM($I28:$T28)),IF($F28="AVG",IFERROR(AVERAGE($I28:$T28),""),IF($F28="LAST",IFERROR(LOOKUP(2,1/($I28:$T28&lt;&gt;""),$I28:$T28),""),"")))</f>
         <v/>
       </c>
-      <c r="V28" s="25">
+      <c r="V28" s="36">
         <f>IF($G28="","",IF($U28="","",IF($G28=0,IF($U28&lt;=0,1,0),IF($E28="↓",IFERROR($G28/$U28,0),IFERROR($U28/$G28,0)))))</f>
         <v/>
       </c>
-      <c r="W28" s="26">
+      <c r="W28" s="16">
         <f>IF($V28="","—",IF($V28&gt;=1,"✅ محقق",IF($V28&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X28" s="44" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="Y28" s="19" t="inlineStr">
+        <is>
+          <t>التوسع في المواقع</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="26" t="n">
+      <c r="A29" s="16" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>التوسع الإقليمي</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>نسبة العقود خارج المدن الرئيسية</t>
         </is>
       </c>
-      <c r="D29" s="28" t="inlineStr">
+      <c r="D29" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="F29" s="38" t="inlineStr">
         <is>
           <t>LAST</t>
         </is>
       </c>
-      <c r="G29" s="36" t="n">
+      <c r="G29" s="45" t="n">
         <v>0.6</v>
       </c>
-      <c r="H29" s="33" t="inlineStr">
+      <c r="H29" s="41" t="inlineStr">
         <is>
           <t>&gt; 60%</t>
         </is>
       </c>
-      <c r="I29" s="37" t="n"/>
-      <c r="J29" s="37" t="n"/>
-      <c r="K29" s="37" t="n"/>
-      <c r="L29" s="37" t="n"/>
-      <c r="M29" s="37" t="n"/>
-      <c r="N29" s="37" t="n"/>
-      <c r="O29" s="37" t="n"/>
-      <c r="P29" s="37" t="n"/>
-      <c r="Q29" s="37" t="n"/>
-      <c r="R29" s="37" t="n"/>
-      <c r="S29" s="37" t="n"/>
-      <c r="T29" s="37" t="n"/>
-      <c r="U29" s="38">
+      <c r="I29" s="46" t="n"/>
+      <c r="J29" s="46" t="n"/>
+      <c r="K29" s="46" t="n"/>
+      <c r="L29" s="46" t="n"/>
+      <c r="M29" s="46" t="n"/>
+      <c r="N29" s="46" t="n"/>
+      <c r="O29" s="46" t="n"/>
+      <c r="P29" s="46" t="n"/>
+      <c r="Q29" s="46" t="n"/>
+      <c r="R29" s="46" t="n"/>
+      <c r="S29" s="46" t="n"/>
+      <c r="T29" s="46" t="n"/>
+      <c r="U29" s="47">
         <f>IF($F29="SUM",IF(COUNT($I29:$T29)=0,"",SUM($I29:$T29)),IF($F29="AVG",IFERROR(AVERAGE($I29:$T29),""),IF($F29="LAST",IFERROR(LOOKUP(2,1/($I29:$T29&lt;&gt;""),$I29:$T29),""),"")))</f>
         <v/>
       </c>
-      <c r="V29" s="25">
+      <c r="V29" s="36">
         <f>IF($G29="","",IF($U29="","",IF($G29=0,IF($U29&lt;=0,1,0),IF($E29="↓",IFERROR($G29/$U29,0),IFERROR($U29/$G29,0)))))</f>
         <v/>
       </c>
-      <c r="W29" s="26">
+      <c r="W29" s="16">
         <f>IF($V29="","—",IF($V29&gt;=1,"✅ محقق",IF($V29&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X29" s="44" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="Y29" s="19" t="inlineStr">
+        <is>
+          <t>التوسع في المواقع</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="26" t="n">
+      <c r="A30" s="16" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>التوسع الإقليمي</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>نسبة العقود على الطرق الإقليمية</t>
         </is>
       </c>
-      <c r="D30" s="28" t="inlineStr">
+      <c r="D30" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="E30" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="F30" s="38" t="inlineStr">
         <is>
           <t>LAST</t>
         </is>
       </c>
-      <c r="G30" s="36" t="n">
+      <c r="G30" s="45" t="n">
         <v>0.25</v>
       </c>
-      <c r="H30" s="33" t="inlineStr">
+      <c r="H30" s="41" t="inlineStr">
         <is>
           <t>&gt; 25%</t>
         </is>
       </c>
-      <c r="I30" s="37" t="n"/>
-      <c r="J30" s="37" t="n"/>
-      <c r="K30" s="37" t="n"/>
-      <c r="L30" s="37" t="n"/>
-      <c r="M30" s="37" t="n"/>
-      <c r="N30" s="37" t="n"/>
-      <c r="O30" s="37" t="n"/>
-      <c r="P30" s="37" t="n"/>
-      <c r="Q30" s="37" t="n"/>
-      <c r="R30" s="37" t="n"/>
-      <c r="S30" s="37" t="n"/>
-      <c r="T30" s="37" t="n"/>
-      <c r="U30" s="38">
+      <c r="I30" s="46" t="n"/>
+      <c r="J30" s="46" t="n"/>
+      <c r="K30" s="46" t="n"/>
+      <c r="L30" s="46" t="n"/>
+      <c r="M30" s="46" t="n"/>
+      <c r="N30" s="46" t="n"/>
+      <c r="O30" s="46" t="n"/>
+      <c r="P30" s="46" t="n"/>
+      <c r="Q30" s="46" t="n"/>
+      <c r="R30" s="46" t="n"/>
+      <c r="S30" s="46" t="n"/>
+      <c r="T30" s="46" t="n"/>
+      <c r="U30" s="47">
         <f>IF($F30="SUM",IF(COUNT($I30:$T30)=0,"",SUM($I30:$T30)),IF($F30="AVG",IFERROR(AVERAGE($I30:$T30),""),IF($F30="LAST",IFERROR(LOOKUP(2,1/($I30:$T30&lt;&gt;""),$I30:$T30),""),"")))</f>
         <v/>
       </c>
-      <c r="V30" s="25">
+      <c r="V30" s="36">
         <f>IF($G30="","",IF($U30="","",IF($G30=0,IF($U30&lt;=0,1,0),IF($E30="↓",IFERROR($G30/$U30,0),IFERROR($U30/$G30,0)))))</f>
         <v/>
       </c>
-      <c r="W30" s="26">
+      <c r="W30" s="16">
         <f>IF($V30="","—",IF($V30&gt;=1,"✅ محقق",IF($V30&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X30" s="44" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="Y30" s="19" t="inlineStr">
+        <is>
+          <t>التوسع في المواقع</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="26" t="n">
+      <c r="A31" s="16" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>تجربة العملاء والشركاء</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>متوسط تقييم المحطات على خرائط قوقل</t>
         </is>
       </c>
-      <c r="D31" s="28" t="inlineStr">
+      <c r="D31" s="38" t="inlineStr">
         <is>
           <t>نجمة/5</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="F31" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G31" s="41" t="n">
+      <c r="G31" s="50" t="n">
         <v>4.7</v>
       </c>
-      <c r="H31" s="33" t="inlineStr">
+      <c r="H31" s="41" t="inlineStr">
         <is>
           <t>≥ 4.7 نجمة</t>
         </is>
       </c>
-      <c r="I31" s="42" t="n"/>
-      <c r="J31" s="42" t="n"/>
-      <c r="K31" s="42" t="n"/>
-      <c r="L31" s="42" t="n"/>
-      <c r="M31" s="42" t="n"/>
-      <c r="N31" s="42" t="n"/>
-      <c r="O31" s="42" t="n"/>
-      <c r="P31" s="42" t="n"/>
-      <c r="Q31" s="42" t="n"/>
-      <c r="R31" s="42" t="n"/>
-      <c r="S31" s="42" t="n"/>
-      <c r="T31" s="42" t="n"/>
-      <c r="U31" s="43">
+      <c r="I31" s="51" t="n"/>
+      <c r="J31" s="51" t="n"/>
+      <c r="K31" s="51" t="n"/>
+      <c r="L31" s="51" t="n"/>
+      <c r="M31" s="51" t="n"/>
+      <c r="N31" s="51" t="n"/>
+      <c r="O31" s="51" t="n"/>
+      <c r="P31" s="51" t="n"/>
+      <c r="Q31" s="51" t="n"/>
+      <c r="R31" s="51" t="n"/>
+      <c r="S31" s="51" t="n"/>
+      <c r="T31" s="51" t="n"/>
+      <c r="U31" s="52">
         <f>IF($F31="SUM",IF(COUNT($I31:$T31)=0,"",SUM($I31:$T31)),IF($F31="AVG",IFERROR(AVERAGE($I31:$T31),""),IF($F31="LAST",IFERROR(LOOKUP(2,1/($I31:$T31&lt;&gt;""),$I31:$T31),""),"")))</f>
         <v/>
       </c>
-      <c r="V31" s="25">
+      <c r="V31" s="36">
         <f>IF($G31="","",IF($U31="","",IF($G31=0,IF($U31&lt;=0,1,0),IF($E31="↓",IFERROR($G31/$U31,0),IFERROR($U31/$G31,0)))))</f>
         <v/>
       </c>
-      <c r="W31" s="26">
+      <c r="W31" s="16">
         <f>IF($V31="","—",IF($V31&gt;=1,"✅ محقق",IF($V31&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X31" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y31" s="19" t="inlineStr">
+        <is>
+          <t>تعزيز تجربة العملاء</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="26" t="n">
+      <c r="A32" s="16" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>تجربة العملاء والشركاء</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>معدل رضا شركاء الامتياز (CSAT)</t>
         </is>
       </c>
-      <c r="D32" s="28" t="inlineStr">
+      <c r="D32" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="E32" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F32" s="28" t="inlineStr">
+      <c r="F32" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G32" s="36" t="n">
+      <c r="G32" s="45" t="n">
         <v>0.9</v>
       </c>
-      <c r="H32" s="33" t="inlineStr">
+      <c r="H32" s="41" t="inlineStr">
         <is>
           <t>90%+</t>
         </is>
       </c>
-      <c r="I32" s="37" t="n"/>
-      <c r="J32" s="37" t="n"/>
-      <c r="K32" s="37" t="n"/>
-      <c r="L32" s="37" t="n"/>
-      <c r="M32" s="37" t="n"/>
-      <c r="N32" s="37" t="n"/>
-      <c r="O32" s="37" t="n"/>
-      <c r="P32" s="37" t="n"/>
-      <c r="Q32" s="37" t="n"/>
-      <c r="R32" s="37" t="n"/>
-      <c r="S32" s="37" t="n"/>
-      <c r="T32" s="37" t="n"/>
-      <c r="U32" s="38">
+      <c r="I32" s="46" t="n"/>
+      <c r="J32" s="46" t="n"/>
+      <c r="K32" s="46" t="n"/>
+      <c r="L32" s="46" t="n"/>
+      <c r="M32" s="46" t="n"/>
+      <c r="N32" s="46" t="n"/>
+      <c r="O32" s="46" t="n"/>
+      <c r="P32" s="46" t="n"/>
+      <c r="Q32" s="46" t="n"/>
+      <c r="R32" s="46" t="n"/>
+      <c r="S32" s="46" t="n"/>
+      <c r="T32" s="46" t="n"/>
+      <c r="U32" s="47">
         <f>IF($F32="SUM",IF(COUNT($I32:$T32)=0,"",SUM($I32:$T32)),IF($F32="AVG",IFERROR(AVERAGE($I32:$T32),""),IF($F32="LAST",IFERROR(LOOKUP(2,1/($I32:$T32&lt;&gt;""),$I32:$T32),""),"")))</f>
         <v/>
       </c>
-      <c r="V32" s="25">
+      <c r="V32" s="36">
         <f>IF($G32="","",IF($U32="","",IF($G32=0,IF($U32&lt;=0,1,0),IF($E32="↓",IFERROR($G32/$U32,0),IFERROR($U32/$G32,0)))))</f>
         <v/>
       </c>
-      <c r="W32" s="26">
+      <c r="W32" s="16">
         <f>IF($V32="","—",IF($V32&gt;=1,"✅ محقق",IF($V32&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X32" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y32" s="19" t="inlineStr">
+        <is>
+          <t>تعزيز تجربة العملاء</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="26" t="n">
+      <c r="A33" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="24" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>تجربة العملاء والشركاء</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>نسبة حل الشكاوى خلال المدة المحددة</t>
         </is>
       </c>
-      <c r="D33" s="28" t="inlineStr">
+      <c r="D33" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr">
+      <c r="E33" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F33" s="28" t="inlineStr">
+      <c r="F33" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G33" s="36" t="n">
+      <c r="G33" s="45" t="n">
         <v>0.95</v>
       </c>
-      <c r="H33" s="33" t="inlineStr">
+      <c r="H33" s="41" t="inlineStr">
         <is>
           <t>95%+</t>
         </is>
       </c>
-      <c r="I33" s="37" t="n"/>
-      <c r="J33" s="37" t="n"/>
-      <c r="K33" s="37" t="n"/>
-      <c r="L33" s="37" t="n"/>
-      <c r="M33" s="37" t="n"/>
-      <c r="N33" s="37" t="n"/>
-      <c r="O33" s="37" t="n"/>
-      <c r="P33" s="37" t="n"/>
-      <c r="Q33" s="37" t="n"/>
-      <c r="R33" s="37" t="n"/>
-      <c r="S33" s="37" t="n"/>
-      <c r="T33" s="37" t="n"/>
-      <c r="U33" s="38">
+      <c r="I33" s="46" t="n"/>
+      <c r="J33" s="46" t="n"/>
+      <c r="K33" s="46" t="n"/>
+      <c r="L33" s="46" t="n"/>
+      <c r="M33" s="46" t="n"/>
+      <c r="N33" s="46" t="n"/>
+      <c r="O33" s="46" t="n"/>
+      <c r="P33" s="46" t="n"/>
+      <c r="Q33" s="46" t="n"/>
+      <c r="R33" s="46" t="n"/>
+      <c r="S33" s="46" t="n"/>
+      <c r="T33" s="46" t="n"/>
+      <c r="U33" s="47">
         <f>IF($F33="SUM",IF(COUNT($I33:$T33)=0,"",SUM($I33:$T33)),IF($F33="AVG",IFERROR(AVERAGE($I33:$T33),""),IF($F33="LAST",IFERROR(LOOKUP(2,1/($I33:$T33&lt;&gt;""),$I33:$T33),""),"")))</f>
         <v/>
       </c>
-      <c r="V33" s="25">
+      <c r="V33" s="36">
         <f>IF($G33="","",IF($U33="","",IF($G33=0,IF($U33&lt;=0,1,0),IF($E33="↓",IFERROR($G33/$U33,0),IFERROR($U33/$G33,0)))))</f>
         <v/>
       </c>
-      <c r="W33" s="26">
+      <c r="W33" s="16">
         <f>IF($V33="","—",IF($V33&gt;=1,"✅ محقق",IF($V33&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X33" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y33" s="19" t="inlineStr">
+        <is>
+          <t>تعزيز تجربة العملاء</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="26" t="n">
+      <c r="A34" s="16" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>تجربة العملاء والشركاء</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>نسبة انخفاض الشكاوى التشغيلية والإدارية</t>
         </is>
       </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="D34" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F34" s="28" t="inlineStr">
+      <c r="F34" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G34" s="28" t="inlineStr"/>
-      <c r="H34" s="33" t="inlineStr">
+      <c r="G34" s="38" t="inlineStr"/>
+      <c r="H34" s="41" t="inlineStr">
         <is>
           <t>-30%</t>
         </is>
       </c>
-      <c r="I34" s="37" t="n"/>
-      <c r="J34" s="37" t="n"/>
-      <c r="K34" s="37" t="n"/>
-      <c r="L34" s="37" t="n"/>
-      <c r="M34" s="37" t="n"/>
-      <c r="N34" s="37" t="n"/>
-      <c r="O34" s="37" t="n"/>
-      <c r="P34" s="37" t="n"/>
-      <c r="Q34" s="37" t="n"/>
-      <c r="R34" s="37" t="n"/>
-      <c r="S34" s="37" t="n"/>
-      <c r="T34" s="37" t="n"/>
-      <c r="U34" s="38">
+      <c r="I34" s="46" t="n"/>
+      <c r="J34" s="46" t="n"/>
+      <c r="K34" s="46" t="n"/>
+      <c r="L34" s="46" t="n"/>
+      <c r="M34" s="46" t="n"/>
+      <c r="N34" s="46" t="n"/>
+      <c r="O34" s="46" t="n"/>
+      <c r="P34" s="46" t="n"/>
+      <c r="Q34" s="46" t="n"/>
+      <c r="R34" s="46" t="n"/>
+      <c r="S34" s="46" t="n"/>
+      <c r="T34" s="46" t="n"/>
+      <c r="U34" s="47">
         <f>IF($F34="SUM",IF(COUNT($I34:$T34)=0,"",SUM($I34:$T34)),IF($F34="AVG",IFERROR(AVERAGE($I34:$T34),""),IF($F34="LAST",IFERROR(LOOKUP(2,1/($I34:$T34&lt;&gt;""),$I34:$T34),""),"")))</f>
         <v/>
       </c>
-      <c r="V34" s="25">
+      <c r="V34" s="36">
         <f>IF($G34="","",IF($U34="","",IF($G34=0,IF($U34&lt;=0,1,0),IF($E34="↓",IFERROR($G34/$U34,0),IFERROR($U34/$G34,0)))))</f>
         <v/>
       </c>
-      <c r="W34" s="26">
+      <c r="W34" s="16">
         <f>IF($V34="","—",IF($V34&gt;=1,"✅ محقق",IF($V34&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X34" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y34" s="19" t="inlineStr">
+        <is>
+          <t>تعزيز تجربة العملاء</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="26" t="n">
+      <c r="A35" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>استدامة الشراكة والامتثال</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>نسبة استدامة أصحاب الامتياز (Retention)</t>
         </is>
       </c>
-      <c r="D35" s="28" t="inlineStr">
+      <c r="D35" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E35" s="28" t="inlineStr">
+      <c r="E35" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F35" s="28" t="inlineStr">
+      <c r="F35" s="38" t="inlineStr">
         <is>
           <t>LAST</t>
         </is>
       </c>
-      <c r="G35" s="36" t="n">
+      <c r="G35" s="45" t="n">
         <v>0.9</v>
       </c>
-      <c r="H35" s="33" t="inlineStr">
+      <c r="H35" s="41" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="I35" s="37" t="n"/>
-      <c r="J35" s="37" t="n"/>
-      <c r="K35" s="37" t="n"/>
-      <c r="L35" s="37" t="n"/>
-      <c r="M35" s="37" t="n"/>
-      <c r="N35" s="37" t="n"/>
-      <c r="O35" s="37" t="n"/>
-      <c r="P35" s="37" t="n"/>
-      <c r="Q35" s="37" t="n"/>
-      <c r="R35" s="37" t="n"/>
-      <c r="S35" s="37" t="n"/>
-      <c r="T35" s="37" t="n"/>
-      <c r="U35" s="38">
+      <c r="I35" s="46" t="n"/>
+      <c r="J35" s="46" t="n"/>
+      <c r="K35" s="46" t="n"/>
+      <c r="L35" s="46" t="n"/>
+      <c r="M35" s="46" t="n"/>
+      <c r="N35" s="46" t="n"/>
+      <c r="O35" s="46" t="n"/>
+      <c r="P35" s="46" t="n"/>
+      <c r="Q35" s="46" t="n"/>
+      <c r="R35" s="46" t="n"/>
+      <c r="S35" s="46" t="n"/>
+      <c r="T35" s="46" t="n"/>
+      <c r="U35" s="47">
         <f>IF($F35="SUM",IF(COUNT($I35:$T35)=0,"",SUM($I35:$T35)),IF($F35="AVG",IFERROR(AVERAGE($I35:$T35),""),IF($F35="LAST",IFERROR(LOOKUP(2,1/($I35:$T35&lt;&gt;""),$I35:$T35),""),"")))</f>
         <v/>
       </c>
-      <c r="V35" s="25">
+      <c r="V35" s="36">
         <f>IF($G35="","",IF($U35="","",IF($G35=0,IF($U35&lt;=0,1,0),IF($E35="↓",IFERROR($G35/$U35,0),IFERROR($U35/$G35,0)))))</f>
         <v/>
       </c>
-      <c r="W35" s="26">
+      <c r="W35" s="16">
         <f>IF($V35="","—",IF($V35&gt;=1,"✅ محقق",IF($V35&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X35" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y35" s="19" t="inlineStr">
+        <is>
+          <t>تعزيز تجربة العملاء</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="26" t="n">
+      <c r="A36" s="16" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>استدامة الشراكة والامتثال</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>نسبة زيادة عدد أصحاب الامتياز</t>
         </is>
       </c>
-      <c r="D36" s="28" t="inlineStr">
+      <c r="D36" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="E36" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F36" s="28" t="inlineStr">
+      <c r="F36" s="38" t="inlineStr">
         <is>
           <t>LAST</t>
         </is>
       </c>
-      <c r="G36" s="36" t="n">
+      <c r="G36" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="33" t="inlineStr">
+      <c r="H36" s="41" t="inlineStr">
         <is>
           <t>100% نمو</t>
         </is>
       </c>
-      <c r="I36" s="37" t="n"/>
-      <c r="J36" s="37" t="n"/>
-      <c r="K36" s="37" t="n"/>
-      <c r="L36" s="37" t="n"/>
-      <c r="M36" s="37" t="n"/>
-      <c r="N36" s="37" t="n"/>
-      <c r="O36" s="37" t="n"/>
-      <c r="P36" s="37" t="n"/>
-      <c r="Q36" s="37" t="n"/>
-      <c r="R36" s="37" t="n"/>
-      <c r="S36" s="37" t="n"/>
-      <c r="T36" s="37" t="n"/>
-      <c r="U36" s="38">
+      <c r="I36" s="46" t="n"/>
+      <c r="J36" s="46" t="n"/>
+      <c r="K36" s="46" t="n"/>
+      <c r="L36" s="46" t="n"/>
+      <c r="M36" s="46" t="n"/>
+      <c r="N36" s="46" t="n"/>
+      <c r="O36" s="46" t="n"/>
+      <c r="P36" s="46" t="n"/>
+      <c r="Q36" s="46" t="n"/>
+      <c r="R36" s="46" t="n"/>
+      <c r="S36" s="46" t="n"/>
+      <c r="T36" s="46" t="n"/>
+      <c r="U36" s="47">
         <f>IF($F36="SUM",IF(COUNT($I36:$T36)=0,"",SUM($I36:$T36)),IF($F36="AVG",IFERROR(AVERAGE($I36:$T36),""),IF($F36="LAST",IFERROR(LOOKUP(2,1/($I36:$T36&lt;&gt;""),$I36:$T36),""),"")))</f>
         <v/>
       </c>
-      <c r="V36" s="25">
+      <c r="V36" s="36">
         <f>IF($G36="","",IF($U36="","",IF($G36=0,IF($U36&lt;=0,1,0),IF($E36="↓",IFERROR($G36/$U36,0),IFERROR($U36/$G36,0)))))</f>
         <v/>
       </c>
-      <c r="W36" s="26">
+      <c r="W36" s="16">
         <f>IF($V36="","—",IF($V36&gt;=1,"✅ محقق",IF($V36&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X36" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y36" s="19" t="inlineStr">
+        <is>
+          <t>تعزيز تجربة العملاء</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="26" t="n">
+      <c r="A37" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>استدامة الشراكة والامتثال</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>نسبة اكتمال المستندات النظامية قبل التوقيع</t>
         </is>
       </c>
-      <c r="D37" s="28" t="inlineStr">
+      <c r="D37" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E37" s="28" t="inlineStr">
+      <c r="E37" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F37" s="28" t="inlineStr">
+      <c r="F37" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G37" s="36" t="n">
+      <c r="G37" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="33" t="inlineStr">
+      <c r="H37" s="41" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I37" s="37" t="n"/>
-      <c r="J37" s="37" t="n"/>
-      <c r="K37" s="37" t="n"/>
-      <c r="L37" s="37" t="n"/>
-      <c r="M37" s="37" t="n"/>
-      <c r="N37" s="37" t="n"/>
-      <c r="O37" s="37" t="n"/>
-      <c r="P37" s="37" t="n"/>
-      <c r="Q37" s="37" t="n"/>
-      <c r="R37" s="37" t="n"/>
-      <c r="S37" s="37" t="n"/>
-      <c r="T37" s="37" t="n"/>
-      <c r="U37" s="38">
+      <c r="I37" s="46" t="n"/>
+      <c r="J37" s="46" t="n"/>
+      <c r="K37" s="46" t="n"/>
+      <c r="L37" s="46" t="n"/>
+      <c r="M37" s="46" t="n"/>
+      <c r="N37" s="46" t="n"/>
+      <c r="O37" s="46" t="n"/>
+      <c r="P37" s="46" t="n"/>
+      <c r="Q37" s="46" t="n"/>
+      <c r="R37" s="46" t="n"/>
+      <c r="S37" s="46" t="n"/>
+      <c r="T37" s="46" t="n"/>
+      <c r="U37" s="47">
         <f>IF($F37="SUM",IF(COUNT($I37:$T37)=0,"",SUM($I37:$T37)),IF($F37="AVG",IFERROR(AVERAGE($I37:$T37),""),IF($F37="LAST",IFERROR(LOOKUP(2,1/($I37:$T37&lt;&gt;""),$I37:$T37),""),"")))</f>
         <v/>
       </c>
-      <c r="V37" s="25">
+      <c r="V37" s="36">
         <f>IF($G37="","",IF($U37="","",IF($G37=0,IF($U37&lt;=0,1,0),IF($E37="↓",IFERROR($G37/$U37,0),IFERROR($U37/$G37,0)))))</f>
         <v/>
       </c>
-      <c r="W37" s="26">
+      <c r="W37" s="16">
         <f>IF($V37="","—",IF($V37&gt;=1,"✅ محقق",IF($V37&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X37" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y37" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="26" t="n">
+      <c r="A38" s="16" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>استدامة الشراكة والامتثال</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>متوسط مدة إغلاق عقد الامتياز</t>
         </is>
       </c>
-      <c r="D38" s="28" t="inlineStr">
+      <c r="D38" s="38" t="inlineStr">
         <is>
           <t>أسبوع</t>
         </is>
       </c>
-      <c r="E38" s="28" t="inlineStr">
+      <c r="E38" s="38" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="F38" s="28" t="inlineStr">
+      <c r="F38" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G38" s="41" t="n">
+      <c r="G38" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="33" t="inlineStr">
+      <c r="H38" s="41" t="inlineStr">
         <is>
           <t>≤ أسبوع</t>
         </is>
       </c>
-      <c r="I38" s="42" t="n"/>
-      <c r="J38" s="42" t="n"/>
-      <c r="K38" s="42" t="n"/>
-      <c r="L38" s="42" t="n"/>
-      <c r="M38" s="42" t="n"/>
-      <c r="N38" s="42" t="n"/>
-      <c r="O38" s="42" t="n"/>
-      <c r="P38" s="42" t="n"/>
-      <c r="Q38" s="42" t="n"/>
-      <c r="R38" s="42" t="n"/>
-      <c r="S38" s="42" t="n"/>
-      <c r="T38" s="42" t="n"/>
-      <c r="U38" s="43">
+      <c r="I38" s="51" t="n"/>
+      <c r="J38" s="51" t="n"/>
+      <c r="K38" s="51" t="n"/>
+      <c r="L38" s="51" t="n"/>
+      <c r="M38" s="51" t="n"/>
+      <c r="N38" s="51" t="n"/>
+      <c r="O38" s="51" t="n"/>
+      <c r="P38" s="51" t="n"/>
+      <c r="Q38" s="51" t="n"/>
+      <c r="R38" s="51" t="n"/>
+      <c r="S38" s="51" t="n"/>
+      <c r="T38" s="51" t="n"/>
+      <c r="U38" s="52">
         <f>IF($F38="SUM",IF(COUNT($I38:$T38)=0,"",SUM($I38:$T38)),IF($F38="AVG",IFERROR(AVERAGE($I38:$T38),""),IF($F38="LAST",IFERROR(LOOKUP(2,1/($I38:$T38&lt;&gt;""),$I38:$T38),""),"")))</f>
         <v/>
       </c>
-      <c r="V38" s="25">
+      <c r="V38" s="36">
         <f>IF($G38="","",IF($U38="","",IF($G38=0,IF($U38&lt;=0,1,0),IF($E38="↓",IFERROR($G38/$U38,0),IFERROR($U38/$G38,0)))))</f>
         <v/>
       </c>
-      <c r="W38" s="26">
+      <c r="W38" s="16">
         <f>IF($V38="","—",IF($V38&gt;=1,"✅ محقق",IF($V38&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
+      <c r="X38" s="44" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="Y38" s="19" t="inlineStr">
+        <is>
+          <t>الامتياز التجاري</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="26" t="n">
+      <c r="A39" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="24" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>استدامة الشراكة والامتثال</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>نسبة إنجاز التقارير الدورية في موعدها</t>
         </is>
       </c>
-      <c r="D39" s="28" t="inlineStr">
+      <c r="D39" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E39" s="28" t="inlineStr">
+      <c r="E39" s="38" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="F39" s="28" t="inlineStr">
+      <c r="F39" s="38" t="inlineStr">
         <is>
           <t>AVG</t>
         </is>
       </c>
-      <c r="G39" s="36" t="n">
+      <c r="G39" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="33" t="inlineStr">
+      <c r="H39" s="41" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I39" s="37" t="n"/>
-      <c r="J39" s="37" t="n"/>
-      <c r="K39" s="37" t="n"/>
-      <c r="L39" s="37" t="n"/>
-      <c r="M39" s="37" t="n"/>
-      <c r="N39" s="37" t="n"/>
-      <c r="O39" s="37" t="n"/>
-      <c r="P39" s="37" t="n"/>
-      <c r="Q39" s="37" t="n"/>
-      <c r="R39" s="37" t="n"/>
-      <c r="S39" s="37" t="n"/>
-      <c r="T39" s="37" t="n"/>
-      <c r="U39" s="38">
+      <c r="I39" s="46" t="n"/>
+      <c r="J39" s="46" t="n"/>
+      <c r="K39" s="46" t="n"/>
+      <c r="L39" s="46" t="n"/>
+      <c r="M39" s="46" t="n"/>
+      <c r="N39" s="46" t="n"/>
+      <c r="O39" s="46" t="n"/>
+      <c r="P39" s="46" t="n"/>
+      <c r="Q39" s="46" t="n"/>
+      <c r="R39" s="46" t="n"/>
+      <c r="S39" s="46" t="n"/>
+      <c r="T39" s="46" t="n"/>
+      <c r="U39" s="47">
         <f>IF($F39="SUM",IF(COUNT($I39:$T39)=0,"",SUM($I39:$T39)),IF($F39="AVG",IFERROR(AVERAGE($I39:$T39),""),IF($F39="LAST",IFERROR(LOOKUP(2,1/($I39:$T39&lt;&gt;""),$I39:$T39),""),"")))</f>
         <v/>
       </c>
-      <c r="V39" s="25">
+      <c r="V39" s="36">
         <f>IF($G39="","",IF($U39="","",IF($G39=0,IF($U39&lt;=0,1,0),IF($E39="↓",IFERROR($G39/$U39,0),IFERROR($U39/$G39,0)))))</f>
         <v/>
       </c>
-      <c r="W39" s="26">
+      <c r="W39" s="16">
         <f>IF($V39="","—",IF($V39&gt;=1,"✅ محقق",IF($V39&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
+      </c>
+      <c r="X39" s="44" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y39" s="19" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:W2"/>
-    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A1:Y1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 N4 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P35 P36 P37 P38 P39 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q35 Q36 Q37 Q38 Q39 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 S4 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 S34 S35 S36 S37 S38 S39 T4 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T35 T36 T37 T38 T39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="قيمة غير صحيحة" error="أدخل رقماً موجباً فقط" type="decimal" operator="greaterThanOrEqual">
@@ -4311,7 +5733,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4328,7 +5750,7 @@
   </cols>
   <sheetData>
     <row r="2" ht="28" customHeight="1">
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>إدارة الامتياز · مؤشرات كل موظف (مرجع الربط)</t>
         </is>
@@ -4342,35 +5764,35 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>●/○</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>الأولوية</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr"/>
+      <c r="E5" s="54" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="B6" s="46" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>عدد عقود الامتياز الجديدة الموقّعة</t>
         </is>
       </c>
-      <c r="D6" s="47" t="inlineStr">
+      <c r="D6" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4378,17 +5800,17 @@
       <c r="E6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="B7" s="46" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>عدد محطات الامتياز المشغّلة (تراكمي)</t>
         </is>
       </c>
-      <c r="D7" s="47" t="inlineStr">
+      <c r="D7" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4396,17 +5818,17 @@
       <c r="E7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="B8" s="46" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>نسبة تحويل الفرص إلى عقود موقّعة</t>
         </is>
       </c>
-      <c r="D8" s="47" t="inlineStr">
+      <c r="D8" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4414,17 +5836,17 @@
       <c r="E8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" s="46" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>إجمالي مبيعات وقود محطات الامتياز</t>
         </is>
       </c>
-      <c r="D9" s="47" t="inlineStr">
+      <c r="D9" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4432,17 +5854,17 @@
       <c r="E9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="46" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>نسبة استدامة أصحاب الامتياز</t>
         </is>
       </c>
-      <c r="D10" s="47" t="inlineStr">
+      <c r="D10" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4457,35 +5879,35 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="44" t="inlineStr">
+      <c r="B13" s="53" t="inlineStr">
         <is>
           <t>●/○</t>
         </is>
       </c>
-      <c r="C13" s="44" t="inlineStr">
+      <c r="C13" s="53" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="D13" s="44" t="inlineStr">
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>الأولوية</t>
         </is>
       </c>
-      <c r="E13" s="45" t="inlineStr"/>
+      <c r="E13" s="54" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>نسبة جاهزية محطات الامتياز</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4493,17 +5915,17 @@
       <c r="E14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>نسبة إغلاق ملاحظات الجودة الميدانية</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4511,17 +5933,17 @@
       <c r="E15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>متوسط درجة تقييم جودة المحطة</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4529,17 +5951,17 @@
       <c r="E16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>نسبة المحطات المستوفية لمعايير السلامة</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4547,17 +5969,17 @@
       <c r="E17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>نسبة التزام المحطات بالهوية المؤسسية</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4572,35 +5994,35 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B21" s="53" t="inlineStr">
         <is>
           <t>●/○</t>
         </is>
       </c>
-      <c r="C21" s="44" t="inlineStr">
+      <c r="C21" s="53" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="D21" s="44" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>الأولوية</t>
         </is>
       </c>
-      <c r="E21" s="45" t="inlineStr"/>
+      <c r="E21" s="54" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="B22" s="46" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>نسبة تنفيذ الزيارات الميدانية المجدولة</t>
         </is>
       </c>
-      <c r="D22" s="47" t="inlineStr">
+      <c r="D22" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4608,17 +6030,17 @@
       <c r="E22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="46" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>عدد عقود الامتياز الجديدة الموقّعة</t>
         </is>
       </c>
-      <c r="D23" s="47" t="inlineStr">
+      <c r="D23" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4626,17 +6048,17 @@
       <c r="E23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="B24" s="46" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>متوسط درجة تقييم جودة المحطة</t>
         </is>
       </c>
-      <c r="D24" s="47" t="inlineStr">
+      <c r="D24" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4644,17 +6066,17 @@
       <c r="E24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="B25" s="46" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>نسبة مبيعات المنتجات غير البترولية</t>
         </is>
       </c>
-      <c r="D25" s="47" t="inlineStr">
+      <c r="D25" s="55" t="inlineStr">
         <is>
           <t>🟡 متابعة</t>
         </is>
@@ -4669,35 +6091,35 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="44" t="inlineStr">
+      <c r="B28" s="53" t="inlineStr">
         <is>
           <t>●/○</t>
         </is>
       </c>
-      <c r="C28" s="44" t="inlineStr">
+      <c r="C28" s="53" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="D28" s="44" t="inlineStr">
+      <c r="D28" s="53" t="inlineStr">
         <is>
           <t>الأولوية</t>
         </is>
       </c>
-      <c r="E28" s="45" t="inlineStr"/>
+      <c r="E28" s="54" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="B29" s="46" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>إجمالي إيرادات إدارة الامتياز</t>
         </is>
       </c>
-      <c r="D29" s="47" t="inlineStr">
+      <c r="D29" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4705,17 +6127,17 @@
       <c r="E29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="B30" s="46" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>نسبة التحصيل المالي من شركاء الامتياز</t>
         </is>
       </c>
-      <c r="D30" s="47" t="inlineStr">
+      <c r="D30" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4723,17 +6145,17 @@
       <c r="E30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="46" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>متوسط تقييم المحطات على خرائط قوقل</t>
         </is>
       </c>
-      <c r="D31" s="47" t="inlineStr">
+      <c r="D31" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4741,17 +6163,17 @@
       <c r="E31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="B32" s="46" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>نسبة الشركاء الملتزمين بمواعيد السداد</t>
         </is>
       </c>
-      <c r="D32" s="47" t="inlineStr">
+      <c r="D32" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -4759,17 +6181,17 @@
       <c r="E32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="B33" s="46" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>عدد الحملات التسويقية الميدانية</t>
         </is>
       </c>
-      <c r="D33" s="47" t="inlineStr">
+      <c r="D33" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -4784,35 +6206,35 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="44" t="inlineStr">
+      <c r="B36" s="53" t="inlineStr">
         <is>
           <t>●/○</t>
         </is>
       </c>
-      <c r="C36" s="44" t="inlineStr">
+      <c r="C36" s="53" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="D36" s="44" t="inlineStr">
+      <c r="D36" s="53" t="inlineStr">
         <is>
           <t>الأولوية</t>
         </is>
       </c>
-      <c r="E36" s="45" t="inlineStr"/>
+      <c r="E36" s="54" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="B37" s="46" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>متوسط أيام التحصيل (DSO)</t>
         </is>
       </c>
-      <c r="D37" s="47" t="inlineStr">
+      <c r="D37" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -4820,17 +6242,17 @@
       <c r="E37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="B38" s="46" t="inlineStr">
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>إجمالي المستحقات المتأخرة (+30 يوم)</t>
         </is>
       </c>
-      <c r="D38" s="47" t="inlineStr">
+      <c r="D38" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -4838,17 +6260,17 @@
       <c r="E38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="B39" s="46" t="inlineStr">
+      <c r="B39" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>نسبة إنجاز التقارير الدورية في موعدها</t>
         </is>
       </c>
-      <c r="D39" s="47" t="inlineStr">
+      <c r="D39" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -4856,17 +6278,17 @@
       <c r="E39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="B40" s="46" t="inlineStr">
+      <c r="B40" s="35" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>عدد محطات الامتياز المشغّلة</t>
         </is>
       </c>
-      <c r="D40" s="47" t="inlineStr">
+      <c r="D40" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4881,35 +6303,35 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="44" t="inlineStr">
+      <c r="B43" s="53" t="inlineStr">
         <is>
           <t>●/○</t>
         </is>
       </c>
-      <c r="C43" s="44" t="inlineStr">
+      <c r="C43" s="53" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="D43" s="44" t="inlineStr">
+      <c r="D43" s="53" t="inlineStr">
         <is>
           <t>الأولوية</t>
         </is>
       </c>
-      <c r="E43" s="45" t="inlineStr"/>
+      <c r="E43" s="54" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="B44" s="46" t="inlineStr">
+      <c r="B44" s="35" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>نسبة اكتمال المستندات النظامية قبل التوقيع</t>
         </is>
       </c>
-      <c r="D44" s="47" t="inlineStr">
+      <c r="D44" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -4917,17 +6339,17 @@
       <c r="E44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="B45" s="46" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>نسبة إنجاز التقارير الدورية في موعدها</t>
         </is>
       </c>
-      <c r="D45" s="47" t="inlineStr">
+      <c r="D45" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -4942,35 +6364,35 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="44" t="inlineStr">
+      <c r="B48" s="53" t="inlineStr">
         <is>
           <t>●/○</t>
         </is>
       </c>
-      <c r="C48" s="44" t="inlineStr">
+      <c r="C48" s="53" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="D48" s="44" t="inlineStr">
+      <c r="D48" s="53" t="inlineStr">
         <is>
           <t>الأولوية</t>
         </is>
       </c>
-      <c r="E48" s="45" t="inlineStr"/>
+      <c r="E48" s="54" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="B49" s="46" t="inlineStr">
+      <c r="B49" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>عدد حالات انقطاع الوقود الموثّقة</t>
         </is>
       </c>
-      <c r="D49" s="47" t="inlineStr">
+      <c r="D49" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -4978,17 +6400,17 @@
       <c r="E49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="B50" s="46" t="inlineStr">
+      <c r="B50" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C50" s="24" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>متوسط وقت معالجة البلاغات التشغيلية</t>
         </is>
       </c>
-      <c r="D50" s="47" t="inlineStr">
+      <c r="D50" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -4996,17 +6418,17 @@
       <c r="E50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="B51" s="46" t="inlineStr">
+      <c r="B51" s="35" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C51" s="24" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>نسبة الشركاء الملتزمين بمواعيد السداد</t>
         </is>
       </c>
-      <c r="D51" s="47" t="inlineStr">
+      <c r="D51" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -5021,35 +6443,35 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="44" t="inlineStr">
+      <c r="B54" s="53" t="inlineStr">
         <is>
           <t>●/○</t>
         </is>
       </c>
-      <c r="C54" s="44" t="inlineStr">
+      <c r="C54" s="53" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="D54" s="44" t="inlineStr">
+      <c r="D54" s="53" t="inlineStr">
         <is>
           <t>الأولوية</t>
         </is>
       </c>
-      <c r="E54" s="45" t="inlineStr"/>
+      <c r="E54" s="54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="B55" s="46" t="inlineStr">
+      <c r="B55" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C55" s="24" t="inlineStr">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>متوسط مبيعات المحطة الواحدة شهرياً</t>
         </is>
       </c>
-      <c r="D55" s="47" t="inlineStr">
+      <c r="D55" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -5057,17 +6479,17 @@
       <c r="E55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="B56" s="46" t="inlineStr">
+      <c r="B56" s="35" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C56" s="24" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
         <is>
           <t>إجمالي مبيعات وقود محطات الامتياز</t>
         </is>
       </c>
-      <c r="D56" s="47" t="inlineStr">
+      <c r="D56" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -5075,17 +6497,17 @@
       <c r="E56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="B57" s="46" t="inlineStr">
+      <c r="B57" s="35" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C57" s="24" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>نسبة جاهزية محطات الامتياز</t>
         </is>
       </c>
-      <c r="D57" s="47" t="inlineStr">
+      <c r="D57" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -5100,35 +6522,35 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="44" t="inlineStr">
+      <c r="B60" s="53" t="inlineStr">
         <is>
           <t>●/○</t>
         </is>
       </c>
-      <c r="C60" s="44" t="inlineStr">
+      <c r="C60" s="53" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="D60" s="44" t="inlineStr">
+      <c r="D60" s="53" t="inlineStr">
         <is>
           <t>الأولوية</t>
         </is>
       </c>
-      <c r="E60" s="45" t="inlineStr"/>
+      <c r="E60" s="54" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="B61" s="46" t="inlineStr">
+      <c r="B61" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C61" s="24" t="inlineStr">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>نسبة اكتمال المستندات النظامية قبل التوقيع</t>
         </is>
       </c>
-      <c r="D61" s="47" t="inlineStr">
+      <c r="D61" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -5136,17 +6558,17 @@
       <c r="E61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="B62" s="46" t="inlineStr">
+      <c r="B62" s="35" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C62" s="24" t="inlineStr">
+      <c r="C62" s="19" t="inlineStr">
         <is>
           <t>نسبة حل الشكاوى خلال المدة المحددة</t>
         </is>
       </c>
-      <c r="D62" s="47" t="inlineStr">
+      <c r="D62" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -5154,17 +6576,17 @@
       <c r="E62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="B63" s="46" t="inlineStr">
+      <c r="B63" s="35" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C63" s="24" t="inlineStr">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>متوسط مدة إغلاق عقد الامتياز</t>
         </is>
       </c>
-      <c r="D63" s="47" t="inlineStr">
+      <c r="D63" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -5179,35 +6601,35 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="44" t="inlineStr">
+      <c r="B66" s="53" t="inlineStr">
         <is>
           <t>●/○</t>
         </is>
       </c>
-      <c r="C66" s="44" t="inlineStr">
+      <c r="C66" s="53" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="D66" s="44" t="inlineStr">
+      <c r="D66" s="53" t="inlineStr">
         <is>
           <t>الأولوية</t>
         </is>
       </c>
-      <c r="E66" s="45" t="inlineStr"/>
+      <c r="E66" s="54" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="B67" s="46" t="inlineStr">
+      <c r="B67" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C67" s="24" t="inlineStr">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>معدل رضا شركاء الامتياز (CSAT)</t>
         </is>
       </c>
-      <c r="D67" s="47" t="inlineStr">
+      <c r="D67" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -5215,17 +6637,17 @@
       <c r="E67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="B68" s="46" t="inlineStr">
+      <c r="B68" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C68" s="24" t="inlineStr">
+      <c r="C68" s="19" t="inlineStr">
         <is>
           <t>نسبة حل الشكاوى خلال المدة المحددة</t>
         </is>
       </c>
-      <c r="D68" s="47" t="inlineStr">
+      <c r="D68" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -5233,17 +6655,17 @@
       <c r="E68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="B69" s="46" t="inlineStr">
+      <c r="B69" s="35" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="C69" s="24" t="inlineStr">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>نسبة انخفاض الشكاوى التشغيلية والإدارية</t>
         </is>
       </c>
-      <c r="D69" s="47" t="inlineStr">
+      <c r="D69" s="55" t="inlineStr">
         <is>
           <t>🟠 مهم</t>
         </is>
@@ -5251,17 +6673,17 @@
       <c r="E69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="B70" s="46" t="inlineStr">
+      <c r="B70" s="35" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C70" s="24" t="inlineStr">
+      <c r="C70" s="19" t="inlineStr">
         <is>
           <t>نسبة استدامة أصحاب الامتياز</t>
         </is>
       </c>
-      <c r="D70" s="47" t="inlineStr">
+      <c r="D70" s="55" t="inlineStr">
         <is>
           <t>🔴 رئيسي</t>
         </is>
@@ -5287,7 +6709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5306,321 +6728,321 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="56" t="inlineStr">
         <is>
           <t>إدارة الامتياز التجاري · نموذج تقييم الأداء — مدير إدارة الامتياز التجاري</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>الكود: FM-01   ·   فترة القياس: ربع سنوي   ·   🟩 أدخل «نسبة التحقيق» فقط — الدرجة تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="57" t="inlineStr">
         <is>
           <t>اسم الموظف:</t>
         </is>
       </c>
-      <c r="B3" s="50" t="inlineStr"/>
-      <c r="C3" s="51" t="n"/>
-      <c r="D3" s="49" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr"/>
+      <c r="C3" s="59" t="n"/>
+      <c r="D3" s="57" t="inlineStr">
         <is>
           <t>القسم: الامتياز التجاري</t>
         </is>
       </c>
-      <c r="E3" s="50" t="inlineStr"/>
-      <c r="F3" s="52" t="n"/>
-      <c r="G3" s="51" t="n"/>
+      <c r="E3" s="58" t="inlineStr"/>
+      <c r="F3" s="60" t="n"/>
+      <c r="G3" s="59" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="57" t="inlineStr">
         <is>
           <t>المدير المباشر:</t>
         </is>
       </c>
-      <c r="B4" s="50" t="inlineStr"/>
-      <c r="C4" s="51" t="n"/>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="57" t="inlineStr">
         <is>
           <t>الربع / السنة:</t>
         </is>
       </c>
-      <c r="E4" s="50" t="inlineStr"/>
-      <c r="F4" s="52" t="n"/>
-      <c r="G4" s="51" t="n"/>
+      <c r="E4" s="58" t="inlineStr"/>
+      <c r="F4" s="60" t="n"/>
+      <c r="G4" s="59" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>تاريخ التقييم:</t>
         </is>
       </c>
-      <c r="B5" s="50" t="inlineStr"/>
-      <c r="C5" s="51" t="n"/>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr"/>
+      <c r="C5" s="59" t="n"/>
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>حالة التقييم:</t>
         </is>
       </c>
-      <c r="E5" s="50" t="inlineStr"/>
-      <c r="F5" s="52" t="n"/>
-      <c r="G5" s="51" t="n"/>
+      <c r="E5" s="58" t="inlineStr"/>
+      <c r="F5" s="60" t="n"/>
+      <c r="G5" s="59" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>مؤشر الأداء</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>الوزن %</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>المستهدف</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>نسبة التحقيق</t>
         </is>
       </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>الدرجة المحققة</t>
         </is>
       </c>
-      <c r="G6" s="31" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>عدد محطات الامتياز الجديدة</t>
         </is>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="45" t="n">
         <v>0.15</v>
       </c>
-      <c r="D7" s="53" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>100%+ من المحطات المستهدفة</t>
         </is>
       </c>
-      <c r="E7" s="54" t="n"/>
-      <c r="F7" s="25">
+      <c r="E7" s="62" t="n"/>
+      <c r="F7" s="36">
         <f>C7*MIN(E7,1)</f>
         <v/>
       </c>
-      <c r="G7" s="50" t="inlineStr"/>
+      <c r="G7" s="58" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>إجمالي مبيعات محطات الامتياز</t>
         </is>
       </c>
-      <c r="C8" s="36" t="n">
+      <c r="C8" s="45" t="n">
         <v>0.15</v>
       </c>
-      <c r="D8" s="53" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>100%+ من مستهدف المبيعات الربعي</t>
         </is>
       </c>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="25">
+      <c r="E8" s="62" t="n"/>
+      <c r="F8" s="36">
         <f>C8*MIN(E8,1)</f>
         <v/>
       </c>
-      <c r="G8" s="50" t="inlineStr"/>
+      <c r="G8" s="58" t="inlineStr"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>استمرارية تزويد الوقود</t>
         </is>
       </c>
-      <c r="C9" s="36" t="n">
+      <c r="C9" s="45" t="n">
         <v>0.1</v>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>0 حالات انقطاع</t>
         </is>
       </c>
-      <c r="E9" s="54" t="n"/>
-      <c r="F9" s="25">
+      <c r="E9" s="62" t="n"/>
+      <c r="F9" s="36">
         <f>C9*MIN(E9,1)</f>
         <v/>
       </c>
-      <c r="G9" s="50" t="inlineStr"/>
+      <c r="G9" s="58" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>نسبة التحصيل المالي</t>
         </is>
       </c>
-      <c r="C10" s="36" t="n">
+      <c r="C10" s="45" t="n">
         <v>0.15</v>
       </c>
-      <c r="D10" s="53" t="inlineStr">
+      <c r="D10" s="61" t="inlineStr">
         <is>
           <t>100%+ من المستحقات الربعية</t>
         </is>
       </c>
-      <c r="E10" s="54" t="n"/>
-      <c r="F10" s="25">
+      <c r="E10" s="62" t="n"/>
+      <c r="F10" s="36">
         <f>C10*MIN(E10,1)</f>
         <v/>
       </c>
-      <c r="G10" s="50" t="inlineStr"/>
+      <c r="G10" s="58" t="inlineStr"/>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>الالتزام بالهوية المؤسسية</t>
         </is>
       </c>
-      <c r="C11" s="36" t="n">
+      <c r="C11" s="45" t="n">
         <v>0.15</v>
       </c>
-      <c r="D11" s="53" t="inlineStr">
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>70%+ من المحطات ملتزمة</t>
         </is>
       </c>
-      <c r="E11" s="54" t="n"/>
-      <c r="F11" s="25">
+      <c r="E11" s="62" t="n"/>
+      <c r="F11" s="36">
         <f>C11*MIN(E11,1)</f>
         <v/>
       </c>
-      <c r="G11" s="50" t="inlineStr"/>
+      <c r="G11" s="58" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="26" t="n">
+      <c r="A12" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>انخفاض عدد الشكاوى</t>
         </is>
       </c>
-      <c r="C12" s="36" t="n">
+      <c r="C12" s="45" t="n">
         <v>0.1</v>
       </c>
-      <c r="D12" s="53" t="inlineStr">
+      <c r="D12" s="61" t="inlineStr">
         <is>
           <t>خفض 20%+ مقارنة بالربع السابق</t>
         </is>
       </c>
-      <c r="E12" s="54" t="n"/>
-      <c r="F12" s="25">
+      <c r="E12" s="62" t="n"/>
+      <c r="F12" s="36">
         <f>C12*MIN(E12,1)</f>
         <v/>
       </c>
-      <c r="G12" s="50" t="inlineStr"/>
+      <c r="G12" s="58" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="26" t="n">
+      <c r="A13" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>تقييمات خرائط قوقل</t>
         </is>
       </c>
-      <c r="C13" s="36" t="n">
+      <c r="C13" s="45" t="n">
         <v>0.1</v>
       </c>
-      <c r="D13" s="53" t="inlineStr">
+      <c r="D13" s="61" t="inlineStr">
         <is>
           <t>4.7 – 5</t>
         </is>
       </c>
-      <c r="E13" s="54" t="n"/>
-      <c r="F13" s="25">
+      <c r="E13" s="62" t="n"/>
+      <c r="F13" s="36">
         <f>C13*MIN(E13,1)</f>
         <v/>
       </c>
-      <c r="G13" s="50" t="inlineStr"/>
+      <c r="G13" s="58" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>انتظام وجودة التقارير</t>
         </is>
       </c>
-      <c r="C14" s="36" t="n">
+      <c r="C14" s="45" t="n">
         <v>0.1</v>
       </c>
-      <c r="D14" s="53" t="inlineStr">
+      <c r="D14" s="61" t="inlineStr">
         <is>
           <t>100% في موعدها</t>
         </is>
       </c>
-      <c r="E14" s="54" t="n"/>
-      <c r="F14" s="25">
+      <c r="E14" s="62" t="n"/>
+      <c r="F14" s="36">
         <f>C14*MIN(E14,1)</f>
         <v/>
       </c>
-      <c r="G14" s="50" t="inlineStr"/>
+      <c r="G14" s="58" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr"/>
-      <c r="B15" s="55" t="inlineStr">
+      <c r="B15" s="63" t="inlineStr">
         <is>
           <t>المجموع الكلي</t>
         </is>
       </c>
-      <c r="C15" s="56">
+      <c r="C15" s="64">
         <f>SUM(C7:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="57" t="inlineStr"/>
-      <c r="E15" s="55" t="inlineStr">
+      <c r="D15" s="65" t="inlineStr"/>
+      <c r="E15" s="63" t="inlineStr">
         <is>
           <t>الدرجة:</t>
         </is>
       </c>
-      <c r="F15" s="58">
+      <c r="F15" s="66">
         <f>SUM(F7:F14)</f>
         <v/>
       </c>
-      <c r="G15" s="57" t="inlineStr"/>
+      <c r="G15" s="65" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="5" t="inlineStr">
@@ -5628,11 +7050,11 @@
           <t>التقدير</t>
         </is>
       </c>
-      <c r="C16" s="59">
+      <c r="C16" s="67">
         <f>IF(F15&gt;=0.9,"ممتاز",IF(F15&gt;=0.8,"جيد جداً",IF(F15&gt;=0.7,"جيد",IF(F15&gt;=0.6,"مقبول","ضعيف"))))</f>
         <v/>
       </c>
-      <c r="D16" s="22" t="n"/>
+      <c r="D16" s="29" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
@@ -5640,89 +7062,89 @@
           <t>سلّم التقييم</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n"/>
-      <c r="D18" s="22" t="n"/>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="29" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>ممتاز</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="55" t="inlineStr">
         <is>
           <t>90% – 100%</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>تجاوز المستهدف</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>جيد جداً</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="55" t="inlineStr">
         <is>
           <t>80% – 89%</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>حقق المستهدف تقريباً</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>جيد</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="55" t="inlineStr">
         <is>
           <t>70% – 79%</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>حقق معظم المستهدفات</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>مقبول</t>
         </is>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C22" s="55" t="inlineStr">
         <is>
           <t>60% – 69%</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>يحتاج تحسين</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>ضعيف</t>
         </is>
       </c>
-      <c r="C23" s="47" t="inlineStr">
+      <c r="C23" s="55" t="inlineStr">
         <is>
           <t>أقل من 60%</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>يحتاج خطة تطوير</t>
         </is>
@@ -5760,431 +7182,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
-        <is>
-          <t>إدارة الامتياز التجاري · نموذج تقييم الأداء — مسؤول الامتياز التجاري</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="30" t="inlineStr">
-        <is>
-          <t>الكود: FM-02   ·   فترة القياس: ربع سنوي   ·   🟩 أدخل «نسبة التحقيق» فقط — الدرجة تُحسب تلقائياً</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="49" t="inlineStr">
-        <is>
-          <t>اسم الموظف:</t>
-        </is>
-      </c>
-      <c r="B3" s="50" t="inlineStr"/>
-      <c r="C3" s="51" t="n"/>
-      <c r="D3" s="49" t="inlineStr">
-        <is>
-          <t>القسم: الامتياز التجاري</t>
-        </is>
-      </c>
-      <c r="E3" s="50" t="inlineStr"/>
-      <c r="F3" s="52" t="n"/>
-      <c r="G3" s="51" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="49" t="inlineStr">
-        <is>
-          <t>المدير المباشر:</t>
-        </is>
-      </c>
-      <c r="B4" s="50" t="inlineStr"/>
-      <c r="C4" s="51" t="n"/>
-      <c r="D4" s="49" t="inlineStr">
-        <is>
-          <t>الربع / السنة:</t>
-        </is>
-      </c>
-      <c r="E4" s="50" t="inlineStr"/>
-      <c r="F4" s="52" t="n"/>
-      <c r="G4" s="51" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="49" t="inlineStr">
-        <is>
-          <t>تاريخ التقييم:</t>
-        </is>
-      </c>
-      <c r="B5" s="50" t="inlineStr"/>
-      <c r="C5" s="51" t="n"/>
-      <c r="D5" s="49" t="inlineStr">
-        <is>
-          <t>حالة التقييم:</t>
-        </is>
-      </c>
-      <c r="E5" s="50" t="inlineStr"/>
-      <c r="F5" s="52" t="n"/>
-      <c r="G5" s="51" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr">
-        <is>
-          <t>مؤشر الأداء</t>
-        </is>
-      </c>
-      <c r="C6" s="31" t="inlineStr">
-        <is>
-          <t>الوزن %</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>المستهدف</t>
-        </is>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t>نسبة التحقيق</t>
-        </is>
-      </c>
-      <c r="F6" s="31" t="inlineStr">
-        <is>
-          <t>الدرجة المحققة</t>
-        </is>
-      </c>
-      <c r="G6" s="31" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>المتابعة مع عملاء الامتياز</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D7" s="53" t="inlineStr">
-        <is>
-          <t>متابعة مستمرة 100%</t>
-        </is>
-      </c>
-      <c r="E7" s="54" t="n"/>
-      <c r="F7" s="25">
-        <f>C7*MIN(E7,1)</f>
-        <v/>
-      </c>
-      <c r="G7" s="50" t="inlineStr"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>عدم انقطاع المحطات من الوقود</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D8" s="53" t="inlineStr">
-        <is>
-          <t>0 حالات انقطاع</t>
-        </is>
-      </c>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="25">
-        <f>C8*MIN(E8,1)</f>
-        <v/>
-      </c>
-      <c r="G8" s="50" t="inlineStr"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>متابعة طلبات وتوريد الوقود</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D9" s="53" t="inlineStr">
-        <is>
-          <t>100% متابعة يومية</t>
-        </is>
-      </c>
-      <c r="E9" s="54" t="n"/>
-      <c r="F9" s="25">
-        <f>C9*MIN(E9,1)</f>
-        <v/>
-      </c>
-      <c r="G9" s="50" t="inlineStr"/>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>إجمالي مبيعات المحطات</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>تحقيق هدف المبيعات</t>
-        </is>
-      </c>
-      <c r="E10" s="54" t="n"/>
-      <c r="F10" s="25">
-        <f>C10*MIN(E10,1)</f>
-        <v/>
-      </c>
-      <c r="G10" s="50" t="inlineStr"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>التحصيل المالي</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D11" s="53" t="inlineStr">
-        <is>
-          <t>100% خلال الربع</t>
-        </is>
-      </c>
-      <c r="E11" s="54" t="n"/>
-      <c r="F11" s="25">
-        <f>C11*MIN(E11,1)</f>
-        <v/>
-      </c>
-      <c r="G11" s="50" t="inlineStr"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>التقارير الدورية الشاملة</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D12" s="53" t="inlineStr">
-        <is>
-          <t>100% في مواعيدها</t>
-        </is>
-      </c>
-      <c r="E12" s="54" t="n"/>
-      <c r="F12" s="25">
-        <f>C12*MIN(E12,1)</f>
-        <v/>
-      </c>
-      <c r="G12" s="50" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr"/>
-      <c r="B13" s="55" t="inlineStr">
-        <is>
-          <t>المجموع الكلي</t>
-        </is>
-      </c>
-      <c r="C13" s="56">
-        <f>SUM(C7:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="57" t="inlineStr"/>
-      <c r="E13" s="55" t="inlineStr">
-        <is>
-          <t>الدرجة:</t>
-        </is>
-      </c>
-      <c r="F13" s="58">
-        <f>SUM(F7:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="57" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>التقدير</t>
-        </is>
-      </c>
-      <c r="C14" s="59">
-        <f>IF(F13&gt;=0.9,"ممتاز",IF(F13&gt;=0.8,"جيد جداً",IF(F13&gt;=0.7,"جيد",IF(F13&gt;=0.6,"مقبول","ضعيف"))))</f>
-        <v/>
-      </c>
-      <c r="D14" s="22" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>سلّم التقييم</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="n"/>
-      <c r="D16" s="22" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>ممتاز</t>
-        </is>
-      </c>
-      <c r="C17" s="47" t="inlineStr">
-        <is>
-          <t>90% – 100%</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>تجاوز المستهدف</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>جيد جداً</t>
-        </is>
-      </c>
-      <c r="C18" s="47" t="inlineStr">
-        <is>
-          <t>80% – 89%</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>حقق المستهدف تقريباً</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>جيد</t>
-        </is>
-      </c>
-      <c r="C19" s="47" t="inlineStr">
-        <is>
-          <t>70% – 79%</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>حقق معظم المستهدفات</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>مقبول</t>
-        </is>
-      </c>
-      <c r="C20" s="47" t="inlineStr">
-        <is>
-          <t>60% – 69%</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>يحتاج تحسين</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>ضعيف</t>
-        </is>
-      </c>
-      <c r="C21" s="47" t="inlineStr">
-        <is>
-          <t>أقل من 60%</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>يحتاج خطة تطوير</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
-  <mergeCells count="18">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D18"/>
-    <mergeCell ref="A4"/>
-    <mergeCell ref="D17"/>
-    <mergeCell ref="A3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="D20"/>
-    <mergeCell ref="D21"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="D19"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A5"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="نسبة التحقيق" error="أدخل نسبة بين 0% و120%" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1.2</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6204,273 +7201,273 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
-        <is>
-          <t>إدارة الامتياز التجاري · نموذج تقييم الأداء — المراقب الميداني</t>
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>إدارة الامتياز التجاري · نموذج تقييم الأداء — مسؤول الامتياز التجاري</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
-        <is>
-          <t>الكود: FM-03   ·   فترة القياس: ربع سنوي   ·   🟩 أدخل «نسبة التحقيق» فقط — الدرجة تُحسب تلقائياً</t>
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>الكود: FM-02   ·   فترة القياس: ربع سنوي   ·   🟩 أدخل «نسبة التحقيق» فقط — الدرجة تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="57" t="inlineStr">
         <is>
           <t>اسم الموظف:</t>
         </is>
       </c>
-      <c r="B3" s="50" t="inlineStr"/>
-      <c r="C3" s="51" t="n"/>
-      <c r="D3" s="49" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr"/>
+      <c r="C3" s="59" t="n"/>
+      <c r="D3" s="57" t="inlineStr">
         <is>
           <t>القسم: الامتياز التجاري</t>
         </is>
       </c>
-      <c r="E3" s="50" t="inlineStr"/>
-      <c r="F3" s="52" t="n"/>
-      <c r="G3" s="51" t="n"/>
+      <c r="E3" s="58" t="inlineStr"/>
+      <c r="F3" s="60" t="n"/>
+      <c r="G3" s="59" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="57" t="inlineStr">
         <is>
           <t>المدير المباشر:</t>
         </is>
       </c>
-      <c r="B4" s="50" t="inlineStr"/>
-      <c r="C4" s="51" t="n"/>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="57" t="inlineStr">
         <is>
           <t>الربع / السنة:</t>
         </is>
       </c>
-      <c r="E4" s="50" t="inlineStr"/>
-      <c r="F4" s="52" t="n"/>
-      <c r="G4" s="51" t="n"/>
+      <c r="E4" s="58" t="inlineStr"/>
+      <c r="F4" s="60" t="n"/>
+      <c r="G4" s="59" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>تاريخ التقييم:</t>
         </is>
       </c>
-      <c r="B5" s="50" t="inlineStr"/>
-      <c r="C5" s="51" t="n"/>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr"/>
+      <c r="C5" s="59" t="n"/>
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>حالة التقييم:</t>
         </is>
       </c>
-      <c r="E5" s="50" t="inlineStr"/>
-      <c r="F5" s="52" t="n"/>
-      <c r="G5" s="51" t="n"/>
+      <c r="E5" s="58" t="inlineStr"/>
+      <c r="F5" s="60" t="n"/>
+      <c r="G5" s="59" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>مؤشر الأداء</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>الوزن %</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>المستهدف</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>نسبة التحقيق</t>
         </is>
       </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>الدرجة المحققة</t>
         </is>
       </c>
-      <c r="G6" s="31" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>عدد الزيارات الميدانية المنفذة</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="n">
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>المتابعة مع عملاء الامتياز</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="n">
         <v>0.3</v>
       </c>
-      <c r="D7" s="53" t="inlineStr">
-        <is>
-          <t>100% من الزيارات المجدولة</t>
-        </is>
-      </c>
-      <c r="E7" s="54" t="n"/>
-      <c r="F7" s="25">
+      <c r="D7" s="61" t="inlineStr">
+        <is>
+          <t>متابعة مستمرة 100%</t>
+        </is>
+      </c>
+      <c r="E7" s="62" t="n"/>
+      <c r="F7" s="36">
         <f>C7*MIN(E7,1)</f>
         <v/>
       </c>
-      <c r="G7" s="50" t="inlineStr"/>
+      <c r="G7" s="58" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>متابعة تطبيق الهوية المؤسسية</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D8" s="53" t="inlineStr">
-        <is>
-          <t>100% دون ملاحظات متكررة</t>
-        </is>
-      </c>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="25">
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>عدم انقطاع المحطات من الوقود</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D8" s="61" t="inlineStr">
+        <is>
+          <t>0 حالات انقطاع</t>
+        </is>
+      </c>
+      <c r="E8" s="62" t="n"/>
+      <c r="F8" s="36">
         <f>C8*MIN(E8,1)</f>
         <v/>
       </c>
-      <c r="G8" s="50" t="inlineStr"/>
+      <c r="G8" s="58" t="inlineStr"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>تقارير الجودة الميدانية والـChecklist</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D9" s="53" t="inlineStr">
-        <is>
-          <t>100% رفع التقارير</t>
-        </is>
-      </c>
-      <c r="E9" s="54" t="n"/>
-      <c r="F9" s="25">
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>متابعة طلبات وتوريد الوقود</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" s="61" t="inlineStr">
+        <is>
+          <t>100% متابعة يومية</t>
+        </is>
+      </c>
+      <c r="E9" s="62" t="n"/>
+      <c r="F9" s="36">
         <f>C9*MIN(E9,1)</f>
         <v/>
       </c>
-      <c r="G9" s="50" t="inlineStr"/>
+      <c r="G9" s="58" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>متابعة العلامات التجارية</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="n">
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>إجمالي مبيعات المحطات</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="n">
         <v>0.1</v>
       </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>100% حسب الجدول</t>
-        </is>
-      </c>
-      <c r="E10" s="54" t="n"/>
-      <c r="F10" s="25">
+      <c r="D10" s="61" t="inlineStr">
+        <is>
+          <t>تحقيق هدف المبيعات</t>
+        </is>
+      </c>
+      <c r="E10" s="62" t="n"/>
+      <c r="F10" s="36">
         <f>C10*MIN(E10,1)</f>
         <v/>
       </c>
-      <c r="G10" s="50" t="inlineStr"/>
+      <c r="G10" s="58" t="inlineStr"/>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>تطبيق معايير السلامة الميدانية</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="n">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>التحصيل المالي</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="n">
         <v>0.1</v>
       </c>
-      <c r="D11" s="53" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E11" s="54" t="n"/>
-      <c r="F11" s="25">
+      <c r="D11" s="61" t="inlineStr">
+        <is>
+          <t>100% خلال الربع</t>
+        </is>
+      </c>
+      <c r="E11" s="62" t="n"/>
+      <c r="F11" s="36">
         <f>C11*MIN(E11,1)</f>
         <v/>
       </c>
-      <c r="G11" s="50" t="inlineStr"/>
+      <c r="G11" s="58" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="26" t="n">
+      <c r="A12" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>متابعة الشكاوى وإغلاقها</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D12" s="53" t="inlineStr">
-        <is>
-          <t>الاستجابة خلال 24 ساعة</t>
-        </is>
-      </c>
-      <c r="E12" s="54" t="n"/>
-      <c r="F12" s="25">
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>التقارير الدورية الشاملة</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" s="61" t="inlineStr">
+        <is>
+          <t>100% في مواعيدها</t>
+        </is>
+      </c>
+      <c r="E12" s="62" t="n"/>
+      <c r="F12" s="36">
         <f>C12*MIN(E12,1)</f>
         <v/>
       </c>
-      <c r="G12" s="50" t="inlineStr"/>
+      <c r="G12" s="58" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr"/>
-      <c r="B13" s="55" t="inlineStr">
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>المجموع الكلي</t>
         </is>
       </c>
-      <c r="C13" s="56">
+      <c r="C13" s="64">
         <f>SUM(C7:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="57" t="inlineStr"/>
-      <c r="E13" s="55" t="inlineStr">
+      <c r="D13" s="65" t="inlineStr"/>
+      <c r="E13" s="63" t="inlineStr">
         <is>
           <t>الدرجة:</t>
         </is>
       </c>
-      <c r="F13" s="58">
+      <c r="F13" s="66">
         <f>SUM(F7:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="57" t="inlineStr"/>
+      <c r="G13" s="65" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="5" t="inlineStr">
@@ -6478,11 +7475,11 @@
           <t>التقدير</t>
         </is>
       </c>
-      <c r="C14" s="59">
+      <c r="C14" s="67">
         <f>IF(F13&gt;=0.9,"ممتاز",IF(F13&gt;=0.8,"جيد جداً",IF(F13&gt;=0.7,"جيد",IF(F13&gt;=0.6,"مقبول","ضعيف"))))</f>
         <v/>
       </c>
-      <c r="D14" s="22" t="n"/>
+      <c r="D14" s="29" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="5" t="inlineStr">
@@ -6490,89 +7487,89 @@
           <t>سلّم التقييم</t>
         </is>
       </c>
-      <c r="C16" s="21" t="n"/>
-      <c r="D16" s="22" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="29" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>ممتاز</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="55" t="inlineStr">
         <is>
           <t>90% – 100%</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>تجاوز المستهدف</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>جيد جداً</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" s="55" t="inlineStr">
         <is>
           <t>80% – 89%</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>حقق المستهدف تقريباً</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>جيد</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="55" t="inlineStr">
         <is>
           <t>70% – 79%</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>حقق معظم المستهدفات</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>مقبول</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="55" t="inlineStr">
         <is>
           <t>60% – 69%</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>يحتاج تحسين</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>ضعيف</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="55" t="inlineStr">
         <is>
           <t>أقل من 60%</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>يحتاج خطة تطوير</t>
         </is>
@@ -6616,7 +7613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6629,399 +7626,375 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
-        <is>
-          <t>إدارة الامتياز التجاري · نموذج تقييم الأداء — مسؤول التعاقدات</t>
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>إدارة الامتياز التجاري · نموذج تقييم الأداء — المراقب الميداني</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
-        <is>
-          <t>الكود: FM-04   ·   فترة القياس: ربع سنوي   ·   🟩 أدخل «نسبة التحقيق» فقط — الدرجة تُحسب تلقائياً</t>
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>الكود: FM-03   ·   فترة القياس: ربع سنوي   ·   🟩 أدخل «نسبة التحقيق» فقط — الدرجة تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="57" t="inlineStr">
         <is>
           <t>اسم الموظف:</t>
         </is>
       </c>
-      <c r="B3" s="50" t="inlineStr"/>
-      <c r="C3" s="51" t="n"/>
-      <c r="D3" s="49" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr"/>
+      <c r="C3" s="59" t="n"/>
+      <c r="D3" s="57" t="inlineStr">
         <is>
           <t>القسم: الامتياز التجاري</t>
         </is>
       </c>
-      <c r="E3" s="50" t="inlineStr"/>
-      <c r="F3" s="52" t="n"/>
-      <c r="G3" s="51" t="n"/>
+      <c r="E3" s="58" t="inlineStr"/>
+      <c r="F3" s="60" t="n"/>
+      <c r="G3" s="59" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="57" t="inlineStr">
         <is>
           <t>المدير المباشر:</t>
         </is>
       </c>
-      <c r="B4" s="50" t="inlineStr"/>
-      <c r="C4" s="51" t="n"/>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="57" t="inlineStr">
         <is>
           <t>الربع / السنة:</t>
         </is>
       </c>
-      <c r="E4" s="50" t="inlineStr"/>
-      <c r="F4" s="52" t="n"/>
-      <c r="G4" s="51" t="n"/>
+      <c r="E4" s="58" t="inlineStr"/>
+      <c r="F4" s="60" t="n"/>
+      <c r="G4" s="59" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>تاريخ التقييم:</t>
         </is>
       </c>
-      <c r="B5" s="50" t="inlineStr"/>
-      <c r="C5" s="51" t="n"/>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr"/>
+      <c r="C5" s="59" t="n"/>
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>حالة التقييم:</t>
         </is>
       </c>
-      <c r="E5" s="50" t="inlineStr"/>
-      <c r="F5" s="52" t="n"/>
-      <c r="G5" s="51" t="n"/>
+      <c r="E5" s="58" t="inlineStr"/>
+      <c r="F5" s="60" t="n"/>
+      <c r="G5" s="59" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>مؤشر الأداء</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>الوزن %</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>المستهدف</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>نسبة التحقيق</t>
         </is>
       </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>الدرجة المحققة</t>
         </is>
       </c>
-      <c r="G6" s="31" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>جودة التفاوض مع العملاء</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="n">
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>عدد الزيارات الميدانية المنفذة</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D7" s="61" t="inlineStr">
+        <is>
+          <t>100% من الزيارات المجدولة</t>
+        </is>
+      </c>
+      <c r="E7" s="62" t="n"/>
+      <c r="F7" s="36">
+        <f>C7*MIN(E7,1)</f>
+        <v/>
+      </c>
+      <c r="G7" s="58" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>متابعة تطبيق الهوية المؤسسية</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="n">
         <v>0.2</v>
       </c>
-      <c r="D7" s="53" t="inlineStr">
-        <is>
-          <t>98% توافق مع المستهدفات</t>
-        </is>
-      </c>
-      <c r="E7" s="54" t="n"/>
-      <c r="F7" s="25">
-        <f>C7*MIN(E7,1)</f>
-        <v/>
-      </c>
-      <c r="G7" s="50" t="inlineStr"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>اكتمال المستندات النظامية قبل التوقيع</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D8" s="53" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
+        <is>
+          <t>100% دون ملاحظات متكررة</t>
+        </is>
+      </c>
+      <c r="E8" s="62" t="n"/>
+      <c r="F8" s="36">
+        <f>C8*MIN(E8,1)</f>
+        <v/>
+      </c>
+      <c r="G8" s="58" t="inlineStr"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>تقارير الجودة الميدانية والـChecklist</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D9" s="61" t="inlineStr">
+        <is>
+          <t>100% رفع التقارير</t>
+        </is>
+      </c>
+      <c r="E9" s="62" t="n"/>
+      <c r="F9" s="36">
+        <f>C9*MIN(E9,1)</f>
+        <v/>
+      </c>
+      <c r="G9" s="58" t="inlineStr"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>متابعة العلامات التجارية</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="61" t="inlineStr">
+        <is>
+          <t>100% حسب الجدول</t>
+        </is>
+      </c>
+      <c r="E10" s="62" t="n"/>
+      <c r="F10" s="36">
+        <f>C10*MIN(E10,1)</f>
+        <v/>
+      </c>
+      <c r="G10" s="58" t="inlineStr"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>تطبيق معايير السلامة الميدانية</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="25">
-        <f>C8*MIN(E8,1)</f>
-        <v/>
-      </c>
-      <c r="G8" s="50" t="inlineStr"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>سرعة إنجاز إجراءات العقد</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D9" s="53" t="inlineStr">
-        <is>
-          <t>خلال يومي عمل 100%</t>
-        </is>
-      </c>
-      <c r="E9" s="54" t="n"/>
-      <c r="F9" s="25">
-        <f>C9*MIN(E9,1)</f>
-        <v/>
-      </c>
-      <c r="G9" s="50" t="inlineStr"/>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>أرشفة العقود الإلكترونية</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="n">
+      <c r="E11" s="62" t="n"/>
+      <c r="F11" s="36">
+        <f>C11*MIN(E11,1)</f>
+        <v/>
+      </c>
+      <c r="G11" s="58" t="inlineStr"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>متابعة الشكاوى وإغلاقها</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="n">
         <v>0.1</v>
       </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>خلال 48 ساعة 100%</t>
-        </is>
-      </c>
-      <c r="E10" s="54" t="n"/>
-      <c r="F10" s="25">
-        <f>C10*MIN(E10,1)</f>
-        <v/>
-      </c>
-      <c r="G10" s="50" t="inlineStr"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>متابعة تنفيذ بنود العقد</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D11" s="53" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E11" s="54" t="n"/>
-      <c r="F11" s="25">
-        <f>C11*MIN(E11,1)</f>
-        <v/>
-      </c>
-      <c r="G11" s="50" t="inlineStr"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>مدى رضا العملاء</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D12" s="53" t="inlineStr">
-        <is>
-          <t>95% رضا</t>
-        </is>
-      </c>
-      <c r="E12" s="54" t="n"/>
-      <c r="F12" s="25">
+      <c r="D12" s="61" t="inlineStr">
+        <is>
+          <t>الاستجابة خلال 24 ساعة</t>
+        </is>
+      </c>
+      <c r="E12" s="62" t="n"/>
+      <c r="F12" s="36">
         <f>C12*MIN(E12,1)</f>
         <v/>
       </c>
-      <c r="G12" s="50" t="inlineStr"/>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>تحديث قاعدة بيانات العملاء</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D13" s="53" t="inlineStr">
-        <is>
-          <t>100% دوري</t>
-        </is>
-      </c>
-      <c r="E13" s="54" t="n"/>
-      <c r="F13" s="25">
-        <f>C13*MIN(E13,1)</f>
-        <v/>
-      </c>
-      <c r="G13" s="50" t="inlineStr"/>
+      <c r="G12" s="58" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr"/>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>المجموع الكلي</t>
+        </is>
+      </c>
+      <c r="C13" s="64">
+        <f>SUM(C7:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="65" t="inlineStr"/>
+      <c r="E13" s="63" t="inlineStr">
+        <is>
+          <t>الدرجة:</t>
+        </is>
+      </c>
+      <c r="F13" s="66">
+        <f>SUM(F7:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="65" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr"/>
-      <c r="B14" s="55" t="inlineStr">
-        <is>
-          <t>المجموع الكلي</t>
-        </is>
-      </c>
-      <c r="C14" s="56">
-        <f>SUM(C7:C13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="57" t="inlineStr"/>
-      <c r="E14" s="55" t="inlineStr">
-        <is>
-          <t>الدرجة:</t>
-        </is>
-      </c>
-      <c r="F14" s="58">
-        <f>SUM(F7:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="57" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>التقدير</t>
         </is>
       </c>
-      <c r="C15" s="59">
-        <f>IF(F14&gt;=0.9,"ممتاز",IF(F14&gt;=0.8,"جيد جداً",IF(F14&gt;=0.7,"جيد",IF(F14&gt;=0.6,"مقبول","ضعيف"))))</f>
-        <v/>
-      </c>
-      <c r="D15" s="22" t="n"/>
+      <c r="C14" s="67">
+        <f>IF(F13&gt;=0.9,"ممتاز",IF(F13&gt;=0.8,"جيد جداً",IF(F13&gt;=0.7,"جيد",IF(F13&gt;=0.6,"مقبول","ضعيف"))))</f>
+        <v/>
+      </c>
+      <c r="D14" s="29" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>سلّم التقييم</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="29" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>سلّم التقييم</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="22" t="n"/>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>ممتاز</t>
+        </is>
+      </c>
+      <c r="C17" s="55" t="inlineStr">
+        <is>
+          <t>90% – 100%</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>تجاوز المستهدف</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>ممتاز</t>
-        </is>
-      </c>
-      <c r="C18" s="47" t="inlineStr">
-        <is>
-          <t>90% – 100%</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>تجاوز المستهدف</t>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>جيد جداً</t>
+        </is>
+      </c>
+      <c r="C18" s="55" t="inlineStr">
+        <is>
+          <t>80% – 89%</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>حقق المستهدف تقريباً</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>جيد جداً</t>
-        </is>
-      </c>
-      <c r="C19" s="47" t="inlineStr">
-        <is>
-          <t>80% – 89%</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>حقق المستهدف تقريباً</t>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>جيد</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="inlineStr">
+        <is>
+          <t>70% – 79%</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>حقق معظم المستهدفات</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>جيد</t>
-        </is>
-      </c>
-      <c r="C20" s="47" t="inlineStr">
-        <is>
-          <t>70% – 79%</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>حقق معظم المستهدفات</t>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>مقبول</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>60% – 69%</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>يحتاج تحسين</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>مقبول</t>
-        </is>
-      </c>
-      <c r="C21" s="47" t="inlineStr">
-        <is>
-          <t>60% – 69%</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>يحتاج تحسين</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>ضعيف</t>
         </is>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C21" s="55" t="inlineStr">
         <is>
           <t>أقل من 60%</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>يحتاج خطة تطوير</t>
         </is>
@@ -7030,19 +8003,19 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
   <mergeCells count="18">
-    <mergeCell ref="D22"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="D18"/>
     <mergeCell ref="A4"/>
-    <mergeCell ref="D20"/>
+    <mergeCell ref="D17"/>
     <mergeCell ref="A3"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="E5:G5"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="D20"/>
     <mergeCell ref="D21"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="D19"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E4:G4"/>
     <mergeCell ref="E3:G3"/>
@@ -7050,7 +8023,7 @@
     <mergeCell ref="A5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="E7 E8 E9 E10 E11 E12 E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="نسبة التحقيق" error="أدخل نسبة بين 0% و120%" type="decimal" operator="between">
+    <dataValidation sqref="E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="نسبة التحقيق" error="أدخل نسبة بين 0% و120%" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1.2</formula2>
     </dataValidation>

--- a/درب-مؤشرات-الأداء-2026.xlsx
+++ b/درب-مؤشرات-الأداء-2026.xlsx
@@ -21997,7 +21997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH12"/>
+  <dimension ref="A1:AH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -22039,7 +22039,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="28" t="inlineStr">
         <is>
-          <t>إدارة التقنية الرقمية · مؤشرات الأداء 2026  (8 مؤشرات) — تانكي والتحول التقني</t>
+          <t>إدارة التقنية · مؤشرات الأداء 2026  (24 مؤشراً) — مشاريع التحول والكفاءة التشغيلية</t>
         </is>
       </c>
     </row>
@@ -22228,17 +22228,17 @@
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>منتج تانكي</t>
+          <t>مشاريع التحول</t>
         </is>
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>عدد مستخدمي تطبيق «تانكي» النشطين شهرياً (MAU)</t>
+          <t>نظام أتمتة الكاش (Cash-In) في المحطات</t>
         </is>
       </c>
       <c r="D4" s="60" t="inlineStr">
         <is>
-          <t>مستخدم</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E4" s="60" t="inlineStr">
@@ -22251,10 +22251,12 @@
           <t>LAST</t>
         </is>
       </c>
-      <c r="G4" s="60" t="inlineStr"/>
+      <c r="G4" s="61" t="n">
+        <v>164</v>
+      </c>
       <c r="H4" s="62" t="inlineStr">
         <is>
-          <t>يُحدد لاحقاً</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="I4" s="63" t="n"/>
@@ -22288,17 +22290,17 @@
       </c>
       <c r="Y4" s="22" t="inlineStr">
         <is>
-          <t>تطبيق «تانكي»</t>
+          <t>التحول التقني</t>
         </is>
       </c>
       <c r="Z4" s="66" t="n"/>
       <c r="AA4" s="21" t="inlineStr">
         <is>
-          <t>🔵 قائد</t>
+          <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB4" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0417</v>
       </c>
       <c r="AC4" s="23">
         <f>IF($V4="","",$AB4*MIN($V4,1))</f>
@@ -22332,17 +22334,17 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>منتج تانكي</t>
+          <t>مشاريع التحول</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>نمو تنزيلات تطبيق تانكي</t>
+          <t>D365 FNO — المرحلة الأولى</t>
         </is>
       </c>
       <c r="D5" s="60" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>وحدة</t>
         </is>
       </c>
       <c r="E5" s="60" t="inlineStr">
@@ -22352,28 +22354,30 @@
       </c>
       <c r="F5" s="60" t="inlineStr">
         <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="G5" s="60" t="inlineStr"/>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G5" s="75" t="n">
+        <v>5</v>
+      </c>
       <c r="H5" s="62" t="inlineStr">
         <is>
-          <t>يُحدد لاحقاً</t>
-        </is>
-      </c>
-      <c r="I5" s="73" t="n"/>
-      <c r="J5" s="73" t="n"/>
-      <c r="K5" s="73" t="n"/>
-      <c r="L5" s="73" t="n"/>
-      <c r="M5" s="73" t="n"/>
-      <c r="N5" s="73" t="n"/>
-      <c r="O5" s="73" t="n"/>
-      <c r="P5" s="73" t="n"/>
-      <c r="Q5" s="73" t="n"/>
-      <c r="R5" s="73" t="n"/>
-      <c r="S5" s="73" t="n"/>
-      <c r="T5" s="73" t="n"/>
-      <c r="U5" s="59">
+          <t>5 وحدات</t>
+        </is>
+      </c>
+      <c r="I5" s="76" t="n"/>
+      <c r="J5" s="76" t="n"/>
+      <c r="K5" s="76" t="n"/>
+      <c r="L5" s="76" t="n"/>
+      <c r="M5" s="76" t="n"/>
+      <c r="N5" s="76" t="n"/>
+      <c r="O5" s="76" t="n"/>
+      <c r="P5" s="76" t="n"/>
+      <c r="Q5" s="76" t="n"/>
+      <c r="R5" s="76" t="n"/>
+      <c r="S5" s="76" t="n"/>
+      <c r="T5" s="76" t="n"/>
+      <c r="U5" s="77">
         <f>IF($F5="SUM",IF(COUNT($I5:$T5)=0,"",SUM($I5:$T5)),IF($F5="AVG",IFERROR(AVERAGE($I5:$T5),""),IF($F5="LAST",IFERROR(LOOKUP(2,1/($I5:$T5&lt;&gt;""),$I5:$T5),""),"")))</f>
         <v/>
       </c>
@@ -22392,31 +22396,31 @@
       </c>
       <c r="Y5" s="22" t="inlineStr">
         <is>
-          <t>تطبيق «تانكي»</t>
-        </is>
-      </c>
-      <c r="Z5" s="53" t="n"/>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="Z5" s="78" t="n"/>
       <c r="AA5" s="21" t="inlineStr">
         <is>
-          <t>🔵 قائد</t>
+          <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB5" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0417</v>
       </c>
       <c r="AC5" s="23">
         <f>IF($V5="","",$AB5*MIN($V5,1))</f>
         <v/>
       </c>
-      <c r="AD5" s="74">
+      <c r="AD5" s="75">
         <f>IF($G5="","",IF($F5="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G5/12*'لوحة الإدارة التنفيذية'!$P$2),$G5))</f>
         <v/>
       </c>
-      <c r="AE5" s="23">
+      <c r="AE5" s="79">
         <f>IF($F5="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U5="","",$U5/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U5="","",$U5))</f>
         <v/>
       </c>
-      <c r="AF5" s="74">
+      <c r="AF5" s="75">
         <f>IF(OR($AE5="",$G5=""),"",$AE5-$G5)</f>
         <v/>
       </c>
@@ -22426,7 +22430,7 @@
       </c>
       <c r="AH5" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
     </row>
@@ -22436,17 +22440,17 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>منتج تانكي</t>
+          <t>مشاريع التحول</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>نسبة المعاملات الرقمية عبر تانكي</t>
+          <t>D365 FNO — المرحلة الثانية</t>
         </is>
       </c>
       <c r="D6" s="60" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>وحدة</t>
         </is>
       </c>
       <c r="E6" s="60" t="inlineStr">
@@ -22456,28 +22460,30 @@
       </c>
       <c r="F6" s="60" t="inlineStr">
         <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="G6" s="60" t="inlineStr"/>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G6" s="61" t="n">
+        <v>4</v>
+      </c>
       <c r="H6" s="62" t="inlineStr">
         <is>
-          <t>يُحدد لاحقاً</t>
-        </is>
-      </c>
-      <c r="I6" s="73" t="n"/>
-      <c r="J6" s="73" t="n"/>
-      <c r="K6" s="73" t="n"/>
-      <c r="L6" s="73" t="n"/>
-      <c r="M6" s="73" t="n"/>
-      <c r="N6" s="73" t="n"/>
-      <c r="O6" s="73" t="n"/>
-      <c r="P6" s="73" t="n"/>
-      <c r="Q6" s="73" t="n"/>
-      <c r="R6" s="73" t="n"/>
-      <c r="S6" s="73" t="n"/>
-      <c r="T6" s="73" t="n"/>
-      <c r="U6" s="59">
+          <t>4 وحدات</t>
+        </is>
+      </c>
+      <c r="I6" s="63" t="n"/>
+      <c r="J6" s="63" t="n"/>
+      <c r="K6" s="63" t="n"/>
+      <c r="L6" s="63" t="n"/>
+      <c r="M6" s="63" t="n"/>
+      <c r="N6" s="63" t="n"/>
+      <c r="O6" s="63" t="n"/>
+      <c r="P6" s="63" t="n"/>
+      <c r="Q6" s="63" t="n"/>
+      <c r="R6" s="63" t="n"/>
+      <c r="S6" s="63" t="n"/>
+      <c r="T6" s="63" t="n"/>
+      <c r="U6" s="64">
         <f>IF($F6="SUM",IF(COUNT($I6:$T6)=0,"",SUM($I6:$T6)),IF($F6="AVG",IFERROR(AVERAGE($I6:$T6),""),IF($F6="LAST",IFERROR(LOOKUP(2,1/($I6:$T6&lt;&gt;""),$I6:$T6),""),"")))</f>
         <v/>
       </c>
@@ -22496,31 +22502,31 @@
       </c>
       <c r="Y6" s="22" t="inlineStr">
         <is>
-          <t>تطبيق «تانكي»</t>
-        </is>
-      </c>
-      <c r="Z6" s="53" t="n"/>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="Z6" s="66" t="n"/>
       <c r="AA6" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB6" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0417</v>
       </c>
       <c r="AC6" s="23">
         <f>IF($V6="","",$AB6*MIN($V6,1))</f>
         <v/>
       </c>
-      <c r="AD6" s="74">
+      <c r="AD6" s="61">
         <f>IF($G6="","",IF($F6="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G6/12*'لوحة الإدارة التنفيذية'!$P$2),$G6))</f>
         <v/>
       </c>
-      <c r="AE6" s="23">
+      <c r="AE6" s="67">
         <f>IF($F6="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U6="","",$U6/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U6="","",$U6))</f>
         <v/>
       </c>
-      <c r="AF6" s="74">
+      <c r="AF6" s="61">
         <f>IF(OR($AE6="",$G6=""),"",$AE6-$G6)</f>
         <v/>
       </c>
@@ -22530,7 +22536,7 @@
       </c>
       <c r="AH6" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
     </row>
@@ -22540,17 +22546,17 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>منتج تانكي</t>
+          <t>مشاريع التحول</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>معدل رضا مستخدمي تطبيق تانكي</t>
+          <t>D365 FNO — المرحلة الثالثة</t>
         </is>
       </c>
       <c r="D7" s="60" t="inlineStr">
         <is>
-          <t>نجمة/5</t>
+          <t>وحدة</t>
         </is>
       </c>
       <c r="E7" s="60" t="inlineStr">
@@ -22560,30 +22566,30 @@
       </c>
       <c r="F7" s="60" t="inlineStr">
         <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="G7" s="75" t="n">
-        <v>4.5</v>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G7" s="61" t="n">
+        <v>2</v>
       </c>
       <c r="H7" s="62" t="inlineStr">
         <is>
-          <t>≥ 4.5</t>
-        </is>
-      </c>
-      <c r="I7" s="76" t="n"/>
-      <c r="J7" s="76" t="n"/>
-      <c r="K7" s="76" t="n"/>
-      <c r="L7" s="76" t="n"/>
-      <c r="M7" s="76" t="n"/>
-      <c r="N7" s="76" t="n"/>
-      <c r="O7" s="76" t="n"/>
-      <c r="P7" s="76" t="n"/>
-      <c r="Q7" s="76" t="n"/>
-      <c r="R7" s="76" t="n"/>
-      <c r="S7" s="76" t="n"/>
-      <c r="T7" s="76" t="n"/>
-      <c r="U7" s="77">
+          <t>وحدتان</t>
+        </is>
+      </c>
+      <c r="I7" s="63" t="n"/>
+      <c r="J7" s="63" t="n"/>
+      <c r="K7" s="63" t="n"/>
+      <c r="L7" s="63" t="n"/>
+      <c r="M7" s="63" t="n"/>
+      <c r="N7" s="63" t="n"/>
+      <c r="O7" s="63" t="n"/>
+      <c r="P7" s="63" t="n"/>
+      <c r="Q7" s="63" t="n"/>
+      <c r="R7" s="63" t="n"/>
+      <c r="S7" s="63" t="n"/>
+      <c r="T7" s="63" t="n"/>
+      <c r="U7" s="64">
         <f>IF($F7="SUM",IF(COUNT($I7:$T7)=0,"",SUM($I7:$T7)),IF($F7="AVG",IFERROR(AVERAGE($I7:$T7),""),IF($F7="LAST",IFERROR(LOOKUP(2,1/($I7:$T7&lt;&gt;""),$I7:$T7),""),"")))</f>
         <v/>
       </c>
@@ -22602,31 +22608,31 @@
       </c>
       <c r="Y7" s="22" t="inlineStr">
         <is>
-          <t>تطبيق «تانكي»</t>
-        </is>
-      </c>
-      <c r="Z7" s="78" t="n"/>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="Z7" s="66" t="n"/>
       <c r="AA7" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB7" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0417</v>
       </c>
       <c r="AC7" s="23">
         <f>IF($V7="","",$AB7*MIN($V7,1))</f>
         <v/>
       </c>
-      <c r="AD7" s="75">
+      <c r="AD7" s="61">
         <f>IF($G7="","",IF($F7="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G7/12*'لوحة الإدارة التنفيذية'!$P$2),$G7))</f>
         <v/>
       </c>
-      <c r="AE7" s="79">
+      <c r="AE7" s="67">
         <f>IF($F7="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U7="","",$U7/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U7="","",$U7))</f>
         <v/>
       </c>
-      <c r="AF7" s="75">
+      <c r="AF7" s="61">
         <f>IF(OR($AE7="",$G7=""),"",$AE7-$G7)</f>
         <v/>
       </c>
@@ -22636,7 +22642,7 @@
       </c>
       <c r="AH7" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
     </row>
@@ -22646,17 +22652,17 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>مشاريع التحول</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>نسبة أتمتة العمليات الأساسية (شركة)</t>
+          <t>تطبيق الامتياز مع واثق</t>
         </is>
       </c>
       <c r="D8" s="60" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>تطبيق</t>
         </is>
       </c>
       <c r="E8" s="60" t="inlineStr">
@@ -22669,25 +22675,27 @@
           <t>LAST</t>
         </is>
       </c>
-      <c r="G8" s="60" t="inlineStr"/>
+      <c r="G8" s="61" t="n">
+        <v>1</v>
+      </c>
       <c r="H8" s="62" t="inlineStr">
         <is>
-          <t>يُحدد لاحقاً</t>
-        </is>
-      </c>
-      <c r="I8" s="73" t="n"/>
-      <c r="J8" s="73" t="n"/>
-      <c r="K8" s="73" t="n"/>
-      <c r="L8" s="73" t="n"/>
-      <c r="M8" s="73" t="n"/>
-      <c r="N8" s="73" t="n"/>
-      <c r="O8" s="73" t="n"/>
-      <c r="P8" s="73" t="n"/>
-      <c r="Q8" s="73" t="n"/>
-      <c r="R8" s="73" t="n"/>
-      <c r="S8" s="73" t="n"/>
-      <c r="T8" s="73" t="n"/>
-      <c r="U8" s="59">
+          <t>تطبيق واحد</t>
+        </is>
+      </c>
+      <c r="I8" s="63" t="n"/>
+      <c r="J8" s="63" t="n"/>
+      <c r="K8" s="63" t="n"/>
+      <c r="L8" s="63" t="n"/>
+      <c r="M8" s="63" t="n"/>
+      <c r="N8" s="63" t="n"/>
+      <c r="O8" s="63" t="n"/>
+      <c r="P8" s="63" t="n"/>
+      <c r="Q8" s="63" t="n"/>
+      <c r="R8" s="63" t="n"/>
+      <c r="S8" s="63" t="n"/>
+      <c r="T8" s="63" t="n"/>
+      <c r="U8" s="64">
         <f>IF($F8="SUM",IF(COUNT($I8:$T8)=0,"",SUM($I8:$T8)),IF($F8="AVG",IFERROR(AVERAGE($I8:$T8),""),IF($F8="LAST",IFERROR(LOOKUP(2,1/($I8:$T8&lt;&gt;""),$I8:$T8),""),"")))</f>
         <v/>
       </c>
@@ -22709,28 +22717,28 @@
           <t>التحول التقني</t>
         </is>
       </c>
-      <c r="Z8" s="53" t="n"/>
+      <c r="Z8" s="66" t="n"/>
       <c r="AA8" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB8" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0417</v>
       </c>
       <c r="AC8" s="23">
         <f>IF($V8="","",$AB8*MIN($V8,1))</f>
         <v/>
       </c>
-      <c r="AD8" s="74">
+      <c r="AD8" s="61">
         <f>IF($G8="","",IF($F8="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G8/12*'لوحة الإدارة التنفيذية'!$P$2),$G8))</f>
         <v/>
       </c>
-      <c r="AE8" s="23">
+      <c r="AE8" s="67">
         <f>IF($F8="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U8="","",$U8/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U8="","",$U8))</f>
         <v/>
       </c>
-      <c r="AF8" s="74">
+      <c r="AF8" s="61">
         <f>IF(OR($AE8="",$G8=""),"",$AE8-$G8)</f>
         <v/>
       </c>
@@ -22740,7 +22748,7 @@
       </c>
       <c r="AH8" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
     </row>
@@ -22750,17 +22758,17 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>مشاريع التحول</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>نسبة جاهزية الأنظمة (Uptime)</t>
+          <t>ربط المحطات بوزارة الطاقة (ATJ)</t>
         </is>
       </c>
       <c r="D9" s="60" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E9" s="60" t="inlineStr">
@@ -22770,30 +22778,30 @@
       </c>
       <c r="F9" s="60" t="inlineStr">
         <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="G9" s="74" t="n">
-        <v>0.995</v>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G9" s="61" t="n">
+        <v>164</v>
       </c>
       <c r="H9" s="62" t="inlineStr">
         <is>
-          <t>≥ 99.5%</t>
-        </is>
-      </c>
-      <c r="I9" s="73" t="n"/>
-      <c r="J9" s="73" t="n"/>
-      <c r="K9" s="73" t="n"/>
-      <c r="L9" s="73" t="n"/>
-      <c r="M9" s="73" t="n"/>
-      <c r="N9" s="73" t="n"/>
-      <c r="O9" s="73" t="n"/>
-      <c r="P9" s="73" t="n"/>
-      <c r="Q9" s="73" t="n"/>
-      <c r="R9" s="73" t="n"/>
-      <c r="S9" s="73" t="n"/>
-      <c r="T9" s="73" t="n"/>
-      <c r="U9" s="59">
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I9" s="63" t="n"/>
+      <c r="J9" s="63" t="n"/>
+      <c r="K9" s="63" t="n"/>
+      <c r="L9" s="63" t="n"/>
+      <c r="M9" s="63" t="n"/>
+      <c r="N9" s="63" t="n"/>
+      <c r="O9" s="63" t="n"/>
+      <c r="P9" s="63" t="n"/>
+      <c r="Q9" s="63" t="n"/>
+      <c r="R9" s="63" t="n"/>
+      <c r="S9" s="63" t="n"/>
+      <c r="T9" s="63" t="n"/>
+      <c r="U9" s="64">
         <f>IF($F9="SUM",IF(COUNT($I9:$T9)=0,"",SUM($I9:$T9)),IF($F9="AVG",IFERROR(AVERAGE($I9:$T9),""),IF($F9="LAST",IFERROR(LOOKUP(2,1/($I9:$T9&lt;&gt;""),$I9:$T9),""),"")))</f>
         <v/>
       </c>
@@ -22815,28 +22823,28 @@
           <t>التحول التقني</t>
         </is>
       </c>
-      <c r="Z9" s="53" t="n"/>
+      <c r="Z9" s="66" t="n"/>
       <c r="AA9" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB9" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0417</v>
       </c>
       <c r="AC9" s="23">
         <f>IF($V9="","",$AB9*MIN($V9,1))</f>
         <v/>
       </c>
-      <c r="AD9" s="74">
+      <c r="AD9" s="61">
         <f>IF($G9="","",IF($F9="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G9/12*'لوحة الإدارة التنفيذية'!$P$2),$G9))</f>
         <v/>
       </c>
-      <c r="AE9" s="23">
+      <c r="AE9" s="67">
         <f>IF($F9="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U9="","",$U9/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U9="","",$U9))</f>
         <v/>
       </c>
-      <c r="AF9" s="74">
+      <c r="AF9" s="61">
         <f>IF(OR($AE9="",$G9=""),"",$AE9-$G9)</f>
         <v/>
       </c>
@@ -22856,50 +22864,50 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>مشاريع التحول</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>متوسط زمن حل أعطال الأنظمة</t>
+          <t>ربط الكاميرات بالمركز الرئيسي</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
         <is>
-          <t>ساعة</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E10" s="60" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="F10" s="60" t="inlineStr">
         <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="G10" s="75" t="n">
-        <v>4</v>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G10" s="61" t="n">
+        <v>164</v>
       </c>
       <c r="H10" s="62" t="inlineStr">
         <is>
-          <t>≤ 4 ساعات</t>
-        </is>
-      </c>
-      <c r="I10" s="76" t="n"/>
-      <c r="J10" s="76" t="n"/>
-      <c r="K10" s="76" t="n"/>
-      <c r="L10" s="76" t="n"/>
-      <c r="M10" s="76" t="n"/>
-      <c r="N10" s="76" t="n"/>
-      <c r="O10" s="76" t="n"/>
-      <c r="P10" s="76" t="n"/>
-      <c r="Q10" s="76" t="n"/>
-      <c r="R10" s="76" t="n"/>
-      <c r="S10" s="76" t="n"/>
-      <c r="T10" s="76" t="n"/>
-      <c r="U10" s="77">
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I10" s="63" t="n"/>
+      <c r="J10" s="63" t="n"/>
+      <c r="K10" s="63" t="n"/>
+      <c r="L10" s="63" t="n"/>
+      <c r="M10" s="63" t="n"/>
+      <c r="N10" s="63" t="n"/>
+      <c r="O10" s="63" t="n"/>
+      <c r="P10" s="63" t="n"/>
+      <c r="Q10" s="63" t="n"/>
+      <c r="R10" s="63" t="n"/>
+      <c r="S10" s="63" t="n"/>
+      <c r="T10" s="63" t="n"/>
+      <c r="U10" s="64">
         <f>IF($F10="SUM",IF(COUNT($I10:$T10)=0,"",SUM($I10:$T10)),IF($F10="AVG",IFERROR(AVERAGE($I10:$T10),""),IF($F10="LAST",IFERROR(LOOKUP(2,1/($I10:$T10&lt;&gt;""),$I10:$T10),""),"")))</f>
         <v/>
       </c>
@@ -22921,28 +22929,28 @@
           <t>التحول التقني</t>
         </is>
       </c>
-      <c r="Z10" s="78" t="n"/>
+      <c r="Z10" s="66" t="n"/>
       <c r="AA10" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB10" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0417</v>
       </c>
       <c r="AC10" s="23">
         <f>IF($V10="","",$AB10*MIN($V10,1))</f>
         <v/>
       </c>
-      <c r="AD10" s="75">
+      <c r="AD10" s="61">
         <f>IF($G10="","",IF($F10="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G10/12*'لوحة الإدارة التنفيذية'!$P$2),$G10))</f>
         <v/>
       </c>
-      <c r="AE10" s="79">
+      <c r="AE10" s="67">
         <f>IF($F10="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U10="","",$U10/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U10="","",$U10))</f>
         <v/>
       </c>
-      <c r="AF10" s="75">
+      <c r="AF10" s="61">
         <f>IF(OR($AE10="",$G10=""),"",$AE10-$G10)</f>
         <v/>
       </c>
@@ -22962,17 +22970,17 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>مشاريع التحول</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>نسبة المشاريع التقنية المنجزة في الوقت</t>
+          <t>تطبيق الولاء (تانكي) في المحطات</t>
         </is>
       </c>
       <c r="D11" s="60" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E11" s="60" t="inlineStr">
@@ -22982,30 +22990,30 @@
       </c>
       <c r="F11" s="60" t="inlineStr">
         <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="G11" s="74" t="n">
-        <v>0.9</v>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G11" s="61" t="n">
+        <v>164</v>
       </c>
       <c r="H11" s="62" t="inlineStr">
         <is>
-          <t>≥ 90%</t>
-        </is>
-      </c>
-      <c r="I11" s="73" t="n"/>
-      <c r="J11" s="73" t="n"/>
-      <c r="K11" s="73" t="n"/>
-      <c r="L11" s="73" t="n"/>
-      <c r="M11" s="73" t="n"/>
-      <c r="N11" s="73" t="n"/>
-      <c r="O11" s="73" t="n"/>
-      <c r="P11" s="73" t="n"/>
-      <c r="Q11" s="73" t="n"/>
-      <c r="R11" s="73" t="n"/>
-      <c r="S11" s="73" t="n"/>
-      <c r="T11" s="73" t="n"/>
-      <c r="U11" s="59">
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I11" s="63" t="n"/>
+      <c r="J11" s="63" t="n"/>
+      <c r="K11" s="63" t="n"/>
+      <c r="L11" s="63" t="n"/>
+      <c r="M11" s="63" t="n"/>
+      <c r="N11" s="63" t="n"/>
+      <c r="O11" s="63" t="n"/>
+      <c r="P11" s="63" t="n"/>
+      <c r="Q11" s="63" t="n"/>
+      <c r="R11" s="63" t="n"/>
+      <c r="S11" s="63" t="n"/>
+      <c r="T11" s="63" t="n"/>
+      <c r="U11" s="64">
         <f>IF($F11="SUM",IF(COUNT($I11:$T11)=0,"",SUM($I11:$T11)),IF($F11="AVG",IFERROR(AVERAGE($I11:$T11),""),IF($F11="LAST",IFERROR(LOOKUP(2,1/($I11:$T11&lt;&gt;""),$I11:$T11),""),"")))</f>
         <v/>
       </c>
@@ -23024,31 +23032,31 @@
       </c>
       <c r="Y11" s="22" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
-        </is>
-      </c>
-      <c r="Z11" s="53" t="n"/>
+          <t>تطبيق «تانكي»</t>
+        </is>
+      </c>
+      <c r="Z11" s="66" t="n"/>
       <c r="AA11" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB11" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0417</v>
       </c>
       <c r="AC11" s="23">
         <f>IF($V11="","",$AB11*MIN($V11,1))</f>
         <v/>
       </c>
-      <c r="AD11" s="74">
+      <c r="AD11" s="61">
         <f>IF($G11="","",IF($F11="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G11/12*'لوحة الإدارة التنفيذية'!$P$2),$G11))</f>
         <v/>
       </c>
-      <c r="AE11" s="23">
+      <c r="AE11" s="67">
         <f>IF($F11="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U11="","",$U11/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U11="","",$U11))</f>
         <v/>
       </c>
-      <c r="AF11" s="74">
+      <c r="AF11" s="61">
         <f>IF(OR($AE11="",$G11=""),"",$AE11-$G11)</f>
         <v/>
       </c>
@@ -23062,31 +23070,1727 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="80" t="inlineStr"/>
-      <c r="B12" s="81" t="inlineStr">
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>مشاريع التحول</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>منصة Tatin السحابية</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E12" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F12" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G12" s="61" t="n">
+        <v>164</v>
+      </c>
+      <c r="H12" s="62" t="inlineStr">
+        <is>
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I12" s="63" t="n"/>
+      <c r="J12" s="63" t="n"/>
+      <c r="K12" s="63" t="n"/>
+      <c r="L12" s="63" t="n"/>
+      <c r="M12" s="63" t="n"/>
+      <c r="N12" s="63" t="n"/>
+      <c r="O12" s="63" t="n"/>
+      <c r="P12" s="63" t="n"/>
+      <c r="Q12" s="63" t="n"/>
+      <c r="R12" s="63" t="n"/>
+      <c r="S12" s="63" t="n"/>
+      <c r="T12" s="63" t="n"/>
+      <c r="U12" s="64">
+        <f>IF($F12="SUM",IF(COUNT($I12:$T12)=0,"",SUM($I12:$T12)),IF($F12="AVG",IFERROR(AVERAGE($I12:$T12),""),IF($F12="LAST",IFERROR(LOOKUP(2,1/($I12:$T12&lt;&gt;""),$I12:$T12),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V12" s="23">
+        <f>IF($G12="","",IF($U12="","",IF($G12=0,IF($U12&lt;=0,1,0),IF($E12="↓",IFERROR($G12/$U12,0),IFERROR($U12/$G12,0)))))</f>
+        <v/>
+      </c>
+      <c r="W12" s="17">
+        <f>IF($V12="","—",IF($V12&gt;=1,"✅ محقق",IF($V12&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X12" s="65" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="Y12" s="22" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="Z12" s="66" t="n"/>
+      <c r="AA12" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB12" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC12" s="23">
+        <f>IF($V12="","",$AB12*MIN($V12,1))</f>
+        <v/>
+      </c>
+      <c r="AD12" s="61">
+        <f>IF($G12="","",IF($F12="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G12/12*'لوحة الإدارة التنفيذية'!$P$2),$G12))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="67">
+        <f>IF($F12="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U12="","",$U12/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U12="","",$U12))</f>
+        <v/>
+      </c>
+      <c r="AF12" s="61">
+        <f>IF(OR($AE12="",$G12=""),"",$AE12-$G12)</f>
+        <v/>
+      </c>
+      <c r="AG12" s="17">
+        <f>IF(OR($AE12="",$G12=""),"—",IF($E12="↓",IF($AE12&lt;=$G12,"🟢 على المسار",IF($AE12&lt;=$G12*1.1,"🟡 متابعة","🔴 خطر")),IF($AE12&gt;=$G12,"🟢 على المسار",IF($AE12&gt;=$G12*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH12" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>مشاريع التحول</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>إدارة العمليات بالذكاء الاصطناعي</t>
+        </is>
+      </c>
+      <c r="D13" s="60" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E13" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F13" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G13" s="61" t="n">
+        <v>164</v>
+      </c>
+      <c r="H13" s="62" t="inlineStr">
+        <is>
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I13" s="63" t="n"/>
+      <c r="J13" s="63" t="n"/>
+      <c r="K13" s="63" t="n"/>
+      <c r="L13" s="63" t="n"/>
+      <c r="M13" s="63" t="n"/>
+      <c r="N13" s="63" t="n"/>
+      <c r="O13" s="63" t="n"/>
+      <c r="P13" s="63" t="n"/>
+      <c r="Q13" s="63" t="n"/>
+      <c r="R13" s="63" t="n"/>
+      <c r="S13" s="63" t="n"/>
+      <c r="T13" s="63" t="n"/>
+      <c r="U13" s="64">
+        <f>IF($F13="SUM",IF(COUNT($I13:$T13)=0,"",SUM($I13:$T13)),IF($F13="AVG",IFERROR(AVERAGE($I13:$T13),""),IF($F13="LAST",IFERROR(LOOKUP(2,1/($I13:$T13&lt;&gt;""),$I13:$T13),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V13" s="23">
+        <f>IF($G13="","",IF($U13="","",IF($G13=0,IF($U13&lt;=0,1,0),IF($E13="↓",IFERROR($G13/$U13,0),IFERROR($U13/$G13,0)))))</f>
+        <v/>
+      </c>
+      <c r="W13" s="17">
+        <f>IF($V13="","—",IF($V13&gt;=1,"✅ محقق",IF($V13&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X13" s="65" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="Y13" s="22" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="Z13" s="66" t="n"/>
+      <c r="AA13" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB13" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC13" s="23">
+        <f>IF($V13="","",$AB13*MIN($V13,1))</f>
+        <v/>
+      </c>
+      <c r="AD13" s="61">
+        <f>IF($G13="","",IF($F13="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G13/12*'لوحة الإدارة التنفيذية'!$P$2),$G13))</f>
+        <v/>
+      </c>
+      <c r="AE13" s="67">
+        <f>IF($F13="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U13="","",$U13/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U13="","",$U13))</f>
+        <v/>
+      </c>
+      <c r="AF13" s="61">
+        <f>IF(OR($AE13="",$G13=""),"",$AE13-$G13)</f>
+        <v/>
+      </c>
+      <c r="AG13" s="17">
+        <f>IF(OR($AE13="",$G13=""),"—",IF($E13="↓",IF($AE13&lt;=$G13,"🟢 على المسار",IF($AE13&lt;=$G13*1.1,"🟡 متابعة","🔴 خطر")),IF($AE13&gt;=$G13,"🟢 على المسار",IF($AE13&gt;=$G13*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH13" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>الكفاءة التشغيلية</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>جاهزية أتمتة المحطات (Forecourt)</t>
+        </is>
+      </c>
+      <c r="D14" s="60" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E14" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F14" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G14" s="61" t="n">
+        <v>164</v>
+      </c>
+      <c r="H14" s="62" t="inlineStr">
+        <is>
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I14" s="63" t="n"/>
+      <c r="J14" s="63" t="n"/>
+      <c r="K14" s="63" t="n"/>
+      <c r="L14" s="63" t="n"/>
+      <c r="M14" s="63" t="n"/>
+      <c r="N14" s="63" t="n"/>
+      <c r="O14" s="63" t="n"/>
+      <c r="P14" s="63" t="n"/>
+      <c r="Q14" s="63" t="n"/>
+      <c r="R14" s="63" t="n"/>
+      <c r="S14" s="63" t="n"/>
+      <c r="T14" s="63" t="n"/>
+      <c r="U14" s="64">
+        <f>IF($F14="SUM",IF(COUNT($I14:$T14)=0,"",SUM($I14:$T14)),IF($F14="AVG",IFERROR(AVERAGE($I14:$T14),""),IF($F14="LAST",IFERROR(LOOKUP(2,1/($I14:$T14&lt;&gt;""),$I14:$T14),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V14" s="23">
+        <f>IF($G14="","",IF($U14="","",IF($G14=0,IF($U14&lt;=0,1,0),IF($E14="↓",IFERROR($G14/$U14,0),IFERROR($U14/$G14,0)))))</f>
+        <v/>
+      </c>
+      <c r="W14" s="17">
+        <f>IF($V14="","—",IF($V14&gt;=1,"✅ محقق",IF($V14&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X14" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y14" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z14" s="66" t="n"/>
+      <c r="AA14" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB14" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC14" s="23">
+        <f>IF($V14="","",$AB14*MIN($V14,1))</f>
+        <v/>
+      </c>
+      <c r="AD14" s="61">
+        <f>IF($G14="","",IF($F14="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G14/12*'لوحة الإدارة التنفيذية'!$P$2),$G14))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="67">
+        <f>IF($F14="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U14="","",$U14/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U14="","",$U14))</f>
+        <v/>
+      </c>
+      <c r="AF14" s="61">
+        <f>IF(OR($AE14="",$G14=""),"",$AE14-$G14)</f>
+        <v/>
+      </c>
+      <c r="AG14" s="17">
+        <f>IF(OR($AE14="",$G14=""),"—",IF($E14="↓",IF($AE14&lt;=$G14,"🟢 على المسار",IF($AE14&lt;=$G14*1.1,"🟡 متابعة","🔴 خطر")),IF($AE14&gt;=$G14,"🟢 على المسار",IF($AE14&gt;=$G14*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH14" s="68" t="inlineStr">
+        <is>
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>الكفاءة التشغيلية</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>جاهزية اتصال الشبكة بالمحطات</t>
+        </is>
+      </c>
+      <c r="D15" s="60" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E15" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F15" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G15" s="61" t="n">
+        <v>164</v>
+      </c>
+      <c r="H15" s="62" t="inlineStr">
+        <is>
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I15" s="63" t="n"/>
+      <c r="J15" s="63" t="n"/>
+      <c r="K15" s="63" t="n"/>
+      <c r="L15" s="63" t="n"/>
+      <c r="M15" s="63" t="n"/>
+      <c r="N15" s="63" t="n"/>
+      <c r="O15" s="63" t="n"/>
+      <c r="P15" s="63" t="n"/>
+      <c r="Q15" s="63" t="n"/>
+      <c r="R15" s="63" t="n"/>
+      <c r="S15" s="63" t="n"/>
+      <c r="T15" s="63" t="n"/>
+      <c r="U15" s="64">
+        <f>IF($F15="SUM",IF(COUNT($I15:$T15)=0,"",SUM($I15:$T15)),IF($F15="AVG",IFERROR(AVERAGE($I15:$T15),""),IF($F15="LAST",IFERROR(LOOKUP(2,1/($I15:$T15&lt;&gt;""),$I15:$T15),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V15" s="23">
+        <f>IF($G15="","",IF($U15="","",IF($G15=0,IF($U15&lt;=0,1,0),IF($E15="↓",IFERROR($G15/$U15,0),IFERROR($U15/$G15,0)))))</f>
+        <v/>
+      </c>
+      <c r="W15" s="17">
+        <f>IF($V15="","—",IF($V15&gt;=1,"✅ محقق",IF($V15&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X15" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y15" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z15" s="66" t="n"/>
+      <c r="AA15" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB15" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC15" s="23">
+        <f>IF($V15="","",$AB15*MIN($V15,1))</f>
+        <v/>
+      </c>
+      <c r="AD15" s="61">
+        <f>IF($G15="","",IF($F15="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G15/12*'لوحة الإدارة التنفيذية'!$P$2),$G15))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="67">
+        <f>IF($F15="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U15="","",$U15/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U15="","",$U15))</f>
+        <v/>
+      </c>
+      <c r="AF15" s="61">
+        <f>IF(OR($AE15="",$G15=""),"",$AE15-$G15)</f>
+        <v/>
+      </c>
+      <c r="AG15" s="17">
+        <f>IF(OR($AE15="",$G15=""),"—",IF($E15="↓",IF($AE15&lt;=$G15,"🟢 على المسار",IF($AE15&lt;=$G15*1.1,"🟡 متابعة","🔴 خطر")),IF($AE15&gt;=$G15,"🟢 على المسار",IF($AE15&gt;=$G15*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH15" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>الكفاءة التشغيلية</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>جاهزية نقاط البيع والمدفوعات (POS)</t>
+        </is>
+      </c>
+      <c r="D16" s="60" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E16" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F16" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G16" s="61" t="n">
+        <v>164</v>
+      </c>
+      <c r="H16" s="62" t="inlineStr">
+        <is>
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I16" s="63" t="n"/>
+      <c r="J16" s="63" t="n"/>
+      <c r="K16" s="63" t="n"/>
+      <c r="L16" s="63" t="n"/>
+      <c r="M16" s="63" t="n"/>
+      <c r="N16" s="63" t="n"/>
+      <c r="O16" s="63" t="n"/>
+      <c r="P16" s="63" t="n"/>
+      <c r="Q16" s="63" t="n"/>
+      <c r="R16" s="63" t="n"/>
+      <c r="S16" s="63" t="n"/>
+      <c r="T16" s="63" t="n"/>
+      <c r="U16" s="64">
+        <f>IF($F16="SUM",IF(COUNT($I16:$T16)=0,"",SUM($I16:$T16)),IF($F16="AVG",IFERROR(AVERAGE($I16:$T16),""),IF($F16="LAST",IFERROR(LOOKUP(2,1/($I16:$T16&lt;&gt;""),$I16:$T16),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V16" s="23">
+        <f>IF($G16="","",IF($U16="","",IF($G16=0,IF($U16&lt;=0,1,0),IF($E16="↓",IFERROR($G16/$U16,0),IFERROR($U16/$G16,0)))))</f>
+        <v/>
+      </c>
+      <c r="W16" s="17">
+        <f>IF($V16="","—",IF($V16&gt;=1,"✅ محقق",IF($V16&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X16" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y16" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z16" s="66" t="n"/>
+      <c r="AA16" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB16" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC16" s="23">
+        <f>IF($V16="","",$AB16*MIN($V16,1))</f>
+        <v/>
+      </c>
+      <c r="AD16" s="61">
+        <f>IF($G16="","",IF($F16="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G16/12*'لوحة الإدارة التنفيذية'!$P$2),$G16))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="67">
+        <f>IF($F16="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U16="","",$U16/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U16="","",$U16))</f>
+        <v/>
+      </c>
+      <c r="AF16" s="61">
+        <f>IF(OR($AE16="",$G16=""),"",$AE16-$G16)</f>
+        <v/>
+      </c>
+      <c r="AG16" s="17">
+        <f>IF(OR($AE16="",$G16=""),"—",IF($E16="↓",IF($AE16&lt;=$G16,"🟢 على المسار",IF($AE16&lt;=$G16*1.1,"🟡 متابعة","🔴 خطر")),IF($AE16&gt;=$G16,"🟢 على المسار",IF($AE16&gt;=$G16*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH16" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>الكفاءة التشغيلية</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>جاهزية نظام الكاميرات (CCTV)</t>
+        </is>
+      </c>
+      <c r="D17" s="60" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E17" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F17" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G17" s="61" t="n">
+        <v>164</v>
+      </c>
+      <c r="H17" s="62" t="inlineStr">
+        <is>
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I17" s="63" t="n"/>
+      <c r="J17" s="63" t="n"/>
+      <c r="K17" s="63" t="n"/>
+      <c r="L17" s="63" t="n"/>
+      <c r="M17" s="63" t="n"/>
+      <c r="N17" s="63" t="n"/>
+      <c r="O17" s="63" t="n"/>
+      <c r="P17" s="63" t="n"/>
+      <c r="Q17" s="63" t="n"/>
+      <c r="R17" s="63" t="n"/>
+      <c r="S17" s="63" t="n"/>
+      <c r="T17" s="63" t="n"/>
+      <c r="U17" s="64">
+        <f>IF($F17="SUM",IF(COUNT($I17:$T17)=0,"",SUM($I17:$T17)),IF($F17="AVG",IFERROR(AVERAGE($I17:$T17),""),IF($F17="LAST",IFERROR(LOOKUP(2,1/($I17:$T17&lt;&gt;""),$I17:$T17),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V17" s="23">
+        <f>IF($G17="","",IF($U17="","",IF($G17=0,IF($U17&lt;=0,1,0),IF($E17="↓",IFERROR($G17/$U17,0),IFERROR($U17/$G17,0)))))</f>
+        <v/>
+      </c>
+      <c r="W17" s="17">
+        <f>IF($V17="","—",IF($V17&gt;=1,"✅ محقق",IF($V17&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X17" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y17" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z17" s="66" t="n"/>
+      <c r="AA17" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB17" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC17" s="23">
+        <f>IF($V17="","",$AB17*MIN($V17,1))</f>
+        <v/>
+      </c>
+      <c r="AD17" s="61">
+        <f>IF($G17="","",IF($F17="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G17/12*'لوحة الإدارة التنفيذية'!$P$2),$G17))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="67">
+        <f>IF($F17="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U17="","",$U17/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U17="","",$U17))</f>
+        <v/>
+      </c>
+      <c r="AF17" s="61">
+        <f>IF(OR($AE17="",$G17=""),"",$AE17-$G17)</f>
+        <v/>
+      </c>
+      <c r="AG17" s="17">
+        <f>IF(OR($AE17="",$G17=""),"—",IF($E17="↓",IF($AE17&lt;=$G17,"🟢 على المسار",IF($AE17&lt;=$G17*1.1,"🟡 متابعة","🔴 خطر")),IF($AE17&gt;=$G17,"🟢 على المسار",IF($AE17&gt;=$G17*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH17" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>الكفاءة التشغيلية</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>جاهزية الشبكة</t>
+        </is>
+      </c>
+      <c r="D18" s="60" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E18" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F18" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G18" s="61" t="n">
+        <v>164</v>
+      </c>
+      <c r="H18" s="62" t="inlineStr">
+        <is>
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I18" s="63" t="n"/>
+      <c r="J18" s="63" t="n"/>
+      <c r="K18" s="63" t="n"/>
+      <c r="L18" s="63" t="n"/>
+      <c r="M18" s="63" t="n"/>
+      <c r="N18" s="63" t="n"/>
+      <c r="O18" s="63" t="n"/>
+      <c r="P18" s="63" t="n"/>
+      <c r="Q18" s="63" t="n"/>
+      <c r="R18" s="63" t="n"/>
+      <c r="S18" s="63" t="n"/>
+      <c r="T18" s="63" t="n"/>
+      <c r="U18" s="64">
+        <f>IF($F18="SUM",IF(COUNT($I18:$T18)=0,"",SUM($I18:$T18)),IF($F18="AVG",IFERROR(AVERAGE($I18:$T18),""),IF($F18="LAST",IFERROR(LOOKUP(2,1/($I18:$T18&lt;&gt;""),$I18:$T18),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V18" s="23">
+        <f>IF($G18="","",IF($U18="","",IF($G18=0,IF($U18&lt;=0,1,0),IF($E18="↓",IFERROR($G18/$U18,0),IFERROR($U18/$G18,0)))))</f>
+        <v/>
+      </c>
+      <c r="W18" s="17">
+        <f>IF($V18="","—",IF($V18&gt;=1,"✅ محقق",IF($V18&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X18" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y18" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z18" s="66" t="n"/>
+      <c r="AA18" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB18" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC18" s="23">
+        <f>IF($V18="","",$AB18*MIN($V18,1))</f>
+        <v/>
+      </c>
+      <c r="AD18" s="61">
+        <f>IF($G18="","",IF($F18="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G18/12*'لوحة الإدارة التنفيذية'!$P$2),$G18))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="67">
+        <f>IF($F18="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U18="","",$U18/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U18="","",$U18))</f>
+        <v/>
+      </c>
+      <c r="AF18" s="61">
+        <f>IF(OR($AE18="",$G18=""),"",$AE18-$G18)</f>
+        <v/>
+      </c>
+      <c r="AG18" s="17">
+        <f>IF(OR($AE18="",$G18=""),"—",IF($E18="↓",IF($AE18&lt;=$G18,"🟢 على المسار",IF($AE18&lt;=$G18*1.1,"🟡 متابعة","🔴 خطر")),IF($AE18&gt;=$G18,"🟢 على المسار",IF($AE18&gt;=$G18*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH18" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>الكفاءة التشغيلية</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>الامتثال للأمن السيبراني (المحطات)</t>
+        </is>
+      </c>
+      <c r="D19" s="60" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E19" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F19" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G19" s="61" t="n">
+        <v>164</v>
+      </c>
+      <c r="H19" s="62" t="inlineStr">
+        <is>
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I19" s="63" t="n"/>
+      <c r="J19" s="63" t="n"/>
+      <c r="K19" s="63" t="n"/>
+      <c r="L19" s="63" t="n"/>
+      <c r="M19" s="63" t="n"/>
+      <c r="N19" s="63" t="n"/>
+      <c r="O19" s="63" t="n"/>
+      <c r="P19" s="63" t="n"/>
+      <c r="Q19" s="63" t="n"/>
+      <c r="R19" s="63" t="n"/>
+      <c r="S19" s="63" t="n"/>
+      <c r="T19" s="63" t="n"/>
+      <c r="U19" s="64">
+        <f>IF($F19="SUM",IF(COUNT($I19:$T19)=0,"",SUM($I19:$T19)),IF($F19="AVG",IFERROR(AVERAGE($I19:$T19),""),IF($F19="LAST",IFERROR(LOOKUP(2,1/($I19:$T19&lt;&gt;""),$I19:$T19),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V19" s="23">
+        <f>IF($G19="","",IF($U19="","",IF($G19=0,IF($U19&lt;=0,1,0),IF($E19="↓",IFERROR($G19/$U19,0),IFERROR($U19/$G19,0)))))</f>
+        <v/>
+      </c>
+      <c r="W19" s="17">
+        <f>IF($V19="","—",IF($V19&gt;=1,"✅ محقق",IF($V19&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X19" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y19" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z19" s="66" t="n"/>
+      <c r="AA19" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB19" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC19" s="23">
+        <f>IF($V19="","",$AB19*MIN($V19,1))</f>
+        <v/>
+      </c>
+      <c r="AD19" s="61">
+        <f>IF($G19="","",IF($F19="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G19/12*'لوحة الإدارة التنفيذية'!$P$2),$G19))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="67">
+        <f>IF($F19="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U19="","",$U19/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U19="","",$U19))</f>
+        <v/>
+      </c>
+      <c r="AF19" s="61">
+        <f>IF(OR($AE19="",$G19=""),"",$AE19-$G19)</f>
+        <v/>
+      </c>
+      <c r="AG19" s="17">
+        <f>IF(OR($AE19="",$G19=""),"—",IF($E19="↓",IF($AE19&lt;=$G19,"🟢 على المسار",IF($AE19&lt;=$G19*1.1,"🟡 متابعة","🔴 خطر")),IF($AE19&gt;=$G19,"🟢 على المسار",IF($AE19&gt;=$G19*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH19" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>الكفاءة التشغيلية</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>زمن استجابة الدعم الفني (المحطات)</t>
+        </is>
+      </c>
+      <c r="D20" s="60" t="inlineStr">
+        <is>
+          <t>يوم</t>
+        </is>
+      </c>
+      <c r="E20" s="60" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="F20" s="60" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="G20" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="62" t="inlineStr">
+        <is>
+          <t>≤ يوم</t>
+        </is>
+      </c>
+      <c r="I20" s="76" t="n"/>
+      <c r="J20" s="76" t="n"/>
+      <c r="K20" s="76" t="n"/>
+      <c r="L20" s="76" t="n"/>
+      <c r="M20" s="76" t="n"/>
+      <c r="N20" s="76" t="n"/>
+      <c r="O20" s="76" t="n"/>
+      <c r="P20" s="76" t="n"/>
+      <c r="Q20" s="76" t="n"/>
+      <c r="R20" s="76" t="n"/>
+      <c r="S20" s="76" t="n"/>
+      <c r="T20" s="76" t="n"/>
+      <c r="U20" s="77">
+        <f>IF($F20="SUM",IF(COUNT($I20:$T20)=0,"",SUM($I20:$T20)),IF($F20="AVG",IFERROR(AVERAGE($I20:$T20),""),IF($F20="LAST",IFERROR(LOOKUP(2,1/($I20:$T20&lt;&gt;""),$I20:$T20),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V20" s="23">
+        <f>IF($G20="","",IF($U20="","",IF($G20=0,IF($U20&lt;=0,1,0),IF($E20="↓",IFERROR($G20/$U20,0),IFERROR($U20/$G20,0)))))</f>
+        <v/>
+      </c>
+      <c r="W20" s="17">
+        <f>IF($V20="","—",IF($V20&gt;=1,"✅ محقق",IF($V20&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X20" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y20" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z20" s="78" t="n"/>
+      <c r="AA20" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB20" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC20" s="23">
+        <f>IF($V20="","",$AB20*MIN($V20,1))</f>
+        <v/>
+      </c>
+      <c r="AD20" s="75">
+        <f>IF($G20="","",IF($F20="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G20/12*'لوحة الإدارة التنفيذية'!$P$2),$G20))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="79">
+        <f>IF($F20="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U20="","",$U20/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U20="","",$U20))</f>
+        <v/>
+      </c>
+      <c r="AF20" s="75">
+        <f>IF(OR($AE20="",$G20=""),"",$AE20-$G20)</f>
+        <v/>
+      </c>
+      <c r="AG20" s="17">
+        <f>IF(OR($AE20="",$G20=""),"—",IF($E20="↓",IF($AE20&lt;=$G20,"🟢 على المسار",IF($AE20&lt;=$G20*1.1,"🟡 متابعة","🔴 خطر")),IF($AE20&gt;=$G20,"🟢 على المسار",IF($AE20&gt;=$G20*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH20" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>الكفاءة التشغيلية</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>ERP والتكامل (المحطات)</t>
+        </is>
+      </c>
+      <c r="D21" s="60" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E21" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F21" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G21" s="61" t="n">
+        <v>164</v>
+      </c>
+      <c r="H21" s="62" t="inlineStr">
+        <is>
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I21" s="63" t="n"/>
+      <c r="J21" s="63" t="n"/>
+      <c r="K21" s="63" t="n"/>
+      <c r="L21" s="63" t="n"/>
+      <c r="M21" s="63" t="n"/>
+      <c r="N21" s="63" t="n"/>
+      <c r="O21" s="63" t="n"/>
+      <c r="P21" s="63" t="n"/>
+      <c r="Q21" s="63" t="n"/>
+      <c r="R21" s="63" t="n"/>
+      <c r="S21" s="63" t="n"/>
+      <c r="T21" s="63" t="n"/>
+      <c r="U21" s="64">
+        <f>IF($F21="SUM",IF(COUNT($I21:$T21)=0,"",SUM($I21:$T21)),IF($F21="AVG",IFERROR(AVERAGE($I21:$T21),""),IF($F21="LAST",IFERROR(LOOKUP(2,1/($I21:$T21&lt;&gt;""),$I21:$T21),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V21" s="23">
+        <f>IF($G21="","",IF($U21="","",IF($G21=0,IF($U21&lt;=0,1,0),IF($E21="↓",IFERROR($G21/$U21,0),IFERROR($U21/$G21,0)))))</f>
+        <v/>
+      </c>
+      <c r="W21" s="17">
+        <f>IF($V21="","—",IF($V21&gt;=1,"✅ محقق",IF($V21&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X21" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y21" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z21" s="66" t="n"/>
+      <c r="AA21" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB21" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC21" s="23">
+        <f>IF($V21="","",$AB21*MIN($V21,1))</f>
+        <v/>
+      </c>
+      <c r="AD21" s="61">
+        <f>IF($G21="","",IF($F21="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G21/12*'لوحة الإدارة التنفيذية'!$P$2),$G21))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="67">
+        <f>IF($F21="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U21="","",$U21/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U21="","",$U21))</f>
+        <v/>
+      </c>
+      <c r="AF21" s="61">
+        <f>IF(OR($AE21="",$G21=""),"",$AE21-$G21)</f>
+        <v/>
+      </c>
+      <c r="AG21" s="17">
+        <f>IF(OR($AE21="",$G21=""),"—",IF($E21="↓",IF($AE21&lt;=$G21,"🟢 على المسار",IF($AE21&lt;=$G21*1.1,"🟡 متابعة","🔴 خطر")),IF($AE21&gt;=$G21,"🟢 على المسار",IF($AE21&gt;=$G21*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH21" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>الكفاءة التشغيلية</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>تكامل واثق (المحطات)</t>
+        </is>
+      </c>
+      <c r="D22" s="60" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E22" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F22" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G22" s="61" t="n">
+        <v>164</v>
+      </c>
+      <c r="H22" s="62" t="inlineStr">
+        <is>
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I22" s="63" t="n"/>
+      <c r="J22" s="63" t="n"/>
+      <c r="K22" s="63" t="n"/>
+      <c r="L22" s="63" t="n"/>
+      <c r="M22" s="63" t="n"/>
+      <c r="N22" s="63" t="n"/>
+      <c r="O22" s="63" t="n"/>
+      <c r="P22" s="63" t="n"/>
+      <c r="Q22" s="63" t="n"/>
+      <c r="R22" s="63" t="n"/>
+      <c r="S22" s="63" t="n"/>
+      <c r="T22" s="63" t="n"/>
+      <c r="U22" s="64">
+        <f>IF($F22="SUM",IF(COUNT($I22:$T22)=0,"",SUM($I22:$T22)),IF($F22="AVG",IFERROR(AVERAGE($I22:$T22),""),IF($F22="LAST",IFERROR(LOOKUP(2,1/($I22:$T22&lt;&gt;""),$I22:$T22),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V22" s="23">
+        <f>IF($G22="","",IF($U22="","",IF($G22=0,IF($U22&lt;=0,1,0),IF($E22="↓",IFERROR($G22/$U22,0),IFERROR($U22/$G22,0)))))</f>
+        <v/>
+      </c>
+      <c r="W22" s="17">
+        <f>IF($V22="","—",IF($V22&gt;=1,"✅ محقق",IF($V22&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X22" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y22" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z22" s="66" t="n"/>
+      <c r="AA22" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB22" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC22" s="23">
+        <f>IF($V22="","",$AB22*MIN($V22,1))</f>
+        <v/>
+      </c>
+      <c r="AD22" s="61">
+        <f>IF($G22="","",IF($F22="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G22/12*'لوحة الإدارة التنفيذية'!$P$2),$G22))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="67">
+        <f>IF($F22="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U22="","",$U22/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U22="","",$U22))</f>
+        <v/>
+      </c>
+      <c r="AF22" s="61">
+        <f>IF(OR($AE22="",$G22=""),"",$AE22-$G22)</f>
+        <v/>
+      </c>
+      <c r="AG22" s="17">
+        <f>IF(OR($AE22="",$G22=""),"—",IF($E22="↓",IF($AE22&lt;=$G22,"🟢 على المسار",IF($AE22&lt;=$G22*1.1,"🟡 متابعة","🔴 خطر")),IF($AE22&gt;=$G22,"🟢 على المسار",IF($AE22&gt;=$G22*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH22" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>الكفاءة التشغيلية</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>تكامل تطبيق الولاء (المحطات)</t>
+        </is>
+      </c>
+      <c r="D23" s="60" t="inlineStr">
+        <is>
+          <t>محطة</t>
+        </is>
+      </c>
+      <c r="E23" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F23" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G23" s="61" t="n">
+        <v>164</v>
+      </c>
+      <c r="H23" s="62" t="inlineStr">
+        <is>
+          <t>164 محطة</t>
+        </is>
+      </c>
+      <c r="I23" s="63" t="n"/>
+      <c r="J23" s="63" t="n"/>
+      <c r="K23" s="63" t="n"/>
+      <c r="L23" s="63" t="n"/>
+      <c r="M23" s="63" t="n"/>
+      <c r="N23" s="63" t="n"/>
+      <c r="O23" s="63" t="n"/>
+      <c r="P23" s="63" t="n"/>
+      <c r="Q23" s="63" t="n"/>
+      <c r="R23" s="63" t="n"/>
+      <c r="S23" s="63" t="n"/>
+      <c r="T23" s="63" t="n"/>
+      <c r="U23" s="64">
+        <f>IF($F23="SUM",IF(COUNT($I23:$T23)=0,"",SUM($I23:$T23)),IF($F23="AVG",IFERROR(AVERAGE($I23:$T23),""),IF($F23="LAST",IFERROR(LOOKUP(2,1/($I23:$T23&lt;&gt;""),$I23:$T23),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V23" s="23">
+        <f>IF($G23="","",IF($U23="","",IF($G23=0,IF($U23&lt;=0,1,0),IF($E23="↓",IFERROR($G23/$U23,0),IFERROR($U23/$G23,0)))))</f>
+        <v/>
+      </c>
+      <c r="W23" s="17">
+        <f>IF($V23="","—",IF($V23&gt;=1,"✅ محقق",IF($V23&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X23" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y23" s="22" t="inlineStr">
+        <is>
+          <t>تطبيق «تانكي»</t>
+        </is>
+      </c>
+      <c r="Z23" s="66" t="n"/>
+      <c r="AA23" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB23" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC23" s="23">
+        <f>IF($V23="","",$AB23*MIN($V23,1))</f>
+        <v/>
+      </c>
+      <c r="AD23" s="61">
+        <f>IF($G23="","",IF($F23="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G23/12*'لوحة الإدارة التنفيذية'!$P$2),$G23))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="67">
+        <f>IF($F23="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U23="","",$U23/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U23="","",$U23))</f>
+        <v/>
+      </c>
+      <c r="AF23" s="61">
+        <f>IF(OR($AE23="",$G23=""),"",$AE23-$G23)</f>
+        <v/>
+      </c>
+      <c r="AG23" s="17">
+        <f>IF(OR($AE23="",$G23=""),"—",IF($E23="↓",IF($AE23&lt;=$G23,"🟢 على المسار",IF($AE23&lt;=$G23*1.1,"🟡 متابعة","🔴 خطر")),IF($AE23&gt;=$G23,"🟢 على المسار",IF($AE23&gt;=$G23*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH23" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>المركز الرئيسي</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>جاهزية شبكة المركز الرئيسي</t>
+        </is>
+      </c>
+      <c r="D24" s="60" t="inlineStr">
+        <is>
+          <t>ساعة</t>
+        </is>
+      </c>
+      <c r="E24" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F24" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G24" s="61" t="n">
+        <v>24</v>
+      </c>
+      <c r="H24" s="62" t="inlineStr">
+        <is>
+          <t>24 ساعة</t>
+        </is>
+      </c>
+      <c r="I24" s="63" t="n"/>
+      <c r="J24" s="63" t="n"/>
+      <c r="K24" s="63" t="n"/>
+      <c r="L24" s="63" t="n"/>
+      <c r="M24" s="63" t="n"/>
+      <c r="N24" s="63" t="n"/>
+      <c r="O24" s="63" t="n"/>
+      <c r="P24" s="63" t="n"/>
+      <c r="Q24" s="63" t="n"/>
+      <c r="R24" s="63" t="n"/>
+      <c r="S24" s="63" t="n"/>
+      <c r="T24" s="63" t="n"/>
+      <c r="U24" s="64">
+        <f>IF($F24="SUM",IF(COUNT($I24:$T24)=0,"",SUM($I24:$T24)),IF($F24="AVG",IFERROR(AVERAGE($I24:$T24),""),IF($F24="LAST",IFERROR(LOOKUP(2,1/($I24:$T24&lt;&gt;""),$I24:$T24),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V24" s="23">
+        <f>IF($G24="","",IF($U24="","",IF($G24=0,IF($U24&lt;=0,1,0),IF($E24="↓",IFERROR($G24/$U24,0),IFERROR($U24/$G24,0)))))</f>
+        <v/>
+      </c>
+      <c r="W24" s="17">
+        <f>IF($V24="","—",IF($V24&gt;=1,"✅ محقق",IF($V24&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X24" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y24" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z24" s="66" t="n"/>
+      <c r="AA24" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB24" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC24" s="23">
+        <f>IF($V24="","",$AB24*MIN($V24,1))</f>
+        <v/>
+      </c>
+      <c r="AD24" s="61">
+        <f>IF($G24="","",IF($F24="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G24/12*'لوحة الإدارة التنفيذية'!$P$2),$G24))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="67">
+        <f>IF($F24="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U24="","",$U24/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U24="","",$U24))</f>
+        <v/>
+      </c>
+      <c r="AF24" s="61">
+        <f>IF(OR($AE24="",$G24=""),"",$AE24-$G24)</f>
+        <v/>
+      </c>
+      <c r="AG24" s="17">
+        <f>IF(OR($AE24="",$G24=""),"—",IF($E24="↓",IF($AE24&lt;=$G24,"🟢 على المسار",IF($AE24&lt;=$G24*1.1,"🟡 متابعة","🔴 خطر")),IF($AE24&gt;=$G24,"🟢 على المسار",IF($AE24&gt;=$G24*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH24" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>المركز الرئيسي</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>جاهزية تطبيقات المركز الرئيسي</t>
+        </is>
+      </c>
+      <c r="D25" s="60" t="inlineStr">
+        <is>
+          <t>ساعة</t>
+        </is>
+      </c>
+      <c r="E25" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F25" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G25" s="61" t="n">
+        <v>24</v>
+      </c>
+      <c r="H25" s="62" t="inlineStr">
+        <is>
+          <t>24 ساعة</t>
+        </is>
+      </c>
+      <c r="I25" s="63" t="n"/>
+      <c r="J25" s="63" t="n"/>
+      <c r="K25" s="63" t="n"/>
+      <c r="L25" s="63" t="n"/>
+      <c r="M25" s="63" t="n"/>
+      <c r="N25" s="63" t="n"/>
+      <c r="O25" s="63" t="n"/>
+      <c r="P25" s="63" t="n"/>
+      <c r="Q25" s="63" t="n"/>
+      <c r="R25" s="63" t="n"/>
+      <c r="S25" s="63" t="n"/>
+      <c r="T25" s="63" t="n"/>
+      <c r="U25" s="64">
+        <f>IF($F25="SUM",IF(COUNT($I25:$T25)=0,"",SUM($I25:$T25)),IF($F25="AVG",IFERROR(AVERAGE($I25:$T25),""),IF($F25="LAST",IFERROR(LOOKUP(2,1/($I25:$T25&lt;&gt;""),$I25:$T25),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V25" s="23">
+        <f>IF($G25="","",IF($U25="","",IF($G25=0,IF($U25&lt;=0,1,0),IF($E25="↓",IFERROR($G25/$U25,0),IFERROR($U25/$G25,0)))))</f>
+        <v/>
+      </c>
+      <c r="W25" s="17">
+        <f>IF($V25="","—",IF($V25&gt;=1,"✅ محقق",IF($V25&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X25" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y25" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z25" s="66" t="n"/>
+      <c r="AA25" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB25" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC25" s="23">
+        <f>IF($V25="","",$AB25*MIN($V25,1))</f>
+        <v/>
+      </c>
+      <c r="AD25" s="61">
+        <f>IF($G25="","",IF($F25="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G25/12*'لوحة الإدارة التنفيذية'!$P$2),$G25))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="67">
+        <f>IF($F25="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U25="","",$U25/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U25="","",$U25))</f>
+        <v/>
+      </c>
+      <c r="AF25" s="61">
+        <f>IF(OR($AE25="",$G25=""),"",$AE25-$G25)</f>
+        <v/>
+      </c>
+      <c r="AG25" s="17">
+        <f>IF(OR($AE25="",$G25=""),"—",IF($E25="↓",IF($AE25&lt;=$G25,"🟢 على المسار",IF($AE25&lt;=$G25*1.1,"🟡 متابعة","🔴 خطر")),IF($AE25&gt;=$G25,"🟢 على المسار",IF($AE25&gt;=$G25*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH25" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>المركز الرئيسي</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>زمن استجابة الدعم (المركز)</t>
+        </is>
+      </c>
+      <c r="D26" s="60" t="inlineStr">
+        <is>
+          <t>ساعة</t>
+        </is>
+      </c>
+      <c r="E26" s="60" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="F26" s="60" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="G26" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="62" t="inlineStr">
+        <is>
+          <t>≤ ساعة</t>
+        </is>
+      </c>
+      <c r="I26" s="76" t="n"/>
+      <c r="J26" s="76" t="n"/>
+      <c r="K26" s="76" t="n"/>
+      <c r="L26" s="76" t="n"/>
+      <c r="M26" s="76" t="n"/>
+      <c r="N26" s="76" t="n"/>
+      <c r="O26" s="76" t="n"/>
+      <c r="P26" s="76" t="n"/>
+      <c r="Q26" s="76" t="n"/>
+      <c r="R26" s="76" t="n"/>
+      <c r="S26" s="76" t="n"/>
+      <c r="T26" s="76" t="n"/>
+      <c r="U26" s="77">
+        <f>IF($F26="SUM",IF(COUNT($I26:$T26)=0,"",SUM($I26:$T26)),IF($F26="AVG",IFERROR(AVERAGE($I26:$T26),""),IF($F26="LAST",IFERROR(LOOKUP(2,1/($I26:$T26&lt;&gt;""),$I26:$T26),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V26" s="23">
+        <f>IF($G26="","",IF($U26="","",IF($G26=0,IF($U26&lt;=0,1,0),IF($E26="↓",IFERROR($G26/$U26,0),IFERROR($U26/$G26,0)))))</f>
+        <v/>
+      </c>
+      <c r="W26" s="17">
+        <f>IF($V26="","—",IF($V26&gt;=1,"✅ محقق",IF($V26&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X26" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y26" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z26" s="78" t="n"/>
+      <c r="AA26" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB26" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC26" s="23">
+        <f>IF($V26="","",$AB26*MIN($V26,1))</f>
+        <v/>
+      </c>
+      <c r="AD26" s="75">
+        <f>IF($G26="","",IF($F26="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G26/12*'لوحة الإدارة التنفيذية'!$P$2),$G26))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="79">
+        <f>IF($F26="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U26="","",$U26/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U26="","",$U26))</f>
+        <v/>
+      </c>
+      <c r="AF26" s="75">
+        <f>IF(OR($AE26="",$G26=""),"",$AE26-$G26)</f>
+        <v/>
+      </c>
+      <c r="AG26" s="17">
+        <f>IF(OR($AE26="",$G26=""),"—",IF($E26="↓",IF($AE26&lt;=$G26,"🟢 على المسار",IF($AE26&lt;=$G26*1.1,"🟡 متابعة","🔴 خطر")),IF($AE26&gt;=$G26,"🟢 على المسار",IF($AE26&gt;=$G26*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH26" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>المركز الرئيسي</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>الامتثال للأمن السيبراني (المركز)</t>
+        </is>
+      </c>
+      <c r="D27" s="60" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E27" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F27" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G27" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="62" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="73" t="n"/>
+      <c r="J27" s="73" t="n"/>
+      <c r="K27" s="73" t="n"/>
+      <c r="L27" s="73" t="n"/>
+      <c r="M27" s="73" t="n"/>
+      <c r="N27" s="73" t="n"/>
+      <c r="O27" s="73" t="n"/>
+      <c r="P27" s="73" t="n"/>
+      <c r="Q27" s="73" t="n"/>
+      <c r="R27" s="73" t="n"/>
+      <c r="S27" s="73" t="n"/>
+      <c r="T27" s="73" t="n"/>
+      <c r="U27" s="59">
+        <f>IF($F27="SUM",IF(COUNT($I27:$T27)=0,"",SUM($I27:$T27)),IF($F27="AVG",IFERROR(AVERAGE($I27:$T27),""),IF($F27="LAST",IFERROR(LOOKUP(2,1/($I27:$T27&lt;&gt;""),$I27:$T27),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V27" s="23">
+        <f>IF($G27="","",IF($U27="","",IF($G27=0,IF($U27&lt;=0,1,0),IF($E27="↓",IFERROR($G27/$U27,0),IFERROR($U27/$G27,0)))))</f>
+        <v/>
+      </c>
+      <c r="W27" s="17">
+        <f>IF($V27="","—",IF($V27&gt;=1,"✅ محقق",IF($V27&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X27" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y27" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z27" s="53" t="n"/>
+      <c r="AA27" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB27" s="53" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AC27" s="23">
+        <f>IF($V27="","",$AB27*MIN($V27,1))</f>
+        <v/>
+      </c>
+      <c r="AD27" s="74">
+        <f>IF($G27="","",IF($F27="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G27/12*'لوحة الإدارة التنفيذية'!$P$2),$G27))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="23">
+        <f>IF($F27="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U27="","",$U27/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U27="","",$U27))</f>
+        <v/>
+      </c>
+      <c r="AF27" s="74">
+        <f>IF(OR($AE27="",$G27=""),"",$AE27-$G27)</f>
+        <v/>
+      </c>
+      <c r="AG27" s="17">
+        <f>IF(OR($AE27="",$G27=""),"—",IF($E27="↓",IF($AE27&lt;=$G27,"🟢 على المسار",IF($AE27&lt;=$G27*1.1,"🟡 متابعة","🔴 خطر")),IF($AE27&gt;=$G27,"🟢 على المسار",IF($AE27&gt;=$G27*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH27" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="80" t="inlineStr"/>
+      <c r="B28" s="81" t="inlineStr">
         <is>
           <t>الإجمالي الموزون للإدارة</t>
         </is>
       </c>
-      <c r="AB12" s="82">
-        <f>SUM(AB4:AB11)</f>
-        <v/>
-      </c>
-      <c r="AC12" s="83">
-        <f>SUM(AC4:AC11)</f>
+      <c r="AB28" s="82">
+        <f>SUM(AB4:AB27)</f>
+        <v/>
+      </c>
+      <c r="AC28" s="83">
+        <f>SUM(AC4:AC27)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
   <mergeCells count="3">
+    <mergeCell ref="B28:AA28"/>
     <mergeCell ref="A2:AH2"/>
     <mergeCell ref="A1:AH1"/>
-    <mergeCell ref="B12:AA12"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 J4 J5 J6 J7 J8 J9 J10 J11 K4 K5 K6 K7 K8 K9 K10 K11 L4 L5 L6 L7 L8 L9 L10 L11 M4 M5 M6 M7 M8 M9 M10 M11 N4 N5 N6 N7 N8 N9 N10 N11 O4 O5 O6 O7 O8 O9 O10 O11 P4 P5 P6 P7 P8 P9 P10 P11 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 R4 R5 R6 R7 R8 R9 R10 R11 S4 S5 S6 S7 S8 S9 S10 S11 T4 T5 T6 T7 T8 T9 T10 T11 Z4 Z5 Z6 Z7 Z8 Z9 Z10 Z11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="قيمة غير صحيحة" error="أدخل رقماً موجباً فقط" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 N4 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 S4 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 T4 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 Z4 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="قيمة غير صحيحة" error="أدخل رقماً موجباً فقط" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -23541,7 +25245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH12"/>
+  <dimension ref="A1:AH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -23583,7 +25287,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="28" t="inlineStr">
         <is>
-          <t>إدارة الموارد البشرية · مؤشرات الأداء 2026  (8 مؤشرات) — الاستثمار في الموظفين</t>
+          <t>إدارة الموارد البشرية · مؤشرات الأداء 2026  (17 مؤشراً) — خطة العمل 2026</t>
         </is>
       </c>
     </row>
@@ -23772,12 +25476,12 @@
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>الاستبقاء</t>
+          <t>التوظيف والتوطين</t>
         </is>
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>معدل استبقاء الموظفين (Retention)</t>
+          <t>نسبة السعودة / التوطين</t>
         </is>
       </c>
       <c r="D4" s="60" t="inlineStr">
@@ -23795,12 +25499,10 @@
           <t>LAST</t>
         </is>
       </c>
-      <c r="G4" s="74" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="G4" s="60" t="inlineStr"/>
       <c r="H4" s="62" t="inlineStr">
         <is>
-          <t>≥ 90%</t>
+          <t>أخضر مرتفع (حسب الوزارة)</t>
         </is>
       </c>
       <c r="I4" s="73" t="n"/>
@@ -23844,7 +25546,7 @@
         </is>
       </c>
       <c r="AB4" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0588</v>
       </c>
       <c r="AC4" s="23">
         <f>IF($V4="","",$AB4*MIN($V4,1))</f>
@@ -23878,12 +25580,12 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>الاستبقاء</t>
+          <t>التوظيف والتوطين</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>معدل دوران الموظفين (Turnover)</t>
+          <t>الارتقاء بآليات اختيار المرشحين</t>
         </is>
       </c>
       <c r="D5" s="60" t="inlineStr">
@@ -23893,20 +25595,20 @@
       </c>
       <c r="E5" s="60" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="F5" s="60" t="inlineStr">
         <is>
-          <t>AVG</t>
+          <t>LAST</t>
         </is>
       </c>
       <c r="G5" s="74" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H5" s="62" t="inlineStr">
         <is>
-          <t>≤ 10%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I5" s="73" t="n"/>
@@ -23950,7 +25652,7 @@
         </is>
       </c>
       <c r="AB5" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0588</v>
       </c>
       <c r="AC5" s="23">
         <f>IF($V5="","",$AB5*MIN($V5,1))</f>
@@ -23974,7 +25676,7 @@
       </c>
       <c r="AH5" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
     </row>
@@ -23984,17 +25686,17 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>التطوير</t>
+          <t>التوظيف والتوطين</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>متوسط ساعات التدريب لكل موظف</t>
+          <t>نسبة شغل الشواغر خلال 30 يوم</t>
         </is>
       </c>
       <c r="D6" s="60" t="inlineStr">
         <is>
-          <t>ساعة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E6" s="60" t="inlineStr">
@@ -24004,30 +25706,30 @@
       </c>
       <c r="F6" s="60" t="inlineStr">
         <is>
-          <t>SUM</t>
-        </is>
-      </c>
-      <c r="G6" s="75" t="n">
-        <v>40</v>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="G6" s="74" t="n">
+        <v>0.85</v>
       </c>
       <c r="H6" s="62" t="inlineStr">
         <is>
-          <t>≥ 40 ساعة</t>
-        </is>
-      </c>
-      <c r="I6" s="76" t="n"/>
-      <c r="J6" s="76" t="n"/>
-      <c r="K6" s="76" t="n"/>
-      <c r="L6" s="76" t="n"/>
-      <c r="M6" s="76" t="n"/>
-      <c r="N6" s="76" t="n"/>
-      <c r="O6" s="76" t="n"/>
-      <c r="P6" s="76" t="n"/>
-      <c r="Q6" s="76" t="n"/>
-      <c r="R6" s="76" t="n"/>
-      <c r="S6" s="76" t="n"/>
-      <c r="T6" s="76" t="n"/>
-      <c r="U6" s="77">
+          <t>≥ 85%</t>
+        </is>
+      </c>
+      <c r="I6" s="73" t="n"/>
+      <c r="J6" s="73" t="n"/>
+      <c r="K6" s="73" t="n"/>
+      <c r="L6" s="73" t="n"/>
+      <c r="M6" s="73" t="n"/>
+      <c r="N6" s="73" t="n"/>
+      <c r="O6" s="73" t="n"/>
+      <c r="P6" s="73" t="n"/>
+      <c r="Q6" s="73" t="n"/>
+      <c r="R6" s="73" t="n"/>
+      <c r="S6" s="73" t="n"/>
+      <c r="T6" s="73" t="n"/>
+      <c r="U6" s="59">
         <f>IF($F6="SUM",IF(COUNT($I6:$T6)=0,"",SUM($I6:$T6)),IF($F6="AVG",IFERROR(AVERAGE($I6:$T6),""),IF($F6="LAST",IFERROR(LOOKUP(2,1/($I6:$T6&lt;&gt;""),$I6:$T6),""),"")))</f>
         <v/>
       </c>
@@ -24049,28 +25751,28 @@
           <t>الاستثمار في الموظفين</t>
         </is>
       </c>
-      <c r="Z6" s="78" t="n"/>
+      <c r="Z6" s="53" t="n"/>
       <c r="AA6" s="21" t="inlineStr">
         <is>
-          <t>🔵 قائد</t>
+          <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB6" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0588</v>
       </c>
       <c r="AC6" s="23">
         <f>IF($V6="","",$AB6*MIN($V6,1))</f>
         <v/>
       </c>
-      <c r="AD6" s="75">
+      <c r="AD6" s="74">
         <f>IF($G6="","",IF($F6="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G6/12*'لوحة الإدارة التنفيذية'!$P$2),$G6))</f>
         <v/>
       </c>
-      <c r="AE6" s="79">
+      <c r="AE6" s="23">
         <f>IF($F6="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U6="","",$U6/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U6="","",$U6))</f>
         <v/>
       </c>
-      <c r="AF6" s="75">
+      <c r="AF6" s="74">
         <f>IF(OR($AE6="",$G6=""),"",$AE6-$G6)</f>
         <v/>
       </c>
@@ -24080,7 +25782,7 @@
       </c>
       <c r="AH6" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
     </row>
@@ -24090,12 +25792,12 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>التطوير</t>
+          <t>الاستبقاء</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>نسبة الموظفين المشمولين بخطة تطوير</t>
+          <t>معدل استبقاء الموظفين (Retention)</t>
         </is>
       </c>
       <c r="D7" s="60" t="inlineStr">
@@ -24114,11 +25816,11 @@
         </is>
       </c>
       <c r="G7" s="74" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H7" s="62" t="inlineStr">
         <is>
-          <t>≥ 80%</t>
+          <t>≥ 90%</t>
         </is>
       </c>
       <c r="I7" s="73" t="n"/>
@@ -24162,7 +25864,7 @@
         </is>
       </c>
       <c r="AB7" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0588</v>
       </c>
       <c r="AC7" s="23">
         <f>IF($V7="","",$AB7*MIN($V7,1))</f>
@@ -24196,22 +25898,22 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>الرضا والانتماء</t>
+          <t>الاستبقاء</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>مؤشر رضا الموظفين (eNPS)</t>
+          <t>معدل دوران الموظفين (Turnover)</t>
         </is>
       </c>
       <c r="D8" s="60" t="inlineStr">
         <is>
-          <t>نقطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E8" s="60" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="F8" s="60" t="inlineStr">
@@ -24219,27 +25921,27 @@
           <t>AVG</t>
         </is>
       </c>
-      <c r="G8" s="75" t="n">
-        <v>30</v>
+      <c r="G8" s="74" t="n">
+        <v>0.1</v>
       </c>
       <c r="H8" s="62" t="inlineStr">
         <is>
-          <t>≥ 30</t>
-        </is>
-      </c>
-      <c r="I8" s="76" t="n"/>
-      <c r="J8" s="76" t="n"/>
-      <c r="K8" s="76" t="n"/>
-      <c r="L8" s="76" t="n"/>
-      <c r="M8" s="76" t="n"/>
-      <c r="N8" s="76" t="n"/>
-      <c r="O8" s="76" t="n"/>
-      <c r="P8" s="76" t="n"/>
-      <c r="Q8" s="76" t="n"/>
-      <c r="R8" s="76" t="n"/>
-      <c r="S8" s="76" t="n"/>
-      <c r="T8" s="76" t="n"/>
-      <c r="U8" s="77">
+          <t>≤ 10%</t>
+        </is>
+      </c>
+      <c r="I8" s="73" t="n"/>
+      <c r="J8" s="73" t="n"/>
+      <c r="K8" s="73" t="n"/>
+      <c r="L8" s="73" t="n"/>
+      <c r="M8" s="73" t="n"/>
+      <c r="N8" s="73" t="n"/>
+      <c r="O8" s="73" t="n"/>
+      <c r="P8" s="73" t="n"/>
+      <c r="Q8" s="73" t="n"/>
+      <c r="R8" s="73" t="n"/>
+      <c r="S8" s="73" t="n"/>
+      <c r="T8" s="73" t="n"/>
+      <c r="U8" s="59">
         <f>IF($F8="SUM",IF(COUNT($I8:$T8)=0,"",SUM($I8:$T8)),IF($F8="AVG",IFERROR(AVERAGE($I8:$T8),""),IF($F8="LAST",IFERROR(LOOKUP(2,1/($I8:$T8&lt;&gt;""),$I8:$T8),""),"")))</f>
         <v/>
       </c>
@@ -24261,28 +25963,28 @@
           <t>الاستثمار في الموظفين</t>
         </is>
       </c>
-      <c r="Z8" s="78" t="n"/>
+      <c r="Z8" s="53" t="n"/>
       <c r="AA8" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB8" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0588</v>
       </c>
       <c r="AC8" s="23">
         <f>IF($V8="","",$AB8*MIN($V8,1))</f>
         <v/>
       </c>
-      <c r="AD8" s="75">
+      <c r="AD8" s="74">
         <f>IF($G8="","",IF($F8="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G8/12*'لوحة الإدارة التنفيذية'!$P$2),$G8))</f>
         <v/>
       </c>
-      <c r="AE8" s="79">
+      <c r="AE8" s="23">
         <f>IF($F8="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U8="","",$U8/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U8="","",$U8))</f>
         <v/>
       </c>
-      <c r="AF8" s="75">
+      <c r="AF8" s="74">
         <f>IF(OR($AE8="",$G8=""),"",$AE8-$G8)</f>
         <v/>
       </c>
@@ -24302,17 +26004,17 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>الاستقطاب</t>
+          <t>التدريب والتطوير</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>نسبة شغل الشواغر خلال 30 يوم</t>
+          <t>عدد الدورات الإدارية المنعقدة</t>
         </is>
       </c>
       <c r="D9" s="60" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>دورة</t>
         </is>
       </c>
       <c r="E9" s="60" t="inlineStr">
@@ -24322,30 +26024,30 @@
       </c>
       <c r="F9" s="60" t="inlineStr">
         <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="G9" s="74" t="n">
-        <v>0.85</v>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="G9" s="61" t="n">
+        <v>6</v>
       </c>
       <c r="H9" s="62" t="inlineStr">
         <is>
-          <t>≥ 85%</t>
-        </is>
-      </c>
-      <c r="I9" s="73" t="n"/>
-      <c r="J9" s="73" t="n"/>
-      <c r="K9" s="73" t="n"/>
-      <c r="L9" s="73" t="n"/>
-      <c r="M9" s="73" t="n"/>
-      <c r="N9" s="73" t="n"/>
-      <c r="O9" s="73" t="n"/>
-      <c r="P9" s="73" t="n"/>
-      <c r="Q9" s="73" t="n"/>
-      <c r="R9" s="73" t="n"/>
-      <c r="S9" s="73" t="n"/>
-      <c r="T9" s="73" t="n"/>
-      <c r="U9" s="59">
+          <t>6 دورات</t>
+        </is>
+      </c>
+      <c r="I9" s="63" t="n"/>
+      <c r="J9" s="63" t="n"/>
+      <c r="K9" s="63" t="n"/>
+      <c r="L9" s="63" t="n"/>
+      <c r="M9" s="63" t="n"/>
+      <c r="N9" s="63" t="n"/>
+      <c r="O9" s="63" t="n"/>
+      <c r="P9" s="63" t="n"/>
+      <c r="Q9" s="63" t="n"/>
+      <c r="R9" s="63" t="n"/>
+      <c r="S9" s="63" t="n"/>
+      <c r="T9" s="63" t="n"/>
+      <c r="U9" s="64">
         <f>IF($F9="SUM",IF(COUNT($I9:$T9)=0,"",SUM($I9:$T9)),IF($F9="AVG",IFERROR(AVERAGE($I9:$T9),""),IF($F9="LAST",IFERROR(LOOKUP(2,1/($I9:$T9&lt;&gt;""),$I9:$T9),""),"")))</f>
         <v/>
       </c>
@@ -24367,28 +26069,28 @@
           <t>الاستثمار في الموظفين</t>
         </is>
       </c>
-      <c r="Z9" s="53" t="n"/>
+      <c r="Z9" s="66" t="n"/>
       <c r="AA9" s="21" t="inlineStr">
         <is>
-          <t>🟣 لاحق</t>
+          <t>🔵 قائد</t>
         </is>
       </c>
       <c r="AB9" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0588</v>
       </c>
       <c r="AC9" s="23">
         <f>IF($V9="","",$AB9*MIN($V9,1))</f>
         <v/>
       </c>
-      <c r="AD9" s="74">
+      <c r="AD9" s="61">
         <f>IF($G9="","",IF($F9="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G9/12*'لوحة الإدارة التنفيذية'!$P$2),$G9))</f>
         <v/>
       </c>
-      <c r="AE9" s="23">
+      <c r="AE9" s="67">
         <f>IF($F9="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U9="","",$U9/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U9="","",$U9))</f>
         <v/>
       </c>
-      <c r="AF9" s="74">
+      <c r="AF9" s="61">
         <f>IF(OR($AE9="",$G9=""),"",$AE9-$G9)</f>
         <v/>
       </c>
@@ -24408,17 +26110,17 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>الأداء</t>
+          <t>التدريب والتطوير</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>نسبة إنجاز تقييمات الأداء في موعدها</t>
+          <t>متوسط ساعات التدريب لكل موظف</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ساعة</t>
         </is>
       </c>
       <c r="E10" s="60" t="inlineStr">
@@ -24428,30 +26130,30 @@
       </c>
       <c r="F10" s="60" t="inlineStr">
         <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="G10" s="74" t="n">
-        <v>1</v>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="G10" s="75" t="n">
+        <v>40</v>
       </c>
       <c r="H10" s="62" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I10" s="73" t="n"/>
-      <c r="J10" s="73" t="n"/>
-      <c r="K10" s="73" t="n"/>
-      <c r="L10" s="73" t="n"/>
-      <c r="M10" s="73" t="n"/>
-      <c r="N10" s="73" t="n"/>
-      <c r="O10" s="73" t="n"/>
-      <c r="P10" s="73" t="n"/>
-      <c r="Q10" s="73" t="n"/>
-      <c r="R10" s="73" t="n"/>
-      <c r="S10" s="73" t="n"/>
-      <c r="T10" s="73" t="n"/>
-      <c r="U10" s="59">
+          <t>≥ 40 ساعة</t>
+        </is>
+      </c>
+      <c r="I10" s="76" t="n"/>
+      <c r="J10" s="76" t="n"/>
+      <c r="K10" s="76" t="n"/>
+      <c r="L10" s="76" t="n"/>
+      <c r="M10" s="76" t="n"/>
+      <c r="N10" s="76" t="n"/>
+      <c r="O10" s="76" t="n"/>
+      <c r="P10" s="76" t="n"/>
+      <c r="Q10" s="76" t="n"/>
+      <c r="R10" s="76" t="n"/>
+      <c r="S10" s="76" t="n"/>
+      <c r="T10" s="76" t="n"/>
+      <c r="U10" s="77">
         <f>IF($F10="SUM",IF(COUNT($I10:$T10)=0,"",SUM($I10:$T10)),IF($F10="AVG",IFERROR(AVERAGE($I10:$T10),""),IF($F10="LAST",IFERROR(LOOKUP(2,1/($I10:$T10&lt;&gt;""),$I10:$T10),""),"")))</f>
         <v/>
       </c>
@@ -24473,28 +26175,28 @@
           <t>الاستثمار في الموظفين</t>
         </is>
       </c>
-      <c r="Z10" s="53" t="n"/>
+      <c r="Z10" s="78" t="n"/>
       <c r="AA10" s="21" t="inlineStr">
         <is>
-          <t>🟣 لاحق</t>
+          <t>🔵 قائد</t>
         </is>
       </c>
       <c r="AB10" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0588</v>
       </c>
       <c r="AC10" s="23">
         <f>IF($V10="","",$AB10*MIN($V10,1))</f>
         <v/>
       </c>
-      <c r="AD10" s="74">
+      <c r="AD10" s="75">
         <f>IF($G10="","",IF($F10="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G10/12*'لوحة الإدارة التنفيذية'!$P$2),$G10))</f>
         <v/>
       </c>
-      <c r="AE10" s="23">
+      <c r="AE10" s="79">
         <f>IF($F10="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U10="","",$U10/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U10="","",$U10))</f>
         <v/>
       </c>
-      <c r="AF10" s="74">
+      <c r="AF10" s="75">
         <f>IF(OR($AE10="",$G10=""),"",$AE10-$G10)</f>
         <v/>
       </c>
@@ -24504,7 +26206,7 @@
       </c>
       <c r="AH10" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
     </row>
@@ -24514,12 +26216,12 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>الامتثال</t>
+          <t>التدريب والتطوير</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>نسبة السعودة</t>
+          <t>نسبة الموظفين المشمولين بخطة تطوير</t>
         </is>
       </c>
       <c r="D11" s="60" t="inlineStr">
@@ -24537,10 +26239,12 @@
           <t>LAST</t>
         </is>
       </c>
-      <c r="G11" s="60" t="inlineStr"/>
+      <c r="G11" s="74" t="n">
+        <v>0.8</v>
+      </c>
       <c r="H11" s="62" t="inlineStr">
         <is>
-          <t>حسب النطاق</t>
+          <t>≥ 80%</t>
         </is>
       </c>
       <c r="I11" s="73" t="n"/>
@@ -24584,7 +26288,7 @@
         </is>
       </c>
       <c r="AB11" s="53" t="n">
-        <v>0.125</v>
+        <v>0.0588</v>
       </c>
       <c r="AC11" s="23">
         <f>IF($V11="","",$AB11*MIN($V11,1))</f>
@@ -24612,19 +26316,971 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="80" t="inlineStr"/>
-      <c r="B12" s="81" t="inlineStr">
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>الرضا والثقافة</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>مؤشر رضا الموظفين (eNPS)</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="inlineStr">
+        <is>
+          <t>نقطة</t>
+        </is>
+      </c>
+      <c r="E12" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F12" s="60" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="G12" s="75" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="62" t="inlineStr">
+        <is>
+          <t>≥ 30</t>
+        </is>
+      </c>
+      <c r="I12" s="76" t="n"/>
+      <c r="J12" s="76" t="n"/>
+      <c r="K12" s="76" t="n"/>
+      <c r="L12" s="76" t="n"/>
+      <c r="M12" s="76" t="n"/>
+      <c r="N12" s="76" t="n"/>
+      <c r="O12" s="76" t="n"/>
+      <c r="P12" s="76" t="n"/>
+      <c r="Q12" s="76" t="n"/>
+      <c r="R12" s="76" t="n"/>
+      <c r="S12" s="76" t="n"/>
+      <c r="T12" s="76" t="n"/>
+      <c r="U12" s="77">
+        <f>IF($F12="SUM",IF(COUNT($I12:$T12)=0,"",SUM($I12:$T12)),IF($F12="AVG",IFERROR(AVERAGE($I12:$T12),""),IF($F12="LAST",IFERROR(LOOKUP(2,1/($I12:$T12&lt;&gt;""),$I12:$T12),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V12" s="23">
+        <f>IF($G12="","",IF($U12="","",IF($G12=0,IF($U12&lt;=0,1,0),IF($E12="↓",IFERROR($G12/$U12,0),IFERROR($U12/$G12,0)))))</f>
+        <v/>
+      </c>
+      <c r="W12" s="17">
+        <f>IF($V12="","—",IF($V12&gt;=1,"✅ محقق",IF($V12&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X12" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y12" s="22" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="Z12" s="78" t="n"/>
+      <c r="AA12" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB12" s="53" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AC12" s="23">
+        <f>IF($V12="","",$AB12*MIN($V12,1))</f>
+        <v/>
+      </c>
+      <c r="AD12" s="75">
+        <f>IF($G12="","",IF($F12="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G12/12*'لوحة الإدارة التنفيذية'!$P$2),$G12))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="79">
+        <f>IF($F12="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U12="","",$U12/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U12="","",$U12))</f>
+        <v/>
+      </c>
+      <c r="AF12" s="75">
+        <f>IF(OR($AE12="",$G12=""),"",$AE12-$G12)</f>
+        <v/>
+      </c>
+      <c r="AG12" s="17">
+        <f>IF(OR($AE12="",$G12=""),"—",IF($E12="↓",IF($AE12&lt;=$G12,"🟢 على المسار",IF($AE12&lt;=$G12*1.1,"🟡 متابعة","🔴 خطر")),IF($AE12&gt;=$G12,"🟢 على المسار",IF($AE12&gt;=$G12*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH12" s="68" t="inlineStr">
+        <is>
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>الرضا والثقافة</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>تحسين مستوى الرضا الوظيفي</t>
+        </is>
+      </c>
+      <c r="D13" s="60" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E13" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F13" s="60" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="G13" s="60" t="inlineStr"/>
+      <c r="H13" s="62" t="inlineStr">
+        <is>
+          <t>مستهدف سنوي</t>
+        </is>
+      </c>
+      <c r="I13" s="73" t="n"/>
+      <c r="J13" s="73" t="n"/>
+      <c r="K13" s="73" t="n"/>
+      <c r="L13" s="73" t="n"/>
+      <c r="M13" s="73" t="n"/>
+      <c r="N13" s="73" t="n"/>
+      <c r="O13" s="73" t="n"/>
+      <c r="P13" s="73" t="n"/>
+      <c r="Q13" s="73" t="n"/>
+      <c r="R13" s="73" t="n"/>
+      <c r="S13" s="73" t="n"/>
+      <c r="T13" s="73" t="n"/>
+      <c r="U13" s="59">
+        <f>IF($F13="SUM",IF(COUNT($I13:$T13)=0,"",SUM($I13:$T13)),IF($F13="AVG",IFERROR(AVERAGE($I13:$T13),""),IF($F13="LAST",IFERROR(LOOKUP(2,1/($I13:$T13&lt;&gt;""),$I13:$T13),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V13" s="23">
+        <f>IF($G13="","",IF($U13="","",IF($G13=0,IF($U13&lt;=0,1,0),IF($E13="↓",IFERROR($G13/$U13,0),IFERROR($U13/$G13,0)))))</f>
+        <v/>
+      </c>
+      <c r="W13" s="17">
+        <f>IF($V13="","—",IF($V13&gt;=1,"✅ محقق",IF($V13&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X13" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y13" s="22" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="Z13" s="53" t="n"/>
+      <c r="AA13" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB13" s="53" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AC13" s="23">
+        <f>IF($V13="","",$AB13*MIN($V13,1))</f>
+        <v/>
+      </c>
+      <c r="AD13" s="74">
+        <f>IF($G13="","",IF($F13="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G13/12*'لوحة الإدارة التنفيذية'!$P$2),$G13))</f>
+        <v/>
+      </c>
+      <c r="AE13" s="23">
+        <f>IF($F13="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U13="","",$U13/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U13="","",$U13))</f>
+        <v/>
+      </c>
+      <c r="AF13" s="74">
+        <f>IF(OR($AE13="",$G13=""),"",$AE13-$G13)</f>
+        <v/>
+      </c>
+      <c r="AG13" s="17">
+        <f>IF(OR($AE13="",$G13=""),"—",IF($E13="↓",IF($AE13&lt;=$G13,"🟢 على المسار",IF($AE13&lt;=$G13*1.1,"🟡 متابعة","🔴 خطر")),IF($AE13&gt;=$G13,"🟢 على المسار",IF($AE13&gt;=$G13*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH13" s="68" t="inlineStr">
+        <is>
+          <t>العملاء</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>الرضا والثقافة</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>ترسيخ القيم والثقافة المؤسسية</t>
+        </is>
+      </c>
+      <c r="D14" s="60" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E14" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F14" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G14" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="62" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I14" s="73" t="n"/>
+      <c r="J14" s="73" t="n"/>
+      <c r="K14" s="73" t="n"/>
+      <c r="L14" s="73" t="n"/>
+      <c r="M14" s="73" t="n"/>
+      <c r="N14" s="73" t="n"/>
+      <c r="O14" s="73" t="n"/>
+      <c r="P14" s="73" t="n"/>
+      <c r="Q14" s="73" t="n"/>
+      <c r="R14" s="73" t="n"/>
+      <c r="S14" s="73" t="n"/>
+      <c r="T14" s="73" t="n"/>
+      <c r="U14" s="59">
+        <f>IF($F14="SUM",IF(COUNT($I14:$T14)=0,"",SUM($I14:$T14)),IF($F14="AVG",IFERROR(AVERAGE($I14:$T14),""),IF($F14="LAST",IFERROR(LOOKUP(2,1/($I14:$T14&lt;&gt;""),$I14:$T14),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V14" s="23">
+        <f>IF($G14="","",IF($U14="","",IF($G14=0,IF($U14&lt;=0,1,0),IF($E14="↓",IFERROR($G14/$U14,0),IFERROR($U14/$G14,0)))))</f>
+        <v/>
+      </c>
+      <c r="W14" s="17">
+        <f>IF($V14="","—",IF($V14&gt;=1,"✅ محقق",IF($V14&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X14" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y14" s="22" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="Z14" s="53" t="n"/>
+      <c r="AA14" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB14" s="53" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AC14" s="23">
+        <f>IF($V14="","",$AB14*MIN($V14,1))</f>
+        <v/>
+      </c>
+      <c r="AD14" s="74">
+        <f>IF($G14="","",IF($F14="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G14/12*'لوحة الإدارة التنفيذية'!$P$2),$G14))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="23">
+        <f>IF($F14="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U14="","",$U14/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U14="","",$U14))</f>
+        <v/>
+      </c>
+      <c r="AF14" s="74">
+        <f>IF(OR($AE14="",$G14=""),"",$AE14-$G14)</f>
+        <v/>
+      </c>
+      <c r="AG14" s="17">
+        <f>IF(OR($AE14="",$G14=""),"—",IF($E14="↓",IF($AE14&lt;=$G14,"🟢 على المسار",IF($AE14&lt;=$G14*1.1,"🟡 متابعة","🔴 خطر")),IF($AE14&gt;=$G14,"🟢 على المسار",IF($AE14&gt;=$G14*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH14" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>الأتمتة والتوثيق</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>نسبة أتمتة عمليات الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="D15" s="60" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E15" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F15" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G15" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="62" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="73" t="n"/>
+      <c r="J15" s="73" t="n"/>
+      <c r="K15" s="73" t="n"/>
+      <c r="L15" s="73" t="n"/>
+      <c r="M15" s="73" t="n"/>
+      <c r="N15" s="73" t="n"/>
+      <c r="O15" s="73" t="n"/>
+      <c r="P15" s="73" t="n"/>
+      <c r="Q15" s="73" t="n"/>
+      <c r="R15" s="73" t="n"/>
+      <c r="S15" s="73" t="n"/>
+      <c r="T15" s="73" t="n"/>
+      <c r="U15" s="59">
+        <f>IF($F15="SUM",IF(COUNT($I15:$T15)=0,"",SUM($I15:$T15)),IF($F15="AVG",IFERROR(AVERAGE($I15:$T15),""),IF($F15="LAST",IFERROR(LOOKUP(2,1/($I15:$T15&lt;&gt;""),$I15:$T15),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V15" s="23">
+        <f>IF($G15="","",IF($U15="","",IF($G15=0,IF($U15&lt;=0,1,0),IF($E15="↓",IFERROR($G15/$U15,0),IFERROR($U15/$G15,0)))))</f>
+        <v/>
+      </c>
+      <c r="W15" s="17">
+        <f>IF($V15="","—",IF($V15&gt;=1,"✅ محقق",IF($V15&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X15" s="65" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="Y15" s="22" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="Z15" s="53" t="n"/>
+      <c r="AA15" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB15" s="53" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AC15" s="23">
+        <f>IF($V15="","",$AB15*MIN($V15,1))</f>
+        <v/>
+      </c>
+      <c r="AD15" s="74">
+        <f>IF($G15="","",IF($F15="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G15/12*'لوحة الإدارة التنفيذية'!$P$2),$G15))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="23">
+        <f>IF($F15="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U15="","",$U15/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U15="","",$U15))</f>
+        <v/>
+      </c>
+      <c r="AF15" s="74">
+        <f>IF(OR($AE15="",$G15=""),"",$AE15-$G15)</f>
+        <v/>
+      </c>
+      <c r="AG15" s="17">
+        <f>IF(OR($AE15="",$G15=""),"—",IF($E15="↓",IF($AE15&lt;=$G15,"🟢 على المسار",IF($AE15&lt;=$G15*1.1,"🟡 متابعة","🔴 خطر")),IF($AE15&gt;=$G15,"🟢 على المسار",IF($AE15&gt;=$G15*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH15" s="68" t="inlineStr">
+        <is>
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>الأتمتة والتوثيق</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>نسبة توثيق أنظمة العمل</t>
+        </is>
+      </c>
+      <c r="D16" s="60" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E16" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F16" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G16" s="74" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H16" s="62" t="inlineStr">
+        <is>
+          <t>≥ 80%</t>
+        </is>
+      </c>
+      <c r="I16" s="73" t="n"/>
+      <c r="J16" s="73" t="n"/>
+      <c r="K16" s="73" t="n"/>
+      <c r="L16" s="73" t="n"/>
+      <c r="M16" s="73" t="n"/>
+      <c r="N16" s="73" t="n"/>
+      <c r="O16" s="73" t="n"/>
+      <c r="P16" s="73" t="n"/>
+      <c r="Q16" s="73" t="n"/>
+      <c r="R16" s="73" t="n"/>
+      <c r="S16" s="73" t="n"/>
+      <c r="T16" s="73" t="n"/>
+      <c r="U16" s="59">
+        <f>IF($F16="SUM",IF(COUNT($I16:$T16)=0,"",SUM($I16:$T16)),IF($F16="AVG",IFERROR(AVERAGE($I16:$T16),""),IF($F16="LAST",IFERROR(LOOKUP(2,1/($I16:$T16&lt;&gt;""),$I16:$T16),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V16" s="23">
+        <f>IF($G16="","",IF($U16="","",IF($G16=0,IF($U16&lt;=0,1,0),IF($E16="↓",IFERROR($G16/$U16,0),IFERROR($U16/$G16,0)))))</f>
+        <v/>
+      </c>
+      <c r="W16" s="17">
+        <f>IF($V16="","—",IF($V16&gt;=1,"✅ محقق",IF($V16&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X16" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y16" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z16" s="53" t="n"/>
+      <c r="AA16" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB16" s="53" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AC16" s="23">
+        <f>IF($V16="","",$AB16*MIN($V16,1))</f>
+        <v/>
+      </c>
+      <c r="AD16" s="74">
+        <f>IF($G16="","",IF($F16="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G16/12*'لوحة الإدارة التنفيذية'!$P$2),$G16))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="23">
+        <f>IF($F16="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U16="","",$U16/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U16="","",$U16))</f>
+        <v/>
+      </c>
+      <c r="AF16" s="74">
+        <f>IF(OR($AE16="",$G16=""),"",$AE16-$G16)</f>
+        <v/>
+      </c>
+      <c r="AG16" s="17">
+        <f>IF(OR($AE16="",$G16=""),"—",IF($E16="↓",IF($AE16&lt;=$G16,"🟢 على المسار",IF($AE16&lt;=$G16*1.1,"🟡 متابعة","🔴 خطر")),IF($AE16&gt;=$G16,"🟢 على المسار",IF($AE16&gt;=$G16*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH16" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>الأتمتة والتوثيق</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>ترسيخ الأنظمة الإدارية</t>
+        </is>
+      </c>
+      <c r="D17" s="60" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E17" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F17" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G17" s="74" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H17" s="62" t="inlineStr">
+        <is>
+          <t>≥ 80%</t>
+        </is>
+      </c>
+      <c r="I17" s="73" t="n"/>
+      <c r="J17" s="73" t="n"/>
+      <c r="K17" s="73" t="n"/>
+      <c r="L17" s="73" t="n"/>
+      <c r="M17" s="73" t="n"/>
+      <c r="N17" s="73" t="n"/>
+      <c r="O17" s="73" t="n"/>
+      <c r="P17" s="73" t="n"/>
+      <c r="Q17" s="73" t="n"/>
+      <c r="R17" s="73" t="n"/>
+      <c r="S17" s="73" t="n"/>
+      <c r="T17" s="73" t="n"/>
+      <c r="U17" s="59">
+        <f>IF($F17="SUM",IF(COUNT($I17:$T17)=0,"",SUM($I17:$T17)),IF($F17="AVG",IFERROR(AVERAGE($I17:$T17),""),IF($F17="LAST",IFERROR(LOOKUP(2,1/($I17:$T17&lt;&gt;""),$I17:$T17),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V17" s="23">
+        <f>IF($G17="","",IF($U17="","",IF($G17=0,IF($U17&lt;=0,1,0),IF($E17="↓",IFERROR($G17/$U17,0),IFERROR($U17/$G17,0)))))</f>
+        <v/>
+      </c>
+      <c r="W17" s="17">
+        <f>IF($V17="","—",IF($V17&gt;=1,"✅ محقق",IF($V17&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X17" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y17" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z17" s="53" t="n"/>
+      <c r="AA17" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB17" s="53" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AC17" s="23">
+        <f>IF($V17="","",$AB17*MIN($V17,1))</f>
+        <v/>
+      </c>
+      <c r="AD17" s="74">
+        <f>IF($G17="","",IF($F17="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G17/12*'لوحة الإدارة التنفيذية'!$P$2),$G17))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="23">
+        <f>IF($F17="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U17="","",$U17/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U17="","",$U17))</f>
+        <v/>
+      </c>
+      <c r="AF17" s="74">
+        <f>IF(OR($AE17="",$G17=""),"",$AE17-$G17)</f>
+        <v/>
+      </c>
+      <c r="AG17" s="17">
+        <f>IF(OR($AE17="",$G17=""),"—",IF($E17="↓",IF($AE17&lt;=$G17,"🟢 على المسار",IF($AE17&lt;=$G17*1.1,"🟡 متابعة","🔴 خطر")),IF($AE17&gt;=$G17,"🟢 على المسار",IF($AE17&gt;=$G17*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH17" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>الهيكلة</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>اعتماد الهيكل التنظيمي</t>
+        </is>
+      </c>
+      <c r="D18" s="60" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E18" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F18" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G18" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="62" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="73" t="n"/>
+      <c r="J18" s="73" t="n"/>
+      <c r="K18" s="73" t="n"/>
+      <c r="L18" s="73" t="n"/>
+      <c r="M18" s="73" t="n"/>
+      <c r="N18" s="73" t="n"/>
+      <c r="O18" s="73" t="n"/>
+      <c r="P18" s="73" t="n"/>
+      <c r="Q18" s="73" t="n"/>
+      <c r="R18" s="73" t="n"/>
+      <c r="S18" s="73" t="n"/>
+      <c r="T18" s="73" t="n"/>
+      <c r="U18" s="59">
+        <f>IF($F18="SUM",IF(COUNT($I18:$T18)=0,"",SUM($I18:$T18)),IF($F18="AVG",IFERROR(AVERAGE($I18:$T18),""),IF($F18="LAST",IFERROR(LOOKUP(2,1/($I18:$T18&lt;&gt;""),$I18:$T18),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V18" s="23">
+        <f>IF($G18="","",IF($U18="","",IF($G18=0,IF($U18&lt;=0,1,0),IF($E18="↓",IFERROR($G18/$U18,0),IFERROR($U18/$G18,0)))))</f>
+        <v/>
+      </c>
+      <c r="W18" s="17">
+        <f>IF($V18="","—",IF($V18&gt;=1,"✅ محقق",IF($V18&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X18" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y18" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z18" s="53" t="n"/>
+      <c r="AA18" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB18" s="53" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AC18" s="23">
+        <f>IF($V18="","",$AB18*MIN($V18,1))</f>
+        <v/>
+      </c>
+      <c r="AD18" s="74">
+        <f>IF($G18="","",IF($F18="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G18/12*'لوحة الإدارة التنفيذية'!$P$2),$G18))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="23">
+        <f>IF($F18="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U18="","",$U18/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U18="","",$U18))</f>
+        <v/>
+      </c>
+      <c r="AF18" s="74">
+        <f>IF(OR($AE18="",$G18=""),"",$AE18-$G18)</f>
+        <v/>
+      </c>
+      <c r="AG18" s="17">
+        <f>IF(OR($AE18="",$G18=""),"—",IF($E18="↓",IF($AE18&lt;=$G18,"🟢 على المسار",IF($AE18&lt;=$G18*1.1,"🟡 متابعة","🔴 خطر")),IF($AE18&gt;=$G18,"🟢 على المسار",IF($AE18&gt;=$G18*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH18" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>الهيكلة</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>اكتمال الأوصاف الوظيفية (+KPI)</t>
+        </is>
+      </c>
+      <c r="D19" s="60" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E19" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F19" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G19" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="62" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="73" t="n"/>
+      <c r="J19" s="73" t="n"/>
+      <c r="K19" s="73" t="n"/>
+      <c r="L19" s="73" t="n"/>
+      <c r="M19" s="73" t="n"/>
+      <c r="N19" s="73" t="n"/>
+      <c r="O19" s="73" t="n"/>
+      <c r="P19" s="73" t="n"/>
+      <c r="Q19" s="73" t="n"/>
+      <c r="R19" s="73" t="n"/>
+      <c r="S19" s="73" t="n"/>
+      <c r="T19" s="73" t="n"/>
+      <c r="U19" s="59">
+        <f>IF($F19="SUM",IF(COUNT($I19:$T19)=0,"",SUM($I19:$T19)),IF($F19="AVG",IFERROR(AVERAGE($I19:$T19),""),IF($F19="LAST",IFERROR(LOOKUP(2,1/($I19:$T19&lt;&gt;""),$I19:$T19),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V19" s="23">
+        <f>IF($G19="","",IF($U19="","",IF($G19=0,IF($U19&lt;=0,1,0),IF($E19="↓",IFERROR($G19/$U19,0),IFERROR($U19/$G19,0)))))</f>
+        <v/>
+      </c>
+      <c r="W19" s="17">
+        <f>IF($V19="","—",IF($V19&gt;=1,"✅ محقق",IF($V19&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X19" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y19" s="22" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z19" s="53" t="n"/>
+      <c r="AA19" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB19" s="53" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AC19" s="23">
+        <f>IF($V19="","",$AB19*MIN($V19,1))</f>
+        <v/>
+      </c>
+      <c r="AD19" s="74">
+        <f>IF($G19="","",IF($F19="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G19/12*'لوحة الإدارة التنفيذية'!$P$2),$G19))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="23">
+        <f>IF($F19="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U19="","",$U19/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U19="","",$U19))</f>
+        <v/>
+      </c>
+      <c r="AF19" s="74">
+        <f>IF(OR($AE19="",$G19=""),"",$AE19-$G19)</f>
+        <v/>
+      </c>
+      <c r="AG19" s="17">
+        <f>IF(OR($AE19="",$G19=""),"—",IF($E19="↓",IF($AE19&lt;=$G19,"🟢 على المسار",IF($AE19&lt;=$G19*1.1,"🟡 متابعة","🔴 خطر")),IF($AE19&gt;=$G19,"🟢 على المسار",IF($AE19&gt;=$G19*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH19" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>الأداء</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز تقييمات الأداء في موعدها</t>
+        </is>
+      </c>
+      <c r="D20" s="60" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E20" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F20" s="60" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="G20" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="62" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I20" s="73" t="n"/>
+      <c r="J20" s="73" t="n"/>
+      <c r="K20" s="73" t="n"/>
+      <c r="L20" s="73" t="n"/>
+      <c r="M20" s="73" t="n"/>
+      <c r="N20" s="73" t="n"/>
+      <c r="O20" s="73" t="n"/>
+      <c r="P20" s="73" t="n"/>
+      <c r="Q20" s="73" t="n"/>
+      <c r="R20" s="73" t="n"/>
+      <c r="S20" s="73" t="n"/>
+      <c r="T20" s="73" t="n"/>
+      <c r="U20" s="59">
+        <f>IF($F20="SUM",IF(COUNT($I20:$T20)=0,"",SUM($I20:$T20)),IF($F20="AVG",IFERROR(AVERAGE($I20:$T20),""),IF($F20="LAST",IFERROR(LOOKUP(2,1/($I20:$T20&lt;&gt;""),$I20:$T20),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V20" s="23">
+        <f>IF($G20="","",IF($U20="","",IF($G20=0,IF($U20&lt;=0,1,0),IF($E20="↓",IFERROR($G20/$U20,0),IFERROR($U20/$G20,0)))))</f>
+        <v/>
+      </c>
+      <c r="W20" s="17">
+        <f>IF($V20="","—",IF($V20&gt;=1,"✅ محقق",IF($V20&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X20" s="65" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="Y20" s="22" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="Z20" s="53" t="n"/>
+      <c r="AA20" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB20" s="53" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AC20" s="23">
+        <f>IF($V20="","",$AB20*MIN($V20,1))</f>
+        <v/>
+      </c>
+      <c r="AD20" s="74">
+        <f>IF($G20="","",IF($F20="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G20/12*'لوحة الإدارة التنفيذية'!$P$2),$G20))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="23">
+        <f>IF($F20="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U20="","",$U20/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U20="","",$U20))</f>
+        <v/>
+      </c>
+      <c r="AF20" s="74">
+        <f>IF(OR($AE20="",$G20=""),"",$AE20-$G20)</f>
+        <v/>
+      </c>
+      <c r="AG20" s="17">
+        <f>IF(OR($AE20="",$G20=""),"—",IF($E20="↓",IF($AE20&lt;=$G20,"🟢 على المسار",IF($AE20&lt;=$G20*1.1,"🟡 متابعة","🔴 خطر")),IF($AE20&gt;=$G20,"🟢 على المسار",IF($AE20&gt;=$G20*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH20" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="80" t="inlineStr"/>
+      <c r="B21" s="81" t="inlineStr">
         <is>
           <t>الإجمالي الموزون للإدارة</t>
         </is>
       </c>
-      <c r="AB12" s="82">
-        <f>SUM(AB4:AB11)</f>
-        <v/>
-      </c>
-      <c r="AC12" s="83">
-        <f>SUM(AC4:AC11)</f>
+      <c r="AB21" s="82">
+        <f>SUM(AB4:AB20)</f>
+        <v/>
+      </c>
+      <c r="AC21" s="83">
+        <f>SUM(AC4:AC20)</f>
         <v/>
       </c>
     </row>
@@ -24633,10 +27289,10 @@
   <mergeCells count="3">
     <mergeCell ref="A2:AH2"/>
     <mergeCell ref="A1:AH1"/>
-    <mergeCell ref="B12:AA12"/>
+    <mergeCell ref="B21:AA21"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 J4 J5 J6 J7 J8 J9 J10 J11 K4 K5 K6 K7 K8 K9 K10 K11 L4 L5 L6 L7 L8 L9 L10 L11 M4 M5 M6 M7 M8 M9 M10 M11 N4 N5 N6 N7 N8 N9 N10 N11 O4 O5 O6 O7 O8 O9 O10 O11 P4 P5 P6 P7 P8 P9 P10 P11 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 R4 R5 R6 R7 R8 R9 R10 R11 S4 S5 S6 S7 S8 S9 S10 S11 T4 T5 T6 T7 T8 T9 T10 T11 Z4 Z5 Z6 Z7 Z8 Z9 Z10 Z11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="قيمة غير صحيحة" error="أدخل رقماً موجباً فقط" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 N4 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 S4 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 T4 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 Z4 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="قيمة غير صحيحة" error="أدخل رقماً موجباً فقط" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -25598,7 +28254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K134"/>
+  <dimension ref="A1:K159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -30898,12 +33554,12 @@
       </c>
       <c r="C106" s="91" t="inlineStr">
         <is>
-          <t>عدد مستخدمي تطبيق «تانكي» النشطين شهرياً (MAU)</t>
+          <t>نظام أتمتة الكاش (Cash-In) في المحطات</t>
         </is>
       </c>
       <c r="D106" s="68" t="inlineStr">
         <is>
-          <t>مستخدم</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E106" s="92" t="inlineStr">
@@ -30913,7 +33569,7 @@
       </c>
       <c r="F106" s="68" t="inlineStr">
         <is>
-          <t>يُحدد لاحقاً</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G106" s="68" t="inlineStr">
@@ -30923,7 +33579,7 @@
       </c>
       <c r="H106" s="91" t="inlineStr">
         <is>
-          <t>تطبيق «تانكي»</t>
+          <t>التحول التقني</t>
         </is>
       </c>
       <c r="I106" s="68" t="inlineStr">
@@ -30933,7 +33589,7 @@
       </c>
       <c r="J106" s="68" t="inlineStr">
         <is>
-          <t>🔵 قائد</t>
+          <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="K106" s="38" t="n"/>
@@ -30949,22 +33605,22 @@
       </c>
       <c r="C107" s="91" t="inlineStr">
         <is>
-          <t>نمو تنزيلات تطبيق تانكي</t>
+          <t>D365 FNO — المرحلة الأولى</t>
         </is>
       </c>
       <c r="D107" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>وحدة</t>
         </is>
       </c>
       <c r="E107" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F107" s="68" t="inlineStr">
         <is>
-          <t>يُحدد لاحقاً</t>
+          <t>5 وحدات</t>
         </is>
       </c>
       <c r="G107" s="68" t="inlineStr">
@@ -30974,17 +33630,17 @@
       </c>
       <c r="H107" s="91" t="inlineStr">
         <is>
-          <t>تطبيق «تانكي»</t>
+          <t>التحول التقني</t>
         </is>
       </c>
       <c r="I107" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J107" s="68" t="inlineStr">
         <is>
-          <t>🔵 قائد</t>
+          <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="K107" s="38" t="n"/>
@@ -31000,22 +33656,22 @@
       </c>
       <c r="C108" s="91" t="inlineStr">
         <is>
-          <t>نسبة المعاملات الرقمية عبر تانكي</t>
+          <t>D365 FNO — المرحلة الثانية</t>
         </is>
       </c>
       <c r="D108" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>وحدة</t>
         </is>
       </c>
       <c r="E108" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F108" s="68" t="inlineStr">
         <is>
-          <t>يُحدد لاحقاً</t>
+          <t>4 وحدات</t>
         </is>
       </c>
       <c r="G108" s="68" t="inlineStr">
@@ -31025,12 +33681,12 @@
       </c>
       <c r="H108" s="91" t="inlineStr">
         <is>
-          <t>تطبيق «تانكي»</t>
+          <t>التحول التقني</t>
         </is>
       </c>
       <c r="I108" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J108" s="68" t="inlineStr">
@@ -31051,22 +33707,22 @@
       </c>
       <c r="C109" s="91" t="inlineStr">
         <is>
-          <t>معدل رضا مستخدمي تطبيق تانكي</t>
+          <t>D365 FNO — المرحلة الثالثة</t>
         </is>
       </c>
       <c r="D109" s="68" t="inlineStr">
         <is>
-          <t>نجمة/5</t>
+          <t>وحدة</t>
         </is>
       </c>
       <c r="E109" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F109" s="68" t="inlineStr">
         <is>
-          <t>≥ 4.5</t>
+          <t>وحدتان</t>
         </is>
       </c>
       <c r="G109" s="68" t="inlineStr">
@@ -31076,12 +33732,12 @@
       </c>
       <c r="H109" s="91" t="inlineStr">
         <is>
-          <t>تطبيق «تانكي»</t>
+          <t>التحول التقني</t>
         </is>
       </c>
       <c r="I109" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J109" s="68" t="inlineStr">
@@ -31102,12 +33758,12 @@
       </c>
       <c r="C110" s="91" t="inlineStr">
         <is>
-          <t>نسبة أتمتة العمليات الأساسية (شركة)</t>
+          <t>تطبيق الامتياز مع واثق</t>
         </is>
       </c>
       <c r="D110" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>تطبيق</t>
         </is>
       </c>
       <c r="E110" s="92" t="inlineStr">
@@ -31117,7 +33773,7 @@
       </c>
       <c r="F110" s="68" t="inlineStr">
         <is>
-          <t>يُحدد لاحقاً</t>
+          <t>تطبيق واحد</t>
         </is>
       </c>
       <c r="G110" s="68" t="inlineStr">
@@ -31132,7 +33788,7 @@
       </c>
       <c r="I110" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J110" s="68" t="inlineStr">
@@ -31153,22 +33809,22 @@
       </c>
       <c r="C111" s="91" t="inlineStr">
         <is>
-          <t>نسبة جاهزية الأنظمة (Uptime)</t>
+          <t>ربط المحطات بوزارة الطاقة (ATJ)</t>
         </is>
       </c>
       <c r="D111" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E111" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F111" s="68" t="inlineStr">
         <is>
-          <t>≥ 99.5%</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G111" s="68" t="inlineStr">
@@ -31204,22 +33860,22 @@
       </c>
       <c r="C112" s="91" t="inlineStr">
         <is>
-          <t>متوسط زمن حل أعطال الأنظمة</t>
+          <t>ربط الكاميرات بالمركز الرئيسي</t>
         </is>
       </c>
       <c r="D112" s="68" t="inlineStr">
         <is>
-          <t>ساعة</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E112" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F112" s="68" t="inlineStr">
         <is>
-          <t>≤ 4 ساعات</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G112" s="68" t="inlineStr">
@@ -31255,22 +33911,22 @@
       </c>
       <c r="C113" s="91" t="inlineStr">
         <is>
-          <t>نسبة المشاريع التقنية المنجزة في الوقت</t>
+          <t>تطبيق الولاء (تانكي) في المحطات</t>
         </is>
       </c>
       <c r="D113" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E113" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F113" s="68" t="inlineStr">
         <is>
-          <t>≥ 90%</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G113" s="68" t="inlineStr">
@@ -31280,7 +33936,7 @@
       </c>
       <c r="H113" s="91" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>تطبيق «تانكي»</t>
         </is>
       </c>
       <c r="I113" s="68" t="inlineStr">
@@ -31301,17 +33957,17 @@
       </c>
       <c r="B114" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C114" s="91" t="inlineStr">
         <is>
-          <t>معدل استبقاء الموظفين (Retention)</t>
+          <t>منصة Tatin السحابية</t>
         </is>
       </c>
       <c r="D114" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E114" s="92" t="inlineStr">
@@ -31321,22 +33977,22 @@
       </c>
       <c r="F114" s="68" t="inlineStr">
         <is>
-          <t>≥ 90%</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G114" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="H114" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>التحول التقني</t>
         </is>
       </c>
       <c r="I114" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J114" s="68" t="inlineStr">
@@ -31352,42 +34008,42 @@
       </c>
       <c r="B115" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C115" s="91" t="inlineStr">
         <is>
-          <t>معدل دوران الموظفين (Turnover)</t>
+          <t>إدارة العمليات بالذكاء الاصطناعي</t>
         </is>
       </c>
       <c r="D115" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E115" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F115" s="68" t="inlineStr">
         <is>
-          <t>≤ 10%</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G115" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="H115" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>التحول التقني</t>
         </is>
       </c>
       <c r="I115" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J115" s="68" t="inlineStr">
@@ -31403,27 +34059,27 @@
       </c>
       <c r="B116" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C116" s="91" t="inlineStr">
         <is>
-          <t>متوسط ساعات التدريب لكل موظف</t>
+          <t>جاهزية أتمتة المحطات (Forecourt)</t>
         </is>
       </c>
       <c r="D116" s="68" t="inlineStr">
         <is>
-          <t>ساعة</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E116" s="92" t="inlineStr">
         <is>
-          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F116" s="68" t="inlineStr">
         <is>
-          <t>≥ 40 ساعة</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G116" s="68" t="inlineStr">
@@ -31433,7 +34089,7 @@
       </c>
       <c r="H116" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I116" s="68" t="inlineStr">
@@ -31443,7 +34099,7 @@
       </c>
       <c r="J116" s="68" t="inlineStr">
         <is>
-          <t>🔵 قائد</t>
+          <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="K116" s="38" t="n"/>
@@ -31454,17 +34110,17 @@
       </c>
       <c r="B117" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C117" s="91" t="inlineStr">
         <is>
-          <t>نسبة الموظفين المشمولين بخطة تطوير</t>
+          <t>جاهزية اتصال الشبكة بالمحطات</t>
         </is>
       </c>
       <c r="D117" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E117" s="92" t="inlineStr">
@@ -31474,7 +34130,7 @@
       </c>
       <c r="F117" s="68" t="inlineStr">
         <is>
-          <t>≥ 80%</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G117" s="68" t="inlineStr">
@@ -31484,12 +34140,12 @@
       </c>
       <c r="H117" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I117" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J117" s="68" t="inlineStr">
@@ -31505,27 +34161,27 @@
       </c>
       <c r="B118" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C118" s="91" t="inlineStr">
         <is>
-          <t>مؤشر رضا الموظفين (eNPS)</t>
+          <t>جاهزية نقاط البيع والمدفوعات (POS)</t>
         </is>
       </c>
       <c r="D118" s="68" t="inlineStr">
         <is>
-          <t>نقطة</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E118" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F118" s="68" t="inlineStr">
         <is>
-          <t>≥ 30</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G118" s="68" t="inlineStr">
@@ -31535,12 +34191,12 @@
       </c>
       <c r="H118" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I118" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J118" s="68" t="inlineStr">
@@ -31556,27 +34212,27 @@
       </c>
       <c r="B119" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C119" s="91" t="inlineStr">
         <is>
-          <t>نسبة شغل الشواغر خلال 30 يوم</t>
+          <t>جاهزية نظام الكاميرات (CCTV)</t>
         </is>
       </c>
       <c r="D119" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E119" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F119" s="68" t="inlineStr">
         <is>
-          <t>≥ 85%</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G119" s="68" t="inlineStr">
@@ -31586,7 +34242,7 @@
       </c>
       <c r="H119" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I119" s="68" t="inlineStr">
@@ -31607,27 +34263,27 @@
       </c>
       <c r="B120" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C120" s="91" t="inlineStr">
         <is>
-          <t>نسبة إنجاز تقييمات الأداء في موعدها</t>
+          <t>جاهزية الشبكة</t>
         </is>
       </c>
       <c r="D120" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E120" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F120" s="68" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G120" s="68" t="inlineStr">
@@ -31637,7 +34293,7 @@
       </c>
       <c r="H120" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I120" s="68" t="inlineStr">
@@ -31658,17 +34314,17 @@
       </c>
       <c r="B121" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C121" s="91" t="inlineStr">
         <is>
-          <t>نسبة السعودة</t>
+          <t>الامتثال للأمن السيبراني (المحطات)</t>
         </is>
       </c>
       <c r="D121" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E121" s="92" t="inlineStr">
@@ -31678,7 +34334,7 @@
       </c>
       <c r="F121" s="68" t="inlineStr">
         <is>
-          <t>حسب النطاق</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G121" s="68" t="inlineStr">
@@ -31688,12 +34344,12 @@
       </c>
       <c r="H121" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I121" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J121" s="68" t="inlineStr">
@@ -31709,42 +34365,42 @@
       </c>
       <c r="B122" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C122" s="91" t="inlineStr">
         <is>
-          <t>الوصول الكلي (Total Reach)</t>
+          <t>زمن استجابة الدعم الفني (المحطات)</t>
         </is>
       </c>
       <c r="D122" s="68" t="inlineStr">
         <is>
-          <t>وصول</t>
+          <t>يوم</t>
         </is>
       </c>
       <c r="E122" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F122" s="68" t="inlineStr">
         <is>
-          <t>50م وصول</t>
+          <t>≤ يوم</t>
         </is>
       </c>
       <c r="G122" s="68" t="inlineStr">
         <is>
-          <t>النمو</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H122" s="91" t="inlineStr">
         <is>
-          <t>زيادة وصول العملاء</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I122" s="68" t="inlineStr">
         <is>
-          <t>العملاء</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J122" s="68" t="inlineStr">
@@ -31760,42 +34416,42 @@
       </c>
       <c r="B123" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C123" s="91" t="inlineStr">
         <is>
-          <t>عملاء تجاريون جدد</t>
+          <t>ERP والتكامل (المحطات)</t>
         </is>
       </c>
       <c r="D123" s="68" t="inlineStr">
         <is>
-          <t>عميل</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E123" s="92" t="inlineStr">
         <is>
-          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F123" s="68" t="inlineStr">
         <is>
-          <t>200 عميل</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G123" s="68" t="inlineStr">
         <is>
-          <t>النمو</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H123" s="91" t="inlineStr">
         <is>
-          <t>زيادة وصول العملاء</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I123" s="68" t="inlineStr">
         <is>
-          <t>العملاء</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J123" s="68" t="inlineStr">
@@ -31811,17 +34467,17 @@
       </c>
       <c r="B124" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C124" s="91" t="inlineStr">
         <is>
-          <t>إجمالي المتابعين (كل المنصات)</t>
+          <t>تكامل واثق (المحطات)</t>
         </is>
       </c>
       <c r="D124" s="68" t="inlineStr">
         <is>
-          <t>متابع</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E124" s="92" t="inlineStr">
@@ -31831,17 +34487,17 @@
       </c>
       <c r="F124" s="68" t="inlineStr">
         <is>
-          <t>380ك متابع</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G124" s="68" t="inlineStr">
         <is>
-          <t>النمو</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H124" s="91" t="inlineStr">
         <is>
-          <t>زيادة وصول العملاء</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I124" s="68" t="inlineStr">
@@ -31862,37 +34518,37 @@
       </c>
       <c r="B125" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C125" s="91" t="inlineStr">
         <is>
-          <t>معدل التفاعل (Engagement)</t>
+          <t>تكامل تطبيق الولاء (المحطات)</t>
         </is>
       </c>
       <c r="D125" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>محطة</t>
         </is>
       </c>
       <c r="E125" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F125" s="68" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>164 محطة</t>
         </is>
       </c>
       <c r="G125" s="68" t="inlineStr">
         <is>
-          <t>النمو</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H125" s="91" t="inlineStr">
         <is>
-          <t>زيادة وصول العملاء</t>
+          <t>تطبيق «تانكي»</t>
         </is>
       </c>
       <c r="I125" s="68" t="inlineStr">
@@ -31913,37 +34569,37 @@
       </c>
       <c r="B126" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C126" s="91" t="inlineStr">
         <is>
-          <t>حملات تسويقية منجزة</t>
+          <t>جاهزية شبكة المركز الرئيسي</t>
         </is>
       </c>
       <c r="D126" s="68" t="inlineStr">
         <is>
-          <t>حملة</t>
+          <t>ساعة</t>
         </is>
       </c>
       <c r="E126" s="92" t="inlineStr">
         <is>
-          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F126" s="68" t="inlineStr">
         <is>
-          <t>48 حملة</t>
+          <t>24 ساعة</t>
         </is>
       </c>
       <c r="G126" s="68" t="inlineStr">
         <is>
-          <t>النمو</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H126" s="91" t="inlineStr">
         <is>
-          <t>زيادة وصول العملاء</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I126" s="68" t="inlineStr">
@@ -31953,7 +34609,7 @@
       </c>
       <c r="J126" s="68" t="inlineStr">
         <is>
-          <t>🔵 قائد</t>
+          <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="K126" s="38" t="n"/>
@@ -31964,37 +34620,37 @@
       </c>
       <c r="B127" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C127" s="91" t="inlineStr">
         <is>
-          <t>تحويل الفرص إلى عقود</t>
+          <t>جاهزية تطبيقات المركز الرئيسي</t>
         </is>
       </c>
       <c r="D127" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ساعة</t>
         </is>
       </c>
       <c r="E127" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F127" s="68" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>24 ساعة</t>
         </is>
       </c>
       <c r="G127" s="68" t="inlineStr">
         <is>
-          <t>النمو</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H127" s="91" t="inlineStr">
         <is>
-          <t>زيادة وصول العملاء</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I127" s="68" t="inlineStr">
@@ -32004,7 +34660,7 @@
       </c>
       <c r="J127" s="68" t="inlineStr">
         <is>
-          <t>🔵 قائد</t>
+          <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="K127" s="38" t="n"/>
@@ -32015,17 +34671,17 @@
       </c>
       <c r="B128" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C128" s="91" t="inlineStr">
         <is>
-          <t>نسبة المبيعات لكل حملة</t>
+          <t>زمن استجابة الدعم (المركز)</t>
         </is>
       </c>
       <c r="D128" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ساعة</t>
         </is>
       </c>
       <c r="E128" s="92" t="inlineStr">
@@ -32035,27 +34691,27 @@
       </c>
       <c r="F128" s="68" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>≤ ساعة</t>
         </is>
       </c>
       <c r="G128" s="68" t="inlineStr">
         <is>
-          <t>النمو</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H128" s="91" t="inlineStr">
         <is>
-          <t>زيادة وصول العملاء</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I128" s="68" t="inlineStr">
         <is>
-          <t>مالي</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J128" s="68" t="inlineStr">
         <is>
-          <t>🔵 قائد</t>
+          <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="K128" s="38" t="n"/>
@@ -32066,12 +34722,12 @@
       </c>
       <c r="B129" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C129" s="91" t="inlineStr">
         <is>
-          <t>نسبة التزام الهوية البصرية</t>
+          <t>الامتثال للأمن السيبراني (المركز)</t>
         </is>
       </c>
       <c r="D129" s="68" t="inlineStr">
@@ -32091,17 +34747,17 @@
       </c>
       <c r="G129" s="68" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H129" s="91" t="inlineStr">
         <is>
-          <t>تطوير التصاميم والهوية</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I129" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J129" s="68" t="inlineStr">
@@ -32117,17 +34773,17 @@
       </c>
       <c r="B130" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C130" s="91" t="inlineStr">
         <is>
-          <t>وصول العلاقات العامة (PR)</t>
+          <t>نسبة السعودة / التوطين</t>
         </is>
       </c>
       <c r="D130" s="68" t="inlineStr">
         <is>
-          <t>وصول</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E130" s="92" t="inlineStr">
@@ -32137,22 +34793,22 @@
       </c>
       <c r="F130" s="68" t="inlineStr">
         <is>
-          <t>7م وصول</t>
+          <t>أخضر مرتفع (حسب الوزارة)</t>
         </is>
       </c>
       <c r="G130" s="68" t="inlineStr">
         <is>
-          <t>النمو</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H130" s="91" t="inlineStr">
         <is>
-          <t>زيادة وصول العملاء</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I130" s="68" t="inlineStr">
         <is>
-          <t>العملاء</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="J130" s="68" t="inlineStr">
@@ -32168,37 +34824,37 @@
       </c>
       <c r="B131" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C131" s="91" t="inlineStr">
         <is>
-          <t>عدد المعارض بالسنة</t>
+          <t>الارتقاء بآليات اختيار المرشحين</t>
         </is>
       </c>
       <c r="D131" s="68" t="inlineStr">
         <is>
-          <t>معرض</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E131" s="92" t="inlineStr">
         <is>
-          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F131" s="68" t="inlineStr">
         <is>
-          <t>3 معارض</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G131" s="68" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H131" s="91" t="inlineStr">
         <is>
-          <t>إطلاق مشاريع جديدة</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I131" s="68" t="inlineStr">
@@ -32208,7 +34864,7 @@
       </c>
       <c r="J131" s="68" t="inlineStr">
         <is>
-          <t>🔵 قائد</t>
+          <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="K131" s="38" t="n"/>
@@ -32219,37 +34875,37 @@
       </c>
       <c r="B132" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C132" s="91" t="inlineStr">
         <is>
-          <t>اتفاقيات استراتيجية</t>
+          <t>نسبة شغل الشواغر خلال 30 يوم</t>
         </is>
       </c>
       <c r="D132" s="68" t="inlineStr">
         <is>
-          <t>اتفاقية</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E132" s="92" t="inlineStr">
         <is>
-          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F132" s="68" t="inlineStr">
         <is>
-          <t>3 اتفاقيات</t>
+          <t>≥ 85%</t>
         </is>
       </c>
       <c r="G132" s="68" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H132" s="91" t="inlineStr">
         <is>
-          <t>إطلاق مشاريع جديدة</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I132" s="68" t="inlineStr">
@@ -32270,27 +34926,27 @@
       </c>
       <c r="B133" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C133" s="91" t="inlineStr">
         <is>
-          <t>تقييم خرائط قوقل</t>
+          <t>معدل استبقاء الموظفين (Retention)</t>
         </is>
       </c>
       <c r="D133" s="68" t="inlineStr">
         <is>
-          <t>نجمة/5</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E133" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F133" s="68" t="inlineStr">
         <is>
-          <t>4.7 ⭐</t>
+          <t>≥ 90%</t>
         </is>
       </c>
       <c r="G133" s="68" t="inlineStr">
@@ -32300,12 +34956,12 @@
       </c>
       <c r="H133" s="91" t="inlineStr">
         <is>
-          <t>تعزيز تجربة العملاء</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I133" s="68" t="inlineStr">
         <is>
-          <t>العملاء</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="J133" s="68" t="inlineStr">
@@ -32321,50 +34977,1325 @@
       </c>
       <c r="B134" s="91" t="inlineStr">
         <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C134" s="91" t="inlineStr">
+        <is>
+          <t>معدل دوران الموظفين (Turnover)</t>
+        </is>
+      </c>
+      <c r="D134" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E134" s="92" t="inlineStr">
+        <is>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F134" s="68" t="inlineStr">
+        <is>
+          <t>≤ 10%</t>
+        </is>
+      </c>
+      <c r="G134" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H134" s="91" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="I134" s="68" t="inlineStr">
+        <is>
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="J134" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K134" s="38" t="n"/>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="68" t="n">
+        <v>132</v>
+      </c>
+      <c r="B135" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C135" s="91" t="inlineStr">
+        <is>
+          <t>عدد الدورات الإدارية المنعقدة</t>
+        </is>
+      </c>
+      <c r="D135" s="68" t="inlineStr">
+        <is>
+          <t>دورة</t>
+        </is>
+      </c>
+      <c r="E135" s="92" t="inlineStr">
+        <is>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F135" s="68" t="inlineStr">
+        <is>
+          <t>6 دورات</t>
+        </is>
+      </c>
+      <c r="G135" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H135" s="91" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="I135" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J135" s="68" t="inlineStr">
+        <is>
+          <t>🔵 قائد</t>
+        </is>
+      </c>
+      <c r="K135" s="38" t="n"/>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="68" t="n">
+        <v>133</v>
+      </c>
+      <c r="B136" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C136" s="91" t="inlineStr">
+        <is>
+          <t>متوسط ساعات التدريب لكل موظف</t>
+        </is>
+      </c>
+      <c r="D136" s="68" t="inlineStr">
+        <is>
+          <t>ساعة</t>
+        </is>
+      </c>
+      <c r="E136" s="92" t="inlineStr">
+        <is>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F136" s="68" t="inlineStr">
+        <is>
+          <t>≥ 40 ساعة</t>
+        </is>
+      </c>
+      <c r="G136" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H136" s="91" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="I136" s="68" t="inlineStr">
+        <is>
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="J136" s="68" t="inlineStr">
+        <is>
+          <t>🔵 قائد</t>
+        </is>
+      </c>
+      <c r="K136" s="38" t="n"/>
+    </row>
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="68" t="n">
+        <v>134</v>
+      </c>
+      <c r="B137" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C137" s="91" t="inlineStr">
+        <is>
+          <t>نسبة الموظفين المشمولين بخطة تطوير</t>
+        </is>
+      </c>
+      <c r="D137" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E137" s="92" t="inlineStr">
+        <is>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F137" s="68" t="inlineStr">
+        <is>
+          <t>≥ 80%</t>
+        </is>
+      </c>
+      <c r="G137" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H137" s="91" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="I137" s="68" t="inlineStr">
+        <is>
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="J137" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K137" s="38" t="n"/>
+    </row>
+    <row r="138" ht="22" customHeight="1">
+      <c r="A138" s="68" t="n">
+        <v>135</v>
+      </c>
+      <c r="B138" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C138" s="91" t="inlineStr">
+        <is>
+          <t>مؤشر رضا الموظفين (eNPS)</t>
+        </is>
+      </c>
+      <c r="D138" s="68" t="inlineStr">
+        <is>
+          <t>نقطة</t>
+        </is>
+      </c>
+      <c r="E138" s="92" t="inlineStr">
+        <is>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F138" s="68" t="inlineStr">
+        <is>
+          <t>≥ 30</t>
+        </is>
+      </c>
+      <c r="G138" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H138" s="91" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="I138" s="68" t="inlineStr">
+        <is>
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="J138" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K138" s="38" t="n"/>
+    </row>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="68" t="n">
+        <v>136</v>
+      </c>
+      <c r="B139" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C139" s="91" t="inlineStr">
+        <is>
+          <t>تحسين مستوى الرضا الوظيفي</t>
+        </is>
+      </c>
+      <c r="D139" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E139" s="92" t="inlineStr">
+        <is>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F139" s="68" t="inlineStr">
+        <is>
+          <t>مستهدف سنوي</t>
+        </is>
+      </c>
+      <c r="G139" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H139" s="91" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="I139" s="68" t="inlineStr">
+        <is>
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="J139" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K139" s="38" t="n"/>
+    </row>
+    <row r="140" ht="22" customHeight="1">
+      <c r="A140" s="68" t="n">
+        <v>137</v>
+      </c>
+      <c r="B140" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C140" s="91" t="inlineStr">
+        <is>
+          <t>ترسيخ القيم والثقافة المؤسسية</t>
+        </is>
+      </c>
+      <c r="D140" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E140" s="92" t="inlineStr">
+        <is>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F140" s="68" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G140" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H140" s="91" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="I140" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J140" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K140" s="38" t="n"/>
+    </row>
+    <row r="141" ht="22" customHeight="1">
+      <c r="A141" s="68" t="n">
+        <v>138</v>
+      </c>
+      <c r="B141" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C141" s="91" t="inlineStr">
+        <is>
+          <t>نسبة أتمتة عمليات الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="D141" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E141" s="92" t="inlineStr">
+        <is>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F141" s="68" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G141" s="68" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="H141" s="91" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="I141" s="68" t="inlineStr">
+        <is>
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="J141" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K141" s="38" t="n"/>
+    </row>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="68" t="n">
+        <v>139</v>
+      </c>
+      <c r="B142" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C142" s="91" t="inlineStr">
+        <is>
+          <t>نسبة توثيق أنظمة العمل</t>
+        </is>
+      </c>
+      <c r="D142" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E142" s="92" t="inlineStr">
+        <is>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F142" s="68" t="inlineStr">
+        <is>
+          <t>≥ 80%</t>
+        </is>
+      </c>
+      <c r="G142" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H142" s="91" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="I142" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J142" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K142" s="38" t="n"/>
+    </row>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="68" t="n">
+        <v>140</v>
+      </c>
+      <c r="B143" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C143" s="91" t="inlineStr">
+        <is>
+          <t>ترسيخ الأنظمة الإدارية</t>
+        </is>
+      </c>
+      <c r="D143" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E143" s="92" t="inlineStr">
+        <is>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F143" s="68" t="inlineStr">
+        <is>
+          <t>≥ 80%</t>
+        </is>
+      </c>
+      <c r="G143" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H143" s="91" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="I143" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J143" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K143" s="38" t="n"/>
+    </row>
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="68" t="n">
+        <v>141</v>
+      </c>
+      <c r="B144" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C144" s="91" t="inlineStr">
+        <is>
+          <t>اعتماد الهيكل التنظيمي</t>
+        </is>
+      </c>
+      <c r="D144" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E144" s="92" t="inlineStr">
+        <is>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F144" s="68" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G144" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H144" s="91" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="I144" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J144" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K144" s="38" t="n"/>
+    </row>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="68" t="n">
+        <v>142</v>
+      </c>
+      <c r="B145" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C145" s="91" t="inlineStr">
+        <is>
+          <t>اكتمال الأوصاف الوظيفية (+KPI)</t>
+        </is>
+      </c>
+      <c r="D145" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E145" s="92" t="inlineStr">
+        <is>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F145" s="68" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G145" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H145" s="91" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="I145" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J145" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K145" s="38" t="n"/>
+    </row>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="68" t="n">
+        <v>143</v>
+      </c>
+      <c r="B146" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C146" s="91" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز تقييمات الأداء في موعدها</t>
+        </is>
+      </c>
+      <c r="D146" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E146" s="92" t="inlineStr">
+        <is>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F146" s="68" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G146" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H146" s="91" t="inlineStr">
+        <is>
+          <t>الاستثمار في الموظفين</t>
+        </is>
+      </c>
+      <c r="I146" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J146" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K146" s="38" t="n"/>
+    </row>
+    <row r="147" ht="22" customHeight="1">
+      <c r="A147" s="68" t="n">
+        <v>144</v>
+      </c>
+      <c r="B147" s="91" t="inlineStr">
+        <is>
           <t>التسويق</t>
         </is>
       </c>
-      <c r="C134" s="91" t="inlineStr">
+      <c r="C147" s="91" t="inlineStr">
+        <is>
+          <t>الوصول الكلي (Total Reach)</t>
+        </is>
+      </c>
+      <c r="D147" s="68" t="inlineStr">
+        <is>
+          <t>وصول</t>
+        </is>
+      </c>
+      <c r="E147" s="92" t="inlineStr">
+        <is>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F147" s="68" t="inlineStr">
+        <is>
+          <t>50م وصول</t>
+        </is>
+      </c>
+      <c r="G147" s="68" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="H147" s="91" t="inlineStr">
+        <is>
+          <t>زيادة وصول العملاء</t>
+        </is>
+      </c>
+      <c r="I147" s="68" t="inlineStr">
+        <is>
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="J147" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K147" s="38" t="n"/>
+    </row>
+    <row r="148" ht="22" customHeight="1">
+      <c r="A148" s="68" t="n">
+        <v>145</v>
+      </c>
+      <c r="B148" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C148" s="91" t="inlineStr">
+        <is>
+          <t>عملاء تجاريون جدد</t>
+        </is>
+      </c>
+      <c r="D148" s="68" t="inlineStr">
+        <is>
+          <t>عميل</t>
+        </is>
+      </c>
+      <c r="E148" s="92" t="inlineStr">
+        <is>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F148" s="68" t="inlineStr">
+        <is>
+          <t>200 عميل</t>
+        </is>
+      </c>
+      <c r="G148" s="68" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="H148" s="91" t="inlineStr">
+        <is>
+          <t>زيادة وصول العملاء</t>
+        </is>
+      </c>
+      <c r="I148" s="68" t="inlineStr">
+        <is>
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="J148" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K148" s="38" t="n"/>
+    </row>
+    <row r="149" ht="22" customHeight="1">
+      <c r="A149" s="68" t="n">
+        <v>146</v>
+      </c>
+      <c r="B149" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C149" s="91" t="inlineStr">
+        <is>
+          <t>إجمالي المتابعين (كل المنصات)</t>
+        </is>
+      </c>
+      <c r="D149" s="68" t="inlineStr">
+        <is>
+          <t>متابع</t>
+        </is>
+      </c>
+      <c r="E149" s="92" t="inlineStr">
+        <is>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F149" s="68" t="inlineStr">
+        <is>
+          <t>380ك متابع</t>
+        </is>
+      </c>
+      <c r="G149" s="68" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="H149" s="91" t="inlineStr">
+        <is>
+          <t>زيادة وصول العملاء</t>
+        </is>
+      </c>
+      <c r="I149" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J149" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K149" s="38" t="n"/>
+    </row>
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="68" t="n">
+        <v>147</v>
+      </c>
+      <c r="B150" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C150" s="91" t="inlineStr">
+        <is>
+          <t>معدل التفاعل (Engagement)</t>
+        </is>
+      </c>
+      <c r="D150" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E150" s="92" t="inlineStr">
+        <is>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F150" s="68" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="G150" s="68" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="H150" s="91" t="inlineStr">
+        <is>
+          <t>زيادة وصول العملاء</t>
+        </is>
+      </c>
+      <c r="I150" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J150" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K150" s="38" t="n"/>
+    </row>
+    <row r="151" ht="22" customHeight="1">
+      <c r="A151" s="68" t="n">
+        <v>148</v>
+      </c>
+      <c r="B151" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C151" s="91" t="inlineStr">
+        <is>
+          <t>حملات تسويقية منجزة</t>
+        </is>
+      </c>
+      <c r="D151" s="68" t="inlineStr">
+        <is>
+          <t>حملة</t>
+        </is>
+      </c>
+      <c r="E151" s="92" t="inlineStr">
+        <is>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F151" s="68" t="inlineStr">
+        <is>
+          <t>48 حملة</t>
+        </is>
+      </c>
+      <c r="G151" s="68" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="H151" s="91" t="inlineStr">
+        <is>
+          <t>زيادة وصول العملاء</t>
+        </is>
+      </c>
+      <c r="I151" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J151" s="68" t="inlineStr">
+        <is>
+          <t>🔵 قائد</t>
+        </is>
+      </c>
+      <c r="K151" s="38" t="n"/>
+    </row>
+    <row r="152" ht="22" customHeight="1">
+      <c r="A152" s="68" t="n">
+        <v>149</v>
+      </c>
+      <c r="B152" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C152" s="91" t="inlineStr">
+        <is>
+          <t>تحويل الفرص إلى عقود</t>
+        </is>
+      </c>
+      <c r="D152" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E152" s="92" t="inlineStr">
+        <is>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F152" s="68" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G152" s="68" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="H152" s="91" t="inlineStr">
+        <is>
+          <t>زيادة وصول العملاء</t>
+        </is>
+      </c>
+      <c r="I152" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J152" s="68" t="inlineStr">
+        <is>
+          <t>🔵 قائد</t>
+        </is>
+      </c>
+      <c r="K152" s="38" t="n"/>
+    </row>
+    <row r="153" ht="22" customHeight="1">
+      <c r="A153" s="68" t="n">
+        <v>150</v>
+      </c>
+      <c r="B153" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C153" s="91" t="inlineStr">
+        <is>
+          <t>نسبة المبيعات لكل حملة</t>
+        </is>
+      </c>
+      <c r="D153" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E153" s="92" t="inlineStr">
+        <is>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F153" s="68" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G153" s="68" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="H153" s="91" t="inlineStr">
+        <is>
+          <t>زيادة وصول العملاء</t>
+        </is>
+      </c>
+      <c r="I153" s="68" t="inlineStr">
+        <is>
+          <t>مالي</t>
+        </is>
+      </c>
+      <c r="J153" s="68" t="inlineStr">
+        <is>
+          <t>🔵 قائد</t>
+        </is>
+      </c>
+      <c r="K153" s="38" t="n"/>
+    </row>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="68" t="n">
+        <v>151</v>
+      </c>
+      <c r="B154" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C154" s="91" t="inlineStr">
+        <is>
+          <t>نسبة التزام الهوية البصرية</t>
+        </is>
+      </c>
+      <c r="D154" s="68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E154" s="92" t="inlineStr">
+        <is>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F154" s="68" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G154" s="68" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="H154" s="91" t="inlineStr">
+        <is>
+          <t>تطوير التصاميم والهوية</t>
+        </is>
+      </c>
+      <c r="I154" s="68" t="inlineStr">
+        <is>
+          <t>التعلّم والنمو</t>
+        </is>
+      </c>
+      <c r="J154" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K154" s="38" t="n"/>
+    </row>
+    <row r="155" ht="22" customHeight="1">
+      <c r="A155" s="68" t="n">
+        <v>152</v>
+      </c>
+      <c r="B155" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C155" s="91" t="inlineStr">
+        <is>
+          <t>وصول العلاقات العامة (PR)</t>
+        </is>
+      </c>
+      <c r="D155" s="68" t="inlineStr">
+        <is>
+          <t>وصول</t>
+        </is>
+      </c>
+      <c r="E155" s="92" t="inlineStr">
+        <is>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F155" s="68" t="inlineStr">
+        <is>
+          <t>7م وصول</t>
+        </is>
+      </c>
+      <c r="G155" s="68" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="H155" s="91" t="inlineStr">
+        <is>
+          <t>زيادة وصول العملاء</t>
+        </is>
+      </c>
+      <c r="I155" s="68" t="inlineStr">
+        <is>
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="J155" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K155" s="38" t="n"/>
+    </row>
+    <row r="156" ht="22" customHeight="1">
+      <c r="A156" s="68" t="n">
+        <v>153</v>
+      </c>
+      <c r="B156" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C156" s="91" t="inlineStr">
+        <is>
+          <t>عدد المعارض بالسنة</t>
+        </is>
+      </c>
+      <c r="D156" s="68" t="inlineStr">
+        <is>
+          <t>معرض</t>
+        </is>
+      </c>
+      <c r="E156" s="92" t="inlineStr">
+        <is>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F156" s="68" t="inlineStr">
+        <is>
+          <t>3 معارض</t>
+        </is>
+      </c>
+      <c r="G156" s="68" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="H156" s="91" t="inlineStr">
+        <is>
+          <t>إطلاق مشاريع جديدة</t>
+        </is>
+      </c>
+      <c r="I156" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J156" s="68" t="inlineStr">
+        <is>
+          <t>🔵 قائد</t>
+        </is>
+      </c>
+      <c r="K156" s="38" t="n"/>
+    </row>
+    <row r="157" ht="22" customHeight="1">
+      <c r="A157" s="68" t="n">
+        <v>154</v>
+      </c>
+      <c r="B157" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C157" s="91" t="inlineStr">
+        <is>
+          <t>اتفاقيات استراتيجية</t>
+        </is>
+      </c>
+      <c r="D157" s="68" t="inlineStr">
+        <is>
+          <t>اتفاقية</t>
+        </is>
+      </c>
+      <c r="E157" s="92" t="inlineStr">
+        <is>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F157" s="68" t="inlineStr">
+        <is>
+          <t>3 اتفاقيات</t>
+        </is>
+      </c>
+      <c r="G157" s="68" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="H157" s="91" t="inlineStr">
+        <is>
+          <t>إطلاق مشاريع جديدة</t>
+        </is>
+      </c>
+      <c r="I157" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J157" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K157" s="38" t="n"/>
+    </row>
+    <row r="158" ht="22" customHeight="1">
+      <c r="A158" s="68" t="n">
+        <v>155</v>
+      </c>
+      <c r="B158" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C158" s="91" t="inlineStr">
+        <is>
+          <t>تقييم خرائط قوقل</t>
+        </is>
+      </c>
+      <c r="D158" s="68" t="inlineStr">
+        <is>
+          <t>نجمة/5</t>
+        </is>
+      </c>
+      <c r="E158" s="92" t="inlineStr">
+        <is>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F158" s="68" t="inlineStr">
+        <is>
+          <t>4.7 ⭐</t>
+        </is>
+      </c>
+      <c r="G158" s="68" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="H158" s="91" t="inlineStr">
+        <is>
+          <t>تعزيز تجربة العملاء</t>
+        </is>
+      </c>
+      <c r="I158" s="68" t="inlineStr">
+        <is>
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="J158" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K158" s="38" t="n"/>
+    </row>
+    <row r="159" ht="22" customHeight="1">
+      <c r="A159" s="68" t="n">
+        <v>156</v>
+      </c>
+      <c r="B159" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C159" s="91" t="inlineStr">
         <is>
           <t>معدل خفض الشكاوى</t>
         </is>
       </c>
-      <c r="D134" s="68" t="inlineStr">
+      <c r="D159" s="68" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E134" s="92" t="inlineStr">
+      <c r="E159" s="92" t="inlineStr">
         <is>
           <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
-      <c r="F134" s="68" t="inlineStr">
+      <c r="F159" s="68" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G134" s="68" t="inlineStr">
+      <c r="G159" s="68" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
       </c>
-      <c r="H134" s="91" t="inlineStr">
+      <c r="H159" s="91" t="inlineStr">
         <is>
           <t>تعزيز تجربة العملاء</t>
         </is>
       </c>
-      <c r="I134" s="68" t="inlineStr">
+      <c r="I159" s="68" t="inlineStr">
         <is>
           <t>العملاء</t>
         </is>
       </c>
-      <c r="J134" s="68" t="inlineStr">
+      <c r="J159" s="68" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
-      <c r="K134" s="38" t="n"/>
+      <c r="K159" s="38" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
@@ -32970,7 +36901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -36785,31 +40716,31 @@
       </c>
       <c r="B114" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C114" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C4</f>
+        <f>'التقنية الرقمية · المؤشرات'!C12</f>
         <v/>
       </c>
       <c r="D114" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X4</f>
+        <f>'التقنية الرقمية · المؤشرات'!X12</f>
         <v/>
       </c>
       <c r="E114" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y4</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y12</f>
         <v/>
       </c>
       <c r="F114" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V4</f>
+        <f>'التقنية الرقمية · المؤشرات'!V12</f>
         <v/>
       </c>
       <c r="G114" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W4</f>
+        <f>'التقنية الرقمية · المؤشرات'!W12</f>
         <v/>
       </c>
       <c r="H114" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH4</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH12</f>
         <v/>
       </c>
     </row>
@@ -36819,31 +40750,31 @@
       </c>
       <c r="B115" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C115" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C5</f>
+        <f>'التقنية الرقمية · المؤشرات'!C13</f>
         <v/>
       </c>
       <c r="D115" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X5</f>
+        <f>'التقنية الرقمية · المؤشرات'!X13</f>
         <v/>
       </c>
       <c r="E115" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y5</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y13</f>
         <v/>
       </c>
       <c r="F115" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V5</f>
+        <f>'التقنية الرقمية · المؤشرات'!V13</f>
         <v/>
       </c>
       <c r="G115" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W5</f>
+        <f>'التقنية الرقمية · المؤشرات'!W13</f>
         <v/>
       </c>
       <c r="H115" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH5</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH13</f>
         <v/>
       </c>
     </row>
@@ -36853,31 +40784,31 @@
       </c>
       <c r="B116" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C116" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C6</f>
+        <f>'التقنية الرقمية · المؤشرات'!C14</f>
         <v/>
       </c>
       <c r="D116" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X6</f>
+        <f>'التقنية الرقمية · المؤشرات'!X14</f>
         <v/>
       </c>
       <c r="E116" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y6</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y14</f>
         <v/>
       </c>
       <c r="F116" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V6</f>
+        <f>'التقنية الرقمية · المؤشرات'!V14</f>
         <v/>
       </c>
       <c r="G116" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W6</f>
+        <f>'التقنية الرقمية · المؤشرات'!W14</f>
         <v/>
       </c>
       <c r="H116" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH6</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH14</f>
         <v/>
       </c>
     </row>
@@ -36887,31 +40818,31 @@
       </c>
       <c r="B117" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C117" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C7</f>
+        <f>'التقنية الرقمية · المؤشرات'!C15</f>
         <v/>
       </c>
       <c r="D117" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X7</f>
+        <f>'التقنية الرقمية · المؤشرات'!X15</f>
         <v/>
       </c>
       <c r="E117" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y7</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y15</f>
         <v/>
       </c>
       <c r="F117" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V7</f>
+        <f>'التقنية الرقمية · المؤشرات'!V15</f>
         <v/>
       </c>
       <c r="G117" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W7</f>
+        <f>'التقنية الرقمية · المؤشرات'!W15</f>
         <v/>
       </c>
       <c r="H117" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH7</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH15</f>
         <v/>
       </c>
     </row>
@@ -36921,31 +40852,31 @@
       </c>
       <c r="B118" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C118" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C8</f>
+        <f>'التقنية الرقمية · المؤشرات'!C16</f>
         <v/>
       </c>
       <c r="D118" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X8</f>
+        <f>'التقنية الرقمية · المؤشرات'!X16</f>
         <v/>
       </c>
       <c r="E118" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y8</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y16</f>
         <v/>
       </c>
       <c r="F118" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V8</f>
+        <f>'التقنية الرقمية · المؤشرات'!V16</f>
         <v/>
       </c>
       <c r="G118" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W8</f>
+        <f>'التقنية الرقمية · المؤشرات'!W16</f>
         <v/>
       </c>
       <c r="H118" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH8</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH16</f>
         <v/>
       </c>
     </row>
@@ -36955,31 +40886,31 @@
       </c>
       <c r="B119" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C119" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C9</f>
+        <f>'التقنية الرقمية · المؤشرات'!C17</f>
         <v/>
       </c>
       <c r="D119" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X9</f>
+        <f>'التقنية الرقمية · المؤشرات'!X17</f>
         <v/>
       </c>
       <c r="E119" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y9</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y17</f>
         <v/>
       </c>
       <c r="F119" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V9</f>
+        <f>'التقنية الرقمية · المؤشرات'!V17</f>
         <v/>
       </c>
       <c r="G119" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W9</f>
+        <f>'التقنية الرقمية · المؤشرات'!W17</f>
         <v/>
       </c>
       <c r="H119" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH9</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH17</f>
         <v/>
       </c>
     </row>
@@ -36989,31 +40920,31 @@
       </c>
       <c r="B120" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C120" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C10</f>
+        <f>'التقنية الرقمية · المؤشرات'!C18</f>
         <v/>
       </c>
       <c r="D120" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X10</f>
+        <f>'التقنية الرقمية · المؤشرات'!X18</f>
         <v/>
       </c>
       <c r="E120" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y10</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y18</f>
         <v/>
       </c>
       <c r="F120" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V10</f>
+        <f>'التقنية الرقمية · المؤشرات'!V18</f>
         <v/>
       </c>
       <c r="G120" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W10</f>
+        <f>'التقنية الرقمية · المؤشرات'!W18</f>
         <v/>
       </c>
       <c r="H120" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH10</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH18</f>
         <v/>
       </c>
     </row>
@@ -37023,31 +40954,31 @@
       </c>
       <c r="B121" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C121" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C11</f>
+        <f>'التقنية الرقمية · المؤشرات'!C19</f>
         <v/>
       </c>
       <c r="D121" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X11</f>
+        <f>'التقنية الرقمية · المؤشرات'!X19</f>
         <v/>
       </c>
       <c r="E121" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y11</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y19</f>
         <v/>
       </c>
       <c r="F121" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V11</f>
+        <f>'التقنية الرقمية · المؤشرات'!V19</f>
         <v/>
       </c>
       <c r="G121" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W11</f>
+        <f>'التقنية الرقمية · المؤشرات'!W19</f>
         <v/>
       </c>
       <c r="H121" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH11</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH19</f>
         <v/>
       </c>
     </row>
@@ -37057,31 +40988,31 @@
       </c>
       <c r="B122" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C122" s="91">
-        <f>'التسويق · المؤشرات'!C4</f>
+        <f>'التقنية الرقمية · المؤشرات'!C20</f>
         <v/>
       </c>
       <c r="D122" s="68">
-        <f>'التسويق · المؤشرات'!X4</f>
+        <f>'التقنية الرقمية · المؤشرات'!X20</f>
         <v/>
       </c>
       <c r="E122" s="91">
-        <f>'التسويق · المؤشرات'!Y4</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y20</f>
         <v/>
       </c>
       <c r="F122" s="93">
-        <f>'التسويق · المؤشرات'!V4</f>
+        <f>'التقنية الرقمية · المؤشرات'!V20</f>
         <v/>
       </c>
       <c r="G122" s="68">
-        <f>'التسويق · المؤشرات'!W4</f>
+        <f>'التقنية الرقمية · المؤشرات'!W20</f>
         <v/>
       </c>
       <c r="H122" s="68">
-        <f>'التسويق · المؤشرات'!AH4</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH20</f>
         <v/>
       </c>
     </row>
@@ -37091,31 +41022,31 @@
       </c>
       <c r="B123" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C123" s="91">
-        <f>'التسويق · المؤشرات'!C5</f>
+        <f>'التقنية الرقمية · المؤشرات'!C21</f>
         <v/>
       </c>
       <c r="D123" s="68">
-        <f>'التسويق · المؤشرات'!X5</f>
+        <f>'التقنية الرقمية · المؤشرات'!X21</f>
         <v/>
       </c>
       <c r="E123" s="91">
-        <f>'التسويق · المؤشرات'!Y5</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y21</f>
         <v/>
       </c>
       <c r="F123" s="93">
-        <f>'التسويق · المؤشرات'!V5</f>
+        <f>'التقنية الرقمية · المؤشرات'!V21</f>
         <v/>
       </c>
       <c r="G123" s="68">
-        <f>'التسويق · المؤشرات'!W5</f>
+        <f>'التقنية الرقمية · المؤشرات'!W21</f>
         <v/>
       </c>
       <c r="H123" s="68">
-        <f>'التسويق · المؤشرات'!AH5</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH21</f>
         <v/>
       </c>
     </row>
@@ -37125,31 +41056,31 @@
       </c>
       <c r="B124" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C124" s="91">
-        <f>'التسويق · المؤشرات'!C6</f>
+        <f>'التقنية الرقمية · المؤشرات'!C22</f>
         <v/>
       </c>
       <c r="D124" s="68">
-        <f>'التسويق · المؤشرات'!X6</f>
+        <f>'التقنية الرقمية · المؤشرات'!X22</f>
         <v/>
       </c>
       <c r="E124" s="91">
-        <f>'التسويق · المؤشرات'!Y6</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y22</f>
         <v/>
       </c>
       <c r="F124" s="93">
-        <f>'التسويق · المؤشرات'!V6</f>
+        <f>'التقنية الرقمية · المؤشرات'!V22</f>
         <v/>
       </c>
       <c r="G124" s="68">
-        <f>'التسويق · المؤشرات'!W6</f>
+        <f>'التقنية الرقمية · المؤشرات'!W22</f>
         <v/>
       </c>
       <c r="H124" s="68">
-        <f>'التسويق · المؤشرات'!AH6</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH22</f>
         <v/>
       </c>
     </row>
@@ -37159,31 +41090,31 @@
       </c>
       <c r="B125" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C125" s="91">
-        <f>'التسويق · المؤشرات'!C7</f>
+        <f>'التقنية الرقمية · المؤشرات'!C23</f>
         <v/>
       </c>
       <c r="D125" s="68">
-        <f>'التسويق · المؤشرات'!X7</f>
+        <f>'التقنية الرقمية · المؤشرات'!X23</f>
         <v/>
       </c>
       <c r="E125" s="91">
-        <f>'التسويق · المؤشرات'!Y7</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y23</f>
         <v/>
       </c>
       <c r="F125" s="93">
-        <f>'التسويق · المؤشرات'!V7</f>
+        <f>'التقنية الرقمية · المؤشرات'!V23</f>
         <v/>
       </c>
       <c r="G125" s="68">
-        <f>'التسويق · المؤشرات'!W7</f>
+        <f>'التقنية الرقمية · المؤشرات'!W23</f>
         <v/>
       </c>
       <c r="H125" s="68">
-        <f>'التسويق · المؤشرات'!AH7</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH23</f>
         <v/>
       </c>
     </row>
@@ -37193,31 +41124,31 @@
       </c>
       <c r="B126" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C126" s="91">
-        <f>'التسويق · المؤشرات'!C8</f>
+        <f>'التقنية الرقمية · المؤشرات'!C24</f>
         <v/>
       </c>
       <c r="D126" s="68">
-        <f>'التسويق · المؤشرات'!X8</f>
+        <f>'التقنية الرقمية · المؤشرات'!X24</f>
         <v/>
       </c>
       <c r="E126" s="91">
-        <f>'التسويق · المؤشرات'!Y8</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y24</f>
         <v/>
       </c>
       <c r="F126" s="93">
-        <f>'التسويق · المؤشرات'!V8</f>
+        <f>'التقنية الرقمية · المؤشرات'!V24</f>
         <v/>
       </c>
       <c r="G126" s="68">
-        <f>'التسويق · المؤشرات'!W8</f>
+        <f>'التقنية الرقمية · المؤشرات'!W24</f>
         <v/>
       </c>
       <c r="H126" s="68">
-        <f>'التسويق · المؤشرات'!AH8</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH24</f>
         <v/>
       </c>
     </row>
@@ -37227,31 +41158,31 @@
       </c>
       <c r="B127" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C127" s="91">
-        <f>'التسويق · المؤشرات'!C9</f>
+        <f>'التقنية الرقمية · المؤشرات'!C25</f>
         <v/>
       </c>
       <c r="D127" s="68">
-        <f>'التسويق · المؤشرات'!X9</f>
+        <f>'التقنية الرقمية · المؤشرات'!X25</f>
         <v/>
       </c>
       <c r="E127" s="91">
-        <f>'التسويق · المؤشرات'!Y9</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y25</f>
         <v/>
       </c>
       <c r="F127" s="93">
-        <f>'التسويق · المؤشرات'!V9</f>
+        <f>'التقنية الرقمية · المؤشرات'!V25</f>
         <v/>
       </c>
       <c r="G127" s="68">
-        <f>'التسويق · المؤشرات'!W9</f>
+        <f>'التقنية الرقمية · المؤشرات'!W25</f>
         <v/>
       </c>
       <c r="H127" s="68">
-        <f>'التسويق · المؤشرات'!AH9</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH25</f>
         <v/>
       </c>
     </row>
@@ -37261,31 +41192,31 @@
       </c>
       <c r="B128" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C128" s="91">
-        <f>'التسويق · المؤشرات'!C10</f>
+        <f>'التقنية الرقمية · المؤشرات'!C26</f>
         <v/>
       </c>
       <c r="D128" s="68">
-        <f>'التسويق · المؤشرات'!X10</f>
+        <f>'التقنية الرقمية · المؤشرات'!X26</f>
         <v/>
       </c>
       <c r="E128" s="91">
-        <f>'التسويق · المؤشرات'!Y10</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y26</f>
         <v/>
       </c>
       <c r="F128" s="93">
-        <f>'التسويق · المؤشرات'!V10</f>
+        <f>'التقنية الرقمية · المؤشرات'!V26</f>
         <v/>
       </c>
       <c r="G128" s="68">
-        <f>'التسويق · المؤشرات'!W10</f>
+        <f>'التقنية الرقمية · المؤشرات'!W26</f>
         <v/>
       </c>
       <c r="H128" s="68">
-        <f>'التسويق · المؤشرات'!AH10</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH26</f>
         <v/>
       </c>
     </row>
@@ -37295,31 +41226,31 @@
       </c>
       <c r="B129" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C129" s="91">
-        <f>'التسويق · المؤشرات'!C11</f>
+        <f>'التقنية الرقمية · المؤشرات'!C27</f>
         <v/>
       </c>
       <c r="D129" s="68">
-        <f>'التسويق · المؤشرات'!X11</f>
+        <f>'التقنية الرقمية · المؤشرات'!X27</f>
         <v/>
       </c>
       <c r="E129" s="91">
-        <f>'التسويق · المؤشرات'!Y11</f>
+        <f>'التقنية الرقمية · المؤشرات'!Y27</f>
         <v/>
       </c>
       <c r="F129" s="93">
-        <f>'التسويق · المؤشرات'!V11</f>
+        <f>'التقنية الرقمية · المؤشرات'!V27</f>
         <v/>
       </c>
       <c r="G129" s="68">
-        <f>'التسويق · المؤشرات'!W11</f>
+        <f>'التقنية الرقمية · المؤشرات'!W27</f>
         <v/>
       </c>
       <c r="H129" s="68">
-        <f>'التسويق · المؤشرات'!AH11</f>
+        <f>'التقنية الرقمية · المؤشرات'!AH27</f>
         <v/>
       </c>
     </row>
@@ -37329,31 +41260,31 @@
       </c>
       <c r="B130" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C130" s="91">
-        <f>'التسويق · المؤشرات'!C12</f>
+        <f>'الموارد البشرية · المؤشرات'!C4</f>
         <v/>
       </c>
       <c r="D130" s="68">
-        <f>'التسويق · المؤشرات'!X12</f>
+        <f>'الموارد البشرية · المؤشرات'!X4</f>
         <v/>
       </c>
       <c r="E130" s="91">
-        <f>'التسويق · المؤشرات'!Y12</f>
+        <f>'الموارد البشرية · المؤشرات'!Y4</f>
         <v/>
       </c>
       <c r="F130" s="93">
-        <f>'التسويق · المؤشرات'!V12</f>
+        <f>'الموارد البشرية · المؤشرات'!V4</f>
         <v/>
       </c>
       <c r="G130" s="68">
-        <f>'التسويق · المؤشرات'!W12</f>
+        <f>'الموارد البشرية · المؤشرات'!W4</f>
         <v/>
       </c>
       <c r="H130" s="68">
-        <f>'التسويق · المؤشرات'!AH12</f>
+        <f>'الموارد البشرية · المؤشرات'!AH4</f>
         <v/>
       </c>
     </row>
@@ -37363,31 +41294,31 @@
       </c>
       <c r="B131" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C131" s="91">
-        <f>'التسويق · المؤشرات'!C13</f>
+        <f>'الموارد البشرية · المؤشرات'!C5</f>
         <v/>
       </c>
       <c r="D131" s="68">
-        <f>'التسويق · المؤشرات'!X13</f>
+        <f>'الموارد البشرية · المؤشرات'!X5</f>
         <v/>
       </c>
       <c r="E131" s="91">
-        <f>'التسويق · المؤشرات'!Y13</f>
+        <f>'الموارد البشرية · المؤشرات'!Y5</f>
         <v/>
       </c>
       <c r="F131" s="93">
-        <f>'التسويق · المؤشرات'!V13</f>
+        <f>'الموارد البشرية · المؤشرات'!V5</f>
         <v/>
       </c>
       <c r="G131" s="68">
-        <f>'التسويق · المؤشرات'!W13</f>
+        <f>'الموارد البشرية · المؤشرات'!W5</f>
         <v/>
       </c>
       <c r="H131" s="68">
-        <f>'التسويق · المؤشرات'!AH13</f>
+        <f>'الموارد البشرية · المؤشرات'!AH5</f>
         <v/>
       </c>
     </row>
@@ -37397,31 +41328,31 @@
       </c>
       <c r="B132" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C132" s="91">
-        <f>'التسويق · المؤشرات'!C14</f>
+        <f>'الموارد البشرية · المؤشرات'!C6</f>
         <v/>
       </c>
       <c r="D132" s="68">
-        <f>'التسويق · المؤشرات'!X14</f>
+        <f>'الموارد البشرية · المؤشرات'!X6</f>
         <v/>
       </c>
       <c r="E132" s="91">
-        <f>'التسويق · المؤشرات'!Y14</f>
+        <f>'الموارد البشرية · المؤشرات'!Y6</f>
         <v/>
       </c>
       <c r="F132" s="93">
-        <f>'التسويق · المؤشرات'!V14</f>
+        <f>'الموارد البشرية · المؤشرات'!V6</f>
         <v/>
       </c>
       <c r="G132" s="68">
-        <f>'التسويق · المؤشرات'!W14</f>
+        <f>'الموارد البشرية · المؤشرات'!W6</f>
         <v/>
       </c>
       <c r="H132" s="68">
-        <f>'التسويق · المؤشرات'!AH14</f>
+        <f>'الموارد البشرية · المؤشرات'!AH6</f>
         <v/>
       </c>
     </row>
@@ -37431,31 +41362,31 @@
       </c>
       <c r="B133" s="91" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C133" s="91">
-        <f>'التسويق · المؤشرات'!C15</f>
+        <f>'الموارد البشرية · المؤشرات'!C7</f>
         <v/>
       </c>
       <c r="D133" s="68">
-        <f>'التسويق · المؤشرات'!X15</f>
+        <f>'الموارد البشرية · المؤشرات'!X7</f>
         <v/>
       </c>
       <c r="E133" s="91">
-        <f>'التسويق · المؤشرات'!Y15</f>
+        <f>'الموارد البشرية · المؤشرات'!Y7</f>
         <v/>
       </c>
       <c r="F133" s="93">
-        <f>'التسويق · المؤشرات'!V15</f>
+        <f>'الموارد البشرية · المؤشرات'!V7</f>
         <v/>
       </c>
       <c r="G133" s="68">
-        <f>'التسويق · المؤشرات'!W15</f>
+        <f>'الموارد البشرية · المؤشرات'!W7</f>
         <v/>
       </c>
       <c r="H133" s="68">
-        <f>'التسويق · المؤشرات'!AH15</f>
+        <f>'الموارد البشرية · المؤشرات'!AH7</f>
         <v/>
       </c>
     </row>
@@ -37465,30 +41396,880 @@
       </c>
       <c r="B134" s="91" t="inlineStr">
         <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C134" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C8</f>
+        <v/>
+      </c>
+      <c r="D134" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X8</f>
+        <v/>
+      </c>
+      <c r="E134" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y8</f>
+        <v/>
+      </c>
+      <c r="F134" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V8</f>
+        <v/>
+      </c>
+      <c r="G134" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W8</f>
+        <v/>
+      </c>
+      <c r="H134" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="68" t="n">
+        <v>132</v>
+      </c>
+      <c r="B135" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C135" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C9</f>
+        <v/>
+      </c>
+      <c r="D135" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X9</f>
+        <v/>
+      </c>
+      <c r="E135" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y9</f>
+        <v/>
+      </c>
+      <c r="F135" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V9</f>
+        <v/>
+      </c>
+      <c r="G135" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W9</f>
+        <v/>
+      </c>
+      <c r="H135" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="68" t="n">
+        <v>133</v>
+      </c>
+      <c r="B136" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C136" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C10</f>
+        <v/>
+      </c>
+      <c r="D136" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X10</f>
+        <v/>
+      </c>
+      <c r="E136" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y10</f>
+        <v/>
+      </c>
+      <c r="F136" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V10</f>
+        <v/>
+      </c>
+      <c r="G136" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W10</f>
+        <v/>
+      </c>
+      <c r="H136" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="68" t="n">
+        <v>134</v>
+      </c>
+      <c r="B137" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C137" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C11</f>
+        <v/>
+      </c>
+      <c r="D137" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X11</f>
+        <v/>
+      </c>
+      <c r="E137" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y11</f>
+        <v/>
+      </c>
+      <c r="F137" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V11</f>
+        <v/>
+      </c>
+      <c r="G137" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W11</f>
+        <v/>
+      </c>
+      <c r="H137" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="68" t="n">
+        <v>135</v>
+      </c>
+      <c r="B138" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C138" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C12</f>
+        <v/>
+      </c>
+      <c r="D138" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X12</f>
+        <v/>
+      </c>
+      <c r="E138" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y12</f>
+        <v/>
+      </c>
+      <c r="F138" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V12</f>
+        <v/>
+      </c>
+      <c r="G138" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W12</f>
+        <v/>
+      </c>
+      <c r="H138" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="68" t="n">
+        <v>136</v>
+      </c>
+      <c r="B139" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C139" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C13</f>
+        <v/>
+      </c>
+      <c r="D139" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X13</f>
+        <v/>
+      </c>
+      <c r="E139" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y13</f>
+        <v/>
+      </c>
+      <c r="F139" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V13</f>
+        <v/>
+      </c>
+      <c r="G139" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W13</f>
+        <v/>
+      </c>
+      <c r="H139" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="68" t="n">
+        <v>137</v>
+      </c>
+      <c r="B140" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C140" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C14</f>
+        <v/>
+      </c>
+      <c r="D140" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X14</f>
+        <v/>
+      </c>
+      <c r="E140" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y14</f>
+        <v/>
+      </c>
+      <c r="F140" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V14</f>
+        <v/>
+      </c>
+      <c r="G140" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W14</f>
+        <v/>
+      </c>
+      <c r="H140" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="68" t="n">
+        <v>138</v>
+      </c>
+      <c r="B141" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C141" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C15</f>
+        <v/>
+      </c>
+      <c r="D141" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X15</f>
+        <v/>
+      </c>
+      <c r="E141" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y15</f>
+        <v/>
+      </c>
+      <c r="F141" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V15</f>
+        <v/>
+      </c>
+      <c r="G141" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W15</f>
+        <v/>
+      </c>
+      <c r="H141" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="68" t="n">
+        <v>139</v>
+      </c>
+      <c r="B142" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C142" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C16</f>
+        <v/>
+      </c>
+      <c r="D142" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X16</f>
+        <v/>
+      </c>
+      <c r="E142" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y16</f>
+        <v/>
+      </c>
+      <c r="F142" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V16</f>
+        <v/>
+      </c>
+      <c r="G142" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W16</f>
+        <v/>
+      </c>
+      <c r="H142" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="68" t="n">
+        <v>140</v>
+      </c>
+      <c r="B143" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C143" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C17</f>
+        <v/>
+      </c>
+      <c r="D143" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X17</f>
+        <v/>
+      </c>
+      <c r="E143" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y17</f>
+        <v/>
+      </c>
+      <c r="F143" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V17</f>
+        <v/>
+      </c>
+      <c r="G143" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W17</f>
+        <v/>
+      </c>
+      <c r="H143" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="68" t="n">
+        <v>141</v>
+      </c>
+      <c r="B144" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C144" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C18</f>
+        <v/>
+      </c>
+      <c r="D144" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X18</f>
+        <v/>
+      </c>
+      <c r="E144" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y18</f>
+        <v/>
+      </c>
+      <c r="F144" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V18</f>
+        <v/>
+      </c>
+      <c r="G144" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W18</f>
+        <v/>
+      </c>
+      <c r="H144" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="68" t="n">
+        <v>142</v>
+      </c>
+      <c r="B145" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C145" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C19</f>
+        <v/>
+      </c>
+      <c r="D145" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X19</f>
+        <v/>
+      </c>
+      <c r="E145" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y19</f>
+        <v/>
+      </c>
+      <c r="F145" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V19</f>
+        <v/>
+      </c>
+      <c r="G145" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W19</f>
+        <v/>
+      </c>
+      <c r="H145" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="68" t="n">
+        <v>143</v>
+      </c>
+      <c r="B146" s="91" t="inlineStr">
+        <is>
+          <t>الموارد البشرية</t>
+        </is>
+      </c>
+      <c r="C146" s="91">
+        <f>'الموارد البشرية · المؤشرات'!C20</f>
+        <v/>
+      </c>
+      <c r="D146" s="68">
+        <f>'الموارد البشرية · المؤشرات'!X20</f>
+        <v/>
+      </c>
+      <c r="E146" s="91">
+        <f>'الموارد البشرية · المؤشرات'!Y20</f>
+        <v/>
+      </c>
+      <c r="F146" s="93">
+        <f>'الموارد البشرية · المؤشرات'!V20</f>
+        <v/>
+      </c>
+      <c r="G146" s="68">
+        <f>'الموارد البشرية · المؤشرات'!W20</f>
+        <v/>
+      </c>
+      <c r="H146" s="68">
+        <f>'الموارد البشرية · المؤشرات'!AH20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="68" t="n">
+        <v>144</v>
+      </c>
+      <c r="B147" s="91" t="inlineStr">
+        <is>
           <t>التسويق</t>
         </is>
       </c>
-      <c r="C134" s="91">
+      <c r="C147" s="91">
+        <f>'التسويق · المؤشرات'!C4</f>
+        <v/>
+      </c>
+      <c r="D147" s="68">
+        <f>'التسويق · المؤشرات'!X4</f>
+        <v/>
+      </c>
+      <c r="E147" s="91">
+        <f>'التسويق · المؤشرات'!Y4</f>
+        <v/>
+      </c>
+      <c r="F147" s="93">
+        <f>'التسويق · المؤشرات'!V4</f>
+        <v/>
+      </c>
+      <c r="G147" s="68">
+        <f>'التسويق · المؤشرات'!W4</f>
+        <v/>
+      </c>
+      <c r="H147" s="68">
+        <f>'التسويق · المؤشرات'!AH4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="68" t="n">
+        <v>145</v>
+      </c>
+      <c r="B148" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C148" s="91">
+        <f>'التسويق · المؤشرات'!C5</f>
+        <v/>
+      </c>
+      <c r="D148" s="68">
+        <f>'التسويق · المؤشرات'!X5</f>
+        <v/>
+      </c>
+      <c r="E148" s="91">
+        <f>'التسويق · المؤشرات'!Y5</f>
+        <v/>
+      </c>
+      <c r="F148" s="93">
+        <f>'التسويق · المؤشرات'!V5</f>
+        <v/>
+      </c>
+      <c r="G148" s="68">
+        <f>'التسويق · المؤشرات'!W5</f>
+        <v/>
+      </c>
+      <c r="H148" s="68">
+        <f>'التسويق · المؤشرات'!AH5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="68" t="n">
+        <v>146</v>
+      </c>
+      <c r="B149" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C149" s="91">
+        <f>'التسويق · المؤشرات'!C6</f>
+        <v/>
+      </c>
+      <c r="D149" s="68">
+        <f>'التسويق · المؤشرات'!X6</f>
+        <v/>
+      </c>
+      <c r="E149" s="91">
+        <f>'التسويق · المؤشرات'!Y6</f>
+        <v/>
+      </c>
+      <c r="F149" s="93">
+        <f>'التسويق · المؤشرات'!V6</f>
+        <v/>
+      </c>
+      <c r="G149" s="68">
+        <f>'التسويق · المؤشرات'!W6</f>
+        <v/>
+      </c>
+      <c r="H149" s="68">
+        <f>'التسويق · المؤشرات'!AH6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="68" t="n">
+        <v>147</v>
+      </c>
+      <c r="B150" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C150" s="91">
+        <f>'التسويق · المؤشرات'!C7</f>
+        <v/>
+      </c>
+      <c r="D150" s="68">
+        <f>'التسويق · المؤشرات'!X7</f>
+        <v/>
+      </c>
+      <c r="E150" s="91">
+        <f>'التسويق · المؤشرات'!Y7</f>
+        <v/>
+      </c>
+      <c r="F150" s="93">
+        <f>'التسويق · المؤشرات'!V7</f>
+        <v/>
+      </c>
+      <c r="G150" s="68">
+        <f>'التسويق · المؤشرات'!W7</f>
+        <v/>
+      </c>
+      <c r="H150" s="68">
+        <f>'التسويق · المؤشرات'!AH7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="68" t="n">
+        <v>148</v>
+      </c>
+      <c r="B151" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C151" s="91">
+        <f>'التسويق · المؤشرات'!C8</f>
+        <v/>
+      </c>
+      <c r="D151" s="68">
+        <f>'التسويق · المؤشرات'!X8</f>
+        <v/>
+      </c>
+      <c r="E151" s="91">
+        <f>'التسويق · المؤشرات'!Y8</f>
+        <v/>
+      </c>
+      <c r="F151" s="93">
+        <f>'التسويق · المؤشرات'!V8</f>
+        <v/>
+      </c>
+      <c r="G151" s="68">
+        <f>'التسويق · المؤشرات'!W8</f>
+        <v/>
+      </c>
+      <c r="H151" s="68">
+        <f>'التسويق · المؤشرات'!AH8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="68" t="n">
+        <v>149</v>
+      </c>
+      <c r="B152" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C152" s="91">
+        <f>'التسويق · المؤشرات'!C9</f>
+        <v/>
+      </c>
+      <c r="D152" s="68">
+        <f>'التسويق · المؤشرات'!X9</f>
+        <v/>
+      </c>
+      <c r="E152" s="91">
+        <f>'التسويق · المؤشرات'!Y9</f>
+        <v/>
+      </c>
+      <c r="F152" s="93">
+        <f>'التسويق · المؤشرات'!V9</f>
+        <v/>
+      </c>
+      <c r="G152" s="68">
+        <f>'التسويق · المؤشرات'!W9</f>
+        <v/>
+      </c>
+      <c r="H152" s="68">
+        <f>'التسويق · المؤشرات'!AH9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="68" t="n">
+        <v>150</v>
+      </c>
+      <c r="B153" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C153" s="91">
+        <f>'التسويق · المؤشرات'!C10</f>
+        <v/>
+      </c>
+      <c r="D153" s="68">
+        <f>'التسويق · المؤشرات'!X10</f>
+        <v/>
+      </c>
+      <c r="E153" s="91">
+        <f>'التسويق · المؤشرات'!Y10</f>
+        <v/>
+      </c>
+      <c r="F153" s="93">
+        <f>'التسويق · المؤشرات'!V10</f>
+        <v/>
+      </c>
+      <c r="G153" s="68">
+        <f>'التسويق · المؤشرات'!W10</f>
+        <v/>
+      </c>
+      <c r="H153" s="68">
+        <f>'التسويق · المؤشرات'!AH10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="68" t="n">
+        <v>151</v>
+      </c>
+      <c r="B154" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C154" s="91">
+        <f>'التسويق · المؤشرات'!C11</f>
+        <v/>
+      </c>
+      <c r="D154" s="68">
+        <f>'التسويق · المؤشرات'!X11</f>
+        <v/>
+      </c>
+      <c r="E154" s="91">
+        <f>'التسويق · المؤشرات'!Y11</f>
+        <v/>
+      </c>
+      <c r="F154" s="93">
+        <f>'التسويق · المؤشرات'!V11</f>
+        <v/>
+      </c>
+      <c r="G154" s="68">
+        <f>'التسويق · المؤشرات'!W11</f>
+        <v/>
+      </c>
+      <c r="H154" s="68">
+        <f>'التسويق · المؤشرات'!AH11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="68" t="n">
+        <v>152</v>
+      </c>
+      <c r="B155" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C155" s="91">
+        <f>'التسويق · المؤشرات'!C12</f>
+        <v/>
+      </c>
+      <c r="D155" s="68">
+        <f>'التسويق · المؤشرات'!X12</f>
+        <v/>
+      </c>
+      <c r="E155" s="91">
+        <f>'التسويق · المؤشرات'!Y12</f>
+        <v/>
+      </c>
+      <c r="F155" s="93">
+        <f>'التسويق · المؤشرات'!V12</f>
+        <v/>
+      </c>
+      <c r="G155" s="68">
+        <f>'التسويق · المؤشرات'!W12</f>
+        <v/>
+      </c>
+      <c r="H155" s="68">
+        <f>'التسويق · المؤشرات'!AH12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="68" t="n">
+        <v>153</v>
+      </c>
+      <c r="B156" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C156" s="91">
+        <f>'التسويق · المؤشرات'!C13</f>
+        <v/>
+      </c>
+      <c r="D156" s="68">
+        <f>'التسويق · المؤشرات'!X13</f>
+        <v/>
+      </c>
+      <c r="E156" s="91">
+        <f>'التسويق · المؤشرات'!Y13</f>
+        <v/>
+      </c>
+      <c r="F156" s="93">
+        <f>'التسويق · المؤشرات'!V13</f>
+        <v/>
+      </c>
+      <c r="G156" s="68">
+        <f>'التسويق · المؤشرات'!W13</f>
+        <v/>
+      </c>
+      <c r="H156" s="68">
+        <f>'التسويق · المؤشرات'!AH13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="68" t="n">
+        <v>154</v>
+      </c>
+      <c r="B157" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C157" s="91">
+        <f>'التسويق · المؤشرات'!C14</f>
+        <v/>
+      </c>
+      <c r="D157" s="68">
+        <f>'التسويق · المؤشرات'!X14</f>
+        <v/>
+      </c>
+      <c r="E157" s="91">
+        <f>'التسويق · المؤشرات'!Y14</f>
+        <v/>
+      </c>
+      <c r="F157" s="93">
+        <f>'التسويق · المؤشرات'!V14</f>
+        <v/>
+      </c>
+      <c r="G157" s="68">
+        <f>'التسويق · المؤشرات'!W14</f>
+        <v/>
+      </c>
+      <c r="H157" s="68">
+        <f>'التسويق · المؤشرات'!AH14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="68" t="n">
+        <v>155</v>
+      </c>
+      <c r="B158" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C158" s="91">
+        <f>'التسويق · المؤشرات'!C15</f>
+        <v/>
+      </c>
+      <c r="D158" s="68">
+        <f>'التسويق · المؤشرات'!X15</f>
+        <v/>
+      </c>
+      <c r="E158" s="91">
+        <f>'التسويق · المؤشرات'!Y15</f>
+        <v/>
+      </c>
+      <c r="F158" s="93">
+        <f>'التسويق · المؤشرات'!V15</f>
+        <v/>
+      </c>
+      <c r="G158" s="68">
+        <f>'التسويق · المؤشرات'!W15</f>
+        <v/>
+      </c>
+      <c r="H158" s="68">
+        <f>'التسويق · المؤشرات'!AH15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="68" t="n">
+        <v>156</v>
+      </c>
+      <c r="B159" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C159" s="91">
         <f>'التسويق · المؤشرات'!C16</f>
         <v/>
       </c>
-      <c r="D134" s="68">
+      <c r="D159" s="68">
         <f>'التسويق · المؤشرات'!X16</f>
         <v/>
       </c>
-      <c r="E134" s="91">
+      <c r="E159" s="91">
         <f>'التسويق · المؤشرات'!Y16</f>
         <v/>
       </c>
-      <c r="F134" s="93">
+      <c r="F159" s="93">
         <f>'التسويق · المؤشرات'!V16</f>
         <v/>
       </c>
-      <c r="G134" s="68">
+      <c r="G159" s="68">
         <f>'التسويق · المؤشرات'!W16</f>
         <v/>
       </c>
-      <c r="H134" s="68">
+      <c r="H159" s="68">
         <f>'التسويق · المؤشرات'!AH16</f>
         <v/>
       </c>
@@ -39203,11 +43984,11 @@
         </is>
       </c>
       <c r="C5" s="25">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$H$4:$H$134,"مالي"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$H$4:$H$159,"مالي"),"—")</f>
         <v/>
       </c>
       <c r="D5" s="26">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$134,"مالي")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$159,"مالي")</f>
         <v/>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -39223,11 +44004,11 @@
         </is>
       </c>
       <c r="C6" s="25">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$H$4:$H$134,"العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$H$4:$H$159,"العملاء"),"—")</f>
         <v/>
       </c>
       <c r="D6" s="26">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$134,"العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$159,"العملاء")</f>
         <v/>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -39243,11 +44024,11 @@
         </is>
       </c>
       <c r="C7" s="25">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$H$4:$H$134,"العمليات الداخلية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$H$4:$H$159,"العمليات الداخلية"),"—")</f>
         <v/>
       </c>
       <c r="D7" s="26">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$134,"العمليات الداخلية")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$159,"العمليات الداخلية")</f>
         <v/>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -39263,11 +44044,11 @@
         </is>
       </c>
       <c r="C8" s="25">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$H$4:$H$134,"التعلّم والنمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$H$4:$H$159,"التعلّم والنمو"),"—")</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$134,"التعلّم والنمو")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$159,"التعلّم والنمو")</f>
         <v/>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -39393,7 +44174,7 @@
         </is>
       </c>
       <c r="G4" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$134,"التوسع في المواقع")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$E$4:$E$134,"التوسع في المواقع"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"التوسع في المواقع")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"التوسع في المواقع"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -39422,7 +44203,7 @@
         </is>
       </c>
       <c r="G5" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$134,"الامتياز التجاري")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$E$4:$E$134,"الامتياز التجاري"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"الامتياز التجاري")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"الامتياز التجاري"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -39451,7 +44232,7 @@
         </is>
       </c>
       <c r="G6" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$134,"زيادة وصول العملاء")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$E$4:$E$134,"زيادة وصول العملاء"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"زيادة وصول العملاء")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"زيادة وصول العملاء"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -39485,7 +44266,7 @@
         </is>
       </c>
       <c r="G7" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$134,"إطلاق مشاريع جديدة")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$E$4:$E$134,"إطلاق مشاريع جديدة"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"إطلاق مشاريع جديدة")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"إطلاق مشاريع جديدة"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -39514,7 +44295,7 @@
         </is>
       </c>
       <c r="G8" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$134,"تطوير التصاميم والهوية")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$E$4:$E$134,"تطوير التصاميم والهوية"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"تطوير التصاميم والهوية")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"تطوير التصاميم والهوية"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -39543,7 +44324,7 @@
         </is>
       </c>
       <c r="G9" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$134,"التحول التقني")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$E$4:$E$134,"التحول التقني"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"التحول التقني")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"التحول التقني"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -39572,7 +44353,7 @@
         </is>
       </c>
       <c r="G10" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$134,"ساحات درب")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$E$4:$E$134,"ساحات درب"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"ساحات درب")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"ساحات درب"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -39601,7 +44382,7 @@
         </is>
       </c>
       <c r="G11" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$134,"تطبيق «تانكي»")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$E$4:$E$134,"تطبيق «تانكي»"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"تطبيق «تانكي»")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"تطبيق «تانكي»"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -39635,7 +44416,7 @@
         </is>
       </c>
       <c r="G12" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$134,"تعزيز تجربة العملاء")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$E$4:$E$134,"تعزيز تجربة العملاء"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"تعزيز تجربة العملاء")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"تعزيز تجربة العملاء"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -39664,7 +44445,7 @@
         </is>
       </c>
       <c r="G13" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$134,"جودة التشغيل")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$E$4:$E$134,"جودة التشغيل"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"جودة التشغيل")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"جودة التشغيل"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -39693,7 +44474,7 @@
         </is>
       </c>
       <c r="G14" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$134,"منظومة التأجير")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$E$4:$E$134,"منظومة التأجير"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"منظومة التأجير")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"منظومة التأجير"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -39722,7 +44503,7 @@
         </is>
       </c>
       <c r="G15" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$134,"الاستثمار في الموظفين")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$E$4:$E$134,"الاستثمار في الموظفين"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"الاستثمار في الموظفين")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"الاستثمار في الموظفين"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -39844,19 +44625,19 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="44">
-        <f>IFERROR(AVERAGE('قاعدة المؤشرات'!$F$4:$F$134),0)</f>
+        <f>IFERROR(AVERAGE('قاعدة المؤشرات'!$F$4:$F$159),0)</f>
         <v/>
       </c>
       <c r="D5" s="45">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$134,"✅ محقق")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"✅ محقق")</f>
         <v/>
       </c>
       <c r="E5" s="45">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$134,"🟡 قريب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"🟡 قريب")</f>
         <v/>
       </c>
       <c r="F5" s="45">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$134,"🔴 تحت الهدف")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"🔴 تحت الهدف")</f>
         <v/>
       </c>
       <c r="H5" s="46" t="inlineStr">
@@ -39885,7 +44666,7 @@
         </is>
       </c>
       <c r="I6" s="33">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$D$4:$D$134,"النمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$D$4:$D$159,"النمو"),"—")</f>
         <v/>
       </c>
       <c r="J6" s="49">
@@ -39900,7 +44681,7 @@
         </is>
       </c>
       <c r="I7" s="33">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$D$4:$D$134,"الابتكار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$D$4:$D$159,"الابتكار"),"—")</f>
         <v/>
       </c>
       <c r="J7" s="49">
@@ -39915,7 +44696,7 @@
         </is>
       </c>
       <c r="I8" s="33">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$D$4:$D$134,"الاستدامة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$D$4:$D$159,"الاستدامة"),"—")</f>
         <v/>
       </c>
       <c r="J8" s="49">
@@ -39956,7 +44737,7 @@
         </is>
       </c>
       <c r="C11" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$B$4:$B$134,"الإدارة التنفيذية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"الإدارة التنفيذية"),"—")</f>
         <v/>
       </c>
       <c r="D11" s="17">
@@ -39971,7 +44752,7 @@
         </is>
       </c>
       <c r="C12" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$B$4:$B$134,"الامتياز التجاري"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"الامتياز التجاري"),"—")</f>
         <v/>
       </c>
       <c r="D12" s="17">
@@ -39986,7 +44767,7 @@
         </is>
       </c>
       <c r="C13" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$B$4:$B$134,"التشغيل والمحطات"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"التشغيل والمحطات"),"—")</f>
         <v/>
       </c>
       <c r="D13" s="17">
@@ -40001,7 +44782,7 @@
         </is>
       </c>
       <c r="C14" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$B$4:$B$134,"الاستثمار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"الاستثمار"),"—")</f>
         <v/>
       </c>
       <c r="D14" s="17">
@@ -40016,7 +44797,7 @@
         </is>
       </c>
       <c r="C15" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$B$4:$B$134,"العقار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"العقار"),"—")</f>
         <v/>
       </c>
       <c r="D15" s="17">
@@ -40031,7 +44812,7 @@
         </is>
       </c>
       <c r="C16" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$B$4:$B$134,"التقنية الرقمية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"التقنية الرقمية"),"—")</f>
         <v/>
       </c>
       <c r="D16" s="17">
@@ -40046,7 +44827,7 @@
         </is>
       </c>
       <c r="C17" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$B$4:$B$134,"الموارد البشرية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"الموارد البشرية"),"—")</f>
         <v/>
       </c>
       <c r="D17" s="17">
@@ -40061,7 +44842,7 @@
         </is>
       </c>
       <c r="C18" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$134,'قاعدة المؤشرات'!$B$4:$B$134,"التسويق"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"التسويق"),"—")</f>
         <v/>
       </c>
       <c r="D18" s="17">
@@ -41054,7 +45835,7 @@
         </is>
       </c>
       <c r="C5" s="58">
-        <f>134-3</f>
+        <f>159-3</f>
         <v/>
       </c>
     </row>
@@ -41065,7 +45846,7 @@
         </is>
       </c>
       <c r="C6" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$134,"✅ محقق")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"✅ محقق")</f>
         <v/>
       </c>
     </row>
@@ -41076,7 +45857,7 @@
         </is>
       </c>
       <c r="C7" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$134,"🟡 قريب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"🟡 قريب")</f>
         <v/>
       </c>
     </row>
@@ -41087,7 +45868,7 @@
         </is>
       </c>
       <c r="C8" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$134,"🔴 تحت الهدف")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"🔴 تحت الهدف")</f>
         <v/>
       </c>
     </row>
@@ -41098,7 +45879,7 @@
         </is>
       </c>
       <c r="C9" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$134,"—")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"—")</f>
         <v/>
       </c>
     </row>
@@ -41210,11 +45991,11 @@
         </is>
       </c>
       <c r="C18" s="59">
-        <f>'التقنية الرقمية · المؤشرات'!AB12</f>
+        <f>'التقنية الرقمية · المؤشرات'!AB28</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF(ROUND('التقنية الرقمية · المؤشرات'!AB12,3)=1,"✅ سليم","⚠️ يحتاج ضبط")</f>
+        <f>IF(ROUND('التقنية الرقمية · المؤشرات'!AB28,3)=1,"✅ سليم","⚠️ يحتاج ضبط")</f>
         <v/>
       </c>
     </row>
@@ -41225,11 +46006,11 @@
         </is>
       </c>
       <c r="C19" s="59">
-        <f>'الموارد البشرية · المؤشرات'!AB12</f>
+        <f>'الموارد البشرية · المؤشرات'!AB21</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IF(ROUND('الموارد البشرية · المؤشرات'!AB12,3)=1,"✅ سليم","⚠️ يحتاج ضبط")</f>
+        <f>IF(ROUND('الموارد البشرية · المؤشرات'!AB21,3)=1,"✅ سليم","⚠️ يحتاج ضبط")</f>
         <v/>
       </c>
     </row>
@@ -41356,11 +46137,11 @@
         </is>
       </c>
       <c r="C29" s="58">
-        <f>COUNTBLANK('التقنية الرقمية · المؤشرات'!Z4:Z11)</f>
+        <f>COUNTBLANK('التقنية الرقمية · المؤشرات'!Z4:Z27)</f>
         <v/>
       </c>
       <c r="D29" s="21">
-        <f>IF(COUNTBLANK('التقنية الرقمية · المؤشرات'!Z4:Z11)=0,"✅ مكتمل","⏳ "&amp;COUNTBLANK('التقنية الرقمية · المؤشرات'!Z4:Z11)&amp;" بانتظار")</f>
+        <f>IF(COUNTBLANK('التقنية الرقمية · المؤشرات'!Z4:Z27)=0,"✅ مكتمل","⏳ "&amp;COUNTBLANK('التقنية الرقمية · المؤشرات'!Z4:Z27)&amp;" بانتظار")</f>
         <v/>
       </c>
     </row>
@@ -41371,11 +46152,11 @@
         </is>
       </c>
       <c r="C30" s="58">
-        <f>COUNTBLANK('الموارد البشرية · المؤشرات'!Z4:Z11)</f>
+        <f>COUNTBLANK('الموارد البشرية · المؤشرات'!Z4:Z20)</f>
         <v/>
       </c>
       <c r="D30" s="21">
-        <f>IF(COUNTBLANK('الموارد البشرية · المؤشرات'!Z4:Z11)=0,"✅ مكتمل","⏳ "&amp;COUNTBLANK('الموارد البشرية · المؤشرات'!Z4:Z11)&amp;" بانتظار")</f>
+        <f>IF(COUNTBLANK('الموارد البشرية · المؤشرات'!Z4:Z20)=0,"✅ مكتمل","⏳ "&amp;COUNTBLANK('الموارد البشرية · المؤشرات'!Z4:Z20)&amp;" بانتظار")</f>
         <v/>
       </c>
     </row>
@@ -41427,11 +46208,11 @@
         </is>
       </c>
       <c r="C35" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"التوسع في المواقع")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"التوسع في المواقع")</f>
         <v/>
       </c>
       <c r="D35" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"التوسع في المواقع")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"التوسع في المواقع")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -41442,11 +46223,11 @@
         </is>
       </c>
       <c r="C36" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"الامتياز التجاري")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"الامتياز التجاري")</f>
         <v/>
       </c>
       <c r="D36" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"الامتياز التجاري")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"الامتياز التجاري")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -41457,11 +46238,11 @@
         </is>
       </c>
       <c r="C37" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"زيادة وصول العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"زيادة وصول العملاء")</f>
         <v/>
       </c>
       <c r="D37" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"زيادة وصول العملاء")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"زيادة وصول العملاء")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -41472,11 +46253,11 @@
         </is>
       </c>
       <c r="C38" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"إطلاق مشاريع جديدة")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"إطلاق مشاريع جديدة")</f>
         <v/>
       </c>
       <c r="D38" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"إطلاق مشاريع جديدة")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"إطلاق مشاريع جديدة")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -41487,11 +46268,11 @@
         </is>
       </c>
       <c r="C39" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"تطوير التصاميم والهوية")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"تطوير التصاميم والهوية")</f>
         <v/>
       </c>
       <c r="D39" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"تطوير التصاميم والهوية")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"تطوير التصاميم والهوية")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -41502,11 +46283,11 @@
         </is>
       </c>
       <c r="C40" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"التحول التقني")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"التحول التقني")</f>
         <v/>
       </c>
       <c r="D40" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"التحول التقني")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"التحول التقني")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -41517,11 +46298,11 @@
         </is>
       </c>
       <c r="C41" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"ساحات درب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"ساحات درب")</f>
         <v/>
       </c>
       <c r="D41" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"ساحات درب")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"ساحات درب")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -41532,11 +46313,11 @@
         </is>
       </c>
       <c r="C42" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"تطبيق «تانكي»")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"تطبيق «تانكي»")</f>
         <v/>
       </c>
       <c r="D42" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"تطبيق «تانكي»")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"تطبيق «تانكي»")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -41547,11 +46328,11 @@
         </is>
       </c>
       <c r="C43" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"تعزيز تجربة العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"تعزيز تجربة العملاء")</f>
         <v/>
       </c>
       <c r="D43" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"تعزيز تجربة العملاء")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"تعزيز تجربة العملاء")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -41562,11 +46343,11 @@
         </is>
       </c>
       <c r="C44" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"جودة التشغيل")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"جودة التشغيل")</f>
         <v/>
       </c>
       <c r="D44" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"جودة التشغيل")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"جودة التشغيل")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -41577,11 +46358,11 @@
         </is>
       </c>
       <c r="C45" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"منظومة التأجير")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"منظومة التأجير")</f>
         <v/>
       </c>
       <c r="D45" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"منظومة التأجير")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"منظومة التأجير")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -41592,11 +46373,11 @@
         </is>
       </c>
       <c r="C46" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"الاستثمار في الموظفين")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"الاستثمار في الموظفين")</f>
         <v/>
       </c>
       <c r="D46" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$134,"الاستثمار في الموظفين")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"الاستثمار في الموظفين")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>

--- a/درب-مؤشرات-الأداء-2026.xlsx
+++ b/درب-مؤشرات-الأداء-2026.xlsx
@@ -23032,7 +23032,7 @@
       </c>
       <c r="Y11" s="22" t="inlineStr">
         <is>
-          <t>تطبيق «تانكي»</t>
+          <t>التحول التقني</t>
         </is>
       </c>
       <c r="Z11" s="66" t="n"/>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="Y23" s="22" t="inlineStr">
         <is>
-          <t>تطبيق «تانكي»</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="Z23" s="66" t="n"/>
@@ -28254,7 +28254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K159"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -33936,7 +33936,7 @@
       </c>
       <c r="H113" s="91" t="inlineStr">
         <is>
-          <t>تطبيق «تانكي»</t>
+          <t>التحول التقني</t>
         </is>
       </c>
       <c r="I113" s="68" t="inlineStr">
@@ -34548,7 +34548,7 @@
       </c>
       <c r="H125" s="91" t="inlineStr">
         <is>
-          <t>تطبيق «تانكي»</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I125" s="68" t="inlineStr">
@@ -36296,6 +36296,108 @@
         </is>
       </c>
       <c r="K159" s="38" t="n"/>
+    </row>
+    <row r="160" ht="22" customHeight="1">
+      <c r="A160" s="68" t="n">
+        <v>157</v>
+      </c>
+      <c r="B160" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C160" s="91" t="inlineStr">
+        <is>
+          <t>وصول محتوى تطبيق تانكي</t>
+        </is>
+      </c>
+      <c r="D160" s="68" t="inlineStr">
+        <is>
+          <t>وصول</t>
+        </is>
+      </c>
+      <c r="E160" s="92" t="inlineStr">
+        <is>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F160" s="68" t="inlineStr">
+        <is>
+          <t>1م وصول</t>
+        </is>
+      </c>
+      <c r="G160" s="68" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="H160" s="91" t="inlineStr">
+        <is>
+          <t>تطبيق «تانكي»</t>
+        </is>
+      </c>
+      <c r="I160" s="68" t="inlineStr">
+        <is>
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="J160" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K160" s="38" t="n"/>
+    </row>
+    <row r="161" ht="22" customHeight="1">
+      <c r="A161" s="68" t="n">
+        <v>158</v>
+      </c>
+      <c r="B161" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C161" s="91" t="inlineStr">
+        <is>
+          <t>مشاركات تطبيق تانكي</t>
+        </is>
+      </c>
+      <c r="D161" s="68" t="inlineStr">
+        <is>
+          <t>مشاركة</t>
+        </is>
+      </c>
+      <c r="E161" s="92" t="inlineStr">
+        <is>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+        </is>
+      </c>
+      <c r="F161" s="68" t="inlineStr">
+        <is>
+          <t>250 مشاركة</t>
+        </is>
+      </c>
+      <c r="G161" s="68" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="H161" s="91" t="inlineStr">
+        <is>
+          <t>تطبيق «تانكي»</t>
+        </is>
+      </c>
+      <c r="I161" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="J161" s="68" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="K161" s="38" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
@@ -36901,7 +37003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -42271,6 +42373,74 @@
       </c>
       <c r="H159" s="68">
         <f>'التسويق · المؤشرات'!AH16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="68" t="n">
+        <v>157</v>
+      </c>
+      <c r="B160" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C160" s="91">
+        <f>'التسويق · المؤشرات'!C17</f>
+        <v/>
+      </c>
+      <c r="D160" s="68">
+        <f>'التسويق · المؤشرات'!X17</f>
+        <v/>
+      </c>
+      <c r="E160" s="91">
+        <f>'التسويق · المؤشرات'!Y17</f>
+        <v/>
+      </c>
+      <c r="F160" s="93">
+        <f>'التسويق · المؤشرات'!V17</f>
+        <v/>
+      </c>
+      <c r="G160" s="68">
+        <f>'التسويق · المؤشرات'!W17</f>
+        <v/>
+      </c>
+      <c r="H160" s="68">
+        <f>'التسويق · المؤشرات'!AH17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="68" t="n">
+        <v>158</v>
+      </c>
+      <c r="B161" s="91" t="inlineStr">
+        <is>
+          <t>التسويق</t>
+        </is>
+      </c>
+      <c r="C161" s="91">
+        <f>'التسويق · المؤشرات'!C18</f>
+        <v/>
+      </c>
+      <c r="D161" s="68">
+        <f>'التسويق · المؤشرات'!X18</f>
+        <v/>
+      </c>
+      <c r="E161" s="91">
+        <f>'التسويق · المؤشرات'!Y18</f>
+        <v/>
+      </c>
+      <c r="F161" s="93">
+        <f>'التسويق · المؤشرات'!V18</f>
+        <v/>
+      </c>
+      <c r="G161" s="68">
+        <f>'التسويق · المؤشرات'!W18</f>
+        <v/>
+      </c>
+      <c r="H161" s="68">
+        <f>'التسويق · المؤشرات'!AH18</f>
         <v/>
       </c>
     </row>
@@ -42290,7 +42460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH17"/>
+  <dimension ref="A1:AH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -42332,7 +42502,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="28" t="inlineStr">
         <is>
-          <t>إدارة التسويق · مؤشرات الأداء 2026  (13 مؤشر / 9 موظفين) — تطوير الهوية وزيادة الوصول</t>
+          <t>إدارة التسويق · مؤشرات الأداء 2026  (15 مؤشراً / 9 موظفين) — تطوير الهوية وزيادة الوصول</t>
         </is>
       </c>
     </row>
@@ -42593,7 +42763,7 @@
         </is>
       </c>
       <c r="AB4" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC4" s="23">
         <f>IF($V4="","",$AB4*MIN($V4,1))</f>
@@ -42699,7 +42869,7 @@
         </is>
       </c>
       <c r="AB5" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC5" s="23">
         <f>IF($V5="","",$AB5*MIN($V5,1))</f>
@@ -42805,7 +42975,7 @@
         </is>
       </c>
       <c r="AB6" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC6" s="23">
         <f>IF($V6="","",$AB6*MIN($V6,1))</f>
@@ -42911,7 +43081,7 @@
         </is>
       </c>
       <c r="AB7" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC7" s="23">
         <f>IF($V7="","",$AB7*MIN($V7,1))</f>
@@ -43017,7 +43187,7 @@
         </is>
       </c>
       <c r="AB8" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC8" s="23">
         <f>IF($V8="","",$AB8*MIN($V8,1))</f>
@@ -43123,7 +43293,7 @@
         </is>
       </c>
       <c r="AB9" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC9" s="23">
         <f>IF($V9="","",$AB9*MIN($V9,1))</f>
@@ -43229,7 +43399,7 @@
         </is>
       </c>
       <c r="AB10" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC10" s="23">
         <f>IF($V10="","",$AB10*MIN($V10,1))</f>
@@ -43335,7 +43505,7 @@
         </is>
       </c>
       <c r="AB11" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC11" s="23">
         <f>IF($V11="","",$AB11*MIN($V11,1))</f>
@@ -43441,7 +43611,7 @@
         </is>
       </c>
       <c r="AB12" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC12" s="23">
         <f>IF($V12="","",$AB12*MIN($V12,1))</f>
@@ -43547,7 +43717,7 @@
         </is>
       </c>
       <c r="AB13" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC13" s="23">
         <f>IF($V13="","",$AB13*MIN($V13,1))</f>
@@ -43653,7 +43823,7 @@
         </is>
       </c>
       <c r="AB14" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC14" s="23">
         <f>IF($V14="","",$AB14*MIN($V14,1))</f>
@@ -43759,7 +43929,7 @@
         </is>
       </c>
       <c r="AB15" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC15" s="23">
         <f>IF($V15="","",$AB15*MIN($V15,1))</f>
@@ -43865,7 +44035,7 @@
         </is>
       </c>
       <c r="AB16" s="53" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="AC16" s="23">
         <f>IF($V16="","",$AB16*MIN($V16,1))</f>
@@ -43893,31 +44063,243 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="80" t="inlineStr"/>
-      <c r="B17" s="81" t="inlineStr">
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>تطبيق تانكي</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>وصول محتوى تطبيق تانكي</t>
+        </is>
+      </c>
+      <c r="D17" s="60" t="inlineStr">
+        <is>
+          <t>وصول</t>
+        </is>
+      </c>
+      <c r="E17" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F17" s="60" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="G17" s="61" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H17" s="62" t="inlineStr">
+        <is>
+          <t>1م وصول</t>
+        </is>
+      </c>
+      <c r="I17" s="63" t="n"/>
+      <c r="J17" s="63" t="n"/>
+      <c r="K17" s="63" t="n"/>
+      <c r="L17" s="63" t="n"/>
+      <c r="M17" s="63" t="n"/>
+      <c r="N17" s="63" t="n"/>
+      <c r="O17" s="63" t="n"/>
+      <c r="P17" s="63" t="n"/>
+      <c r="Q17" s="63" t="n"/>
+      <c r="R17" s="63" t="n"/>
+      <c r="S17" s="63" t="n"/>
+      <c r="T17" s="63" t="n"/>
+      <c r="U17" s="64">
+        <f>IF($F17="SUM",IF(COUNT($I17:$T17)=0,"",SUM($I17:$T17)),IF($F17="AVG",IFERROR(AVERAGE($I17:$T17),""),IF($F17="LAST",IFERROR(LOOKUP(2,1/($I17:$T17&lt;&gt;""),$I17:$T17),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V17" s="23">
+        <f>IF($G17="","",IF($U17="","",IF($G17=0,IF($U17&lt;=0,1,0),IF($E17="↓",IFERROR($G17/$U17,0),IFERROR($U17/$G17,0)))))</f>
+        <v/>
+      </c>
+      <c r="W17" s="17">
+        <f>IF($V17="","—",IF($V17&gt;=1,"✅ محقق",IF($V17&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X17" s="65" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="Y17" s="22" t="inlineStr">
+        <is>
+          <t>تطبيق «تانكي»</t>
+        </is>
+      </c>
+      <c r="Z17" s="66" t="n"/>
+      <c r="AA17" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB17" s="53" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="AC17" s="23">
+        <f>IF($V17="","",$AB17*MIN($V17,1))</f>
+        <v/>
+      </c>
+      <c r="AD17" s="61">
+        <f>IF($G17="","",IF($F17="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G17/12*'لوحة الإدارة التنفيذية'!$P$2),$G17))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="67">
+        <f>IF($F17="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U17="","",$U17/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U17="","",$U17))</f>
+        <v/>
+      </c>
+      <c r="AF17" s="61">
+        <f>IF(OR($AE17="",$G17=""),"",$AE17-$G17)</f>
+        <v/>
+      </c>
+      <c r="AG17" s="17">
+        <f>IF(OR($AE17="",$G17=""),"—",IF($E17="↓",IF($AE17&lt;=$G17,"🟢 على المسار",IF($AE17&lt;=$G17*1.1,"🟡 متابعة","🔴 خطر")),IF($AE17&gt;=$G17,"🟢 على المسار",IF($AE17&gt;=$G17*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH17" s="68" t="inlineStr">
+        <is>
+          <t>العملاء</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>تطبيق تانكي</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>مشاركات تطبيق تانكي</t>
+        </is>
+      </c>
+      <c r="D18" s="60" t="inlineStr">
+        <is>
+          <t>مشاركة</t>
+        </is>
+      </c>
+      <c r="E18" s="60" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F18" s="60" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="G18" s="61" t="n">
+        <v>250</v>
+      </c>
+      <c r="H18" s="62" t="inlineStr">
+        <is>
+          <t>250 مشاركة</t>
+        </is>
+      </c>
+      <c r="I18" s="63" t="n"/>
+      <c r="J18" s="63" t="n"/>
+      <c r="K18" s="63" t="n"/>
+      <c r="L18" s="63" t="n"/>
+      <c r="M18" s="63" t="n"/>
+      <c r="N18" s="63" t="n"/>
+      <c r="O18" s="63" t="n"/>
+      <c r="P18" s="63" t="n"/>
+      <c r="Q18" s="63" t="n"/>
+      <c r="R18" s="63" t="n"/>
+      <c r="S18" s="63" t="n"/>
+      <c r="T18" s="63" t="n"/>
+      <c r="U18" s="64">
+        <f>IF($F18="SUM",IF(COUNT($I18:$T18)=0,"",SUM($I18:$T18)),IF($F18="AVG",IFERROR(AVERAGE($I18:$T18),""),IF($F18="LAST",IFERROR(LOOKUP(2,1/($I18:$T18&lt;&gt;""),$I18:$T18),""),"")))</f>
+        <v/>
+      </c>
+      <c r="V18" s="23">
+        <f>IF($G18="","",IF($U18="","",IF($G18=0,IF($U18&lt;=0,1,0),IF($E18="↓",IFERROR($G18/$U18,0),IFERROR($U18/$G18,0)))))</f>
+        <v/>
+      </c>
+      <c r="W18" s="17">
+        <f>IF($V18="","—",IF($V18&gt;=1,"✅ محقق",IF($V18&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="X18" s="65" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="Y18" s="22" t="inlineStr">
+        <is>
+          <t>تطبيق «تانكي»</t>
+        </is>
+      </c>
+      <c r="Z18" s="66" t="n"/>
+      <c r="AA18" s="21" t="inlineStr">
+        <is>
+          <t>🟣 لاحق</t>
+        </is>
+      </c>
+      <c r="AB18" s="53" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="AC18" s="23">
+        <f>IF($V18="","",$AB18*MIN($V18,1))</f>
+        <v/>
+      </c>
+      <c r="AD18" s="61">
+        <f>IF($G18="","",IF($F18="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G18/12*'لوحة الإدارة التنفيذية'!$P$2),$G18))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="67">
+        <f>IF($F18="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U18="","",$U18/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U18="","",$U18))</f>
+        <v/>
+      </c>
+      <c r="AF18" s="61">
+        <f>IF(OR($AE18="",$G18=""),"",$AE18-$G18)</f>
+        <v/>
+      </c>
+      <c r="AG18" s="17">
+        <f>IF(OR($AE18="",$G18=""),"—",IF($E18="↓",IF($AE18&lt;=$G18,"🟢 على المسار",IF($AE18&lt;=$G18*1.1,"🟡 متابعة","🔴 خطر")),IF($AE18&gt;=$G18,"🟢 على المسار",IF($AE18&gt;=$G18*0.85,"🟡 متابعة","🔴 خطر"))))</f>
+        <v/>
+      </c>
+      <c r="AH18" s="68" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="80" t="inlineStr"/>
+      <c r="B19" s="81" t="inlineStr">
         <is>
           <t>الإجمالي الموزون للإدارة</t>
         </is>
       </c>
-      <c r="AB17" s="82">
-        <f>SUM(AB4:AB16)</f>
-        <v/>
-      </c>
-      <c r="AC17" s="83">
-        <f>SUM(AC4:AC16)</f>
+      <c r="AB19" s="82">
+        <f>SUM(AB4:AB18)</f>
+        <v/>
+      </c>
+      <c r="AC19" s="83">
+        <f>SUM(AC4:AC18)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
   <mergeCells count="3">
-    <mergeCell ref="B17:AA17"/>
     <mergeCell ref="A2:AH2"/>
     <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="B19:AA19"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 N4 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 S4 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 T4 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 Z4 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="قيمة غير صحيحة" error="أدخل رقماً موجباً فقط" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 N4 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 S4 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 T4 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 Z4 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="قيمة غير صحيحة" error="أدخل رقماً موجباً فقط" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -43984,11 +44366,11 @@
         </is>
       </c>
       <c r="C5" s="25">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$H$4:$H$159,"مالي"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$H$4:$H$161,"مالي"),"—")</f>
         <v/>
       </c>
       <c r="D5" s="26">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$159,"مالي")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$161,"مالي")</f>
         <v/>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -44004,11 +44386,11 @@
         </is>
       </c>
       <c r="C6" s="25">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$H$4:$H$159,"العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$H$4:$H$161,"العملاء"),"—")</f>
         <v/>
       </c>
       <c r="D6" s="26">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$159,"العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$161,"العملاء")</f>
         <v/>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -44024,11 +44406,11 @@
         </is>
       </c>
       <c r="C7" s="25">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$H$4:$H$159,"العمليات الداخلية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$H$4:$H$161,"العمليات الداخلية"),"—")</f>
         <v/>
       </c>
       <c r="D7" s="26">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$159,"العمليات الداخلية")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$161,"العمليات الداخلية")</f>
         <v/>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -44044,11 +44426,11 @@
         </is>
       </c>
       <c r="C8" s="25">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$H$4:$H$159,"التعلّم والنمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$H$4:$H$161,"التعلّم والنمو"),"—")</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$159,"التعلّم والنمو")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$161,"التعلّم والنمو")</f>
         <v/>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -44174,7 +44556,7 @@
         </is>
       </c>
       <c r="G4" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"التوسع في المواقع")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"التوسع في المواقع"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"التوسع في المواقع")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"التوسع في المواقع"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44203,7 +44585,7 @@
         </is>
       </c>
       <c r="G5" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"الامتياز التجاري")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"الامتياز التجاري"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"الامتياز التجاري")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"الامتياز التجاري"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44232,7 +44614,7 @@
         </is>
       </c>
       <c r="G6" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"زيادة وصول العملاء")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"زيادة وصول العملاء"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"زيادة وصول العملاء")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"زيادة وصول العملاء"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44266,7 +44648,7 @@
         </is>
       </c>
       <c r="G7" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"إطلاق مشاريع جديدة")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"إطلاق مشاريع جديدة"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"إطلاق مشاريع جديدة")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"إطلاق مشاريع جديدة"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44295,7 +44677,7 @@
         </is>
       </c>
       <c r="G8" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"تطوير التصاميم والهوية")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"تطوير التصاميم والهوية"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"تطوير التصاميم والهوية")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"تطوير التصاميم والهوية"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44324,7 +44706,7 @@
         </is>
       </c>
       <c r="G9" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"التحول التقني")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"التحول التقني"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"التحول التقني")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"التحول التقني"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44353,7 +44735,7 @@
         </is>
       </c>
       <c r="G10" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"ساحات درب")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"ساحات درب"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"ساحات درب")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"ساحات درب"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44368,12 +44750,12 @@
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>التسويق (المنتج) + التقنية (التكامل)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>MAU · التنزيلات · المعاملات الرقمية · الرضا</t>
+          <t>وصول ومشاركات تانكي · تكامل المحطات</t>
         </is>
       </c>
       <c r="F11" s="32" t="inlineStr">
@@ -44382,7 +44764,7 @@
         </is>
       </c>
       <c r="G11" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"تطبيق «تانكي»")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"تطبيق «تانكي»"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"تطبيق «تانكي»")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"تطبيق «تانكي»"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44416,7 +44798,7 @@
         </is>
       </c>
       <c r="G12" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"تعزيز تجربة العملاء")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"تعزيز تجربة العملاء"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"تعزيز تجربة العملاء")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"تعزيز تجربة العملاء"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44445,7 +44827,7 @@
         </is>
       </c>
       <c r="G13" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"جودة التشغيل")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"جودة التشغيل"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"جودة التشغيل")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"جودة التشغيل"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44474,7 +44856,7 @@
         </is>
       </c>
       <c r="G14" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"منظومة التأجير")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"منظومة التأجير"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"منظومة التأجير")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"منظومة التأجير"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44503,7 +44885,7 @@
         </is>
       </c>
       <c r="G15" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$159,"الاستثمار في الموظفين")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$E$4:$E$159,"الاستثمار في الموظفين"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"الاستثمار في الموظفين")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"الاستثمار في الموظفين"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44625,19 +45007,19 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="44">
-        <f>IFERROR(AVERAGE('قاعدة المؤشرات'!$F$4:$F$159),0)</f>
+        <f>IFERROR(AVERAGE('قاعدة المؤشرات'!$F$4:$F$161),0)</f>
         <v/>
       </c>
       <c r="D5" s="45">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"✅ محقق")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"✅ محقق")</f>
         <v/>
       </c>
       <c r="E5" s="45">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"🟡 قريب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"🟡 قريب")</f>
         <v/>
       </c>
       <c r="F5" s="45">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"🔴 تحت الهدف")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"🔴 تحت الهدف")</f>
         <v/>
       </c>
       <c r="H5" s="46" t="inlineStr">
@@ -44666,7 +45048,7 @@
         </is>
       </c>
       <c r="I6" s="33">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$D$4:$D$159,"النمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$D$4:$D$161,"النمو"),"—")</f>
         <v/>
       </c>
       <c r="J6" s="49">
@@ -44681,7 +45063,7 @@
         </is>
       </c>
       <c r="I7" s="33">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$D$4:$D$159,"الابتكار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$D$4:$D$161,"الابتكار"),"—")</f>
         <v/>
       </c>
       <c r="J7" s="49">
@@ -44696,7 +45078,7 @@
         </is>
       </c>
       <c r="I8" s="33">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$D$4:$D$159,"الاستدامة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$D$4:$D$161,"الاستدامة"),"—")</f>
         <v/>
       </c>
       <c r="J8" s="49">
@@ -44737,7 +45119,7 @@
         </is>
       </c>
       <c r="C11" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"الإدارة التنفيذية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"الإدارة التنفيذية"),"—")</f>
         <v/>
       </c>
       <c r="D11" s="17">
@@ -44752,7 +45134,7 @@
         </is>
       </c>
       <c r="C12" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"الامتياز التجاري"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"الامتياز التجاري"),"—")</f>
         <v/>
       </c>
       <c r="D12" s="17">
@@ -44767,7 +45149,7 @@
         </is>
       </c>
       <c r="C13" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"التشغيل والمحطات"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"التشغيل والمحطات"),"—")</f>
         <v/>
       </c>
       <c r="D13" s="17">
@@ -44782,7 +45164,7 @@
         </is>
       </c>
       <c r="C14" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"الاستثمار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"الاستثمار"),"—")</f>
         <v/>
       </c>
       <c r="D14" s="17">
@@ -44797,7 +45179,7 @@
         </is>
       </c>
       <c r="C15" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"العقار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"العقار"),"—")</f>
         <v/>
       </c>
       <c r="D15" s="17">
@@ -44812,7 +45194,7 @@
         </is>
       </c>
       <c r="C16" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"التقنية الرقمية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"التقنية الرقمية"),"—")</f>
         <v/>
       </c>
       <c r="D16" s="17">
@@ -44827,7 +45209,7 @@
         </is>
       </c>
       <c r="C17" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"الموارد البشرية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"الموارد البشرية"),"—")</f>
         <v/>
       </c>
       <c r="D17" s="17">
@@ -44842,7 +45224,7 @@
         </is>
       </c>
       <c r="C18" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$159,'قاعدة المؤشرات'!$B$4:$B$159,"التسويق"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"التسويق"),"—")</f>
         <v/>
       </c>
       <c r="D18" s="17">
@@ -45835,7 +46217,7 @@
         </is>
       </c>
       <c r="C5" s="58">
-        <f>159-3</f>
+        <f>161-3</f>
         <v/>
       </c>
     </row>
@@ -45846,7 +46228,7 @@
         </is>
       </c>
       <c r="C6" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"✅ محقق")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"✅ محقق")</f>
         <v/>
       </c>
     </row>
@@ -45857,7 +46239,7 @@
         </is>
       </c>
       <c r="C7" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"🟡 قريب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"🟡 قريب")</f>
         <v/>
       </c>
     </row>
@@ -45868,7 +46250,7 @@
         </is>
       </c>
       <c r="C8" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"🔴 تحت الهدف")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"🔴 تحت الهدف")</f>
         <v/>
       </c>
     </row>
@@ -45879,7 +46261,7 @@
         </is>
       </c>
       <c r="C9" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$159,"—")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"—")</f>
         <v/>
       </c>
     </row>
@@ -46021,11 +46403,11 @@
         </is>
       </c>
       <c r="C20" s="59">
-        <f>'التسويق · المؤشرات'!AB17</f>
+        <f>'التسويق · المؤشرات'!AB19</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>IF(ROUND('التسويق · المؤشرات'!AB17,3)=1,"✅ سليم","⚠️ يحتاج ضبط")</f>
+        <f>IF(ROUND('التسويق · المؤشرات'!AB19,3)=1,"✅ سليم","⚠️ يحتاج ضبط")</f>
         <v/>
       </c>
     </row>
@@ -46167,11 +46549,11 @@
         </is>
       </c>
       <c r="C31" s="58">
-        <f>COUNTBLANK('التسويق · المؤشرات'!Z4:Z16)</f>
+        <f>COUNTBLANK('التسويق · المؤشرات'!Z4:Z18)</f>
         <v/>
       </c>
       <c r="D31" s="21">
-        <f>IF(COUNTBLANK('التسويق · المؤشرات'!Z4:Z16)=0,"✅ مكتمل","⏳ "&amp;COUNTBLANK('التسويق · المؤشرات'!Z4:Z16)&amp;" بانتظار")</f>
+        <f>IF(COUNTBLANK('التسويق · المؤشرات'!Z4:Z18)=0,"✅ مكتمل","⏳ "&amp;COUNTBLANK('التسويق · المؤشرات'!Z4:Z18)&amp;" بانتظار")</f>
         <v/>
       </c>
     </row>
@@ -46208,11 +46590,11 @@
         </is>
       </c>
       <c r="C35" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"التوسع في المواقع")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"التوسع في المواقع")</f>
         <v/>
       </c>
       <c r="D35" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"التوسع في المواقع")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"التوسع في المواقع")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46223,11 +46605,11 @@
         </is>
       </c>
       <c r="C36" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"الامتياز التجاري")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"الامتياز التجاري")</f>
         <v/>
       </c>
       <c r="D36" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"الامتياز التجاري")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"الامتياز التجاري")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46238,11 +46620,11 @@
         </is>
       </c>
       <c r="C37" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"زيادة وصول العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"زيادة وصول العملاء")</f>
         <v/>
       </c>
       <c r="D37" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"زيادة وصول العملاء")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"زيادة وصول العملاء")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46253,11 +46635,11 @@
         </is>
       </c>
       <c r="C38" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"إطلاق مشاريع جديدة")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"إطلاق مشاريع جديدة")</f>
         <v/>
       </c>
       <c r="D38" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"إطلاق مشاريع جديدة")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"إطلاق مشاريع جديدة")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46268,11 +46650,11 @@
         </is>
       </c>
       <c r="C39" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"تطوير التصاميم والهوية")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"تطوير التصاميم والهوية")</f>
         <v/>
       </c>
       <c r="D39" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"تطوير التصاميم والهوية")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"تطوير التصاميم والهوية")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46283,11 +46665,11 @@
         </is>
       </c>
       <c r="C40" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"التحول التقني")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"التحول التقني")</f>
         <v/>
       </c>
       <c r="D40" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"التحول التقني")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"التحول التقني")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46298,11 +46680,11 @@
         </is>
       </c>
       <c r="C41" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"ساحات درب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"ساحات درب")</f>
         <v/>
       </c>
       <c r="D41" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"ساحات درب")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"ساحات درب")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46313,11 +46695,11 @@
         </is>
       </c>
       <c r="C42" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"تطبيق «تانكي»")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"تطبيق «تانكي»")</f>
         <v/>
       </c>
       <c r="D42" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"تطبيق «تانكي»")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"تطبيق «تانكي»")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46328,11 +46710,11 @@
         </is>
       </c>
       <c r="C43" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"تعزيز تجربة العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"تعزيز تجربة العملاء")</f>
         <v/>
       </c>
       <c r="D43" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"تعزيز تجربة العملاء")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"تعزيز تجربة العملاء")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46343,11 +46725,11 @@
         </is>
       </c>
       <c r="C44" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"جودة التشغيل")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"جودة التشغيل")</f>
         <v/>
       </c>
       <c r="D44" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"جودة التشغيل")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"جودة التشغيل")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46358,11 +46740,11 @@
         </is>
       </c>
       <c r="C45" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"منظومة التأجير")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"منظومة التأجير")</f>
         <v/>
       </c>
       <c r="D45" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"منظومة التأجير")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"منظومة التأجير")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46373,11 +46755,11 @@
         </is>
       </c>
       <c r="C46" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"الاستثمار في الموظفين")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"الاستثمار في الموظفين")</f>
         <v/>
       </c>
       <c r="D46" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$159,"الاستثمار في الموظفين")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"الاستثمار في الموظفين")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>

--- a/درب-مؤشرات-الأداء-2026.xlsx
+++ b/درب-مؤشرات-الأداء-2026.xlsx
@@ -21997,7 +21997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH28"/>
+  <dimension ref="A1:AH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -22039,7 +22039,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="28" t="inlineStr">
         <is>
-          <t>إدارة التقنية · مؤشرات الأداء 2026  (24 مؤشراً) — مشاريع التحول والكفاءة التشغيلية</t>
+          <t>إدارة التقنية · مؤشرات الأداء 2026  (9 مؤشرات) — المشاريع في سجل المبادرات</t>
         </is>
       </c>
     </row>
@@ -22228,17 +22228,17 @@
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>أداء المشاريع</t>
         </is>
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>نظام أتمتة الكاش (Cash-In) في المحطات</t>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
       </c>
       <c r="D4" s="60" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E4" s="60" t="inlineStr">
@@ -22251,27 +22251,27 @@
           <t>LAST</t>
         </is>
       </c>
-      <c r="G4" s="61" t="n">
-        <v>164</v>
+      <c r="G4" s="74" t="n">
+        <v>1</v>
       </c>
       <c r="H4" s="62" t="inlineStr">
         <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I4" s="63" t="n"/>
-      <c r="J4" s="63" t="n"/>
-      <c r="K4" s="63" t="n"/>
-      <c r="L4" s="63" t="n"/>
-      <c r="M4" s="63" t="n"/>
-      <c r="N4" s="63" t="n"/>
-      <c r="O4" s="63" t="n"/>
-      <c r="P4" s="63" t="n"/>
-      <c r="Q4" s="63" t="n"/>
-      <c r="R4" s="63" t="n"/>
-      <c r="S4" s="63" t="n"/>
-      <c r="T4" s="63" t="n"/>
-      <c r="U4" s="64">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I4" s="73" t="n"/>
+      <c r="J4" s="73" t="n"/>
+      <c r="K4" s="73" t="n"/>
+      <c r="L4" s="73" t="n"/>
+      <c r="M4" s="73" t="n"/>
+      <c r="N4" s="73" t="n"/>
+      <c r="O4" s="73" t="n"/>
+      <c r="P4" s="73" t="n"/>
+      <c r="Q4" s="73" t="n"/>
+      <c r="R4" s="73" t="n"/>
+      <c r="S4" s="73" t="n"/>
+      <c r="T4" s="73" t="n"/>
+      <c r="U4" s="59">
         <f>IF($F4="SUM",IF(COUNT($I4:$T4)=0,"",SUM($I4:$T4)),IF($F4="AVG",IFERROR(AVERAGE($I4:$T4),""),IF($F4="LAST",IFERROR(LOOKUP(2,1/($I4:$T4&lt;&gt;""),$I4:$T4),""),"")))</f>
         <v/>
       </c>
@@ -22293,28 +22293,28 @@
           <t>التحول التقني</t>
         </is>
       </c>
-      <c r="Z4" s="66" t="n"/>
+      <c r="Z4" s="53" t="n"/>
       <c r="AA4" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB4" s="53" t="n">
-        <v>0.0417</v>
+        <v>0.1111</v>
       </c>
       <c r="AC4" s="23">
         <f>IF($V4="","",$AB4*MIN($V4,1))</f>
         <v/>
       </c>
-      <c r="AD4" s="61">
+      <c r="AD4" s="74">
         <f>IF($G4="","",IF($F4="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G4/12*'لوحة الإدارة التنفيذية'!$P$2),$G4))</f>
         <v/>
       </c>
-      <c r="AE4" s="67">
+      <c r="AE4" s="23">
         <f>IF($F4="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U4="","",$U4/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U4="","",$U4))</f>
         <v/>
       </c>
-      <c r="AF4" s="61">
+      <c r="AF4" s="74">
         <f>IF(OR($AE4="",$G4=""),"",$AE4-$G4)</f>
         <v/>
       </c>
@@ -22334,17 +22334,17 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>أداء المشاريع</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>D365 FNO — المرحلة الأولى</t>
+          <t>معدل تسليم المشاريع في الموعد المحدد</t>
         </is>
       </c>
       <c r="D5" s="60" t="inlineStr">
         <is>
-          <t>وحدة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E5" s="60" t="inlineStr">
@@ -22354,30 +22354,30 @@
       </c>
       <c r="F5" s="60" t="inlineStr">
         <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G5" s="75" t="n">
-        <v>5</v>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="G5" s="74" t="n">
+        <v>0.9</v>
       </c>
       <c r="H5" s="62" t="inlineStr">
         <is>
-          <t>5 وحدات</t>
-        </is>
-      </c>
-      <c r="I5" s="76" t="n"/>
-      <c r="J5" s="76" t="n"/>
-      <c r="K5" s="76" t="n"/>
-      <c r="L5" s="76" t="n"/>
-      <c r="M5" s="76" t="n"/>
-      <c r="N5" s="76" t="n"/>
-      <c r="O5" s="76" t="n"/>
-      <c r="P5" s="76" t="n"/>
-      <c r="Q5" s="76" t="n"/>
-      <c r="R5" s="76" t="n"/>
-      <c r="S5" s="76" t="n"/>
-      <c r="T5" s="76" t="n"/>
-      <c r="U5" s="77">
+          <t>≥ 90%</t>
+        </is>
+      </c>
+      <c r="I5" s="73" t="n"/>
+      <c r="J5" s="73" t="n"/>
+      <c r="K5" s="73" t="n"/>
+      <c r="L5" s="73" t="n"/>
+      <c r="M5" s="73" t="n"/>
+      <c r="N5" s="73" t="n"/>
+      <c r="O5" s="73" t="n"/>
+      <c r="P5" s="73" t="n"/>
+      <c r="Q5" s="73" t="n"/>
+      <c r="R5" s="73" t="n"/>
+      <c r="S5" s="73" t="n"/>
+      <c r="T5" s="73" t="n"/>
+      <c r="U5" s="59">
         <f>IF($F5="SUM",IF(COUNT($I5:$T5)=0,"",SUM($I5:$T5)),IF($F5="AVG",IFERROR(AVERAGE($I5:$T5),""),IF($F5="LAST",IFERROR(LOOKUP(2,1/($I5:$T5&lt;&gt;""),$I5:$T5),""),"")))</f>
         <v/>
       </c>
@@ -22399,28 +22399,28 @@
           <t>التحول التقني</t>
         </is>
       </c>
-      <c r="Z5" s="78" t="n"/>
+      <c r="Z5" s="53" t="n"/>
       <c r="AA5" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB5" s="53" t="n">
-        <v>0.0417</v>
+        <v>0.1111</v>
       </c>
       <c r="AC5" s="23">
         <f>IF($V5="","",$AB5*MIN($V5,1))</f>
         <v/>
       </c>
-      <c r="AD5" s="75">
+      <c r="AD5" s="74">
         <f>IF($G5="","",IF($F5="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G5/12*'لوحة الإدارة التنفيذية'!$P$2),$G5))</f>
         <v/>
       </c>
-      <c r="AE5" s="79">
+      <c r="AE5" s="23">
         <f>IF($F5="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U5="","",$U5/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U5="","",$U5))</f>
         <v/>
       </c>
-      <c r="AF5" s="75">
+      <c r="AF5" s="74">
         <f>IF(OR($AE5="",$G5=""),"",$AE5-$G5)</f>
         <v/>
       </c>
@@ -22440,17 +22440,17 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>أداء المشاريع</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>D365 FNO — المرحلة الثانية</t>
+          <t>نسبة الالتزام بميزانية المشاريع</t>
         </is>
       </c>
       <c r="D6" s="60" t="inlineStr">
         <is>
-          <t>وحدة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E6" s="60" t="inlineStr">
@@ -22460,30 +22460,30 @@
       </c>
       <c r="F6" s="60" t="inlineStr">
         <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G6" s="61" t="n">
-        <v>4</v>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="G6" s="74" t="n">
+        <v>0.95</v>
       </c>
       <c r="H6" s="62" t="inlineStr">
         <is>
-          <t>4 وحدات</t>
-        </is>
-      </c>
-      <c r="I6" s="63" t="n"/>
-      <c r="J6" s="63" t="n"/>
-      <c r="K6" s="63" t="n"/>
-      <c r="L6" s="63" t="n"/>
-      <c r="M6" s="63" t="n"/>
-      <c r="N6" s="63" t="n"/>
-      <c r="O6" s="63" t="n"/>
-      <c r="P6" s="63" t="n"/>
-      <c r="Q6" s="63" t="n"/>
-      <c r="R6" s="63" t="n"/>
-      <c r="S6" s="63" t="n"/>
-      <c r="T6" s="63" t="n"/>
-      <c r="U6" s="64">
+          <t>≥ 95%</t>
+        </is>
+      </c>
+      <c r="I6" s="73" t="n"/>
+      <c r="J6" s="73" t="n"/>
+      <c r="K6" s="73" t="n"/>
+      <c r="L6" s="73" t="n"/>
+      <c r="M6" s="73" t="n"/>
+      <c r="N6" s="73" t="n"/>
+      <c r="O6" s="73" t="n"/>
+      <c r="P6" s="73" t="n"/>
+      <c r="Q6" s="73" t="n"/>
+      <c r="R6" s="73" t="n"/>
+      <c r="S6" s="73" t="n"/>
+      <c r="T6" s="73" t="n"/>
+      <c r="U6" s="59">
         <f>IF($F6="SUM",IF(COUNT($I6:$T6)=0,"",SUM($I6:$T6)),IF($F6="AVG",IFERROR(AVERAGE($I6:$T6),""),IF($F6="LAST",IFERROR(LOOKUP(2,1/($I6:$T6&lt;&gt;""),$I6:$T6),""),"")))</f>
         <v/>
       </c>
@@ -22505,28 +22505,28 @@
           <t>التحول التقني</t>
         </is>
       </c>
-      <c r="Z6" s="66" t="n"/>
+      <c r="Z6" s="53" t="n"/>
       <c r="AA6" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB6" s="53" t="n">
-        <v>0.0417</v>
+        <v>0.1111</v>
       </c>
       <c r="AC6" s="23">
         <f>IF($V6="","",$AB6*MIN($V6,1))</f>
         <v/>
       </c>
-      <c r="AD6" s="61">
+      <c r="AD6" s="74">
         <f>IF($G6="","",IF($F6="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G6/12*'لوحة الإدارة التنفيذية'!$P$2),$G6))</f>
         <v/>
       </c>
-      <c r="AE6" s="67">
+      <c r="AE6" s="23">
         <f>IF($F6="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U6="","",$U6/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U6="","",$U6))</f>
         <v/>
       </c>
-      <c r="AF6" s="61">
+      <c r="AF6" s="74">
         <f>IF(OR($AE6="",$G6=""),"",$AE6-$G6)</f>
         <v/>
       </c>
@@ -22546,17 +22546,17 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>أداء المشاريع</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>D365 FNO — المرحلة الثالثة</t>
+          <t>نسبة الالتزام بنطاق العمل</t>
         </is>
       </c>
       <c r="D7" s="60" t="inlineStr">
         <is>
-          <t>وحدة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E7" s="60" t="inlineStr">
@@ -22569,27 +22569,27 @@
           <t>LAST</t>
         </is>
       </c>
-      <c r="G7" s="61" t="n">
-        <v>2</v>
+      <c r="G7" s="74" t="n">
+        <v>0.95</v>
       </c>
       <c r="H7" s="62" t="inlineStr">
         <is>
-          <t>وحدتان</t>
-        </is>
-      </c>
-      <c r="I7" s="63" t="n"/>
-      <c r="J7" s="63" t="n"/>
-      <c r="K7" s="63" t="n"/>
-      <c r="L7" s="63" t="n"/>
-      <c r="M7" s="63" t="n"/>
-      <c r="N7" s="63" t="n"/>
-      <c r="O7" s="63" t="n"/>
-      <c r="P7" s="63" t="n"/>
-      <c r="Q7" s="63" t="n"/>
-      <c r="R7" s="63" t="n"/>
-      <c r="S7" s="63" t="n"/>
-      <c r="T7" s="63" t="n"/>
-      <c r="U7" s="64">
+          <t>≥ 95%</t>
+        </is>
+      </c>
+      <c r="I7" s="73" t="n"/>
+      <c r="J7" s="73" t="n"/>
+      <c r="K7" s="73" t="n"/>
+      <c r="L7" s="73" t="n"/>
+      <c r="M7" s="73" t="n"/>
+      <c r="N7" s="73" t="n"/>
+      <c r="O7" s="73" t="n"/>
+      <c r="P7" s="73" t="n"/>
+      <c r="Q7" s="73" t="n"/>
+      <c r="R7" s="73" t="n"/>
+      <c r="S7" s="73" t="n"/>
+      <c r="T7" s="73" t="n"/>
+      <c r="U7" s="59">
         <f>IF($F7="SUM",IF(COUNT($I7:$T7)=0,"",SUM($I7:$T7)),IF($F7="AVG",IFERROR(AVERAGE($I7:$T7),""),IF($F7="LAST",IFERROR(LOOKUP(2,1/($I7:$T7&lt;&gt;""),$I7:$T7),""),"")))</f>
         <v/>
       </c>
@@ -22611,28 +22611,28 @@
           <t>التحول التقني</t>
         </is>
       </c>
-      <c r="Z7" s="66" t="n"/>
+      <c r="Z7" s="53" t="n"/>
       <c r="AA7" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB7" s="53" t="n">
-        <v>0.0417</v>
+        <v>0.1111</v>
       </c>
       <c r="AC7" s="23">
         <f>IF($V7="","",$AB7*MIN($V7,1))</f>
         <v/>
       </c>
-      <c r="AD7" s="61">
+      <c r="AD7" s="74">
         <f>IF($G7="","",IF($F7="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G7/12*'لوحة الإدارة التنفيذية'!$P$2),$G7))</f>
         <v/>
       </c>
-      <c r="AE7" s="67">
+      <c r="AE7" s="23">
         <f>IF($F7="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U7="","",$U7/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U7="","",$U7))</f>
         <v/>
       </c>
-      <c r="AF7" s="61">
+      <c r="AF7" s="74">
         <f>IF(OR($AE7="",$G7=""),"",$AE7-$G7)</f>
         <v/>
       </c>
@@ -22652,17 +22652,17 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>الكفاءة التشغيلية</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>تطبيق الامتياز مع واثق</t>
+          <t>نسبة تفعيل الأنظمة الأساسية بالمحطات</t>
         </is>
       </c>
       <c r="D8" s="60" t="inlineStr">
         <is>
-          <t>تطبيق</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E8" s="60" t="inlineStr">
@@ -22675,27 +22675,27 @@
           <t>LAST</t>
         </is>
       </c>
-      <c r="G8" s="61" t="n">
+      <c r="G8" s="74" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="62" t="inlineStr">
         <is>
-          <t>تطبيق واحد</t>
-        </is>
-      </c>
-      <c r="I8" s="63" t="n"/>
-      <c r="J8" s="63" t="n"/>
-      <c r="K8" s="63" t="n"/>
-      <c r="L8" s="63" t="n"/>
-      <c r="M8" s="63" t="n"/>
-      <c r="N8" s="63" t="n"/>
-      <c r="O8" s="63" t="n"/>
-      <c r="P8" s="63" t="n"/>
-      <c r="Q8" s="63" t="n"/>
-      <c r="R8" s="63" t="n"/>
-      <c r="S8" s="63" t="n"/>
-      <c r="T8" s="63" t="n"/>
-      <c r="U8" s="64">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="73" t="n"/>
+      <c r="J8" s="73" t="n"/>
+      <c r="K8" s="73" t="n"/>
+      <c r="L8" s="73" t="n"/>
+      <c r="M8" s="73" t="n"/>
+      <c r="N8" s="73" t="n"/>
+      <c r="O8" s="73" t="n"/>
+      <c r="P8" s="73" t="n"/>
+      <c r="Q8" s="73" t="n"/>
+      <c r="R8" s="73" t="n"/>
+      <c r="S8" s="73" t="n"/>
+      <c r="T8" s="73" t="n"/>
+      <c r="U8" s="59">
         <f>IF($F8="SUM",IF(COUNT($I8:$T8)=0,"",SUM($I8:$T8)),IF($F8="AVG",IFERROR(AVERAGE($I8:$T8),""),IF($F8="LAST",IFERROR(LOOKUP(2,1/($I8:$T8&lt;&gt;""),$I8:$T8),""),"")))</f>
         <v/>
       </c>
@@ -22709,36 +22709,36 @@
       </c>
       <c r="X8" s="65" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="Y8" s="22" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
-        </is>
-      </c>
-      <c r="Z8" s="66" t="n"/>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z8" s="53" t="n"/>
       <c r="AA8" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB8" s="53" t="n">
-        <v>0.0417</v>
+        <v>0.1111</v>
       </c>
       <c r="AC8" s="23">
         <f>IF($V8="","",$AB8*MIN($V8,1))</f>
         <v/>
       </c>
-      <c r="AD8" s="61">
+      <c r="AD8" s="74">
         <f>IF($G8="","",IF($F8="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G8/12*'لوحة الإدارة التنفيذية'!$P$2),$G8))</f>
         <v/>
       </c>
-      <c r="AE8" s="67">
+      <c r="AE8" s="23">
         <f>IF($F8="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U8="","",$U8/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U8="","",$U8))</f>
         <v/>
       </c>
-      <c r="AF8" s="61">
+      <c r="AF8" s="74">
         <f>IF(OR($AE8="",$G8=""),"",$AE8-$G8)</f>
         <v/>
       </c>
@@ -22758,17 +22758,17 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>الكفاءة التشغيلية</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>ربط المحطات بوزارة الطاقة (ATJ)</t>
+          <t>متوسط جاهزية أنظمة المركز الرئيسي (Uptime)</t>
         </is>
       </c>
       <c r="D9" s="60" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E9" s="60" t="inlineStr">
@@ -22778,30 +22778,30 @@
       </c>
       <c r="F9" s="60" t="inlineStr">
         <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G9" s="61" t="n">
-        <v>164</v>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="G9" s="74" t="n">
+        <v>0.99</v>
       </c>
       <c r="H9" s="62" t="inlineStr">
         <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I9" s="63" t="n"/>
-      <c r="J9" s="63" t="n"/>
-      <c r="K9" s="63" t="n"/>
-      <c r="L9" s="63" t="n"/>
-      <c r="M9" s="63" t="n"/>
-      <c r="N9" s="63" t="n"/>
-      <c r="O9" s="63" t="n"/>
-      <c r="P9" s="63" t="n"/>
-      <c r="Q9" s="63" t="n"/>
-      <c r="R9" s="63" t="n"/>
-      <c r="S9" s="63" t="n"/>
-      <c r="T9" s="63" t="n"/>
-      <c r="U9" s="64">
+          <t>≥ 99%</t>
+        </is>
+      </c>
+      <c r="I9" s="73" t="n"/>
+      <c r="J9" s="73" t="n"/>
+      <c r="K9" s="73" t="n"/>
+      <c r="L9" s="73" t="n"/>
+      <c r="M9" s="73" t="n"/>
+      <c r="N9" s="73" t="n"/>
+      <c r="O9" s="73" t="n"/>
+      <c r="P9" s="73" t="n"/>
+      <c r="Q9" s="73" t="n"/>
+      <c r="R9" s="73" t="n"/>
+      <c r="S9" s="73" t="n"/>
+      <c r="T9" s="73" t="n"/>
+      <c r="U9" s="59">
         <f>IF($F9="SUM",IF(COUNT($I9:$T9)=0,"",SUM($I9:$T9)),IF($F9="AVG",IFERROR(AVERAGE($I9:$T9),""),IF($F9="LAST",IFERROR(LOOKUP(2,1/($I9:$T9&lt;&gt;""),$I9:$T9),""),"")))</f>
         <v/>
       </c>
@@ -22815,36 +22815,36 @@
       </c>
       <c r="X9" s="65" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="Y9" s="22" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
-        </is>
-      </c>
-      <c r="Z9" s="66" t="n"/>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z9" s="53" t="n"/>
       <c r="AA9" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB9" s="53" t="n">
-        <v>0.0417</v>
+        <v>0.1111</v>
       </c>
       <c r="AC9" s="23">
         <f>IF($V9="","",$AB9*MIN($V9,1))</f>
         <v/>
       </c>
-      <c r="AD9" s="61">
+      <c r="AD9" s="74">
         <f>IF($G9="","",IF($F9="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G9/12*'لوحة الإدارة التنفيذية'!$P$2),$G9))</f>
         <v/>
       </c>
-      <c r="AE9" s="67">
+      <c r="AE9" s="23">
         <f>IF($F9="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U9="","",$U9/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U9="","",$U9))</f>
         <v/>
       </c>
-      <c r="AF9" s="61">
+      <c r="AF9" s="74">
         <f>IF(OR($AE9="",$G9=""),"",$AE9-$G9)</f>
         <v/>
       </c>
@@ -22864,17 +22864,17 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>الكفاءة التشغيلية</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>ربط الكاميرات بالمركز الرئيسي</t>
+          <t>نسبة الامتثال للأمن السيبراني</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" s="60" t="inlineStr">
@@ -22887,27 +22887,27 @@
           <t>LAST</t>
         </is>
       </c>
-      <c r="G10" s="61" t="n">
-        <v>164</v>
+      <c r="G10" s="74" t="n">
+        <v>1</v>
       </c>
       <c r="H10" s="62" t="inlineStr">
         <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I10" s="63" t="n"/>
-      <c r="J10" s="63" t="n"/>
-      <c r="K10" s="63" t="n"/>
-      <c r="L10" s="63" t="n"/>
-      <c r="M10" s="63" t="n"/>
-      <c r="N10" s="63" t="n"/>
-      <c r="O10" s="63" t="n"/>
-      <c r="P10" s="63" t="n"/>
-      <c r="Q10" s="63" t="n"/>
-      <c r="R10" s="63" t="n"/>
-      <c r="S10" s="63" t="n"/>
-      <c r="T10" s="63" t="n"/>
-      <c r="U10" s="64">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="73" t="n"/>
+      <c r="J10" s="73" t="n"/>
+      <c r="K10" s="73" t="n"/>
+      <c r="L10" s="73" t="n"/>
+      <c r="M10" s="73" t="n"/>
+      <c r="N10" s="73" t="n"/>
+      <c r="O10" s="73" t="n"/>
+      <c r="P10" s="73" t="n"/>
+      <c r="Q10" s="73" t="n"/>
+      <c r="R10" s="73" t="n"/>
+      <c r="S10" s="73" t="n"/>
+      <c r="T10" s="73" t="n"/>
+      <c r="U10" s="59">
         <f>IF($F10="SUM",IF(COUNT($I10:$T10)=0,"",SUM($I10:$T10)),IF($F10="AVG",IFERROR(AVERAGE($I10:$T10),""),IF($F10="LAST",IFERROR(LOOKUP(2,1/($I10:$T10&lt;&gt;""),$I10:$T10),""),"")))</f>
         <v/>
       </c>
@@ -22921,36 +22921,36 @@
       </c>
       <c r="X10" s="65" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="Y10" s="22" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
-        </is>
-      </c>
-      <c r="Z10" s="66" t="n"/>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z10" s="53" t="n"/>
       <c r="AA10" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB10" s="53" t="n">
-        <v>0.0417</v>
+        <v>0.1111</v>
       </c>
       <c r="AC10" s="23">
         <f>IF($V10="","",$AB10*MIN($V10,1))</f>
         <v/>
       </c>
-      <c r="AD10" s="61">
+      <c r="AD10" s="74">
         <f>IF($G10="","",IF($F10="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G10/12*'لوحة الإدارة التنفيذية'!$P$2),$G10))</f>
         <v/>
       </c>
-      <c r="AE10" s="67">
+      <c r="AE10" s="23">
         <f>IF($F10="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U10="","",$U10/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U10="","",$U10))</f>
         <v/>
       </c>
-      <c r="AF10" s="61">
+      <c r="AF10" s="74">
         <f>IF(OR($AE10="",$G10=""),"",$AE10-$G10)</f>
         <v/>
       </c>
@@ -22970,50 +22970,50 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>الكفاءة التشغيلية</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>تطبيق الولاء (تانكي) في المحطات</t>
+          <t>متوسط زمن استجابة الدعم الفني</t>
         </is>
       </c>
       <c r="D11" s="60" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>ساعة</t>
         </is>
       </c>
       <c r="E11" s="60" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="F11" s="60" t="inlineStr">
         <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G11" s="61" t="n">
-        <v>164</v>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="G11" s="75" t="n">
+        <v>1</v>
       </c>
       <c r="H11" s="62" t="inlineStr">
         <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I11" s="63" t="n"/>
-      <c r="J11" s="63" t="n"/>
-      <c r="K11" s="63" t="n"/>
-      <c r="L11" s="63" t="n"/>
-      <c r="M11" s="63" t="n"/>
-      <c r="N11" s="63" t="n"/>
-      <c r="O11" s="63" t="n"/>
-      <c r="P11" s="63" t="n"/>
-      <c r="Q11" s="63" t="n"/>
-      <c r="R11" s="63" t="n"/>
-      <c r="S11" s="63" t="n"/>
-      <c r="T11" s="63" t="n"/>
-      <c r="U11" s="64">
+          <t>≤ ساعة</t>
+        </is>
+      </c>
+      <c r="I11" s="76" t="n"/>
+      <c r="J11" s="76" t="n"/>
+      <c r="K11" s="76" t="n"/>
+      <c r="L11" s="76" t="n"/>
+      <c r="M11" s="76" t="n"/>
+      <c r="N11" s="76" t="n"/>
+      <c r="O11" s="76" t="n"/>
+      <c r="P11" s="76" t="n"/>
+      <c r="Q11" s="76" t="n"/>
+      <c r="R11" s="76" t="n"/>
+      <c r="S11" s="76" t="n"/>
+      <c r="T11" s="76" t="n"/>
+      <c r="U11" s="77">
         <f>IF($F11="SUM",IF(COUNT($I11:$T11)=0,"",SUM($I11:$T11)),IF($F11="AVG",IFERROR(AVERAGE($I11:$T11),""),IF($F11="LAST",IFERROR(LOOKUP(2,1/($I11:$T11&lt;&gt;""),$I11:$T11),""),"")))</f>
         <v/>
       </c>
@@ -23027,36 +23027,36 @@
       </c>
       <c r="X11" s="65" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="Y11" s="22" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
-        </is>
-      </c>
-      <c r="Z11" s="66" t="n"/>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z11" s="78" t="n"/>
       <c r="AA11" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB11" s="53" t="n">
-        <v>0.0417</v>
+        <v>0.1111</v>
       </c>
       <c r="AC11" s="23">
         <f>IF($V11="","",$AB11*MIN($V11,1))</f>
         <v/>
       </c>
-      <c r="AD11" s="61">
+      <c r="AD11" s="75">
         <f>IF($G11="","",IF($F11="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G11/12*'لوحة الإدارة التنفيذية'!$P$2),$G11))</f>
         <v/>
       </c>
-      <c r="AE11" s="67">
+      <c r="AE11" s="79">
         <f>IF($F11="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U11="","",$U11/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U11="","",$U11))</f>
         <v/>
       </c>
-      <c r="AF11" s="61">
+      <c r="AF11" s="75">
         <f>IF(OR($AE11="",$G11=""),"",$AE11-$G11)</f>
         <v/>
       </c>
@@ -23076,17 +23076,17 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>مشاريع التحول</t>
+          <t>الكفاءة التشغيلية</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>منصة Tatin السحابية</t>
+          <t>نسبة التكامل الرقمي (ERP/واثق/الولاء)</t>
         </is>
       </c>
       <c r="D12" s="60" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E12" s="60" t="inlineStr">
@@ -23099,27 +23099,27 @@
           <t>LAST</t>
         </is>
       </c>
-      <c r="G12" s="61" t="n">
-        <v>164</v>
+      <c r="G12" s="74" t="n">
+        <v>1</v>
       </c>
       <c r="H12" s="62" t="inlineStr">
         <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I12" s="63" t="n"/>
-      <c r="J12" s="63" t="n"/>
-      <c r="K12" s="63" t="n"/>
-      <c r="L12" s="63" t="n"/>
-      <c r="M12" s="63" t="n"/>
-      <c r="N12" s="63" t="n"/>
-      <c r="O12" s="63" t="n"/>
-      <c r="P12" s="63" t="n"/>
-      <c r="Q12" s="63" t="n"/>
-      <c r="R12" s="63" t="n"/>
-      <c r="S12" s="63" t="n"/>
-      <c r="T12" s="63" t="n"/>
-      <c r="U12" s="64">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="73" t="n"/>
+      <c r="J12" s="73" t="n"/>
+      <c r="K12" s="73" t="n"/>
+      <c r="L12" s="73" t="n"/>
+      <c r="M12" s="73" t="n"/>
+      <c r="N12" s="73" t="n"/>
+      <c r="O12" s="73" t="n"/>
+      <c r="P12" s="73" t="n"/>
+      <c r="Q12" s="73" t="n"/>
+      <c r="R12" s="73" t="n"/>
+      <c r="S12" s="73" t="n"/>
+      <c r="T12" s="73" t="n"/>
+      <c r="U12" s="59">
         <f>IF($F12="SUM",IF(COUNT($I12:$T12)=0,"",SUM($I12:$T12)),IF($F12="AVG",IFERROR(AVERAGE($I12:$T12),""),IF($F12="LAST",IFERROR(LOOKUP(2,1/($I12:$T12&lt;&gt;""),$I12:$T12),""),"")))</f>
         <v/>
       </c>
@@ -23133,36 +23133,36 @@
       </c>
       <c r="X12" s="65" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="Y12" s="22" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
-        </is>
-      </c>
-      <c r="Z12" s="66" t="n"/>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="Z12" s="53" t="n"/>
       <c r="AA12" s="21" t="inlineStr">
         <is>
           <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="AB12" s="53" t="n">
-        <v>0.0417</v>
+        <v>0.1111</v>
       </c>
       <c r="AC12" s="23">
         <f>IF($V12="","",$AB12*MIN($V12,1))</f>
         <v/>
       </c>
-      <c r="AD12" s="61">
+      <c r="AD12" s="74">
         <f>IF($G12="","",IF($F12="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G12/12*'لوحة الإدارة التنفيذية'!$P$2),$G12))</f>
         <v/>
       </c>
-      <c r="AE12" s="67">
+      <c r="AE12" s="23">
         <f>IF($F12="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U12="","",$U12/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U12="","",$U12))</f>
         <v/>
       </c>
-      <c r="AF12" s="61">
+      <c r="AF12" s="74">
         <f>IF(OR($AE12="",$G12=""),"",$AE12-$G12)</f>
         <v/>
       </c>
@@ -23172,1625 +23172,35 @@
       </c>
       <c r="AH12" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>مشاريع التحول</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>إدارة العمليات بالذكاء الاصطناعي</t>
-        </is>
-      </c>
-      <c r="D13" s="60" t="inlineStr">
-        <is>
-          <t>محطة</t>
-        </is>
-      </c>
-      <c r="E13" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F13" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G13" s="61" t="n">
-        <v>164</v>
-      </c>
-      <c r="H13" s="62" t="inlineStr">
-        <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I13" s="63" t="n"/>
-      <c r="J13" s="63" t="n"/>
-      <c r="K13" s="63" t="n"/>
-      <c r="L13" s="63" t="n"/>
-      <c r="M13" s="63" t="n"/>
-      <c r="N13" s="63" t="n"/>
-      <c r="O13" s="63" t="n"/>
-      <c r="P13" s="63" t="n"/>
-      <c r="Q13" s="63" t="n"/>
-      <c r="R13" s="63" t="n"/>
-      <c r="S13" s="63" t="n"/>
-      <c r="T13" s="63" t="n"/>
-      <c r="U13" s="64">
-        <f>IF($F13="SUM",IF(COUNT($I13:$T13)=0,"",SUM($I13:$T13)),IF($F13="AVG",IFERROR(AVERAGE($I13:$T13),""),IF($F13="LAST",IFERROR(LOOKUP(2,1/($I13:$T13&lt;&gt;""),$I13:$T13),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V13" s="23">
-        <f>IF($G13="","",IF($U13="","",IF($G13=0,IF($U13&lt;=0,1,0),IF($E13="↓",IFERROR($G13/$U13,0),IFERROR($U13/$G13,0)))))</f>
-        <v/>
-      </c>
-      <c r="W13" s="17">
-        <f>IF($V13="","—",IF($V13&gt;=1,"✅ محقق",IF($V13&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X13" s="65" t="inlineStr">
-        <is>
-          <t>الابتكار</t>
-        </is>
-      </c>
-      <c r="Y13" s="22" t="inlineStr">
-        <is>
-          <t>التحول التقني</t>
-        </is>
-      </c>
-      <c r="Z13" s="66" t="n"/>
-      <c r="AA13" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB13" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC13" s="23">
-        <f>IF($V13="","",$AB13*MIN($V13,1))</f>
-        <v/>
-      </c>
-      <c r="AD13" s="61">
-        <f>IF($G13="","",IF($F13="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G13/12*'لوحة الإدارة التنفيذية'!$P$2),$G13))</f>
-        <v/>
-      </c>
-      <c r="AE13" s="67">
-        <f>IF($F13="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U13="","",$U13/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U13="","",$U13))</f>
-        <v/>
-      </c>
-      <c r="AF13" s="61">
-        <f>IF(OR($AE13="",$G13=""),"",$AE13-$G13)</f>
-        <v/>
-      </c>
-      <c r="AG13" s="17">
-        <f>IF(OR($AE13="",$G13=""),"—",IF($E13="↓",IF($AE13&lt;=$G13,"🟢 على المسار",IF($AE13&lt;=$G13*1.1,"🟡 متابعة","🔴 خطر")),IF($AE13&gt;=$G13,"🟢 على المسار",IF($AE13&gt;=$G13*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH13" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>الكفاءة التشغيلية</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>جاهزية أتمتة المحطات (Forecourt)</t>
-        </is>
-      </c>
-      <c r="D14" s="60" t="inlineStr">
-        <is>
-          <t>محطة</t>
-        </is>
-      </c>
-      <c r="E14" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F14" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G14" s="61" t="n">
-        <v>164</v>
-      </c>
-      <c r="H14" s="62" t="inlineStr">
-        <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I14" s="63" t="n"/>
-      <c r="J14" s="63" t="n"/>
-      <c r="K14" s="63" t="n"/>
-      <c r="L14" s="63" t="n"/>
-      <c r="M14" s="63" t="n"/>
-      <c r="N14" s="63" t="n"/>
-      <c r="O14" s="63" t="n"/>
-      <c r="P14" s="63" t="n"/>
-      <c r="Q14" s="63" t="n"/>
-      <c r="R14" s="63" t="n"/>
-      <c r="S14" s="63" t="n"/>
-      <c r="T14" s="63" t="n"/>
-      <c r="U14" s="64">
-        <f>IF($F14="SUM",IF(COUNT($I14:$T14)=0,"",SUM($I14:$T14)),IF($F14="AVG",IFERROR(AVERAGE($I14:$T14),""),IF($F14="LAST",IFERROR(LOOKUP(2,1/($I14:$T14&lt;&gt;""),$I14:$T14),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V14" s="23">
-        <f>IF($G14="","",IF($U14="","",IF($G14=0,IF($U14&lt;=0,1,0),IF($E14="↓",IFERROR($G14/$U14,0),IFERROR($U14/$G14,0)))))</f>
-        <v/>
-      </c>
-      <c r="W14" s="17">
-        <f>IF($V14="","—",IF($V14&gt;=1,"✅ محقق",IF($V14&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X14" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y14" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z14" s="66" t="n"/>
-      <c r="AA14" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB14" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC14" s="23">
-        <f>IF($V14="","",$AB14*MIN($V14,1))</f>
-        <v/>
-      </c>
-      <c r="AD14" s="61">
-        <f>IF($G14="","",IF($F14="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G14/12*'لوحة الإدارة التنفيذية'!$P$2),$G14))</f>
-        <v/>
-      </c>
-      <c r="AE14" s="67">
-        <f>IF($F14="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U14="","",$U14/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U14="","",$U14))</f>
-        <v/>
-      </c>
-      <c r="AF14" s="61">
-        <f>IF(OR($AE14="",$G14=""),"",$AE14-$G14)</f>
-        <v/>
-      </c>
-      <c r="AG14" s="17">
-        <f>IF(OR($AE14="",$G14=""),"—",IF($E14="↓",IF($AE14&lt;=$G14,"🟢 على المسار",IF($AE14&lt;=$G14*1.1,"🟡 متابعة","🔴 خطر")),IF($AE14&gt;=$G14,"🟢 على المسار",IF($AE14&gt;=$G14*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH14" s="68" t="inlineStr">
-        <is>
           <t>التعلّم والنمو</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>الكفاءة التشغيلية</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>جاهزية اتصال الشبكة بالمحطات</t>
-        </is>
-      </c>
-      <c r="D15" s="60" t="inlineStr">
-        <is>
-          <t>محطة</t>
-        </is>
-      </c>
-      <c r="E15" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F15" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G15" s="61" t="n">
-        <v>164</v>
-      </c>
-      <c r="H15" s="62" t="inlineStr">
-        <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I15" s="63" t="n"/>
-      <c r="J15" s="63" t="n"/>
-      <c r="K15" s="63" t="n"/>
-      <c r="L15" s="63" t="n"/>
-      <c r="M15" s="63" t="n"/>
-      <c r="N15" s="63" t="n"/>
-      <c r="O15" s="63" t="n"/>
-      <c r="P15" s="63" t="n"/>
-      <c r="Q15" s="63" t="n"/>
-      <c r="R15" s="63" t="n"/>
-      <c r="S15" s="63" t="n"/>
-      <c r="T15" s="63" t="n"/>
-      <c r="U15" s="64">
-        <f>IF($F15="SUM",IF(COUNT($I15:$T15)=0,"",SUM($I15:$T15)),IF($F15="AVG",IFERROR(AVERAGE($I15:$T15),""),IF($F15="LAST",IFERROR(LOOKUP(2,1/($I15:$T15&lt;&gt;""),$I15:$T15),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V15" s="23">
-        <f>IF($G15="","",IF($U15="","",IF($G15=0,IF($U15&lt;=0,1,0),IF($E15="↓",IFERROR($G15/$U15,0),IFERROR($U15/$G15,0)))))</f>
-        <v/>
-      </c>
-      <c r="W15" s="17">
-        <f>IF($V15="","—",IF($V15&gt;=1,"✅ محقق",IF($V15&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X15" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y15" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z15" s="66" t="n"/>
-      <c r="AA15" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB15" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC15" s="23">
-        <f>IF($V15="","",$AB15*MIN($V15,1))</f>
-        <v/>
-      </c>
-      <c r="AD15" s="61">
-        <f>IF($G15="","",IF($F15="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G15/12*'لوحة الإدارة التنفيذية'!$P$2),$G15))</f>
-        <v/>
-      </c>
-      <c r="AE15" s="67">
-        <f>IF($F15="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U15="","",$U15/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U15="","",$U15))</f>
-        <v/>
-      </c>
-      <c r="AF15" s="61">
-        <f>IF(OR($AE15="",$G15=""),"",$AE15-$G15)</f>
-        <v/>
-      </c>
-      <c r="AG15" s="17">
-        <f>IF(OR($AE15="",$G15=""),"—",IF($E15="↓",IF($AE15&lt;=$G15,"🟢 على المسار",IF($AE15&lt;=$G15*1.1,"🟡 متابعة","🔴 خطر")),IF($AE15&gt;=$G15,"🟢 على المسار",IF($AE15&gt;=$G15*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH15" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>الكفاءة التشغيلية</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>جاهزية نقاط البيع والمدفوعات (POS)</t>
-        </is>
-      </c>
-      <c r="D16" s="60" t="inlineStr">
-        <is>
-          <t>محطة</t>
-        </is>
-      </c>
-      <c r="E16" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F16" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G16" s="61" t="n">
-        <v>164</v>
-      </c>
-      <c r="H16" s="62" t="inlineStr">
-        <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I16" s="63" t="n"/>
-      <c r="J16" s="63" t="n"/>
-      <c r="K16" s="63" t="n"/>
-      <c r="L16" s="63" t="n"/>
-      <c r="M16" s="63" t="n"/>
-      <c r="N16" s="63" t="n"/>
-      <c r="O16" s="63" t="n"/>
-      <c r="P16" s="63" t="n"/>
-      <c r="Q16" s="63" t="n"/>
-      <c r="R16" s="63" t="n"/>
-      <c r="S16" s="63" t="n"/>
-      <c r="T16" s="63" t="n"/>
-      <c r="U16" s="64">
-        <f>IF($F16="SUM",IF(COUNT($I16:$T16)=0,"",SUM($I16:$T16)),IF($F16="AVG",IFERROR(AVERAGE($I16:$T16),""),IF($F16="LAST",IFERROR(LOOKUP(2,1/($I16:$T16&lt;&gt;""),$I16:$T16),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V16" s="23">
-        <f>IF($G16="","",IF($U16="","",IF($G16=0,IF($U16&lt;=0,1,0),IF($E16="↓",IFERROR($G16/$U16,0),IFERROR($U16/$G16,0)))))</f>
-        <v/>
-      </c>
-      <c r="W16" s="17">
-        <f>IF($V16="","—",IF($V16&gt;=1,"✅ محقق",IF($V16&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X16" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y16" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z16" s="66" t="n"/>
-      <c r="AA16" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB16" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC16" s="23">
-        <f>IF($V16="","",$AB16*MIN($V16,1))</f>
-        <v/>
-      </c>
-      <c r="AD16" s="61">
-        <f>IF($G16="","",IF($F16="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G16/12*'لوحة الإدارة التنفيذية'!$P$2),$G16))</f>
-        <v/>
-      </c>
-      <c r="AE16" s="67">
-        <f>IF($F16="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U16="","",$U16/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U16="","",$U16))</f>
-        <v/>
-      </c>
-      <c r="AF16" s="61">
-        <f>IF(OR($AE16="",$G16=""),"",$AE16-$G16)</f>
-        <v/>
-      </c>
-      <c r="AG16" s="17">
-        <f>IF(OR($AE16="",$G16=""),"—",IF($E16="↓",IF($AE16&lt;=$G16,"🟢 على المسار",IF($AE16&lt;=$G16*1.1,"🟡 متابعة","🔴 خطر")),IF($AE16&gt;=$G16,"🟢 على المسار",IF($AE16&gt;=$G16*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH16" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>الكفاءة التشغيلية</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>جاهزية نظام الكاميرات (CCTV)</t>
-        </is>
-      </c>
-      <c r="D17" s="60" t="inlineStr">
-        <is>
-          <t>محطة</t>
-        </is>
-      </c>
-      <c r="E17" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F17" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G17" s="61" t="n">
-        <v>164</v>
-      </c>
-      <c r="H17" s="62" t="inlineStr">
-        <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I17" s="63" t="n"/>
-      <c r="J17" s="63" t="n"/>
-      <c r="K17" s="63" t="n"/>
-      <c r="L17" s="63" t="n"/>
-      <c r="M17" s="63" t="n"/>
-      <c r="N17" s="63" t="n"/>
-      <c r="O17" s="63" t="n"/>
-      <c r="P17" s="63" t="n"/>
-      <c r="Q17" s="63" t="n"/>
-      <c r="R17" s="63" t="n"/>
-      <c r="S17" s="63" t="n"/>
-      <c r="T17" s="63" t="n"/>
-      <c r="U17" s="64">
-        <f>IF($F17="SUM",IF(COUNT($I17:$T17)=0,"",SUM($I17:$T17)),IF($F17="AVG",IFERROR(AVERAGE($I17:$T17),""),IF($F17="LAST",IFERROR(LOOKUP(2,1/($I17:$T17&lt;&gt;""),$I17:$T17),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V17" s="23">
-        <f>IF($G17="","",IF($U17="","",IF($G17=0,IF($U17&lt;=0,1,0),IF($E17="↓",IFERROR($G17/$U17,0),IFERROR($U17/$G17,0)))))</f>
-        <v/>
-      </c>
-      <c r="W17" s="17">
-        <f>IF($V17="","—",IF($V17&gt;=1,"✅ محقق",IF($V17&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X17" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y17" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z17" s="66" t="n"/>
-      <c r="AA17" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB17" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC17" s="23">
-        <f>IF($V17="","",$AB17*MIN($V17,1))</f>
-        <v/>
-      </c>
-      <c r="AD17" s="61">
-        <f>IF($G17="","",IF($F17="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G17/12*'لوحة الإدارة التنفيذية'!$P$2),$G17))</f>
-        <v/>
-      </c>
-      <c r="AE17" s="67">
-        <f>IF($F17="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U17="","",$U17/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U17="","",$U17))</f>
-        <v/>
-      </c>
-      <c r="AF17" s="61">
-        <f>IF(OR($AE17="",$G17=""),"",$AE17-$G17)</f>
-        <v/>
-      </c>
-      <c r="AG17" s="17">
-        <f>IF(OR($AE17="",$G17=""),"—",IF($E17="↓",IF($AE17&lt;=$G17,"🟢 على المسار",IF($AE17&lt;=$G17*1.1,"🟡 متابعة","🔴 خطر")),IF($AE17&gt;=$G17,"🟢 على المسار",IF($AE17&gt;=$G17*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH17" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>الكفاءة التشغيلية</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>جاهزية الشبكة</t>
-        </is>
-      </c>
-      <c r="D18" s="60" t="inlineStr">
-        <is>
-          <t>محطة</t>
-        </is>
-      </c>
-      <c r="E18" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F18" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G18" s="61" t="n">
-        <v>164</v>
-      </c>
-      <c r="H18" s="62" t="inlineStr">
-        <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I18" s="63" t="n"/>
-      <c r="J18" s="63" t="n"/>
-      <c r="K18" s="63" t="n"/>
-      <c r="L18" s="63" t="n"/>
-      <c r="M18" s="63" t="n"/>
-      <c r="N18" s="63" t="n"/>
-      <c r="O18" s="63" t="n"/>
-      <c r="P18" s="63" t="n"/>
-      <c r="Q18" s="63" t="n"/>
-      <c r="R18" s="63" t="n"/>
-      <c r="S18" s="63" t="n"/>
-      <c r="T18" s="63" t="n"/>
-      <c r="U18" s="64">
-        <f>IF($F18="SUM",IF(COUNT($I18:$T18)=0,"",SUM($I18:$T18)),IF($F18="AVG",IFERROR(AVERAGE($I18:$T18),""),IF($F18="LAST",IFERROR(LOOKUP(2,1/($I18:$T18&lt;&gt;""),$I18:$T18),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V18" s="23">
-        <f>IF($G18="","",IF($U18="","",IF($G18=0,IF($U18&lt;=0,1,0),IF($E18="↓",IFERROR($G18/$U18,0),IFERROR($U18/$G18,0)))))</f>
-        <v/>
-      </c>
-      <c r="W18" s="17">
-        <f>IF($V18="","—",IF($V18&gt;=1,"✅ محقق",IF($V18&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X18" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y18" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z18" s="66" t="n"/>
-      <c r="AA18" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB18" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC18" s="23">
-        <f>IF($V18="","",$AB18*MIN($V18,1))</f>
-        <v/>
-      </c>
-      <c r="AD18" s="61">
-        <f>IF($G18="","",IF($F18="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G18/12*'لوحة الإدارة التنفيذية'!$P$2),$G18))</f>
-        <v/>
-      </c>
-      <c r="AE18" s="67">
-        <f>IF($F18="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U18="","",$U18/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U18="","",$U18))</f>
-        <v/>
-      </c>
-      <c r="AF18" s="61">
-        <f>IF(OR($AE18="",$G18=""),"",$AE18-$G18)</f>
-        <v/>
-      </c>
-      <c r="AG18" s="17">
-        <f>IF(OR($AE18="",$G18=""),"—",IF($E18="↓",IF($AE18&lt;=$G18,"🟢 على المسار",IF($AE18&lt;=$G18*1.1,"🟡 متابعة","🔴 خطر")),IF($AE18&gt;=$G18,"🟢 على المسار",IF($AE18&gt;=$G18*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH18" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>الكفاءة التشغيلية</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>الامتثال للأمن السيبراني (المحطات)</t>
-        </is>
-      </c>
-      <c r="D19" s="60" t="inlineStr">
-        <is>
-          <t>محطة</t>
-        </is>
-      </c>
-      <c r="E19" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F19" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G19" s="61" t="n">
-        <v>164</v>
-      </c>
-      <c r="H19" s="62" t="inlineStr">
-        <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I19" s="63" t="n"/>
-      <c r="J19" s="63" t="n"/>
-      <c r="K19" s="63" t="n"/>
-      <c r="L19" s="63" t="n"/>
-      <c r="M19" s="63" t="n"/>
-      <c r="N19" s="63" t="n"/>
-      <c r="O19" s="63" t="n"/>
-      <c r="P19" s="63" t="n"/>
-      <c r="Q19" s="63" t="n"/>
-      <c r="R19" s="63" t="n"/>
-      <c r="S19" s="63" t="n"/>
-      <c r="T19" s="63" t="n"/>
-      <c r="U19" s="64">
-        <f>IF($F19="SUM",IF(COUNT($I19:$T19)=0,"",SUM($I19:$T19)),IF($F19="AVG",IFERROR(AVERAGE($I19:$T19),""),IF($F19="LAST",IFERROR(LOOKUP(2,1/($I19:$T19&lt;&gt;""),$I19:$T19),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V19" s="23">
-        <f>IF($G19="","",IF($U19="","",IF($G19=0,IF($U19&lt;=0,1,0),IF($E19="↓",IFERROR($G19/$U19,0),IFERROR($U19/$G19,0)))))</f>
-        <v/>
-      </c>
-      <c r="W19" s="17">
-        <f>IF($V19="","—",IF($V19&gt;=1,"✅ محقق",IF($V19&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X19" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y19" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z19" s="66" t="n"/>
-      <c r="AA19" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB19" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC19" s="23">
-        <f>IF($V19="","",$AB19*MIN($V19,1))</f>
-        <v/>
-      </c>
-      <c r="AD19" s="61">
-        <f>IF($G19="","",IF($F19="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G19/12*'لوحة الإدارة التنفيذية'!$P$2),$G19))</f>
-        <v/>
-      </c>
-      <c r="AE19" s="67">
-        <f>IF($F19="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U19="","",$U19/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U19="","",$U19))</f>
-        <v/>
-      </c>
-      <c r="AF19" s="61">
-        <f>IF(OR($AE19="",$G19=""),"",$AE19-$G19)</f>
-        <v/>
-      </c>
-      <c r="AG19" s="17">
-        <f>IF(OR($AE19="",$G19=""),"—",IF($E19="↓",IF($AE19&lt;=$G19,"🟢 على المسار",IF($AE19&lt;=$G19*1.1,"🟡 متابعة","🔴 خطر")),IF($AE19&gt;=$G19,"🟢 على المسار",IF($AE19&gt;=$G19*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH19" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>الكفاءة التشغيلية</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>زمن استجابة الدعم الفني (المحطات)</t>
-        </is>
-      </c>
-      <c r="D20" s="60" t="inlineStr">
-        <is>
-          <t>يوم</t>
-        </is>
-      </c>
-      <c r="E20" s="60" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="F20" s="60" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="G20" s="75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="62" t="inlineStr">
-        <is>
-          <t>≤ يوم</t>
-        </is>
-      </c>
-      <c r="I20" s="76" t="n"/>
-      <c r="J20" s="76" t="n"/>
-      <c r="K20" s="76" t="n"/>
-      <c r="L20" s="76" t="n"/>
-      <c r="M20" s="76" t="n"/>
-      <c r="N20" s="76" t="n"/>
-      <c r="O20" s="76" t="n"/>
-      <c r="P20" s="76" t="n"/>
-      <c r="Q20" s="76" t="n"/>
-      <c r="R20" s="76" t="n"/>
-      <c r="S20" s="76" t="n"/>
-      <c r="T20" s="76" t="n"/>
-      <c r="U20" s="77">
-        <f>IF($F20="SUM",IF(COUNT($I20:$T20)=0,"",SUM($I20:$T20)),IF($F20="AVG",IFERROR(AVERAGE($I20:$T20),""),IF($F20="LAST",IFERROR(LOOKUP(2,1/($I20:$T20&lt;&gt;""),$I20:$T20),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V20" s="23">
-        <f>IF($G20="","",IF($U20="","",IF($G20=0,IF($U20&lt;=0,1,0),IF($E20="↓",IFERROR($G20/$U20,0),IFERROR($U20/$G20,0)))))</f>
-        <v/>
-      </c>
-      <c r="W20" s="17">
-        <f>IF($V20="","—",IF($V20&gt;=1,"✅ محقق",IF($V20&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X20" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y20" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z20" s="78" t="n"/>
-      <c r="AA20" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB20" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC20" s="23">
-        <f>IF($V20="","",$AB20*MIN($V20,1))</f>
-        <v/>
-      </c>
-      <c r="AD20" s="75">
-        <f>IF($G20="","",IF($F20="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G20/12*'لوحة الإدارة التنفيذية'!$P$2),$G20))</f>
-        <v/>
-      </c>
-      <c r="AE20" s="79">
-        <f>IF($F20="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U20="","",$U20/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U20="","",$U20))</f>
-        <v/>
-      </c>
-      <c r="AF20" s="75">
-        <f>IF(OR($AE20="",$G20=""),"",$AE20-$G20)</f>
-        <v/>
-      </c>
-      <c r="AG20" s="17">
-        <f>IF(OR($AE20="",$G20=""),"—",IF($E20="↓",IF($AE20&lt;=$G20,"🟢 على المسار",IF($AE20&lt;=$G20*1.1,"🟡 متابعة","🔴 خطر")),IF($AE20&gt;=$G20,"🟢 على المسار",IF($AE20&gt;=$G20*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH20" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>الكفاءة التشغيلية</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>ERP والتكامل (المحطات)</t>
-        </is>
-      </c>
-      <c r="D21" s="60" t="inlineStr">
-        <is>
-          <t>محطة</t>
-        </is>
-      </c>
-      <c r="E21" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F21" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G21" s="61" t="n">
-        <v>164</v>
-      </c>
-      <c r="H21" s="62" t="inlineStr">
-        <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I21" s="63" t="n"/>
-      <c r="J21" s="63" t="n"/>
-      <c r="K21" s="63" t="n"/>
-      <c r="L21" s="63" t="n"/>
-      <c r="M21" s="63" t="n"/>
-      <c r="N21" s="63" t="n"/>
-      <c r="O21" s="63" t="n"/>
-      <c r="P21" s="63" t="n"/>
-      <c r="Q21" s="63" t="n"/>
-      <c r="R21" s="63" t="n"/>
-      <c r="S21" s="63" t="n"/>
-      <c r="T21" s="63" t="n"/>
-      <c r="U21" s="64">
-        <f>IF($F21="SUM",IF(COUNT($I21:$T21)=0,"",SUM($I21:$T21)),IF($F21="AVG",IFERROR(AVERAGE($I21:$T21),""),IF($F21="LAST",IFERROR(LOOKUP(2,1/($I21:$T21&lt;&gt;""),$I21:$T21),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V21" s="23">
-        <f>IF($G21="","",IF($U21="","",IF($G21=0,IF($U21&lt;=0,1,0),IF($E21="↓",IFERROR($G21/$U21,0),IFERROR($U21/$G21,0)))))</f>
-        <v/>
-      </c>
-      <c r="W21" s="17">
-        <f>IF($V21="","—",IF($V21&gt;=1,"✅ محقق",IF($V21&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X21" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y21" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z21" s="66" t="n"/>
-      <c r="AA21" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB21" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC21" s="23">
-        <f>IF($V21="","",$AB21*MIN($V21,1))</f>
-        <v/>
-      </c>
-      <c r="AD21" s="61">
-        <f>IF($G21="","",IF($F21="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G21/12*'لوحة الإدارة التنفيذية'!$P$2),$G21))</f>
-        <v/>
-      </c>
-      <c r="AE21" s="67">
-        <f>IF($F21="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U21="","",$U21/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U21="","",$U21))</f>
-        <v/>
-      </c>
-      <c r="AF21" s="61">
-        <f>IF(OR($AE21="",$G21=""),"",$AE21-$G21)</f>
-        <v/>
-      </c>
-      <c r="AG21" s="17">
-        <f>IF(OR($AE21="",$G21=""),"—",IF($E21="↓",IF($AE21&lt;=$G21,"🟢 على المسار",IF($AE21&lt;=$G21*1.1,"🟡 متابعة","🔴 خطر")),IF($AE21&gt;=$G21,"🟢 على المسار",IF($AE21&gt;=$G21*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH21" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>الكفاءة التشغيلية</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>تكامل واثق (المحطات)</t>
-        </is>
-      </c>
-      <c r="D22" s="60" t="inlineStr">
-        <is>
-          <t>محطة</t>
-        </is>
-      </c>
-      <c r="E22" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F22" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G22" s="61" t="n">
-        <v>164</v>
-      </c>
-      <c r="H22" s="62" t="inlineStr">
-        <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I22" s="63" t="n"/>
-      <c r="J22" s="63" t="n"/>
-      <c r="K22" s="63" t="n"/>
-      <c r="L22" s="63" t="n"/>
-      <c r="M22" s="63" t="n"/>
-      <c r="N22" s="63" t="n"/>
-      <c r="O22" s="63" t="n"/>
-      <c r="P22" s="63" t="n"/>
-      <c r="Q22" s="63" t="n"/>
-      <c r="R22" s="63" t="n"/>
-      <c r="S22" s="63" t="n"/>
-      <c r="T22" s="63" t="n"/>
-      <c r="U22" s="64">
-        <f>IF($F22="SUM",IF(COUNT($I22:$T22)=0,"",SUM($I22:$T22)),IF($F22="AVG",IFERROR(AVERAGE($I22:$T22),""),IF($F22="LAST",IFERROR(LOOKUP(2,1/($I22:$T22&lt;&gt;""),$I22:$T22),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V22" s="23">
-        <f>IF($G22="","",IF($U22="","",IF($G22=0,IF($U22&lt;=0,1,0),IF($E22="↓",IFERROR($G22/$U22,0),IFERROR($U22/$G22,0)))))</f>
-        <v/>
-      </c>
-      <c r="W22" s="17">
-        <f>IF($V22="","—",IF($V22&gt;=1,"✅ محقق",IF($V22&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X22" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y22" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z22" s="66" t="n"/>
-      <c r="AA22" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB22" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC22" s="23">
-        <f>IF($V22="","",$AB22*MIN($V22,1))</f>
-        <v/>
-      </c>
-      <c r="AD22" s="61">
-        <f>IF($G22="","",IF($F22="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G22/12*'لوحة الإدارة التنفيذية'!$P$2),$G22))</f>
-        <v/>
-      </c>
-      <c r="AE22" s="67">
-        <f>IF($F22="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U22="","",$U22/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U22="","",$U22))</f>
-        <v/>
-      </c>
-      <c r="AF22" s="61">
-        <f>IF(OR($AE22="",$G22=""),"",$AE22-$G22)</f>
-        <v/>
-      </c>
-      <c r="AG22" s="17">
-        <f>IF(OR($AE22="",$G22=""),"—",IF($E22="↓",IF($AE22&lt;=$G22,"🟢 على المسار",IF($AE22&lt;=$G22*1.1,"🟡 متابعة","🔴 خطر")),IF($AE22&gt;=$G22,"🟢 على المسار",IF($AE22&gt;=$G22*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH22" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>الكفاءة التشغيلية</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>تكامل تطبيق الولاء (المحطات)</t>
-        </is>
-      </c>
-      <c r="D23" s="60" t="inlineStr">
-        <is>
-          <t>محطة</t>
-        </is>
-      </c>
-      <c r="E23" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F23" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G23" s="61" t="n">
-        <v>164</v>
-      </c>
-      <c r="H23" s="62" t="inlineStr">
-        <is>
-          <t>164 محطة</t>
-        </is>
-      </c>
-      <c r="I23" s="63" t="n"/>
-      <c r="J23" s="63" t="n"/>
-      <c r="K23" s="63" t="n"/>
-      <c r="L23" s="63" t="n"/>
-      <c r="M23" s="63" t="n"/>
-      <c r="N23" s="63" t="n"/>
-      <c r="O23" s="63" t="n"/>
-      <c r="P23" s="63" t="n"/>
-      <c r="Q23" s="63" t="n"/>
-      <c r="R23" s="63" t="n"/>
-      <c r="S23" s="63" t="n"/>
-      <c r="T23" s="63" t="n"/>
-      <c r="U23" s="64">
-        <f>IF($F23="SUM",IF(COUNT($I23:$T23)=0,"",SUM($I23:$T23)),IF($F23="AVG",IFERROR(AVERAGE($I23:$T23),""),IF($F23="LAST",IFERROR(LOOKUP(2,1/($I23:$T23&lt;&gt;""),$I23:$T23),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V23" s="23">
-        <f>IF($G23="","",IF($U23="","",IF($G23=0,IF($U23&lt;=0,1,0),IF($E23="↓",IFERROR($G23/$U23,0),IFERROR($U23/$G23,0)))))</f>
-        <v/>
-      </c>
-      <c r="W23" s="17">
-        <f>IF($V23="","—",IF($V23&gt;=1,"✅ محقق",IF($V23&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X23" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y23" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z23" s="66" t="n"/>
-      <c r="AA23" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB23" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC23" s="23">
-        <f>IF($V23="","",$AB23*MIN($V23,1))</f>
-        <v/>
-      </c>
-      <c r="AD23" s="61">
-        <f>IF($G23="","",IF($F23="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G23/12*'لوحة الإدارة التنفيذية'!$P$2),$G23))</f>
-        <v/>
-      </c>
-      <c r="AE23" s="67">
-        <f>IF($F23="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U23="","",$U23/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U23="","",$U23))</f>
-        <v/>
-      </c>
-      <c r="AF23" s="61">
-        <f>IF(OR($AE23="",$G23=""),"",$AE23-$G23)</f>
-        <v/>
-      </c>
-      <c r="AG23" s="17">
-        <f>IF(OR($AE23="",$G23=""),"—",IF($E23="↓",IF($AE23&lt;=$G23,"🟢 على المسار",IF($AE23&lt;=$G23*1.1,"🟡 متابعة","🔴 خطر")),IF($AE23&gt;=$G23,"🟢 على المسار",IF($AE23&gt;=$G23*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH23" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>المركز الرئيسي</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>جاهزية شبكة المركز الرئيسي</t>
-        </is>
-      </c>
-      <c r="D24" s="60" t="inlineStr">
-        <is>
-          <t>ساعة</t>
-        </is>
-      </c>
-      <c r="E24" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F24" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G24" s="61" t="n">
-        <v>24</v>
-      </c>
-      <c r="H24" s="62" t="inlineStr">
-        <is>
-          <t>24 ساعة</t>
-        </is>
-      </c>
-      <c r="I24" s="63" t="n"/>
-      <c r="J24" s="63" t="n"/>
-      <c r="K24" s="63" t="n"/>
-      <c r="L24" s="63" t="n"/>
-      <c r="M24" s="63" t="n"/>
-      <c r="N24" s="63" t="n"/>
-      <c r="O24" s="63" t="n"/>
-      <c r="P24" s="63" t="n"/>
-      <c r="Q24" s="63" t="n"/>
-      <c r="R24" s="63" t="n"/>
-      <c r="S24" s="63" t="n"/>
-      <c r="T24" s="63" t="n"/>
-      <c r="U24" s="64">
-        <f>IF($F24="SUM",IF(COUNT($I24:$T24)=0,"",SUM($I24:$T24)),IF($F24="AVG",IFERROR(AVERAGE($I24:$T24),""),IF($F24="LAST",IFERROR(LOOKUP(2,1/($I24:$T24&lt;&gt;""),$I24:$T24),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V24" s="23">
-        <f>IF($G24="","",IF($U24="","",IF($G24=0,IF($U24&lt;=0,1,0),IF($E24="↓",IFERROR($G24/$U24,0),IFERROR($U24/$G24,0)))))</f>
-        <v/>
-      </c>
-      <c r="W24" s="17">
-        <f>IF($V24="","—",IF($V24&gt;=1,"✅ محقق",IF($V24&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X24" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y24" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z24" s="66" t="n"/>
-      <c r="AA24" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB24" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC24" s="23">
-        <f>IF($V24="","",$AB24*MIN($V24,1))</f>
-        <v/>
-      </c>
-      <c r="AD24" s="61">
-        <f>IF($G24="","",IF($F24="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G24/12*'لوحة الإدارة التنفيذية'!$P$2),$G24))</f>
-        <v/>
-      </c>
-      <c r="AE24" s="67">
-        <f>IF($F24="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U24="","",$U24/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U24="","",$U24))</f>
-        <v/>
-      </c>
-      <c r="AF24" s="61">
-        <f>IF(OR($AE24="",$G24=""),"",$AE24-$G24)</f>
-        <v/>
-      </c>
-      <c r="AG24" s="17">
-        <f>IF(OR($AE24="",$G24=""),"—",IF($E24="↓",IF($AE24&lt;=$G24,"🟢 على المسار",IF($AE24&lt;=$G24*1.1,"🟡 متابعة","🔴 خطر")),IF($AE24&gt;=$G24,"🟢 على المسار",IF($AE24&gt;=$G24*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH24" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="17" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
-        <is>
-          <t>المركز الرئيسي</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>جاهزية تطبيقات المركز الرئيسي</t>
-        </is>
-      </c>
-      <c r="D25" s="60" t="inlineStr">
-        <is>
-          <t>ساعة</t>
-        </is>
-      </c>
-      <c r="E25" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F25" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G25" s="61" t="n">
-        <v>24</v>
-      </c>
-      <c r="H25" s="62" t="inlineStr">
-        <is>
-          <t>24 ساعة</t>
-        </is>
-      </c>
-      <c r="I25" s="63" t="n"/>
-      <c r="J25" s="63" t="n"/>
-      <c r="K25" s="63" t="n"/>
-      <c r="L25" s="63" t="n"/>
-      <c r="M25" s="63" t="n"/>
-      <c r="N25" s="63" t="n"/>
-      <c r="O25" s="63" t="n"/>
-      <c r="P25" s="63" t="n"/>
-      <c r="Q25" s="63" t="n"/>
-      <c r="R25" s="63" t="n"/>
-      <c r="S25" s="63" t="n"/>
-      <c r="T25" s="63" t="n"/>
-      <c r="U25" s="64">
-        <f>IF($F25="SUM",IF(COUNT($I25:$T25)=0,"",SUM($I25:$T25)),IF($F25="AVG",IFERROR(AVERAGE($I25:$T25),""),IF($F25="LAST",IFERROR(LOOKUP(2,1/($I25:$T25&lt;&gt;""),$I25:$T25),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V25" s="23">
-        <f>IF($G25="","",IF($U25="","",IF($G25=0,IF($U25&lt;=0,1,0),IF($E25="↓",IFERROR($G25/$U25,0),IFERROR($U25/$G25,0)))))</f>
-        <v/>
-      </c>
-      <c r="W25" s="17">
-        <f>IF($V25="","—",IF($V25&gt;=1,"✅ محقق",IF($V25&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X25" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y25" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z25" s="66" t="n"/>
-      <c r="AA25" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB25" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC25" s="23">
-        <f>IF($V25="","",$AB25*MIN($V25,1))</f>
-        <v/>
-      </c>
-      <c r="AD25" s="61">
-        <f>IF($G25="","",IF($F25="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G25/12*'لوحة الإدارة التنفيذية'!$P$2),$G25))</f>
-        <v/>
-      </c>
-      <c r="AE25" s="67">
-        <f>IF($F25="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U25="","",$U25/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U25="","",$U25))</f>
-        <v/>
-      </c>
-      <c r="AF25" s="61">
-        <f>IF(OR($AE25="",$G25=""),"",$AE25-$G25)</f>
-        <v/>
-      </c>
-      <c r="AG25" s="17">
-        <f>IF(OR($AE25="",$G25=""),"—",IF($E25="↓",IF($AE25&lt;=$G25,"🟢 على المسار",IF($AE25&lt;=$G25*1.1,"🟡 متابعة","🔴 خطر")),IF($AE25&gt;=$G25,"🟢 على المسار",IF($AE25&gt;=$G25*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH25" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="22" t="inlineStr">
-        <is>
-          <t>المركز الرئيسي</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>زمن استجابة الدعم (المركز)</t>
-        </is>
-      </c>
-      <c r="D26" s="60" t="inlineStr">
-        <is>
-          <t>ساعة</t>
-        </is>
-      </c>
-      <c r="E26" s="60" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="F26" s="60" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="G26" s="75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="62" t="inlineStr">
-        <is>
-          <t>≤ ساعة</t>
-        </is>
-      </c>
-      <c r="I26" s="76" t="n"/>
-      <c r="J26" s="76" t="n"/>
-      <c r="K26" s="76" t="n"/>
-      <c r="L26" s="76" t="n"/>
-      <c r="M26" s="76" t="n"/>
-      <c r="N26" s="76" t="n"/>
-      <c r="O26" s="76" t="n"/>
-      <c r="P26" s="76" t="n"/>
-      <c r="Q26" s="76" t="n"/>
-      <c r="R26" s="76" t="n"/>
-      <c r="S26" s="76" t="n"/>
-      <c r="T26" s="76" t="n"/>
-      <c r="U26" s="77">
-        <f>IF($F26="SUM",IF(COUNT($I26:$T26)=0,"",SUM($I26:$T26)),IF($F26="AVG",IFERROR(AVERAGE($I26:$T26),""),IF($F26="LAST",IFERROR(LOOKUP(2,1/($I26:$T26&lt;&gt;""),$I26:$T26),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V26" s="23">
-        <f>IF($G26="","",IF($U26="","",IF($G26=0,IF($U26&lt;=0,1,0),IF($E26="↓",IFERROR($G26/$U26,0),IFERROR($U26/$G26,0)))))</f>
-        <v/>
-      </c>
-      <c r="W26" s="17">
-        <f>IF($V26="","—",IF($V26&gt;=1,"✅ محقق",IF($V26&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X26" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y26" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z26" s="78" t="n"/>
-      <c r="AA26" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB26" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC26" s="23">
-        <f>IF($V26="","",$AB26*MIN($V26,1))</f>
-        <v/>
-      </c>
-      <c r="AD26" s="75">
-        <f>IF($G26="","",IF($F26="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G26/12*'لوحة الإدارة التنفيذية'!$P$2),$G26))</f>
-        <v/>
-      </c>
-      <c r="AE26" s="79">
-        <f>IF($F26="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U26="","",$U26/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U26="","",$U26))</f>
-        <v/>
-      </c>
-      <c r="AF26" s="75">
-        <f>IF(OR($AE26="",$G26=""),"",$AE26-$G26)</f>
-        <v/>
-      </c>
-      <c r="AG26" s="17">
-        <f>IF(OR($AE26="",$G26=""),"—",IF($E26="↓",IF($AE26&lt;=$G26,"🟢 على المسار",IF($AE26&lt;=$G26*1.1,"🟡 متابعة","🔴 خطر")),IF($AE26&gt;=$G26,"🟢 على المسار",IF($AE26&gt;=$G26*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH26" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>المركز الرئيسي</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>الامتثال للأمن السيبراني (المركز)</t>
-        </is>
-      </c>
-      <c r="D27" s="60" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E27" s="60" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F27" s="60" t="inlineStr">
-        <is>
-          <t>LAST</t>
-        </is>
-      </c>
-      <c r="G27" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="73" t="n"/>
-      <c r="J27" s="73" t="n"/>
-      <c r="K27" s="73" t="n"/>
-      <c r="L27" s="73" t="n"/>
-      <c r="M27" s="73" t="n"/>
-      <c r="N27" s="73" t="n"/>
-      <c r="O27" s="73" t="n"/>
-      <c r="P27" s="73" t="n"/>
-      <c r="Q27" s="73" t="n"/>
-      <c r="R27" s="73" t="n"/>
-      <c r="S27" s="73" t="n"/>
-      <c r="T27" s="73" t="n"/>
-      <c r="U27" s="59">
-        <f>IF($F27="SUM",IF(COUNT($I27:$T27)=0,"",SUM($I27:$T27)),IF($F27="AVG",IFERROR(AVERAGE($I27:$T27),""),IF($F27="LAST",IFERROR(LOOKUP(2,1/($I27:$T27&lt;&gt;""),$I27:$T27),""),"")))</f>
-        <v/>
-      </c>
-      <c r="V27" s="23">
-        <f>IF($G27="","",IF($U27="","",IF($G27=0,IF($U27&lt;=0,1,0),IF($E27="↓",IFERROR($G27/$U27,0),IFERROR($U27/$G27,0)))))</f>
-        <v/>
-      </c>
-      <c r="W27" s="17">
-        <f>IF($V27="","—",IF($V27&gt;=1,"✅ محقق",IF($V27&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="X27" s="65" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="Y27" s="22" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="Z27" s="53" t="n"/>
-      <c r="AA27" s="21" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="AB27" s="53" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="AC27" s="23">
-        <f>IF($V27="","",$AB27*MIN($V27,1))</f>
-        <v/>
-      </c>
-      <c r="AD27" s="74">
-        <f>IF($G27="","",IF($F27="SUM",IF('لوحة الإدارة التنفيذية'!$P$2="","",$G27/12*'لوحة الإدارة التنفيذية'!$P$2),$G27))</f>
-        <v/>
-      </c>
-      <c r="AE27" s="23">
-        <f>IF($F27="SUM",IF(OR('لوحة الإدارة التنفيذية'!$P$2="",'لوحة الإدارة التنفيذية'!$P$2=0),"",IF($U27="","",$U27/'لوحة الإدارة التنفيذية'!$P$2*12)),IF($U27="","",$U27))</f>
-        <v/>
-      </c>
-      <c r="AF27" s="74">
-        <f>IF(OR($AE27="",$G27=""),"",$AE27-$G27)</f>
-        <v/>
-      </c>
-      <c r="AG27" s="17">
-        <f>IF(OR($AE27="",$G27=""),"—",IF($E27="↓",IF($AE27&lt;=$G27,"🟢 على المسار",IF($AE27&lt;=$G27*1.1,"🟡 متابعة","🔴 خطر")),IF($AE27&gt;=$G27,"🟢 على المسار",IF($AE27&gt;=$G27*0.85,"🟡 متابعة","🔴 خطر"))))</f>
-        <v/>
-      </c>
-      <c r="AH27" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="80" t="inlineStr"/>
-      <c r="B28" s="81" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="80" t="inlineStr"/>
+      <c r="B13" s="81" t="inlineStr">
         <is>
           <t>الإجمالي الموزون للإدارة</t>
         </is>
       </c>
-      <c r="AB28" s="82">
-        <f>SUM(AB4:AB27)</f>
-        <v/>
-      </c>
-      <c r="AC28" s="83">
-        <f>SUM(AC4:AC27)</f>
+      <c r="AB13" s="82">
+        <f>SUM(AB4:AB12)</f>
+        <v/>
+      </c>
+      <c r="AC13" s="83">
+        <f>SUM(AC4:AC12)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
   <mergeCells count="3">
-    <mergeCell ref="B28:AA28"/>
     <mergeCell ref="A2:AH2"/>
+    <mergeCell ref="B13:AA13"/>
     <mergeCell ref="A1:AH1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 N4 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 S4 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 T4 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 Z4 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="قيمة غير صحيحة" error="أدخل رقماً موجباً فقط" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 I12 J4 J5 J6 J7 J8 J9 J10 J11 J12 K4 K5 K6 K7 K8 K9 K10 K11 K12 L4 L5 L6 L7 L8 L9 L10 L11 L12 M4 M5 M6 M7 M8 M9 M10 M11 M12 N4 N5 N6 N7 N8 N9 N10 N11 N12 O4 O5 O6 O7 O8 O9 O10 O11 O12 P4 P5 P6 P7 P8 P9 P10 P11 P12 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 R4 R5 R6 R7 R8 R9 R10 R11 R12 S4 S5 S6 S7 S8 S9 S10 S11 S12 T4 T5 T6 T7 T8 T9 T10 T11 T12 Z4 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="قيمة غير صحيحة" error="أدخل رقماً موجباً فقط" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -28254,7 +26664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K161"/>
+  <dimension ref="A1:K146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -33554,12 +31964,12 @@
       </c>
       <c r="C106" s="91" t="inlineStr">
         <is>
-          <t>نظام أتمتة الكاش (Cash-In) في المحطات</t>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
       </c>
       <c r="D106" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E106" s="92" t="inlineStr">
@@ -33569,7 +31979,7 @@
       </c>
       <c r="F106" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G106" s="68" t="inlineStr">
@@ -33605,22 +32015,22 @@
       </c>
       <c r="C107" s="91" t="inlineStr">
         <is>
-          <t>D365 FNO — المرحلة الأولى</t>
+          <t>معدل تسليم المشاريع في الموعد المحدد</t>
         </is>
       </c>
       <c r="D107" s="68" t="inlineStr">
         <is>
-          <t>وحدة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E107" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F107" s="68" t="inlineStr">
         <is>
-          <t>5 وحدات</t>
+          <t>≥ 90%</t>
         </is>
       </c>
       <c r="G107" s="68" t="inlineStr">
@@ -33656,22 +32066,22 @@
       </c>
       <c r="C108" s="91" t="inlineStr">
         <is>
-          <t>D365 FNO — المرحلة الثانية</t>
+          <t>نسبة الالتزام بميزانية المشاريع</t>
         </is>
       </c>
       <c r="D108" s="68" t="inlineStr">
         <is>
-          <t>وحدة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E108" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F108" s="68" t="inlineStr">
         <is>
-          <t>4 وحدات</t>
+          <t>≥ 95%</t>
         </is>
       </c>
       <c r="G108" s="68" t="inlineStr">
@@ -33707,12 +32117,12 @@
       </c>
       <c r="C109" s="91" t="inlineStr">
         <is>
-          <t>D365 FNO — المرحلة الثالثة</t>
+          <t>نسبة الالتزام بنطاق العمل</t>
         </is>
       </c>
       <c r="D109" s="68" t="inlineStr">
         <is>
-          <t>وحدة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E109" s="92" t="inlineStr">
@@ -33722,7 +32132,7 @@
       </c>
       <c r="F109" s="68" t="inlineStr">
         <is>
-          <t>وحدتان</t>
+          <t>≥ 95%</t>
         </is>
       </c>
       <c r="G109" s="68" t="inlineStr">
@@ -33758,12 +32168,12 @@
       </c>
       <c r="C110" s="91" t="inlineStr">
         <is>
-          <t>تطبيق الامتياز مع واثق</t>
+          <t>نسبة تفعيل الأنظمة الأساسية بالمحطات</t>
         </is>
       </c>
       <c r="D110" s="68" t="inlineStr">
         <is>
-          <t>تطبيق</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E110" s="92" t="inlineStr">
@@ -33773,17 +32183,17 @@
       </c>
       <c r="F110" s="68" t="inlineStr">
         <is>
-          <t>تطبيق واحد</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G110" s="68" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H110" s="91" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I110" s="68" t="inlineStr">
@@ -33809,32 +32219,32 @@
       </c>
       <c r="C111" s="91" t="inlineStr">
         <is>
-          <t>ربط المحطات بوزارة الطاقة (ATJ)</t>
+          <t>متوسط جاهزية أنظمة المركز الرئيسي (Uptime)</t>
         </is>
       </c>
       <c r="D111" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E111" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F111" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≥ 99%</t>
         </is>
       </c>
       <c r="G111" s="68" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H111" s="91" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I111" s="68" t="inlineStr">
@@ -33860,12 +32270,12 @@
       </c>
       <c r="C112" s="91" t="inlineStr">
         <is>
-          <t>ربط الكاميرات بالمركز الرئيسي</t>
+          <t>نسبة الامتثال للأمن السيبراني</t>
         </is>
       </c>
       <c r="D112" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E112" s="92" t="inlineStr">
@@ -33875,17 +32285,17 @@
       </c>
       <c r="F112" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G112" s="68" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H112" s="91" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I112" s="68" t="inlineStr">
@@ -33911,32 +32321,32 @@
       </c>
       <c r="C113" s="91" t="inlineStr">
         <is>
-          <t>تطبيق الولاء (تانكي) في المحطات</t>
+          <t>متوسط زمن استجابة الدعم الفني</t>
         </is>
       </c>
       <c r="D113" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>ساعة</t>
         </is>
       </c>
       <c r="E113" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F113" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≤ ساعة</t>
         </is>
       </c>
       <c r="G113" s="68" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H113" s="91" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I113" s="68" t="inlineStr">
@@ -33962,12 +32372,12 @@
       </c>
       <c r="C114" s="91" t="inlineStr">
         <is>
-          <t>منصة Tatin السحابية</t>
+          <t>نسبة التكامل الرقمي (ERP/واثق/الولاء)</t>
         </is>
       </c>
       <c r="D114" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E114" s="92" t="inlineStr">
@@ -33977,22 +32387,22 @@
       </c>
       <c r="F114" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G114" s="68" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H114" s="91" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I114" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="J114" s="68" t="inlineStr">
@@ -34008,17 +32418,17 @@
       </c>
       <c r="B115" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C115" s="91" t="inlineStr">
         <is>
-          <t>إدارة العمليات بالذكاء الاصطناعي</t>
+          <t>نسبة السعودة / التوطين</t>
         </is>
       </c>
       <c r="D115" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E115" s="92" t="inlineStr">
@@ -34028,22 +32438,22 @@
       </c>
       <c r="F115" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>أخضر مرتفع (حسب الوزارة)</t>
         </is>
       </c>
       <c r="G115" s="68" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="H115" s="91" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I115" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="J115" s="68" t="inlineStr">
@@ -34059,17 +32469,17 @@
       </c>
       <c r="B116" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C116" s="91" t="inlineStr">
         <is>
-          <t>جاهزية أتمتة المحطات (Forecourt)</t>
+          <t>الارتقاء بآليات اختيار المرشحين</t>
         </is>
       </c>
       <c r="D116" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E116" s="92" t="inlineStr">
@@ -34079,7 +32489,7 @@
       </c>
       <c r="F116" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G116" s="68" t="inlineStr">
@@ -34089,12 +32499,12 @@
       </c>
       <c r="H116" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I116" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J116" s="68" t="inlineStr">
@@ -34110,27 +32520,27 @@
       </c>
       <c r="B117" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C117" s="91" t="inlineStr">
         <is>
-          <t>جاهزية اتصال الشبكة بالمحطات</t>
+          <t>نسبة شغل الشواغر خلال 30 يوم</t>
         </is>
       </c>
       <c r="D117" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E117" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F117" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≥ 85%</t>
         </is>
       </c>
       <c r="G117" s="68" t="inlineStr">
@@ -34140,7 +32550,7 @@
       </c>
       <c r="H117" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I117" s="68" t="inlineStr">
@@ -34161,17 +32571,17 @@
       </c>
       <c r="B118" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C118" s="91" t="inlineStr">
         <is>
-          <t>جاهزية نقاط البيع والمدفوعات (POS)</t>
+          <t>معدل استبقاء الموظفين (Retention)</t>
         </is>
       </c>
       <c r="D118" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E118" s="92" t="inlineStr">
@@ -34181,7 +32591,7 @@
       </c>
       <c r="F118" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≥ 90%</t>
         </is>
       </c>
       <c r="G118" s="68" t="inlineStr">
@@ -34191,12 +32601,12 @@
       </c>
       <c r="H118" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I118" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="J118" s="68" t="inlineStr">
@@ -34212,27 +32622,27 @@
       </c>
       <c r="B119" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C119" s="91" t="inlineStr">
         <is>
-          <t>جاهزية نظام الكاميرات (CCTV)</t>
+          <t>معدل دوران الموظفين (Turnover)</t>
         </is>
       </c>
       <c r="D119" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E119" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F119" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≤ 10%</t>
         </is>
       </c>
       <c r="G119" s="68" t="inlineStr">
@@ -34242,12 +32652,12 @@
       </c>
       <c r="H119" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I119" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="J119" s="68" t="inlineStr">
@@ -34263,27 +32673,27 @@
       </c>
       <c r="B120" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C120" s="91" t="inlineStr">
         <is>
-          <t>جاهزية الشبكة</t>
+          <t>عدد الدورات الإدارية المنعقدة</t>
         </is>
       </c>
       <c r="D120" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>دورة</t>
         </is>
       </c>
       <c r="E120" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F120" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>6 دورات</t>
         </is>
       </c>
       <c r="G120" s="68" t="inlineStr">
@@ -34293,7 +32703,7 @@
       </c>
       <c r="H120" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I120" s="68" t="inlineStr">
@@ -34303,7 +32713,7 @@
       </c>
       <c r="J120" s="68" t="inlineStr">
         <is>
-          <t>🟣 لاحق</t>
+          <t>🔵 قائد</t>
         </is>
       </c>
       <c r="K120" s="38" t="n"/>
@@ -34314,27 +32724,27 @@
       </c>
       <c r="B121" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C121" s="91" t="inlineStr">
         <is>
-          <t>الامتثال للأمن السيبراني (المحطات)</t>
+          <t>متوسط ساعات التدريب لكل موظف</t>
         </is>
       </c>
       <c r="D121" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>ساعة</t>
         </is>
       </c>
       <c r="E121" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F121" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≥ 40 ساعة</t>
         </is>
       </c>
       <c r="G121" s="68" t="inlineStr">
@@ -34344,17 +32754,17 @@
       </c>
       <c r="H121" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I121" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="J121" s="68" t="inlineStr">
         <is>
-          <t>🟣 لاحق</t>
+          <t>🔵 قائد</t>
         </is>
       </c>
       <c r="K121" s="38" t="n"/>
@@ -34365,27 +32775,27 @@
       </c>
       <c r="B122" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C122" s="91" t="inlineStr">
         <is>
-          <t>زمن استجابة الدعم الفني (المحطات)</t>
+          <t>نسبة الموظفين المشمولين بخطة تطوير</t>
         </is>
       </c>
       <c r="D122" s="68" t="inlineStr">
         <is>
-          <t>يوم</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E122" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F122" s="68" t="inlineStr">
         <is>
-          <t>≤ يوم</t>
+          <t>≥ 80%</t>
         </is>
       </c>
       <c r="G122" s="68" t="inlineStr">
@@ -34395,12 +32805,12 @@
       </c>
       <c r="H122" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I122" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="J122" s="68" t="inlineStr">
@@ -34416,27 +32826,27 @@
       </c>
       <c r="B123" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C123" s="91" t="inlineStr">
         <is>
-          <t>ERP والتكامل (المحطات)</t>
+          <t>مؤشر رضا الموظفين (eNPS)</t>
         </is>
       </c>
       <c r="D123" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>نقطة</t>
         </is>
       </c>
       <c r="E123" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F123" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>≥ 30</t>
         </is>
       </c>
       <c r="G123" s="68" t="inlineStr">
@@ -34446,12 +32856,12 @@
       </c>
       <c r="H123" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I123" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="J123" s="68" t="inlineStr">
@@ -34467,27 +32877,27 @@
       </c>
       <c r="B124" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C124" s="91" t="inlineStr">
         <is>
-          <t>تكامل واثق (المحطات)</t>
+          <t>تحسين مستوى الرضا الوظيفي</t>
         </is>
       </c>
       <c r="D124" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E124" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F124" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>مستهدف سنوي</t>
         </is>
       </c>
       <c r="G124" s="68" t="inlineStr">
@@ -34497,12 +32907,12 @@
       </c>
       <c r="H124" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I124" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="J124" s="68" t="inlineStr">
@@ -34518,17 +32928,17 @@
       </c>
       <c r="B125" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C125" s="91" t="inlineStr">
         <is>
-          <t>تكامل تطبيق الولاء (المحطات)</t>
+          <t>ترسيخ القيم والثقافة المؤسسية</t>
         </is>
       </c>
       <c r="D125" s="68" t="inlineStr">
         <is>
-          <t>محطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E125" s="92" t="inlineStr">
@@ -34538,7 +32948,7 @@
       </c>
       <c r="F125" s="68" t="inlineStr">
         <is>
-          <t>164 محطة</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G125" s="68" t="inlineStr">
@@ -34548,7 +32958,7 @@
       </c>
       <c r="H125" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>الاستثمار في الموظفين</t>
         </is>
       </c>
       <c r="I125" s="68" t="inlineStr">
@@ -34569,17 +32979,17 @@
       </c>
       <c r="B126" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C126" s="91" t="inlineStr">
         <is>
-          <t>جاهزية شبكة المركز الرئيسي</t>
+          <t>نسبة أتمتة عمليات الموارد البشرية</t>
         </is>
       </c>
       <c r="D126" s="68" t="inlineStr">
         <is>
-          <t>ساعة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E126" s="92" t="inlineStr">
@@ -34589,22 +32999,22 @@
       </c>
       <c r="F126" s="68" t="inlineStr">
         <is>
-          <t>24 ساعة</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G126" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="H126" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>التحول التقني</t>
         </is>
       </c>
       <c r="I126" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="J126" s="68" t="inlineStr">
@@ -34620,17 +33030,17 @@
       </c>
       <c r="B127" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C127" s="91" t="inlineStr">
         <is>
-          <t>جاهزية تطبيقات المركز الرئيسي</t>
+          <t>نسبة توثيق أنظمة العمل</t>
         </is>
       </c>
       <c r="D127" s="68" t="inlineStr">
         <is>
-          <t>ساعة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E127" s="92" t="inlineStr">
@@ -34640,7 +33050,7 @@
       </c>
       <c r="F127" s="68" t="inlineStr">
         <is>
-          <t>24 ساعة</t>
+          <t>≥ 80%</t>
         </is>
       </c>
       <c r="G127" s="68" t="inlineStr">
@@ -34671,27 +33081,27 @@
       </c>
       <c r="B128" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C128" s="91" t="inlineStr">
         <is>
-          <t>زمن استجابة الدعم (المركز)</t>
+          <t>ترسيخ الأنظمة الإدارية</t>
         </is>
       </c>
       <c r="D128" s="68" t="inlineStr">
         <is>
-          <t>ساعة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E128" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F128" s="68" t="inlineStr">
         <is>
-          <t>≤ ساعة</t>
+          <t>≥ 80%</t>
         </is>
       </c>
       <c r="G128" s="68" t="inlineStr">
@@ -34722,12 +33132,12 @@
       </c>
       <c r="B129" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C129" s="91" t="inlineStr">
         <is>
-          <t>الامتثال للأمن السيبراني (المركز)</t>
+          <t>اعتماد الهيكل التنظيمي</t>
         </is>
       </c>
       <c r="D129" s="68" t="inlineStr">
@@ -34778,7 +33188,7 @@
       </c>
       <c r="C130" s="91" t="inlineStr">
         <is>
-          <t>نسبة السعودة / التوطين</t>
+          <t>اكتمال الأوصاف الوظيفية (+KPI)</t>
         </is>
       </c>
       <c r="D130" s="68" t="inlineStr">
@@ -34793,7 +33203,7 @@
       </c>
       <c r="F130" s="68" t="inlineStr">
         <is>
-          <t>أخضر مرتفع (حسب الوزارة)</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G130" s="68" t="inlineStr">
@@ -34803,12 +33213,12 @@
       </c>
       <c r="H130" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="I130" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J130" s="68" t="inlineStr">
@@ -34829,7 +33239,7 @@
       </c>
       <c r="C131" s="91" t="inlineStr">
         <is>
-          <t>الارتقاء بآليات اختيار المرشحين</t>
+          <t>نسبة إنجاز تقييمات الأداء في موعدها</t>
         </is>
       </c>
       <c r="D131" s="68" t="inlineStr">
@@ -34839,7 +33249,7 @@
       </c>
       <c r="E131" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F131" s="68" t="inlineStr">
@@ -34875,42 +33285,42 @@
       </c>
       <c r="B132" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C132" s="91" t="inlineStr">
         <is>
-          <t>نسبة شغل الشواغر خلال 30 يوم</t>
+          <t>الوصول الكلي (Total Reach)</t>
         </is>
       </c>
       <c r="D132" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>وصول</t>
         </is>
       </c>
       <c r="E132" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F132" s="68" t="inlineStr">
         <is>
-          <t>≥ 85%</t>
+          <t>50م وصول</t>
         </is>
       </c>
       <c r="G132" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="H132" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="I132" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="J132" s="68" t="inlineStr">
@@ -34926,42 +33336,42 @@
       </c>
       <c r="B133" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C133" s="91" t="inlineStr">
         <is>
-          <t>معدل استبقاء الموظفين (Retention)</t>
+          <t>عملاء تجاريون جدد</t>
         </is>
       </c>
       <c r="D133" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>عميل</t>
         </is>
       </c>
       <c r="E133" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F133" s="68" t="inlineStr">
         <is>
-          <t>≥ 90%</t>
+          <t>200 عميل</t>
         </is>
       </c>
       <c r="G133" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="H133" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="I133" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="J133" s="68" t="inlineStr">
@@ -34977,42 +33387,42 @@
       </c>
       <c r="B134" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C134" s="91" t="inlineStr">
         <is>
-          <t>معدل دوران الموظفين (Turnover)</t>
+          <t>إجمالي المتابعين (كل المنصات)</t>
         </is>
       </c>
       <c r="D134" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>متابع</t>
         </is>
       </c>
       <c r="E134" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F134" s="68" t="inlineStr">
         <is>
-          <t>≤ 10%</t>
+          <t>380ك متابع</t>
         </is>
       </c>
       <c r="G134" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="H134" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="I134" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J134" s="68" t="inlineStr">
@@ -35028,37 +33438,37 @@
       </c>
       <c r="B135" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C135" s="91" t="inlineStr">
         <is>
-          <t>عدد الدورات الإدارية المنعقدة</t>
+          <t>معدل التفاعل (Engagement)</t>
         </is>
       </c>
       <c r="D135" s="68" t="inlineStr">
         <is>
-          <t>دورة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E135" s="92" t="inlineStr">
         <is>
-          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F135" s="68" t="inlineStr">
         <is>
-          <t>6 دورات</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="G135" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="H135" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="I135" s="68" t="inlineStr">
@@ -35068,7 +33478,7 @@
       </c>
       <c r="J135" s="68" t="inlineStr">
         <is>
-          <t>🔵 قائد</t>
+          <t>🟣 لاحق</t>
         </is>
       </c>
       <c r="K135" s="38" t="n"/>
@@ -35079,17 +33489,17 @@
       </c>
       <c r="B136" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C136" s="91" t="inlineStr">
         <is>
-          <t>متوسط ساعات التدريب لكل موظف</t>
+          <t>حملات تسويقية منجزة</t>
         </is>
       </c>
       <c r="D136" s="68" t="inlineStr">
         <is>
-          <t>ساعة</t>
+          <t>حملة</t>
         </is>
       </c>
       <c r="E136" s="92" t="inlineStr">
@@ -35099,22 +33509,22 @@
       </c>
       <c r="F136" s="68" t="inlineStr">
         <is>
-          <t>≥ 40 ساعة</t>
+          <t>48 حملة</t>
         </is>
       </c>
       <c r="G136" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="H136" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="I136" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J136" s="68" t="inlineStr">
@@ -35130,12 +33540,12 @@
       </c>
       <c r="B137" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C137" s="91" t="inlineStr">
         <is>
-          <t>نسبة الموظفين المشمولين بخطة تطوير</t>
+          <t>تحويل الفرص إلى عقود</t>
         </is>
       </c>
       <c r="D137" s="68" t="inlineStr">
@@ -35145,32 +33555,32 @@
       </c>
       <c r="E137" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F137" s="68" t="inlineStr">
         <is>
-          <t>≥ 80%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G137" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="H137" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="I137" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J137" s="68" t="inlineStr">
         <is>
-          <t>🟣 لاحق</t>
+          <t>🔵 قائد</t>
         </is>
       </c>
       <c r="K137" s="38" t="n"/>
@@ -35181,17 +33591,17 @@
       </c>
       <c r="B138" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C138" s="91" t="inlineStr">
         <is>
-          <t>مؤشر رضا الموظفين (eNPS)</t>
+          <t>نسبة المبيعات لكل حملة</t>
         </is>
       </c>
       <c r="D138" s="68" t="inlineStr">
         <is>
-          <t>نقطة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E138" s="92" t="inlineStr">
@@ -35201,27 +33611,27 @@
       </c>
       <c r="F138" s="68" t="inlineStr">
         <is>
-          <t>≥ 30</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G138" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="H138" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="I138" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>مالي</t>
         </is>
       </c>
       <c r="J138" s="68" t="inlineStr">
         <is>
-          <t>🟣 لاحق</t>
+          <t>🔵 قائد</t>
         </is>
       </c>
       <c r="K138" s="38" t="n"/>
@@ -35232,12 +33642,12 @@
       </c>
       <c r="B139" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C139" s="91" t="inlineStr">
         <is>
-          <t>تحسين مستوى الرضا الوظيفي</t>
+          <t>نسبة التزام الهوية البصرية</t>
         </is>
       </c>
       <c r="D139" s="68" t="inlineStr">
@@ -35247,27 +33657,27 @@
       </c>
       <c r="E139" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F139" s="68" t="inlineStr">
         <is>
-          <t>مستهدف سنوي</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G139" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="H139" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>تطوير التصاميم والهوية</t>
         </is>
       </c>
       <c r="I139" s="68" t="inlineStr">
         <is>
-          <t>العملاء</t>
+          <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="J139" s="68" t="inlineStr">
@@ -35283,17 +33693,17 @@
       </c>
       <c r="B140" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C140" s="91" t="inlineStr">
         <is>
-          <t>ترسيخ القيم والثقافة المؤسسية</t>
+          <t>وصول العلاقات العامة (PR)</t>
         </is>
       </c>
       <c r="D140" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>وصول</t>
         </is>
       </c>
       <c r="E140" s="92" t="inlineStr">
@@ -35303,22 +33713,22 @@
       </c>
       <c r="F140" s="68" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7م وصول</t>
         </is>
       </c>
       <c r="G140" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>النمو</t>
         </is>
       </c>
       <c r="H140" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>زيادة وصول العملاء</t>
         </is>
       </c>
       <c r="I140" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="J140" s="68" t="inlineStr">
@@ -35334,27 +33744,27 @@
       </c>
       <c r="B141" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C141" s="91" t="inlineStr">
         <is>
-          <t>نسبة أتمتة عمليات الموارد البشرية</t>
+          <t>عدد المعارض بالسنة</t>
         </is>
       </c>
       <c r="D141" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>معرض</t>
         </is>
       </c>
       <c r="E141" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F141" s="68" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3 معارض</t>
         </is>
       </c>
       <c r="G141" s="68" t="inlineStr">
@@ -35364,17 +33774,17 @@
       </c>
       <c r="H141" s="91" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>إطلاق مشاريع جديدة</t>
         </is>
       </c>
       <c r="I141" s="68" t="inlineStr">
         <is>
-          <t>التعلّم والنمو</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="J141" s="68" t="inlineStr">
         <is>
-          <t>🟣 لاحق</t>
+          <t>🔵 قائد</t>
         </is>
       </c>
       <c r="K141" s="38" t="n"/>
@@ -35385,37 +33795,37 @@
       </c>
       <c r="B142" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C142" s="91" t="inlineStr">
         <is>
-          <t>نسبة توثيق أنظمة العمل</t>
+          <t>اتفاقيات استراتيجية</t>
         </is>
       </c>
       <c r="D142" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>اتفاقية</t>
         </is>
       </c>
       <c r="E142" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F142" s="68" t="inlineStr">
         <is>
-          <t>≥ 80%</t>
+          <t>3 اتفاقيات</t>
         </is>
       </c>
       <c r="G142" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="H142" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>إطلاق مشاريع جديدة</t>
         </is>
       </c>
       <c r="I142" s="68" t="inlineStr">
@@ -35436,27 +33846,27 @@
       </c>
       <c r="B143" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C143" s="91" t="inlineStr">
         <is>
-          <t>ترسيخ الأنظمة الإدارية</t>
+          <t>تقييم خرائط قوقل</t>
         </is>
       </c>
       <c r="D143" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>نجمة/5</t>
         </is>
       </c>
       <c r="E143" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F143" s="68" t="inlineStr">
         <is>
-          <t>≥ 80%</t>
+          <t>4.7 ⭐</t>
         </is>
       </c>
       <c r="G143" s="68" t="inlineStr">
@@ -35466,12 +33876,12 @@
       </c>
       <c r="H143" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>تعزيز تجربة العملاء</t>
         </is>
       </c>
       <c r="I143" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="J143" s="68" t="inlineStr">
@@ -35487,12 +33897,12 @@
       </c>
       <c r="B144" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C144" s="91" t="inlineStr">
         <is>
-          <t>اعتماد الهيكل التنظيمي</t>
+          <t>معدل خفض الشكاوى</t>
         </is>
       </c>
       <c r="D144" s="68" t="inlineStr">
@@ -35502,12 +33912,12 @@
       </c>
       <c r="E144" s="92" t="inlineStr">
         <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
+          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F144" s="68" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G144" s="68" t="inlineStr">
@@ -35517,12 +33927,12 @@
       </c>
       <c r="H144" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>تعزيز تجربة العملاء</t>
         </is>
       </c>
       <c r="I144" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="J144" s="68" t="inlineStr">
@@ -35538,17 +33948,17 @@
       </c>
       <c r="B145" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C145" s="91" t="inlineStr">
         <is>
-          <t>اكتمال الأوصاف الوظيفية (+KPI)</t>
+          <t>وصول محتوى تطبيق تانكي</t>
         </is>
       </c>
       <c r="D145" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>وصول</t>
         </is>
       </c>
       <c r="E145" s="92" t="inlineStr">
@@ -35558,22 +33968,22 @@
       </c>
       <c r="F145" s="68" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1م وصول</t>
         </is>
       </c>
       <c r="G145" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="H145" s="91" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>تطبيق «تانكي»</t>
         </is>
       </c>
       <c r="I145" s="68" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="J145" s="68" t="inlineStr">
@@ -35589,37 +33999,37 @@
       </c>
       <c r="B146" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C146" s="91" t="inlineStr">
         <is>
-          <t>نسبة إنجاز تقييمات الأداء في موعدها</t>
+          <t>مشاركات تطبيق تانكي</t>
         </is>
       </c>
       <c r="D146" s="68" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مشاركة</t>
         </is>
       </c>
       <c r="E146" s="92" t="inlineStr">
         <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
+          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
         </is>
       </c>
       <c r="F146" s="68" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>250 مشاركة</t>
         </is>
       </c>
       <c r="G146" s="68" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="H146" s="91" t="inlineStr">
         <is>
-          <t>الاستثمار في الموظفين</t>
+          <t>تطبيق «تانكي»</t>
         </is>
       </c>
       <c r="I146" s="68" t="inlineStr">
@@ -35633,771 +34043,6 @@
         </is>
       </c>
       <c r="K146" s="38" t="n"/>
-    </row>
-    <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="68" t="n">
-        <v>144</v>
-      </c>
-      <c r="B147" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C147" s="91" t="inlineStr">
-        <is>
-          <t>الوصول الكلي (Total Reach)</t>
-        </is>
-      </c>
-      <c r="D147" s="68" t="inlineStr">
-        <is>
-          <t>وصول</t>
-        </is>
-      </c>
-      <c r="E147" s="92" t="inlineStr">
-        <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F147" s="68" t="inlineStr">
-        <is>
-          <t>50م وصول</t>
-        </is>
-      </c>
-      <c r="G147" s="68" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="H147" s="91" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="I147" s="68" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="J147" s="68" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="K147" s="38" t="n"/>
-    </row>
-    <row r="148" ht="22" customHeight="1">
-      <c r="A148" s="68" t="n">
-        <v>145</v>
-      </c>
-      <c r="B148" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C148" s="91" t="inlineStr">
-        <is>
-          <t>عملاء تجاريون جدد</t>
-        </is>
-      </c>
-      <c r="D148" s="68" t="inlineStr">
-        <is>
-          <t>عميل</t>
-        </is>
-      </c>
-      <c r="E148" s="92" t="inlineStr">
-        <is>
-          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F148" s="68" t="inlineStr">
-        <is>
-          <t>200 عميل</t>
-        </is>
-      </c>
-      <c r="G148" s="68" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="H148" s="91" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="I148" s="68" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="J148" s="68" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="K148" s="38" t="n"/>
-    </row>
-    <row r="149" ht="22" customHeight="1">
-      <c r="A149" s="68" t="n">
-        <v>146</v>
-      </c>
-      <c r="B149" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C149" s="91" t="inlineStr">
-        <is>
-          <t>إجمالي المتابعين (كل المنصات)</t>
-        </is>
-      </c>
-      <c r="D149" s="68" t="inlineStr">
-        <is>
-          <t>متابع</t>
-        </is>
-      </c>
-      <c r="E149" s="92" t="inlineStr">
-        <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F149" s="68" t="inlineStr">
-        <is>
-          <t>380ك متابع</t>
-        </is>
-      </c>
-      <c r="G149" s="68" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="H149" s="91" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="I149" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="J149" s="68" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="K149" s="38" t="n"/>
-    </row>
-    <row r="150" ht="22" customHeight="1">
-      <c r="A150" s="68" t="n">
-        <v>147</v>
-      </c>
-      <c r="B150" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C150" s="91" t="inlineStr">
-        <is>
-          <t>معدل التفاعل (Engagement)</t>
-        </is>
-      </c>
-      <c r="D150" s="68" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E150" s="92" t="inlineStr">
-        <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F150" s="68" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="G150" s="68" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="H150" s="91" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="I150" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="J150" s="68" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="K150" s="38" t="n"/>
-    </row>
-    <row r="151" ht="22" customHeight="1">
-      <c r="A151" s="68" t="n">
-        <v>148</v>
-      </c>
-      <c r="B151" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C151" s="91" t="inlineStr">
-        <is>
-          <t>حملات تسويقية منجزة</t>
-        </is>
-      </c>
-      <c r="D151" s="68" t="inlineStr">
-        <is>
-          <t>حملة</t>
-        </is>
-      </c>
-      <c r="E151" s="92" t="inlineStr">
-        <is>
-          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F151" s="68" t="inlineStr">
-        <is>
-          <t>48 حملة</t>
-        </is>
-      </c>
-      <c r="G151" s="68" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="H151" s="91" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="I151" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="J151" s="68" t="inlineStr">
-        <is>
-          <t>🔵 قائد</t>
-        </is>
-      </c>
-      <c r="K151" s="38" t="n"/>
-    </row>
-    <row r="152" ht="22" customHeight="1">
-      <c r="A152" s="68" t="n">
-        <v>149</v>
-      </c>
-      <c r="B152" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C152" s="91" t="inlineStr">
-        <is>
-          <t>تحويل الفرص إلى عقود</t>
-        </is>
-      </c>
-      <c r="D152" s="68" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E152" s="92" t="inlineStr">
-        <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F152" s="68" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G152" s="68" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="H152" s="91" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="I152" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="J152" s="68" t="inlineStr">
-        <is>
-          <t>🔵 قائد</t>
-        </is>
-      </c>
-      <c r="K152" s="38" t="n"/>
-    </row>
-    <row r="153" ht="22" customHeight="1">
-      <c r="A153" s="68" t="n">
-        <v>150</v>
-      </c>
-      <c r="B153" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C153" s="91" t="inlineStr">
-        <is>
-          <t>نسبة المبيعات لكل حملة</t>
-        </is>
-      </c>
-      <c r="D153" s="68" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E153" s="92" t="inlineStr">
-        <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F153" s="68" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G153" s="68" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="H153" s="91" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="I153" s="68" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="J153" s="68" t="inlineStr">
-        <is>
-          <t>🔵 قائد</t>
-        </is>
-      </c>
-      <c r="K153" s="38" t="n"/>
-    </row>
-    <row r="154" ht="22" customHeight="1">
-      <c r="A154" s="68" t="n">
-        <v>151</v>
-      </c>
-      <c r="B154" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C154" s="91" t="inlineStr">
-        <is>
-          <t>نسبة التزام الهوية البصرية</t>
-        </is>
-      </c>
-      <c r="D154" s="68" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E154" s="92" t="inlineStr">
-        <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F154" s="68" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G154" s="68" t="inlineStr">
-        <is>
-          <t>الابتكار</t>
-        </is>
-      </c>
-      <c r="H154" s="91" t="inlineStr">
-        <is>
-          <t>تطوير التصاميم والهوية</t>
-        </is>
-      </c>
-      <c r="I154" s="68" t="inlineStr">
-        <is>
-          <t>التعلّم والنمو</t>
-        </is>
-      </c>
-      <c r="J154" s="68" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="K154" s="38" t="n"/>
-    </row>
-    <row r="155" ht="22" customHeight="1">
-      <c r="A155" s="68" t="n">
-        <v>152</v>
-      </c>
-      <c r="B155" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C155" s="91" t="inlineStr">
-        <is>
-          <t>وصول العلاقات العامة (PR)</t>
-        </is>
-      </c>
-      <c r="D155" s="68" t="inlineStr">
-        <is>
-          <t>وصول</t>
-        </is>
-      </c>
-      <c r="E155" s="92" t="inlineStr">
-        <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F155" s="68" t="inlineStr">
-        <is>
-          <t>7م وصول</t>
-        </is>
-      </c>
-      <c r="G155" s="68" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="H155" s="91" t="inlineStr">
-        <is>
-          <t>زيادة وصول العملاء</t>
-        </is>
-      </c>
-      <c r="I155" s="68" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="J155" s="68" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="K155" s="38" t="n"/>
-    </row>
-    <row r="156" ht="22" customHeight="1">
-      <c r="A156" s="68" t="n">
-        <v>153</v>
-      </c>
-      <c r="B156" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C156" s="91" t="inlineStr">
-        <is>
-          <t>عدد المعارض بالسنة</t>
-        </is>
-      </c>
-      <c r="D156" s="68" t="inlineStr">
-        <is>
-          <t>معرض</t>
-        </is>
-      </c>
-      <c r="E156" s="92" t="inlineStr">
-        <is>
-          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F156" s="68" t="inlineStr">
-        <is>
-          <t>3 معارض</t>
-        </is>
-      </c>
-      <c r="G156" s="68" t="inlineStr">
-        <is>
-          <t>الابتكار</t>
-        </is>
-      </c>
-      <c r="H156" s="91" t="inlineStr">
-        <is>
-          <t>إطلاق مشاريع جديدة</t>
-        </is>
-      </c>
-      <c r="I156" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="J156" s="68" t="inlineStr">
-        <is>
-          <t>🔵 قائد</t>
-        </is>
-      </c>
-      <c r="K156" s="38" t="n"/>
-    </row>
-    <row r="157" ht="22" customHeight="1">
-      <c r="A157" s="68" t="n">
-        <v>154</v>
-      </c>
-      <c r="B157" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C157" s="91" t="inlineStr">
-        <is>
-          <t>اتفاقيات استراتيجية</t>
-        </is>
-      </c>
-      <c r="D157" s="68" t="inlineStr">
-        <is>
-          <t>اتفاقية</t>
-        </is>
-      </c>
-      <c r="E157" s="92" t="inlineStr">
-        <is>
-          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F157" s="68" t="inlineStr">
-        <is>
-          <t>3 اتفاقيات</t>
-        </is>
-      </c>
-      <c r="G157" s="68" t="inlineStr">
-        <is>
-          <t>الابتكار</t>
-        </is>
-      </c>
-      <c r="H157" s="91" t="inlineStr">
-        <is>
-          <t>إطلاق مشاريع جديدة</t>
-        </is>
-      </c>
-      <c r="I157" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="J157" s="68" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="K157" s="38" t="n"/>
-    </row>
-    <row r="158" ht="22" customHeight="1">
-      <c r="A158" s="68" t="n">
-        <v>155</v>
-      </c>
-      <c r="B158" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C158" s="91" t="inlineStr">
-        <is>
-          <t>تقييم خرائط قوقل</t>
-        </is>
-      </c>
-      <c r="D158" s="68" t="inlineStr">
-        <is>
-          <t>نجمة/5</t>
-        </is>
-      </c>
-      <c r="E158" s="92" t="inlineStr">
-        <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F158" s="68" t="inlineStr">
-        <is>
-          <t>4.7 ⭐</t>
-        </is>
-      </c>
-      <c r="G158" s="68" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="H158" s="91" t="inlineStr">
-        <is>
-          <t>تعزيز تجربة العملاء</t>
-        </is>
-      </c>
-      <c r="I158" s="68" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="J158" s="68" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="K158" s="38" t="n"/>
-    </row>
-    <row r="159" ht="22" customHeight="1">
-      <c r="A159" s="68" t="n">
-        <v>156</v>
-      </c>
-      <c r="B159" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C159" s="91" t="inlineStr">
-        <is>
-          <t>معدل خفض الشكاوى</t>
-        </is>
-      </c>
-      <c r="D159" s="68" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E159" s="92" t="inlineStr">
-        <is>
-          <t>متوسط شهري · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F159" s="68" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G159" s="68" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="H159" s="91" t="inlineStr">
-        <is>
-          <t>تعزيز تجربة العملاء</t>
-        </is>
-      </c>
-      <c r="I159" s="68" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="J159" s="68" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="K159" s="38" t="n"/>
-    </row>
-    <row r="160" ht="22" customHeight="1">
-      <c r="A160" s="68" t="n">
-        <v>157</v>
-      </c>
-      <c r="B160" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C160" s="91" t="inlineStr">
-        <is>
-          <t>وصول محتوى تطبيق تانكي</t>
-        </is>
-      </c>
-      <c r="D160" s="68" t="inlineStr">
-        <is>
-          <t>وصول</t>
-        </is>
-      </c>
-      <c r="E160" s="92" t="inlineStr">
-        <is>
-          <t>تراكمي (آخر قيمة) · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F160" s="68" t="inlineStr">
-        <is>
-          <t>1م وصول</t>
-        </is>
-      </c>
-      <c r="G160" s="68" t="inlineStr">
-        <is>
-          <t>الابتكار</t>
-        </is>
-      </c>
-      <c r="H160" s="91" t="inlineStr">
-        <is>
-          <t>تطبيق «تانكي»</t>
-        </is>
-      </c>
-      <c r="I160" s="68" t="inlineStr">
-        <is>
-          <t>العملاء</t>
-        </is>
-      </c>
-      <c r="J160" s="68" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="K160" s="38" t="n"/>
-    </row>
-    <row r="161" ht="22" customHeight="1">
-      <c r="A161" s="68" t="n">
-        <v>158</v>
-      </c>
-      <c r="B161" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C161" s="91" t="inlineStr">
-        <is>
-          <t>مشاركات تطبيق تانكي</t>
-        </is>
-      </c>
-      <c r="D161" s="68" t="inlineStr">
-        <is>
-          <t>مشاركة</t>
-        </is>
-      </c>
-      <c r="E161" s="92" t="inlineStr">
-        <is>
-          <t>تجميعي (مجموع شهري) · (الفعلي÷المستهدف)×100</t>
-        </is>
-      </c>
-      <c r="F161" s="68" t="inlineStr">
-        <is>
-          <t>250 مشاركة</t>
-        </is>
-      </c>
-      <c r="G161" s="68" t="inlineStr">
-        <is>
-          <t>الابتكار</t>
-        </is>
-      </c>
-      <c r="H161" s="91" t="inlineStr">
-        <is>
-          <t>تطبيق «تانكي»</t>
-        </is>
-      </c>
-      <c r="I161" s="68" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="J161" s="68" t="inlineStr">
-        <is>
-          <t>🟣 لاحق</t>
-        </is>
-      </c>
-      <c r="K161" s="38" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
@@ -37003,7 +34648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -40852,31 +38497,31 @@
       </c>
       <c r="B115" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C115" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C13</f>
+        <f>'الموارد البشرية · المؤشرات'!C4</f>
         <v/>
       </c>
       <c r="D115" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X13</f>
+        <f>'الموارد البشرية · المؤشرات'!X4</f>
         <v/>
       </c>
       <c r="E115" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y13</f>
+        <f>'الموارد البشرية · المؤشرات'!Y4</f>
         <v/>
       </c>
       <c r="F115" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V13</f>
+        <f>'الموارد البشرية · المؤشرات'!V4</f>
         <v/>
       </c>
       <c r="G115" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W13</f>
+        <f>'الموارد البشرية · المؤشرات'!W4</f>
         <v/>
       </c>
       <c r="H115" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH13</f>
+        <f>'الموارد البشرية · المؤشرات'!AH4</f>
         <v/>
       </c>
     </row>
@@ -40886,31 +38531,31 @@
       </c>
       <c r="B116" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C116" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C14</f>
+        <f>'الموارد البشرية · المؤشرات'!C5</f>
         <v/>
       </c>
       <c r="D116" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X14</f>
+        <f>'الموارد البشرية · المؤشرات'!X5</f>
         <v/>
       </c>
       <c r="E116" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y14</f>
+        <f>'الموارد البشرية · المؤشرات'!Y5</f>
         <v/>
       </c>
       <c r="F116" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V14</f>
+        <f>'الموارد البشرية · المؤشرات'!V5</f>
         <v/>
       </c>
       <c r="G116" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W14</f>
+        <f>'الموارد البشرية · المؤشرات'!W5</f>
         <v/>
       </c>
       <c r="H116" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH14</f>
+        <f>'الموارد البشرية · المؤشرات'!AH5</f>
         <v/>
       </c>
     </row>
@@ -40920,31 +38565,31 @@
       </c>
       <c r="B117" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C117" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C15</f>
+        <f>'الموارد البشرية · المؤشرات'!C6</f>
         <v/>
       </c>
       <c r="D117" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X15</f>
+        <f>'الموارد البشرية · المؤشرات'!X6</f>
         <v/>
       </c>
       <c r="E117" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y15</f>
+        <f>'الموارد البشرية · المؤشرات'!Y6</f>
         <v/>
       </c>
       <c r="F117" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V15</f>
+        <f>'الموارد البشرية · المؤشرات'!V6</f>
         <v/>
       </c>
       <c r="G117" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W15</f>
+        <f>'الموارد البشرية · المؤشرات'!W6</f>
         <v/>
       </c>
       <c r="H117" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH15</f>
+        <f>'الموارد البشرية · المؤشرات'!AH6</f>
         <v/>
       </c>
     </row>
@@ -40954,31 +38599,31 @@
       </c>
       <c r="B118" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C118" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C16</f>
+        <f>'الموارد البشرية · المؤشرات'!C7</f>
         <v/>
       </c>
       <c r="D118" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X16</f>
+        <f>'الموارد البشرية · المؤشرات'!X7</f>
         <v/>
       </c>
       <c r="E118" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y16</f>
+        <f>'الموارد البشرية · المؤشرات'!Y7</f>
         <v/>
       </c>
       <c r="F118" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V16</f>
+        <f>'الموارد البشرية · المؤشرات'!V7</f>
         <v/>
       </c>
       <c r="G118" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W16</f>
+        <f>'الموارد البشرية · المؤشرات'!W7</f>
         <v/>
       </c>
       <c r="H118" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH16</f>
+        <f>'الموارد البشرية · المؤشرات'!AH7</f>
         <v/>
       </c>
     </row>
@@ -40988,31 +38633,31 @@
       </c>
       <c r="B119" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C119" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C17</f>
+        <f>'الموارد البشرية · المؤشرات'!C8</f>
         <v/>
       </c>
       <c r="D119" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X17</f>
+        <f>'الموارد البشرية · المؤشرات'!X8</f>
         <v/>
       </c>
       <c r="E119" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y17</f>
+        <f>'الموارد البشرية · المؤشرات'!Y8</f>
         <v/>
       </c>
       <c r="F119" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V17</f>
+        <f>'الموارد البشرية · المؤشرات'!V8</f>
         <v/>
       </c>
       <c r="G119" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W17</f>
+        <f>'الموارد البشرية · المؤشرات'!W8</f>
         <v/>
       </c>
       <c r="H119" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH17</f>
+        <f>'الموارد البشرية · المؤشرات'!AH8</f>
         <v/>
       </c>
     </row>
@@ -41022,31 +38667,31 @@
       </c>
       <c r="B120" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C120" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C18</f>
+        <f>'الموارد البشرية · المؤشرات'!C9</f>
         <v/>
       </c>
       <c r="D120" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X18</f>
+        <f>'الموارد البشرية · المؤشرات'!X9</f>
         <v/>
       </c>
       <c r="E120" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y18</f>
+        <f>'الموارد البشرية · المؤشرات'!Y9</f>
         <v/>
       </c>
       <c r="F120" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V18</f>
+        <f>'الموارد البشرية · المؤشرات'!V9</f>
         <v/>
       </c>
       <c r="G120" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W18</f>
+        <f>'الموارد البشرية · المؤشرات'!W9</f>
         <v/>
       </c>
       <c r="H120" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH18</f>
+        <f>'الموارد البشرية · المؤشرات'!AH9</f>
         <v/>
       </c>
     </row>
@@ -41056,31 +38701,31 @@
       </c>
       <c r="B121" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C121" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C19</f>
+        <f>'الموارد البشرية · المؤشرات'!C10</f>
         <v/>
       </c>
       <c r="D121" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X19</f>
+        <f>'الموارد البشرية · المؤشرات'!X10</f>
         <v/>
       </c>
       <c r="E121" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y19</f>
+        <f>'الموارد البشرية · المؤشرات'!Y10</f>
         <v/>
       </c>
       <c r="F121" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V19</f>
+        <f>'الموارد البشرية · المؤشرات'!V10</f>
         <v/>
       </c>
       <c r="G121" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W19</f>
+        <f>'الموارد البشرية · المؤشرات'!W10</f>
         <v/>
       </c>
       <c r="H121" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH19</f>
+        <f>'الموارد البشرية · المؤشرات'!AH10</f>
         <v/>
       </c>
     </row>
@@ -41090,31 +38735,31 @@
       </c>
       <c r="B122" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C122" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C20</f>
+        <f>'الموارد البشرية · المؤشرات'!C11</f>
         <v/>
       </c>
       <c r="D122" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X20</f>
+        <f>'الموارد البشرية · المؤشرات'!X11</f>
         <v/>
       </c>
       <c r="E122" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y20</f>
+        <f>'الموارد البشرية · المؤشرات'!Y11</f>
         <v/>
       </c>
       <c r="F122" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V20</f>
+        <f>'الموارد البشرية · المؤشرات'!V11</f>
         <v/>
       </c>
       <c r="G122" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W20</f>
+        <f>'الموارد البشرية · المؤشرات'!W11</f>
         <v/>
       </c>
       <c r="H122" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH20</f>
+        <f>'الموارد البشرية · المؤشرات'!AH11</f>
         <v/>
       </c>
     </row>
@@ -41124,31 +38769,31 @@
       </c>
       <c r="B123" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C123" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C21</f>
+        <f>'الموارد البشرية · المؤشرات'!C12</f>
         <v/>
       </c>
       <c r="D123" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X21</f>
+        <f>'الموارد البشرية · المؤشرات'!X12</f>
         <v/>
       </c>
       <c r="E123" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y21</f>
+        <f>'الموارد البشرية · المؤشرات'!Y12</f>
         <v/>
       </c>
       <c r="F123" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V21</f>
+        <f>'الموارد البشرية · المؤشرات'!V12</f>
         <v/>
       </c>
       <c r="G123" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W21</f>
+        <f>'الموارد البشرية · المؤشرات'!W12</f>
         <v/>
       </c>
       <c r="H123" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH21</f>
+        <f>'الموارد البشرية · المؤشرات'!AH12</f>
         <v/>
       </c>
     </row>
@@ -41158,31 +38803,31 @@
       </c>
       <c r="B124" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C124" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C22</f>
+        <f>'الموارد البشرية · المؤشرات'!C13</f>
         <v/>
       </c>
       <c r="D124" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X22</f>
+        <f>'الموارد البشرية · المؤشرات'!X13</f>
         <v/>
       </c>
       <c r="E124" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y22</f>
+        <f>'الموارد البشرية · المؤشرات'!Y13</f>
         <v/>
       </c>
       <c r="F124" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V22</f>
+        <f>'الموارد البشرية · المؤشرات'!V13</f>
         <v/>
       </c>
       <c r="G124" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W22</f>
+        <f>'الموارد البشرية · المؤشرات'!W13</f>
         <v/>
       </c>
       <c r="H124" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH22</f>
+        <f>'الموارد البشرية · المؤشرات'!AH13</f>
         <v/>
       </c>
     </row>
@@ -41192,31 +38837,31 @@
       </c>
       <c r="B125" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C125" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C23</f>
+        <f>'الموارد البشرية · المؤشرات'!C14</f>
         <v/>
       </c>
       <c r="D125" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X23</f>
+        <f>'الموارد البشرية · المؤشرات'!X14</f>
         <v/>
       </c>
       <c r="E125" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y23</f>
+        <f>'الموارد البشرية · المؤشرات'!Y14</f>
         <v/>
       </c>
       <c r="F125" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V23</f>
+        <f>'الموارد البشرية · المؤشرات'!V14</f>
         <v/>
       </c>
       <c r="G125" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W23</f>
+        <f>'الموارد البشرية · المؤشرات'!W14</f>
         <v/>
       </c>
       <c r="H125" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH23</f>
+        <f>'الموارد البشرية · المؤشرات'!AH14</f>
         <v/>
       </c>
     </row>
@@ -41226,31 +38871,31 @@
       </c>
       <c r="B126" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C126" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C24</f>
+        <f>'الموارد البشرية · المؤشرات'!C15</f>
         <v/>
       </c>
       <c r="D126" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X24</f>
+        <f>'الموارد البشرية · المؤشرات'!X15</f>
         <v/>
       </c>
       <c r="E126" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y24</f>
+        <f>'الموارد البشرية · المؤشرات'!Y15</f>
         <v/>
       </c>
       <c r="F126" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V24</f>
+        <f>'الموارد البشرية · المؤشرات'!V15</f>
         <v/>
       </c>
       <c r="G126" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W24</f>
+        <f>'الموارد البشرية · المؤشرات'!W15</f>
         <v/>
       </c>
       <c r="H126" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH24</f>
+        <f>'الموارد البشرية · المؤشرات'!AH15</f>
         <v/>
       </c>
     </row>
@@ -41260,31 +38905,31 @@
       </c>
       <c r="B127" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C127" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C25</f>
+        <f>'الموارد البشرية · المؤشرات'!C16</f>
         <v/>
       </c>
       <c r="D127" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X25</f>
+        <f>'الموارد البشرية · المؤشرات'!X16</f>
         <v/>
       </c>
       <c r="E127" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y25</f>
+        <f>'الموارد البشرية · المؤشرات'!Y16</f>
         <v/>
       </c>
       <c r="F127" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V25</f>
+        <f>'الموارد البشرية · المؤشرات'!V16</f>
         <v/>
       </c>
       <c r="G127" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W25</f>
+        <f>'الموارد البشرية · المؤشرات'!W16</f>
         <v/>
       </c>
       <c r="H127" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH25</f>
+        <f>'الموارد البشرية · المؤشرات'!AH16</f>
         <v/>
       </c>
     </row>
@@ -41294,31 +38939,31 @@
       </c>
       <c r="B128" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C128" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C26</f>
+        <f>'الموارد البشرية · المؤشرات'!C17</f>
         <v/>
       </c>
       <c r="D128" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X26</f>
+        <f>'الموارد البشرية · المؤشرات'!X17</f>
         <v/>
       </c>
       <c r="E128" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y26</f>
+        <f>'الموارد البشرية · المؤشرات'!Y17</f>
         <v/>
       </c>
       <c r="F128" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V26</f>
+        <f>'الموارد البشرية · المؤشرات'!V17</f>
         <v/>
       </c>
       <c r="G128" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W26</f>
+        <f>'الموارد البشرية · المؤشرات'!W17</f>
         <v/>
       </c>
       <c r="H128" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH26</f>
+        <f>'الموارد البشرية · المؤشرات'!AH17</f>
         <v/>
       </c>
     </row>
@@ -41328,31 +38973,31 @@
       </c>
       <c r="B129" s="91" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C129" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!C27</f>
+        <f>'الموارد البشرية · المؤشرات'!C18</f>
         <v/>
       </c>
       <c r="D129" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!X27</f>
+        <f>'الموارد البشرية · المؤشرات'!X18</f>
         <v/>
       </c>
       <c r="E129" s="91">
-        <f>'التقنية الرقمية · المؤشرات'!Y27</f>
+        <f>'الموارد البشرية · المؤشرات'!Y18</f>
         <v/>
       </c>
       <c r="F129" s="93">
-        <f>'التقنية الرقمية · المؤشرات'!V27</f>
+        <f>'الموارد البشرية · المؤشرات'!V18</f>
         <v/>
       </c>
       <c r="G129" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!W27</f>
+        <f>'الموارد البشرية · المؤشرات'!W18</f>
         <v/>
       </c>
       <c r="H129" s="68">
-        <f>'التقنية الرقمية · المؤشرات'!AH27</f>
+        <f>'الموارد البشرية · المؤشرات'!AH18</f>
         <v/>
       </c>
     </row>
@@ -41366,27 +39011,27 @@
         </is>
       </c>
       <c r="C130" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C4</f>
+        <f>'الموارد البشرية · المؤشرات'!C19</f>
         <v/>
       </c>
       <c r="D130" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X4</f>
+        <f>'الموارد البشرية · المؤشرات'!X19</f>
         <v/>
       </c>
       <c r="E130" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y4</f>
+        <f>'الموارد البشرية · المؤشرات'!Y19</f>
         <v/>
       </c>
       <c r="F130" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V4</f>
+        <f>'الموارد البشرية · المؤشرات'!V19</f>
         <v/>
       </c>
       <c r="G130" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W4</f>
+        <f>'الموارد البشرية · المؤشرات'!W19</f>
         <v/>
       </c>
       <c r="H130" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH4</f>
+        <f>'الموارد البشرية · المؤشرات'!AH19</f>
         <v/>
       </c>
     </row>
@@ -41400,27 +39045,27 @@
         </is>
       </c>
       <c r="C131" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C5</f>
+        <f>'الموارد البشرية · المؤشرات'!C20</f>
         <v/>
       </c>
       <c r="D131" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X5</f>
+        <f>'الموارد البشرية · المؤشرات'!X20</f>
         <v/>
       </c>
       <c r="E131" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y5</f>
+        <f>'الموارد البشرية · المؤشرات'!Y20</f>
         <v/>
       </c>
       <c r="F131" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V5</f>
+        <f>'الموارد البشرية · المؤشرات'!V20</f>
         <v/>
       </c>
       <c r="G131" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W5</f>
+        <f>'الموارد البشرية · المؤشرات'!W20</f>
         <v/>
       </c>
       <c r="H131" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH5</f>
+        <f>'الموارد البشرية · المؤشرات'!AH20</f>
         <v/>
       </c>
     </row>
@@ -41430,31 +39075,31 @@
       </c>
       <c r="B132" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C132" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C6</f>
+        <f>'التسويق · المؤشرات'!C4</f>
         <v/>
       </c>
       <c r="D132" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X6</f>
+        <f>'التسويق · المؤشرات'!X4</f>
         <v/>
       </c>
       <c r="E132" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y6</f>
+        <f>'التسويق · المؤشرات'!Y4</f>
         <v/>
       </c>
       <c r="F132" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V6</f>
+        <f>'التسويق · المؤشرات'!V4</f>
         <v/>
       </c>
       <c r="G132" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W6</f>
+        <f>'التسويق · المؤشرات'!W4</f>
         <v/>
       </c>
       <c r="H132" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH6</f>
+        <f>'التسويق · المؤشرات'!AH4</f>
         <v/>
       </c>
     </row>
@@ -41464,31 +39109,31 @@
       </c>
       <c r="B133" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C133" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C7</f>
+        <f>'التسويق · المؤشرات'!C5</f>
         <v/>
       </c>
       <c r="D133" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X7</f>
+        <f>'التسويق · المؤشرات'!X5</f>
         <v/>
       </c>
       <c r="E133" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y7</f>
+        <f>'التسويق · المؤشرات'!Y5</f>
         <v/>
       </c>
       <c r="F133" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V7</f>
+        <f>'التسويق · المؤشرات'!V5</f>
         <v/>
       </c>
       <c r="G133" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W7</f>
+        <f>'التسويق · المؤشرات'!W5</f>
         <v/>
       </c>
       <c r="H133" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH7</f>
+        <f>'التسويق · المؤشرات'!AH5</f>
         <v/>
       </c>
     </row>
@@ -41498,31 +39143,31 @@
       </c>
       <c r="B134" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C134" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C8</f>
+        <f>'التسويق · المؤشرات'!C6</f>
         <v/>
       </c>
       <c r="D134" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X8</f>
+        <f>'التسويق · المؤشرات'!X6</f>
         <v/>
       </c>
       <c r="E134" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y8</f>
+        <f>'التسويق · المؤشرات'!Y6</f>
         <v/>
       </c>
       <c r="F134" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V8</f>
+        <f>'التسويق · المؤشرات'!V6</f>
         <v/>
       </c>
       <c r="G134" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W8</f>
+        <f>'التسويق · المؤشرات'!W6</f>
         <v/>
       </c>
       <c r="H134" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH8</f>
+        <f>'التسويق · المؤشرات'!AH6</f>
         <v/>
       </c>
     </row>
@@ -41532,31 +39177,31 @@
       </c>
       <c r="B135" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C135" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C9</f>
+        <f>'التسويق · المؤشرات'!C7</f>
         <v/>
       </c>
       <c r="D135" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X9</f>
+        <f>'التسويق · المؤشرات'!X7</f>
         <v/>
       </c>
       <c r="E135" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y9</f>
+        <f>'التسويق · المؤشرات'!Y7</f>
         <v/>
       </c>
       <c r="F135" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V9</f>
+        <f>'التسويق · المؤشرات'!V7</f>
         <v/>
       </c>
       <c r="G135" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W9</f>
+        <f>'التسويق · المؤشرات'!W7</f>
         <v/>
       </c>
       <c r="H135" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH9</f>
+        <f>'التسويق · المؤشرات'!AH7</f>
         <v/>
       </c>
     </row>
@@ -41566,31 +39211,31 @@
       </c>
       <c r="B136" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C136" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C10</f>
+        <f>'التسويق · المؤشرات'!C8</f>
         <v/>
       </c>
       <c r="D136" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X10</f>
+        <f>'التسويق · المؤشرات'!X8</f>
         <v/>
       </c>
       <c r="E136" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y10</f>
+        <f>'التسويق · المؤشرات'!Y8</f>
         <v/>
       </c>
       <c r="F136" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V10</f>
+        <f>'التسويق · المؤشرات'!V8</f>
         <v/>
       </c>
       <c r="G136" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W10</f>
+        <f>'التسويق · المؤشرات'!W8</f>
         <v/>
       </c>
       <c r="H136" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH10</f>
+        <f>'التسويق · المؤشرات'!AH8</f>
         <v/>
       </c>
     </row>
@@ -41600,31 +39245,31 @@
       </c>
       <c r="B137" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C137" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C11</f>
+        <f>'التسويق · المؤشرات'!C9</f>
         <v/>
       </c>
       <c r="D137" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X11</f>
+        <f>'التسويق · المؤشرات'!X9</f>
         <v/>
       </c>
       <c r="E137" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y11</f>
+        <f>'التسويق · المؤشرات'!Y9</f>
         <v/>
       </c>
       <c r="F137" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V11</f>
+        <f>'التسويق · المؤشرات'!V9</f>
         <v/>
       </c>
       <c r="G137" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W11</f>
+        <f>'التسويق · المؤشرات'!W9</f>
         <v/>
       </c>
       <c r="H137" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH11</f>
+        <f>'التسويق · المؤشرات'!AH9</f>
         <v/>
       </c>
     </row>
@@ -41634,31 +39279,31 @@
       </c>
       <c r="B138" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C138" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C12</f>
+        <f>'التسويق · المؤشرات'!C10</f>
         <v/>
       </c>
       <c r="D138" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X12</f>
+        <f>'التسويق · المؤشرات'!X10</f>
         <v/>
       </c>
       <c r="E138" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y12</f>
+        <f>'التسويق · المؤشرات'!Y10</f>
         <v/>
       </c>
       <c r="F138" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V12</f>
+        <f>'التسويق · المؤشرات'!V10</f>
         <v/>
       </c>
       <c r="G138" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W12</f>
+        <f>'التسويق · المؤشرات'!W10</f>
         <v/>
       </c>
       <c r="H138" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH12</f>
+        <f>'التسويق · المؤشرات'!AH10</f>
         <v/>
       </c>
     </row>
@@ -41668,31 +39313,31 @@
       </c>
       <c r="B139" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C139" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C13</f>
+        <f>'التسويق · المؤشرات'!C11</f>
         <v/>
       </c>
       <c r="D139" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X13</f>
+        <f>'التسويق · المؤشرات'!X11</f>
         <v/>
       </c>
       <c r="E139" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y13</f>
+        <f>'التسويق · المؤشرات'!Y11</f>
         <v/>
       </c>
       <c r="F139" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V13</f>
+        <f>'التسويق · المؤشرات'!V11</f>
         <v/>
       </c>
       <c r="G139" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W13</f>
+        <f>'التسويق · المؤشرات'!W11</f>
         <v/>
       </c>
       <c r="H139" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH13</f>
+        <f>'التسويق · المؤشرات'!AH11</f>
         <v/>
       </c>
     </row>
@@ -41702,31 +39347,31 @@
       </c>
       <c r="B140" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C140" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C14</f>
+        <f>'التسويق · المؤشرات'!C12</f>
         <v/>
       </c>
       <c r="D140" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X14</f>
+        <f>'التسويق · المؤشرات'!X12</f>
         <v/>
       </c>
       <c r="E140" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y14</f>
+        <f>'التسويق · المؤشرات'!Y12</f>
         <v/>
       </c>
       <c r="F140" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V14</f>
+        <f>'التسويق · المؤشرات'!V12</f>
         <v/>
       </c>
       <c r="G140" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W14</f>
+        <f>'التسويق · المؤشرات'!W12</f>
         <v/>
       </c>
       <c r="H140" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH14</f>
+        <f>'التسويق · المؤشرات'!AH12</f>
         <v/>
       </c>
     </row>
@@ -41736,31 +39381,31 @@
       </c>
       <c r="B141" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C141" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C15</f>
+        <f>'التسويق · المؤشرات'!C13</f>
         <v/>
       </c>
       <c r="D141" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X15</f>
+        <f>'التسويق · المؤشرات'!X13</f>
         <v/>
       </c>
       <c r="E141" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y15</f>
+        <f>'التسويق · المؤشرات'!Y13</f>
         <v/>
       </c>
       <c r="F141" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V15</f>
+        <f>'التسويق · المؤشرات'!V13</f>
         <v/>
       </c>
       <c r="G141" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W15</f>
+        <f>'التسويق · المؤشرات'!W13</f>
         <v/>
       </c>
       <c r="H141" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH15</f>
+        <f>'التسويق · المؤشرات'!AH13</f>
         <v/>
       </c>
     </row>
@@ -41770,31 +39415,31 @@
       </c>
       <c r="B142" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C142" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C16</f>
+        <f>'التسويق · المؤشرات'!C14</f>
         <v/>
       </c>
       <c r="D142" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X16</f>
+        <f>'التسويق · المؤشرات'!X14</f>
         <v/>
       </c>
       <c r="E142" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y16</f>
+        <f>'التسويق · المؤشرات'!Y14</f>
         <v/>
       </c>
       <c r="F142" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V16</f>
+        <f>'التسويق · المؤشرات'!V14</f>
         <v/>
       </c>
       <c r="G142" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W16</f>
+        <f>'التسويق · المؤشرات'!W14</f>
         <v/>
       </c>
       <c r="H142" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH16</f>
+        <f>'التسويق · المؤشرات'!AH14</f>
         <v/>
       </c>
     </row>
@@ -41804,31 +39449,31 @@
       </c>
       <c r="B143" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C143" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C17</f>
+        <f>'التسويق · المؤشرات'!C15</f>
         <v/>
       </c>
       <c r="D143" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X17</f>
+        <f>'التسويق · المؤشرات'!X15</f>
         <v/>
       </c>
       <c r="E143" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y17</f>
+        <f>'التسويق · المؤشرات'!Y15</f>
         <v/>
       </c>
       <c r="F143" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V17</f>
+        <f>'التسويق · المؤشرات'!V15</f>
         <v/>
       </c>
       <c r="G143" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W17</f>
+        <f>'التسويق · المؤشرات'!W15</f>
         <v/>
       </c>
       <c r="H143" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH17</f>
+        <f>'التسويق · المؤشرات'!AH15</f>
         <v/>
       </c>
     </row>
@@ -41838,31 +39483,31 @@
       </c>
       <c r="B144" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C144" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C18</f>
+        <f>'التسويق · المؤشرات'!C16</f>
         <v/>
       </c>
       <c r="D144" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X18</f>
+        <f>'التسويق · المؤشرات'!X16</f>
         <v/>
       </c>
       <c r="E144" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y18</f>
+        <f>'التسويق · المؤشرات'!Y16</f>
         <v/>
       </c>
       <c r="F144" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V18</f>
+        <f>'التسويق · المؤشرات'!V16</f>
         <v/>
       </c>
       <c r="G144" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W18</f>
+        <f>'التسويق · المؤشرات'!W16</f>
         <v/>
       </c>
       <c r="H144" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH18</f>
+        <f>'التسويق · المؤشرات'!AH16</f>
         <v/>
       </c>
     </row>
@@ -41872,31 +39517,31 @@
       </c>
       <c r="B145" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C145" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C19</f>
+        <f>'التسويق · المؤشرات'!C17</f>
         <v/>
       </c>
       <c r="D145" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X19</f>
+        <f>'التسويق · المؤشرات'!X17</f>
         <v/>
       </c>
       <c r="E145" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y19</f>
+        <f>'التسويق · المؤشرات'!Y17</f>
         <v/>
       </c>
       <c r="F145" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V19</f>
+        <f>'التسويق · المؤشرات'!V17</f>
         <v/>
       </c>
       <c r="G145" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W19</f>
+        <f>'التسويق · المؤشرات'!W17</f>
         <v/>
       </c>
       <c r="H145" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH19</f>
+        <f>'التسويق · المؤشرات'!AH17</f>
         <v/>
       </c>
     </row>
@@ -41906,540 +39551,30 @@
       </c>
       <c r="B146" s="91" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C146" s="91">
-        <f>'الموارد البشرية · المؤشرات'!C20</f>
+        <f>'التسويق · المؤشرات'!C18</f>
         <v/>
       </c>
       <c r="D146" s="68">
-        <f>'الموارد البشرية · المؤشرات'!X20</f>
+        <f>'التسويق · المؤشرات'!X18</f>
         <v/>
       </c>
       <c r="E146" s="91">
-        <f>'الموارد البشرية · المؤشرات'!Y20</f>
+        <f>'التسويق · المؤشرات'!Y18</f>
         <v/>
       </c>
       <c r="F146" s="93">
-        <f>'الموارد البشرية · المؤشرات'!V20</f>
+        <f>'التسويق · المؤشرات'!V18</f>
         <v/>
       </c>
       <c r="G146" s="68">
-        <f>'الموارد البشرية · المؤشرات'!W20</f>
+        <f>'التسويق · المؤشرات'!W18</f>
         <v/>
       </c>
       <c r="H146" s="68">
-        <f>'الموارد البشرية · المؤشرات'!AH20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="68" t="n">
-        <v>144</v>
-      </c>
-      <c r="B147" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C147" s="91">
-        <f>'التسويق · المؤشرات'!C4</f>
-        <v/>
-      </c>
-      <c r="D147" s="68">
-        <f>'التسويق · المؤشرات'!X4</f>
-        <v/>
-      </c>
-      <c r="E147" s="91">
-        <f>'التسويق · المؤشرات'!Y4</f>
-        <v/>
-      </c>
-      <c r="F147" s="93">
-        <f>'التسويق · المؤشرات'!V4</f>
-        <v/>
-      </c>
-      <c r="G147" s="68">
-        <f>'التسويق · المؤشرات'!W4</f>
-        <v/>
-      </c>
-      <c r="H147" s="68">
-        <f>'التسويق · المؤشرات'!AH4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="68" t="n">
-        <v>145</v>
-      </c>
-      <c r="B148" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C148" s="91">
-        <f>'التسويق · المؤشرات'!C5</f>
-        <v/>
-      </c>
-      <c r="D148" s="68">
-        <f>'التسويق · المؤشرات'!X5</f>
-        <v/>
-      </c>
-      <c r="E148" s="91">
-        <f>'التسويق · المؤشرات'!Y5</f>
-        <v/>
-      </c>
-      <c r="F148" s="93">
-        <f>'التسويق · المؤشرات'!V5</f>
-        <v/>
-      </c>
-      <c r="G148" s="68">
-        <f>'التسويق · المؤشرات'!W5</f>
-        <v/>
-      </c>
-      <c r="H148" s="68">
-        <f>'التسويق · المؤشرات'!AH5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="68" t="n">
-        <v>146</v>
-      </c>
-      <c r="B149" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C149" s="91">
-        <f>'التسويق · المؤشرات'!C6</f>
-        <v/>
-      </c>
-      <c r="D149" s="68">
-        <f>'التسويق · المؤشرات'!X6</f>
-        <v/>
-      </c>
-      <c r="E149" s="91">
-        <f>'التسويق · المؤشرات'!Y6</f>
-        <v/>
-      </c>
-      <c r="F149" s="93">
-        <f>'التسويق · المؤشرات'!V6</f>
-        <v/>
-      </c>
-      <c r="G149" s="68">
-        <f>'التسويق · المؤشرات'!W6</f>
-        <v/>
-      </c>
-      <c r="H149" s="68">
-        <f>'التسويق · المؤشرات'!AH6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="68" t="n">
-        <v>147</v>
-      </c>
-      <c r="B150" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C150" s="91">
-        <f>'التسويق · المؤشرات'!C7</f>
-        <v/>
-      </c>
-      <c r="D150" s="68">
-        <f>'التسويق · المؤشرات'!X7</f>
-        <v/>
-      </c>
-      <c r="E150" s="91">
-        <f>'التسويق · المؤشرات'!Y7</f>
-        <v/>
-      </c>
-      <c r="F150" s="93">
-        <f>'التسويق · المؤشرات'!V7</f>
-        <v/>
-      </c>
-      <c r="G150" s="68">
-        <f>'التسويق · المؤشرات'!W7</f>
-        <v/>
-      </c>
-      <c r="H150" s="68">
-        <f>'التسويق · المؤشرات'!AH7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="68" t="n">
-        <v>148</v>
-      </c>
-      <c r="B151" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C151" s="91">
-        <f>'التسويق · المؤشرات'!C8</f>
-        <v/>
-      </c>
-      <c r="D151" s="68">
-        <f>'التسويق · المؤشرات'!X8</f>
-        <v/>
-      </c>
-      <c r="E151" s="91">
-        <f>'التسويق · المؤشرات'!Y8</f>
-        <v/>
-      </c>
-      <c r="F151" s="93">
-        <f>'التسويق · المؤشرات'!V8</f>
-        <v/>
-      </c>
-      <c r="G151" s="68">
-        <f>'التسويق · المؤشرات'!W8</f>
-        <v/>
-      </c>
-      <c r="H151" s="68">
-        <f>'التسويق · المؤشرات'!AH8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="68" t="n">
-        <v>149</v>
-      </c>
-      <c r="B152" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C152" s="91">
-        <f>'التسويق · المؤشرات'!C9</f>
-        <v/>
-      </c>
-      <c r="D152" s="68">
-        <f>'التسويق · المؤشرات'!X9</f>
-        <v/>
-      </c>
-      <c r="E152" s="91">
-        <f>'التسويق · المؤشرات'!Y9</f>
-        <v/>
-      </c>
-      <c r="F152" s="93">
-        <f>'التسويق · المؤشرات'!V9</f>
-        <v/>
-      </c>
-      <c r="G152" s="68">
-        <f>'التسويق · المؤشرات'!W9</f>
-        <v/>
-      </c>
-      <c r="H152" s="68">
-        <f>'التسويق · المؤشرات'!AH9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="68" t="n">
-        <v>150</v>
-      </c>
-      <c r="B153" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C153" s="91">
-        <f>'التسويق · المؤشرات'!C10</f>
-        <v/>
-      </c>
-      <c r="D153" s="68">
-        <f>'التسويق · المؤشرات'!X10</f>
-        <v/>
-      </c>
-      <c r="E153" s="91">
-        <f>'التسويق · المؤشرات'!Y10</f>
-        <v/>
-      </c>
-      <c r="F153" s="93">
-        <f>'التسويق · المؤشرات'!V10</f>
-        <v/>
-      </c>
-      <c r="G153" s="68">
-        <f>'التسويق · المؤشرات'!W10</f>
-        <v/>
-      </c>
-      <c r="H153" s="68">
-        <f>'التسويق · المؤشرات'!AH10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="68" t="n">
-        <v>151</v>
-      </c>
-      <c r="B154" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C154" s="91">
-        <f>'التسويق · المؤشرات'!C11</f>
-        <v/>
-      </c>
-      <c r="D154" s="68">
-        <f>'التسويق · المؤشرات'!X11</f>
-        <v/>
-      </c>
-      <c r="E154" s="91">
-        <f>'التسويق · المؤشرات'!Y11</f>
-        <v/>
-      </c>
-      <c r="F154" s="93">
-        <f>'التسويق · المؤشرات'!V11</f>
-        <v/>
-      </c>
-      <c r="G154" s="68">
-        <f>'التسويق · المؤشرات'!W11</f>
-        <v/>
-      </c>
-      <c r="H154" s="68">
-        <f>'التسويق · المؤشرات'!AH11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="68" t="n">
-        <v>152</v>
-      </c>
-      <c r="B155" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C155" s="91">
-        <f>'التسويق · المؤشرات'!C12</f>
-        <v/>
-      </c>
-      <c r="D155" s="68">
-        <f>'التسويق · المؤشرات'!X12</f>
-        <v/>
-      </c>
-      <c r="E155" s="91">
-        <f>'التسويق · المؤشرات'!Y12</f>
-        <v/>
-      </c>
-      <c r="F155" s="93">
-        <f>'التسويق · المؤشرات'!V12</f>
-        <v/>
-      </c>
-      <c r="G155" s="68">
-        <f>'التسويق · المؤشرات'!W12</f>
-        <v/>
-      </c>
-      <c r="H155" s="68">
-        <f>'التسويق · المؤشرات'!AH12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="68" t="n">
-        <v>153</v>
-      </c>
-      <c r="B156" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C156" s="91">
-        <f>'التسويق · المؤشرات'!C13</f>
-        <v/>
-      </c>
-      <c r="D156" s="68">
-        <f>'التسويق · المؤشرات'!X13</f>
-        <v/>
-      </c>
-      <c r="E156" s="91">
-        <f>'التسويق · المؤشرات'!Y13</f>
-        <v/>
-      </c>
-      <c r="F156" s="93">
-        <f>'التسويق · المؤشرات'!V13</f>
-        <v/>
-      </c>
-      <c r="G156" s="68">
-        <f>'التسويق · المؤشرات'!W13</f>
-        <v/>
-      </c>
-      <c r="H156" s="68">
-        <f>'التسويق · المؤشرات'!AH13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="68" t="n">
-        <v>154</v>
-      </c>
-      <c r="B157" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C157" s="91">
-        <f>'التسويق · المؤشرات'!C14</f>
-        <v/>
-      </c>
-      <c r="D157" s="68">
-        <f>'التسويق · المؤشرات'!X14</f>
-        <v/>
-      </c>
-      <c r="E157" s="91">
-        <f>'التسويق · المؤشرات'!Y14</f>
-        <v/>
-      </c>
-      <c r="F157" s="93">
-        <f>'التسويق · المؤشرات'!V14</f>
-        <v/>
-      </c>
-      <c r="G157" s="68">
-        <f>'التسويق · المؤشرات'!W14</f>
-        <v/>
-      </c>
-      <c r="H157" s="68">
-        <f>'التسويق · المؤشرات'!AH14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="68" t="n">
-        <v>155</v>
-      </c>
-      <c r="B158" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C158" s="91">
-        <f>'التسويق · المؤشرات'!C15</f>
-        <v/>
-      </c>
-      <c r="D158" s="68">
-        <f>'التسويق · المؤشرات'!X15</f>
-        <v/>
-      </c>
-      <c r="E158" s="91">
-        <f>'التسويق · المؤشرات'!Y15</f>
-        <v/>
-      </c>
-      <c r="F158" s="93">
-        <f>'التسويق · المؤشرات'!V15</f>
-        <v/>
-      </c>
-      <c r="G158" s="68">
-        <f>'التسويق · المؤشرات'!W15</f>
-        <v/>
-      </c>
-      <c r="H158" s="68">
-        <f>'التسويق · المؤشرات'!AH15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="68" t="n">
-        <v>156</v>
-      </c>
-      <c r="B159" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C159" s="91">
-        <f>'التسويق · المؤشرات'!C16</f>
-        <v/>
-      </c>
-      <c r="D159" s="68">
-        <f>'التسويق · المؤشرات'!X16</f>
-        <v/>
-      </c>
-      <c r="E159" s="91">
-        <f>'التسويق · المؤشرات'!Y16</f>
-        <v/>
-      </c>
-      <c r="F159" s="93">
-        <f>'التسويق · المؤشرات'!V16</f>
-        <v/>
-      </c>
-      <c r="G159" s="68">
-        <f>'التسويق · المؤشرات'!W16</f>
-        <v/>
-      </c>
-      <c r="H159" s="68">
-        <f>'التسويق · المؤشرات'!AH16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="68" t="n">
-        <v>157</v>
-      </c>
-      <c r="B160" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C160" s="91">
-        <f>'التسويق · المؤشرات'!C17</f>
-        <v/>
-      </c>
-      <c r="D160" s="68">
-        <f>'التسويق · المؤشرات'!X17</f>
-        <v/>
-      </c>
-      <c r="E160" s="91">
-        <f>'التسويق · المؤشرات'!Y17</f>
-        <v/>
-      </c>
-      <c r="F160" s="93">
-        <f>'التسويق · المؤشرات'!V17</f>
-        <v/>
-      </c>
-      <c r="G160" s="68">
-        <f>'التسويق · المؤشرات'!W17</f>
-        <v/>
-      </c>
-      <c r="H160" s="68">
-        <f>'التسويق · المؤشرات'!AH17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="68" t="n">
-        <v>158</v>
-      </c>
-      <c r="B161" s="91" t="inlineStr">
-        <is>
-          <t>التسويق</t>
-        </is>
-      </c>
-      <c r="C161" s="91">
-        <f>'التسويق · المؤشرات'!C18</f>
-        <v/>
-      </c>
-      <c r="D161" s="68">
-        <f>'التسويق · المؤشرات'!X18</f>
-        <v/>
-      </c>
-      <c r="E161" s="91">
-        <f>'التسويق · المؤشرات'!Y18</f>
-        <v/>
-      </c>
-      <c r="F161" s="93">
-        <f>'التسويق · المؤشرات'!V18</f>
-        <v/>
-      </c>
-      <c r="G161" s="68">
-        <f>'التسويق · المؤشرات'!W18</f>
-        <v/>
-      </c>
-      <c r="H161" s="68">
         <f>'التسويق · المؤشرات'!AH18</f>
         <v/>
       </c>
@@ -44366,11 +41501,11 @@
         </is>
       </c>
       <c r="C5" s="25">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$H$4:$H$161,"مالي"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$H$4:$H$146,"مالي"),"—")</f>
         <v/>
       </c>
       <c r="D5" s="26">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$161,"مالي")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$146,"مالي")</f>
         <v/>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -44386,11 +41521,11 @@
         </is>
       </c>
       <c r="C6" s="25">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$H$4:$H$161,"العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$H$4:$H$146,"العملاء"),"—")</f>
         <v/>
       </c>
       <c r="D6" s="26">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$161,"العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$146,"العملاء")</f>
         <v/>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -44406,11 +41541,11 @@
         </is>
       </c>
       <c r="C7" s="25">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$H$4:$H$161,"العمليات الداخلية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$H$4:$H$146,"العمليات الداخلية"),"—")</f>
         <v/>
       </c>
       <c r="D7" s="26">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$161,"العمليات الداخلية")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$146,"العمليات الداخلية")</f>
         <v/>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -44426,11 +41561,11 @@
         </is>
       </c>
       <c r="C8" s="25">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$H$4:$H$161,"التعلّم والنمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$H$4:$H$146,"التعلّم والنمو"),"—")</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$161,"التعلّم والنمو")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$4:$H$146,"التعلّم والنمو")</f>
         <v/>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -44556,7 +41691,7 @@
         </is>
       </c>
       <c r="G4" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"التوسع في المواقع")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"التوسع في المواقع"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$146,"التوسع في المواقع")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$E$4:$E$146,"التوسع في المواقع"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44585,7 +41720,7 @@
         </is>
       </c>
       <c r="G5" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"الامتياز التجاري")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"الامتياز التجاري"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$146,"الامتياز التجاري")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$E$4:$E$146,"الامتياز التجاري"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44614,7 +41749,7 @@
         </is>
       </c>
       <c r="G6" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"زيادة وصول العملاء")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"زيادة وصول العملاء"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$146,"زيادة وصول العملاء")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$E$4:$E$146,"زيادة وصول العملاء"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44648,7 +41783,7 @@
         </is>
       </c>
       <c r="G7" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"إطلاق مشاريع جديدة")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"إطلاق مشاريع جديدة"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$146,"إطلاق مشاريع جديدة")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$E$4:$E$146,"إطلاق مشاريع جديدة"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44677,7 +41812,7 @@
         </is>
       </c>
       <c r="G8" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"تطوير التصاميم والهوية")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"تطوير التصاميم والهوية"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$146,"تطوير التصاميم والهوية")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$E$4:$E$146,"تطوير التصاميم والهوية"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44706,7 +41841,7 @@
         </is>
       </c>
       <c r="G9" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"التحول التقني")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"التحول التقني"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$146,"التحول التقني")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$E$4:$E$146,"التحول التقني"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44735,7 +41870,7 @@
         </is>
       </c>
       <c r="G10" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"ساحات درب")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"ساحات درب"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$146,"ساحات درب")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$E$4:$E$146,"ساحات درب"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44764,7 +41899,7 @@
         </is>
       </c>
       <c r="G11" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"تطبيق «تانكي»")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"تطبيق «تانكي»"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$146,"تطبيق «تانكي»")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$E$4:$E$146,"تطبيق «تانكي»"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44798,7 +41933,7 @@
         </is>
       </c>
       <c r="G12" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"تعزيز تجربة العملاء")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"تعزيز تجربة العملاء"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$146,"تعزيز تجربة العملاء")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$E$4:$E$146,"تعزيز تجربة العملاء"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44827,7 +41962,7 @@
         </is>
       </c>
       <c r="G13" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"جودة التشغيل")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"جودة التشغيل"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$146,"جودة التشغيل")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$E$4:$E$146,"جودة التشغيل"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44856,7 +41991,7 @@
         </is>
       </c>
       <c r="G14" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"منظومة التأجير")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"منظومة التأجير"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$146,"منظومة التأجير")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$E$4:$E$146,"منظومة التأجير"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -44885,7 +42020,7 @@
         </is>
       </c>
       <c r="G15" s="33">
-        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$161,"الاستثمار في الموظفين")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$E$4:$E$161,"الاستثمار في الموظفين"),"—"))</f>
+        <f>IF(COUNTIFS('قاعدة المؤشرات'!$E$4:$E$146,"الاستثمار في الموظفين")=0,"—",IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$E$4:$E$146,"الاستثمار في الموظفين"),"—"))</f>
         <v/>
       </c>
     </row>
@@ -45007,19 +42142,19 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="44">
-        <f>IFERROR(AVERAGE('قاعدة المؤشرات'!$F$4:$F$161),0)</f>
+        <f>IFERROR(AVERAGE('قاعدة المؤشرات'!$F$4:$F$146),0)</f>
         <v/>
       </c>
       <c r="D5" s="45">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"✅ محقق")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$146,"✅ محقق")</f>
         <v/>
       </c>
       <c r="E5" s="45">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"🟡 قريب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$146,"🟡 قريب")</f>
         <v/>
       </c>
       <c r="F5" s="45">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"🔴 تحت الهدف")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$146,"🔴 تحت الهدف")</f>
         <v/>
       </c>
       <c r="H5" s="46" t="inlineStr">
@@ -45048,7 +42183,7 @@
         </is>
       </c>
       <c r="I6" s="33">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$D$4:$D$161,"النمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$D$4:$D$146,"النمو"),"—")</f>
         <v/>
       </c>
       <c r="J6" s="49">
@@ -45063,7 +42198,7 @@
         </is>
       </c>
       <c r="I7" s="33">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$D$4:$D$161,"الابتكار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$D$4:$D$146,"الابتكار"),"—")</f>
         <v/>
       </c>
       <c r="J7" s="49">
@@ -45078,7 +42213,7 @@
         </is>
       </c>
       <c r="I8" s="33">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$D$4:$D$161,"الاستدامة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$D$4:$D$146,"الاستدامة"),"—")</f>
         <v/>
       </c>
       <c r="J8" s="49">
@@ -45119,7 +42254,7 @@
         </is>
       </c>
       <c r="C11" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"الإدارة التنفيذية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$B$4:$B$146,"الإدارة التنفيذية"),"—")</f>
         <v/>
       </c>
       <c r="D11" s="17">
@@ -45134,7 +42269,7 @@
         </is>
       </c>
       <c r="C12" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"الامتياز التجاري"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$B$4:$B$146,"الامتياز التجاري"),"—")</f>
         <v/>
       </c>
       <c r="D12" s="17">
@@ -45149,7 +42284,7 @@
         </is>
       </c>
       <c r="C13" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"التشغيل والمحطات"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$B$4:$B$146,"التشغيل والمحطات"),"—")</f>
         <v/>
       </c>
       <c r="D13" s="17">
@@ -45164,7 +42299,7 @@
         </is>
       </c>
       <c r="C14" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"الاستثمار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$B$4:$B$146,"الاستثمار"),"—")</f>
         <v/>
       </c>
       <c r="D14" s="17">
@@ -45179,7 +42314,7 @@
         </is>
       </c>
       <c r="C15" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"العقار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$B$4:$B$146,"العقار"),"—")</f>
         <v/>
       </c>
       <c r="D15" s="17">
@@ -45194,7 +42329,7 @@
         </is>
       </c>
       <c r="C16" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"التقنية الرقمية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$B$4:$B$146,"التقنية الرقمية"),"—")</f>
         <v/>
       </c>
       <c r="D16" s="17">
@@ -45209,7 +42344,7 @@
         </is>
       </c>
       <c r="C17" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"الموارد البشرية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$B$4:$B$146,"الموارد البشرية"),"—")</f>
         <v/>
       </c>
       <c r="D17" s="17">
@@ -45224,7 +42359,7 @@
         </is>
       </c>
       <c r="C18" s="23">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$161,'قاعدة المؤشرات'!$B$4:$B$161,"التسويق"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$F$4:$F$146,'قاعدة المؤشرات'!$B$4:$B$146,"التسويق"),"—")</f>
         <v/>
       </c>
       <c r="D18" s="17">
@@ -45261,7 +42396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -45631,11 +42766,31 @@
       <c r="A11" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="51" t="n"/>
-      <c r="C11" s="38" t="n"/>
-      <c r="D11" s="51" t="n"/>
-      <c r="E11" s="51" t="n"/>
-      <c r="F11" s="38" t="n"/>
+      <c r="B11" s="51" t="inlineStr">
+        <is>
+          <t>نظام أتمتة الكاش (Cash-In)  (59/164 محطة · 36%)</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="E11" s="51" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+      <c r="F11" s="38" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
       <c r="G11" s="38" t="n"/>
       <c r="H11" s="38" t="n"/>
       <c r="I11" s="52" t="n"/>
@@ -45650,11 +42805,31 @@
       <c r="A12" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="51" t="n"/>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="51" t="n"/>
-      <c r="E12" s="51" t="n"/>
-      <c r="F12" s="38" t="n"/>
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t>D365 FNO — المرحلة الأولى  (3.5/5 وحدة · 70%)</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="E12" s="51" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+      <c r="F12" s="38" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
       <c r="G12" s="38" t="n"/>
       <c r="H12" s="38" t="n"/>
       <c r="I12" s="52" t="n"/>
@@ -45669,11 +42844,31 @@
       <c r="A13" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="51" t="n"/>
-      <c r="C13" s="38" t="n"/>
-      <c r="D13" s="51" t="n"/>
-      <c r="E13" s="51" t="n"/>
-      <c r="F13" s="38" t="n"/>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>D365 FNO — المرحلة الثانية  (0/4 وحدة · 0%)</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="E13" s="51" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+      <c r="F13" s="38" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
       <c r="G13" s="38" t="n"/>
       <c r="H13" s="38" t="n"/>
       <c r="I13" s="52" t="n"/>
@@ -45688,11 +42883,31 @@
       <c r="A14" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="51" t="n"/>
-      <c r="C14" s="38" t="n"/>
-      <c r="D14" s="51" t="n"/>
-      <c r="E14" s="51" t="n"/>
-      <c r="F14" s="38" t="n"/>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t>D365 FNO — المرحلة الثالثة  (0/2 وحدة · 0%)</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="E14" s="51" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+      <c r="F14" s="38" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
       <c r="G14" s="38" t="n"/>
       <c r="H14" s="38" t="n"/>
       <c r="I14" s="52" t="n"/>
@@ -45707,11 +42922,31 @@
       <c r="A15" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="51" t="n"/>
-      <c r="C15" s="38" t="n"/>
-      <c r="D15" s="51" t="n"/>
-      <c r="E15" s="51" t="n"/>
-      <c r="F15" s="38" t="n"/>
+      <c r="B15" s="51" t="inlineStr">
+        <is>
+          <t>تطبيق الامتياز مع واثق  (0/1 تطبيق · 0%)</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="E15" s="51" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+      <c r="F15" s="38" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
       <c r="G15" s="38" t="n"/>
       <c r="H15" s="38" t="n"/>
       <c r="I15" s="52" t="n"/>
@@ -45726,11 +42961,31 @@
       <c r="A16" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="51" t="n"/>
-      <c r="C16" s="38" t="n"/>
-      <c r="D16" s="51" t="n"/>
-      <c r="E16" s="51" t="n"/>
-      <c r="F16" s="38" t="n"/>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>ربط المحطات بوزارة الطاقة (ATJ)  (0/164 محطة · 0%)</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="E16" s="51" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+      <c r="F16" s="38" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
       <c r="G16" s="38" t="n"/>
       <c r="H16" s="38" t="n"/>
       <c r="I16" s="52" t="n"/>
@@ -45740,6 +42995,276 @@
         <v/>
       </c>
       <c r="L16" s="51" t="n"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="51" t="inlineStr">
+        <is>
+          <t>ربط الكاميرات بالمركز الرئيسي  (0/164 محطة · 0%)</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="E17" s="51" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+      <c r="F17" s="38" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="G17" s="38" t="n"/>
+      <c r="H17" s="38" t="n"/>
+      <c r="I17" s="52" t="n"/>
+      <c r="J17" s="53" t="n"/>
+      <c r="K17" s="17">
+        <f>IF($J17="","—",IF($J17&gt;=1,"✅ مكتملة",IF($J17&gt;0,"🟠 جارية","⚪ لم تبدأ")))</f>
+        <v/>
+      </c>
+      <c r="L17" s="51" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t>تطبيق الولاء (تانكي) في المحطات  (0/164 محطة · 0%)</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="E18" s="51" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+      <c r="F18" s="38" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="G18" s="38" t="n"/>
+      <c r="H18" s="38" t="n"/>
+      <c r="I18" s="52" t="n"/>
+      <c r="J18" s="53" t="n"/>
+      <c r="K18" s="17">
+        <f>IF($J18="","—",IF($J18&gt;=1,"✅ مكتملة",IF($J18&gt;0,"🟠 جارية","⚪ لم تبدأ")))</f>
+        <v/>
+      </c>
+      <c r="L18" s="51" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="51" t="inlineStr">
+        <is>
+          <t>منصة Tatin السحابية  (2/164 محطة · 1%)</t>
+        </is>
+      </c>
+      <c r="C19" s="38" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="D19" s="51" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="E19" s="51" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+      <c r="F19" s="38" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="52" t="n"/>
+      <c r="J19" s="53" t="n"/>
+      <c r="K19" s="17">
+        <f>IF($J19="","—",IF($J19&gt;=1,"✅ مكتملة",IF($J19&gt;0,"🟠 جارية","⚪ لم تبدأ")))</f>
+        <v/>
+      </c>
+      <c r="L19" s="51" t="n"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="51" t="inlineStr">
+        <is>
+          <t>إدارة العمليات بالذكاء الاصطناعي  (0/164 محطة · 0%)</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="E20" s="51" t="inlineStr">
+        <is>
+          <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
+        </is>
+      </c>
+      <c r="F20" s="38" t="inlineStr">
+        <is>
+          <t>إدارة التقنية</t>
+        </is>
+      </c>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="38" t="n"/>
+      <c r="I20" s="52" t="n"/>
+      <c r="J20" s="53" t="n"/>
+      <c r="K20" s="17">
+        <f>IF($J20="","—",IF($J20&gt;=1,"✅ مكتملة",IF($J20&gt;0,"🟠 جارية","⚪ لم تبدأ")))</f>
+        <v/>
+      </c>
+      <c r="L20" s="51" t="n"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="51" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="51" t="n"/>
+      <c r="E21" s="51" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="38" t="n"/>
+      <c r="H21" s="38" t="n"/>
+      <c r="I21" s="52" t="n"/>
+      <c r="J21" s="53" t="n"/>
+      <c r="K21" s="17">
+        <f>IF($J21="","—",IF($J21&gt;=1,"✅ مكتملة",IF($J21&gt;0,"🟠 جارية","⚪ لم تبدأ")))</f>
+        <v/>
+      </c>
+      <c r="L21" s="51" t="n"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="51" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="51" t="n"/>
+      <c r="E22" s="51" t="n"/>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="38" t="n"/>
+      <c r="H22" s="38" t="n"/>
+      <c r="I22" s="52" t="n"/>
+      <c r="J22" s="53" t="n"/>
+      <c r="K22" s="17">
+        <f>IF($J22="","—",IF($J22&gt;=1,"✅ مكتملة",IF($J22&gt;0,"🟠 جارية","⚪ لم تبدأ")))</f>
+        <v/>
+      </c>
+      <c r="L22" s="51" t="n"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="51" t="n"/>
+      <c r="C23" s="38" t="n"/>
+      <c r="D23" s="51" t="n"/>
+      <c r="E23" s="51" t="n"/>
+      <c r="F23" s="38" t="n"/>
+      <c r="G23" s="38" t="n"/>
+      <c r="H23" s="38" t="n"/>
+      <c r="I23" s="52" t="n"/>
+      <c r="J23" s="53" t="n"/>
+      <c r="K23" s="17">
+        <f>IF($J23="","—",IF($J23&gt;=1,"✅ مكتملة",IF($J23&gt;0,"🟠 جارية","⚪ لم تبدأ")))</f>
+        <v/>
+      </c>
+      <c r="L23" s="51" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="51" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="51" t="n"/>
+      <c r="E24" s="51" t="n"/>
+      <c r="F24" s="38" t="n"/>
+      <c r="G24" s="38" t="n"/>
+      <c r="H24" s="38" t="n"/>
+      <c r="I24" s="52" t="n"/>
+      <c r="J24" s="53" t="n"/>
+      <c r="K24" s="17">
+        <f>IF($J24="","—",IF($J24&gt;=1,"✅ مكتملة",IF($J24&gt;0,"🟠 جارية","⚪ لم تبدأ")))</f>
+        <v/>
+      </c>
+      <c r="L24" s="51" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="51" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="51" t="n"/>
+      <c r="E25" s="51" t="n"/>
+      <c r="F25" s="38" t="n"/>
+      <c r="G25" s="38" t="n"/>
+      <c r="H25" s="38" t="n"/>
+      <c r="I25" s="52" t="n"/>
+      <c r="J25" s="53" t="n"/>
+      <c r="K25" s="17">
+        <f>IF($J25="","—",IF($J25&gt;=1,"✅ مكتملة",IF($J25&gt;0,"🟠 جارية","⚪ لم تبدأ")))</f>
+        <v/>
+      </c>
+      <c r="L25" s="51" t="n"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="51" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="51" t="n"/>
+      <c r="E26" s="51" t="n"/>
+      <c r="F26" s="38" t="n"/>
+      <c r="G26" s="38" t="n"/>
+      <c r="H26" s="38" t="n"/>
+      <c r="I26" s="52" t="n"/>
+      <c r="J26" s="53" t="n"/>
+      <c r="K26" s="17">
+        <f>IF($J26="","—",IF($J26&gt;=1,"✅ مكتملة",IF($J26&gt;0,"🟠 جارية","⚪ لم تبدأ")))</f>
+        <v/>
+      </c>
+      <c r="L26" s="51" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1" password="EFFF"/>
@@ -45748,10 +43273,10 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"النمو,الابتكار,الاستدامة"</formula1>
     </dataValidation>
-    <dataValidation sqref="J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+    <dataValidation sqref="J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -46217,7 +43742,7 @@
         </is>
       </c>
       <c r="C5" s="58">
-        <f>161-3</f>
+        <f>146-3</f>
         <v/>
       </c>
     </row>
@@ -46228,7 +43753,7 @@
         </is>
       </c>
       <c r="C6" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"✅ محقق")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$146,"✅ محقق")</f>
         <v/>
       </c>
     </row>
@@ -46239,7 +43764,7 @@
         </is>
       </c>
       <c r="C7" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"🟡 قريب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$146,"🟡 قريب")</f>
         <v/>
       </c>
     </row>
@@ -46250,7 +43775,7 @@
         </is>
       </c>
       <c r="C8" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"🔴 تحت الهدف")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$146,"🔴 تحت الهدف")</f>
         <v/>
       </c>
     </row>
@@ -46261,7 +43786,7 @@
         </is>
       </c>
       <c r="C9" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$161,"—")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$G$4:$G$146,"—")</f>
         <v/>
       </c>
     </row>
@@ -46373,11 +43898,11 @@
         </is>
       </c>
       <c r="C18" s="59">
-        <f>'التقنية الرقمية · المؤشرات'!AB28</f>
+        <f>'التقنية الرقمية · المؤشرات'!AB13</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF(ROUND('التقنية الرقمية · المؤشرات'!AB28,3)=1,"✅ سليم","⚠️ يحتاج ضبط")</f>
+        <f>IF(ROUND('التقنية الرقمية · المؤشرات'!AB13,3)=1,"✅ سليم","⚠️ يحتاج ضبط")</f>
         <v/>
       </c>
     </row>
@@ -46519,11 +44044,11 @@
         </is>
       </c>
       <c r="C29" s="58">
-        <f>COUNTBLANK('التقنية الرقمية · المؤشرات'!Z4:Z27)</f>
+        <f>COUNTBLANK('التقنية الرقمية · المؤشرات'!Z4:Z12)</f>
         <v/>
       </c>
       <c r="D29" s="21">
-        <f>IF(COUNTBLANK('التقنية الرقمية · المؤشرات'!Z4:Z27)=0,"✅ مكتمل","⏳ "&amp;COUNTBLANK('التقنية الرقمية · المؤشرات'!Z4:Z27)&amp;" بانتظار")</f>
+        <f>IF(COUNTBLANK('التقنية الرقمية · المؤشرات'!Z4:Z12)=0,"✅ مكتمل","⏳ "&amp;COUNTBLANK('التقنية الرقمية · المؤشرات'!Z4:Z12)&amp;" بانتظار")</f>
         <v/>
       </c>
     </row>
@@ -46590,11 +44115,11 @@
         </is>
       </c>
       <c r="C35" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"التوسع في المواقع")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"التوسع في المواقع")</f>
         <v/>
       </c>
       <c r="D35" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"التوسع في المواقع")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"التوسع في المواقع")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46605,11 +44130,11 @@
         </is>
       </c>
       <c r="C36" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"الامتياز التجاري")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"الامتياز التجاري")</f>
         <v/>
       </c>
       <c r="D36" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"الامتياز التجاري")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"الامتياز التجاري")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46620,11 +44145,11 @@
         </is>
       </c>
       <c r="C37" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"زيادة وصول العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"زيادة وصول العملاء")</f>
         <v/>
       </c>
       <c r="D37" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"زيادة وصول العملاء")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"زيادة وصول العملاء")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46635,11 +44160,11 @@
         </is>
       </c>
       <c r="C38" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"إطلاق مشاريع جديدة")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"إطلاق مشاريع جديدة")</f>
         <v/>
       </c>
       <c r="D38" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"إطلاق مشاريع جديدة")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"إطلاق مشاريع جديدة")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46650,11 +44175,11 @@
         </is>
       </c>
       <c r="C39" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"تطوير التصاميم والهوية")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"تطوير التصاميم والهوية")</f>
         <v/>
       </c>
       <c r="D39" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"تطوير التصاميم والهوية")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"تطوير التصاميم والهوية")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46665,11 +44190,11 @@
         </is>
       </c>
       <c r="C40" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"التحول التقني")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"التحول التقني")</f>
         <v/>
       </c>
       <c r="D40" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"التحول التقني")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"التحول التقني")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46680,11 +44205,11 @@
         </is>
       </c>
       <c r="C41" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"ساحات درب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"ساحات درب")</f>
         <v/>
       </c>
       <c r="D41" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"ساحات درب")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"ساحات درب")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46695,11 +44220,11 @@
         </is>
       </c>
       <c r="C42" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"تطبيق «تانكي»")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"تطبيق «تانكي»")</f>
         <v/>
       </c>
       <c r="D42" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"تطبيق «تانكي»")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"تطبيق «تانكي»")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46710,11 +44235,11 @@
         </is>
       </c>
       <c r="C43" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"تعزيز تجربة العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"تعزيز تجربة العملاء")</f>
         <v/>
       </c>
       <c r="D43" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"تعزيز تجربة العملاء")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"تعزيز تجربة العملاء")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46725,11 +44250,11 @@
         </is>
       </c>
       <c r="C44" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"جودة التشغيل")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"جودة التشغيل")</f>
         <v/>
       </c>
       <c r="D44" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"جودة التشغيل")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"جودة التشغيل")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46740,11 +44265,11 @@
         </is>
       </c>
       <c r="C45" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"منظومة التأجير")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"منظومة التأجير")</f>
         <v/>
       </c>
       <c r="D45" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"منظومة التأجير")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"منظومة التأجير")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
@@ -46755,11 +44280,11 @@
         </is>
       </c>
       <c r="C46" s="58">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"الاستثمار في الموظفين")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"الاستثمار في الموظفين")</f>
         <v/>
       </c>
       <c r="D46" s="17">
-        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$161,"الاستثمار في الموظفين")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
+        <f>IF(COUNTIF('قاعدة المؤشرات'!$E$4:$E$146,"الاستثمار في الموظفين")=0,"🔴 فجوة — بلا مؤشر","✅ مغطّى")</f>
         <v/>
       </c>
     </row>
